--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN1"/>
+  <dimension ref="A1:AN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -615,6 +615,1320 @@
       <c r="AN1" t="inlineStr">
         <is>
           <t>最後更新日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>8487</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>愛爾達-創</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>78</v>
+      </c>
+      <c r="G2" t="n">
+        <v>78.25499992370605</v>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>39.14775751377626</v>
+      </c>
+      <c r="J2" t="n">
+        <v>34.68911539348966</v>
+      </c>
+      <c r="K2" t="n">
+        <v>46.46770789658576</v>
+      </c>
+      <c r="L2" t="n">
+        <v>101436.2</v>
+      </c>
+      <c r="M2" t="n">
+        <v>53907.3</v>
+      </c>
+      <c r="N2" t="n">
+        <v>41043.65</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.881678362670733</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-0.5441615464101801</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-0.6477499846452816</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.1035884382351014</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.07736743790408696</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.07958822384735953</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>9.738</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>13.938</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>61.998</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>75.19800000000001</v>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>80</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2114</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>鑫永銓</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>88</v>
+      </c>
+      <c r="G3" t="n">
+        <v>88.3950008392334</v>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>40.67502530054776</v>
+      </c>
+      <c r="J3" t="n">
+        <v>34.1890566601808</v>
+      </c>
+      <c r="K3" t="n">
+        <v>44.57368438769481</v>
+      </c>
+      <c r="L3" t="n">
+        <v>78607.60000000001</v>
+      </c>
+      <c r="M3" t="n">
+        <v>49673.5</v>
+      </c>
+      <c r="N3" t="n">
+        <v>40651.6</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.58248563117155</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-0.1808840313655367</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-0.1408225222788201</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-0.04006150908671657</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-0.05093762199336851</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-0.05194541608982742</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>-11</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-11</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>22.886</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>23.886</v>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>70</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3523</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>迎輝</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>12.39999961853027</v>
+      </c>
+      <c r="G4" t="n">
+        <v>12.82749996185303</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>48.74658670686937</v>
+      </c>
+      <c r="J4" t="n">
+        <v>44.51019693037161</v>
+      </c>
+      <c r="K4" t="n">
+        <v>37.71440342086395</v>
+      </c>
+      <c r="L4" t="n">
+        <v>172014.8</v>
+      </c>
+      <c r="M4" t="n">
+        <v>51072.6</v>
+      </c>
+      <c r="N4" t="n">
+        <v>40461.25</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.368044704988585</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0.455176588593444</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0.4985450554719721</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.04336846687852813</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.04526563362469704</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.05191589189844181</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1538</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>正峰</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>12.19999980926514</v>
+      </c>
+      <c r="G5" t="n">
+        <v>12.89499998092651</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>36.55404909991231</v>
+      </c>
+      <c r="J5" t="n">
+        <v>35.38920695637704</v>
+      </c>
+      <c r="K5" t="n">
+        <v>34.89998605763309</v>
+      </c>
+      <c r="L5" t="n">
+        <v>50872.4</v>
+      </c>
+      <c r="M5" t="n">
+        <v>22442.85</v>
+      </c>
+      <c r="N5" t="n">
+        <v>29388.05</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.266753108451022</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.7132395143728978</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.7662871133930196</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.05304759902012179</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.05140381760834511</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.06091183394929145</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-0.023</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-1.023</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>4.995</v>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>70</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>4558</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>寶緯</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>19.45000076293945</v>
+      </c>
+      <c r="G6" t="n">
+        <v>19.42499990463257</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>38.89548766809799</v>
+      </c>
+      <c r="J6" t="n">
+        <v>35.90554022605892</v>
+      </c>
+      <c r="K6" t="n">
+        <v>49.94440666336983</v>
+      </c>
+      <c r="L6" t="n">
+        <v>125263.6</v>
+      </c>
+      <c r="M6" t="n">
+        <v>65615.89999999999</v>
+      </c>
+      <c r="N6" t="n">
+        <v>88310.35000000001</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.909043387349713</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.04362516696046015</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.01235375325367065</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.0559789202141308</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.075981786659512</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.05610579588288976</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>70</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>6612</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>奈米醫材</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>67.80000305175781</v>
+      </c>
+      <c r="G7" t="n">
+        <v>68.54000015258789</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>38.10164862527157</v>
+      </c>
+      <c r="J7" t="n">
+        <v>34.44611798354443</v>
+      </c>
+      <c r="K7" t="n">
+        <v>44.70522960945206</v>
+      </c>
+      <c r="L7" t="n">
+        <v>58799</v>
+      </c>
+      <c r="M7" t="n">
+        <v>31140.7</v>
+      </c>
+      <c r="N7" t="n">
+        <v>23715.2</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.88817207063425</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0.4615906912318479</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.3646952075721979</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-0.09689548365965001</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.1401967369944709</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0.07042177855564036</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>70</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>4729</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>熒茂</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>20.04999923706055</v>
+      </c>
+      <c r="G8" t="n">
+        <v>20.11500005722046</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>40.03252914870374</v>
+      </c>
+      <c r="J8" t="n">
+        <v>35.48079451561392</v>
+      </c>
+      <c r="K8" t="n">
+        <v>48.39118698503333</v>
+      </c>
+      <c r="L8" t="n">
+        <v>746918.8</v>
+      </c>
+      <c r="M8" t="n">
+        <v>408118.9</v>
+      </c>
+      <c r="N8" t="n">
+        <v>286134.725</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.830149988152962</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0.001968290326107791</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.09126974622303025</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.08930145589692245</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.1217865254905505</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.124354059723645</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>70</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>8101</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>華冠</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>13</v>
+      </c>
+      <c r="G9" t="n">
+        <v>13.07749996185303</v>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>45.1279707796968</v>
+      </c>
+      <c r="J9" t="n">
+        <v>35.66039521645349</v>
+      </c>
+      <c r="K9" t="n">
+        <v>47.34339692506855</v>
+      </c>
+      <c r="L9" t="n">
+        <v>16633.4</v>
+      </c>
+      <c r="M9" t="n">
+        <v>9894.799999999999</v>
+      </c>
+      <c r="N9" t="n">
+        <v>8571.85</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.681024376440151</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0.3881676954178754</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-0.431135773024979</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.04296807760710353</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.00374273470610087</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.02217975833307273</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-0.6220000000000001</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-3.622</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>-0.715</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-0.715</v>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>70</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>7738</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>東聯互動</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>177</v>
+      </c>
+      <c r="G10" t="n">
+        <v>180.325</v>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>36.68151509603008</v>
+      </c>
+      <c r="J10" t="n">
+        <v>33.03368499743637</v>
+      </c>
+      <c r="K10" t="n">
+        <v>44.95830643351373</v>
+      </c>
+      <c r="L10" t="n">
+        <v>76302.39999999999</v>
+      </c>
+      <c r="M10" t="n">
+        <v>49901.95</v>
+      </c>
+      <c r="N10" t="n">
+        <v>48822.075</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.529046460108272</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-1.528502331054284</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.9303190476927872</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-0.5981832833614968</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-0.6797005246170519</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0.6397350141707487</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -735,28 +735,28 @@
         <v>2</v>
       </c>
       <c r="AF2" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>9.738</v>
+        <v>6.739</v>
       </c>
       <c r="AI2" t="n">
-        <v>13.938</v>
+        <v>9.739000000000001</v>
       </c>
       <c r="AJ2" t="n">
-        <v>13.2</v>
+        <v>30</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>61.998</v>
+        <v>53.999</v>
       </c>
       <c r="AM2" t="n">
-        <v>75.19800000000001</v>
+        <v>83.999</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>-11</v>
       </c>
       <c r="AF3" t="n">
-        <v>-8.5</v>
+        <v>-25</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -890,19 +890,19 @@
         <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>-7.5</v>
+        <v>-24</v>
       </c>
       <c r="AJ3" t="n">
-        <v>22.886</v>
+        <v>32</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1</v>
+        <v>1.531</v>
       </c>
       <c r="AM3" t="n">
-        <v>23.886</v>
+        <v>33.531</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
@@ -1173,28 +1173,28 @@
         <v>4</v>
       </c>
       <c r="AF5" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>-1</v>
       </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-0.023</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-1.023</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>5</v>
-      </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.005</v>
+        <v>-0.002999999999999998</v>
       </c>
       <c r="AM5" t="n">
-        <v>4.995</v>
+        <v>-1.003</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
@@ -1769,16 +1769,16 @@
         <v>-3.622</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>-0.715</v>
+        <v>-1.213</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0.715</v>
+        <v>-4.213</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -735,28 +735,28 @@
         <v>2</v>
       </c>
       <c r="AF2" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>6.739</v>
+        <v>7.738</v>
       </c>
       <c r="AI2" t="n">
-        <v>9.739000000000001</v>
+        <v>9.938000000000001</v>
       </c>
       <c r="AJ2" t="n">
-        <v>30</v>
+        <v>21.2</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>53.999</v>
+        <v>59.998</v>
       </c>
       <c r="AM2" t="n">
-        <v>83.999</v>
+        <v>81.19800000000001</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
@@ -807,16 +807,16 @@
         <v>44.57368438769481</v>
       </c>
       <c r="L3" t="n">
-        <v>78607.60000000001</v>
+        <v>78463</v>
       </c>
       <c r="M3" t="n">
-        <v>49673.5</v>
+        <v>49637.35</v>
       </c>
       <c r="N3" t="n">
-        <v>40651.6</v>
+        <v>40633.525</v>
       </c>
       <c r="O3" t="n">
-        <v>1.58248563117155</v>
+        <v>1.580724998413493</v>
       </c>
       <c r="P3" t="n">
         <v>-0.1808840313655367</v>
@@ -881,7 +881,7 @@
         <v>-11</v>
       </c>
       <c r="AF3" t="n">
-        <v>-25</v>
+        <v>-15.5</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -890,19 +890,19 @@
         <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>-24</v>
+        <v>-14.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>32</v>
+        <v>20.886</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.531</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>33.531</v>
+        <v>20.886</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
@@ -953,16 +953,16 @@
         <v>37.71440342086395</v>
       </c>
       <c r="L4" t="n">
-        <v>172014.8</v>
+        <v>172107</v>
       </c>
       <c r="M4" t="n">
-        <v>51072.6</v>
+        <v>51095.65</v>
       </c>
       <c r="N4" t="n">
-        <v>40461.25</v>
+        <v>40472.775</v>
       </c>
       <c r="O4" t="n">
-        <v>3.368044704988585</v>
+        <v>3.368329789326489</v>
       </c>
       <c r="P4" t="n">
         <v>-0.455176588593444</v>
@@ -1099,16 +1099,16 @@
         <v>34.89998605763309</v>
       </c>
       <c r="L5" t="n">
-        <v>50872.4</v>
+        <v>50582.6</v>
       </c>
       <c r="M5" t="n">
-        <v>22442.85</v>
+        <v>22370.4</v>
       </c>
       <c r="N5" t="n">
-        <v>29388.05</v>
+        <v>29351.825</v>
       </c>
       <c r="O5" t="n">
-        <v>2.266753108451022</v>
+        <v>2.261139720344741</v>
       </c>
       <c r="P5" t="n">
         <v>-0.7132395143728978</v>
@@ -1173,28 +1173,28 @@
         <v>4</v>
       </c>
       <c r="AF5" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>-0.022</v>
       </c>
       <c r="AI5" t="n">
-        <v>-7</v>
+        <v>-4.022</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.002999999999999998</v>
+        <v>-0.005</v>
       </c>
       <c r="AM5" t="n">
-        <v>-1.003</v>
+        <v>1.995000000000001</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
@@ -1245,16 +1245,16 @@
         <v>49.94440666336983</v>
       </c>
       <c r="L6" t="n">
-        <v>125263.6</v>
+        <v>125260</v>
       </c>
       <c r="M6" t="n">
-        <v>65615.89999999999</v>
+        <v>65615</v>
       </c>
       <c r="N6" t="n">
-        <v>88310.35000000001</v>
+        <v>88309.89999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>1.909043387349713</v>
+        <v>1.909014707002972</v>
       </c>
       <c r="P6" t="n">
         <v>0.04362516696046015</v>
@@ -1391,16 +1391,16 @@
         <v>44.70522960945206</v>
       </c>
       <c r="L7" t="n">
-        <v>58799</v>
+        <v>58444.8</v>
       </c>
       <c r="M7" t="n">
-        <v>31140.7</v>
+        <v>31052.15</v>
       </c>
       <c r="N7" t="n">
-        <v>23715.2</v>
+        <v>23670.925</v>
       </c>
       <c r="O7" t="n">
-        <v>1.88817207063425</v>
+        <v>1.882149867239467</v>
       </c>
       <c r="P7" t="n">
         <v>-0.4615906912318479</v>
@@ -1537,16 +1537,16 @@
         <v>48.39118698503333</v>
       </c>
       <c r="L8" t="n">
-        <v>746918.8</v>
+        <v>746686</v>
       </c>
       <c r="M8" t="n">
-        <v>408118.9</v>
+        <v>408060.7</v>
       </c>
       <c r="N8" t="n">
-        <v>286134.725</v>
+        <v>286105.625</v>
       </c>
       <c r="O8" t="n">
-        <v>1.830149988152962</v>
+        <v>1.829840511472925</v>
       </c>
       <c r="P8" t="n">
         <v>-0.001968290326107791</v>
@@ -1683,16 +1683,16 @@
         <v>47.34339692506855</v>
       </c>
       <c r="L9" t="n">
-        <v>16633.4</v>
+        <v>16672</v>
       </c>
       <c r="M9" t="n">
-        <v>9894.799999999999</v>
+        <v>9904.450000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>8571.85</v>
+        <v>8576.674999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>1.681024376440151</v>
+        <v>1.683283776484307</v>
       </c>
       <c r="P9" t="n">
         <v>-0.3881676954178754</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>-1.213</v>
+        <v>-1.252</v>
       </c>
       <c r="AM9" t="n">
-        <v>-4.213</v>
+        <v>-4.252</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
@@ -1829,16 +1829,16 @@
         <v>44.95830643351373</v>
       </c>
       <c r="L10" t="n">
-        <v>76302.39999999999</v>
+        <v>76404</v>
       </c>
       <c r="M10" t="n">
-        <v>49901.95</v>
+        <v>49927.35</v>
       </c>
       <c r="N10" t="n">
-        <v>48822.075</v>
+        <v>48834.775</v>
       </c>
       <c r="O10" t="n">
-        <v>1.529046460108272</v>
+        <v>1.530303531030587</v>
       </c>
       <c r="P10" t="n">
         <v>-1.528502331054284</v>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -747,16 +747,16 @@
         <v>9.938000000000001</v>
       </c>
       <c r="AJ2" t="n">
-        <v>21.2</v>
+        <v>16.2</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>59.998</v>
+        <v>60.738</v>
       </c>
       <c r="AM2" t="n">
-        <v>81.19800000000001</v>
+        <v>76.938</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
@@ -775,12 +775,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>鑫永銓</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,53 +789,53 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>88</v>
+        <v>13</v>
       </c>
       <c r="G3" t="n">
-        <v>88.3950008392334</v>
+        <v>13.07749996185303</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>40.67502530054776</v>
+        <v>45.1279707796968</v>
       </c>
       <c r="J3" t="n">
-        <v>34.1890566601808</v>
+        <v>35.66039521645349</v>
       </c>
       <c r="K3" t="n">
-        <v>44.57368438769481</v>
+        <v>47.34339692506855</v>
       </c>
       <c r="L3" t="n">
-        <v>78463</v>
+        <v>16672</v>
       </c>
       <c r="M3" t="n">
-        <v>49637.35</v>
+        <v>9904.450000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>40633.525</v>
+        <v>8576.674999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>1.580724998413493</v>
+        <v>1.683283776484307</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1808840313655367</v>
+        <v>-0.3881676954178754</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1408225222788201</v>
+        <v>-0.431135773024979</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.04006150908671657</v>
+        <v>0.04296807760710353</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.05093762199336851</v>
+        <v>0.00374273470610087</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.05194541608982742</v>
+        <v>-0.02217975833307273</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -855,12 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -869,40 +869,40 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="AE3" t="n">
-        <v>-11</v>
+        <v>-0.03</v>
       </c>
       <c r="AF3" t="n">
-        <v>-15.5</v>
+        <v>3</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1</v>
+        <v>-1.207</v>
       </c>
       <c r="AI3" t="n">
-        <v>-14.5</v>
+        <v>1.793</v>
       </c>
       <c r="AJ3" t="n">
-        <v>20.886</v>
+        <v>3</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>-0.2519999999999999</v>
       </c>
       <c r="AM3" t="n">
-        <v>20.886</v>
+        <v>2.747999999999999</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
@@ -917,71 +917,71 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3523</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>迎輝</t>
+          <t>鑫永銓</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>12.39999961853027</v>
+        <v>88</v>
       </c>
       <c r="G4" t="n">
-        <v>12.82749996185303</v>
+        <v>88.3950008392334</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>48.74658670686937</v>
+        <v>40.67502530054776</v>
       </c>
       <c r="J4" t="n">
-        <v>44.51019693037161</v>
+        <v>34.1890566601808</v>
       </c>
       <c r="K4" t="n">
-        <v>37.71440342086395</v>
+        <v>44.57368438769481</v>
       </c>
       <c r="L4" t="n">
-        <v>172107</v>
+        <v>78463</v>
       </c>
       <c r="M4" t="n">
-        <v>51095.65</v>
+        <v>49637.35</v>
       </c>
       <c r="N4" t="n">
-        <v>40472.775</v>
+        <v>40633.525</v>
       </c>
       <c r="O4" t="n">
-        <v>3.368329789326489</v>
+        <v>1.580724998413493</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.455176588593444</v>
+        <v>-0.1808840313655367</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.4985450554719721</v>
+        <v>-0.1408225222788201</v>
       </c>
       <c r="R4" t="n">
-        <v>0.04336846687852813</v>
+        <v>-0.04006150908671657</v>
       </c>
       <c r="S4" t="n">
-        <v>0.04526563362469704</v>
+        <v>-0.05093762199336851</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05191589189844181</v>
+        <v>-0.05194541608982742</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1024,31 +1024,31 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>-15.5</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-14.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>11.886</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>10.886</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
@@ -1067,63 +1067,63 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1538</t>
+          <t>3523</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>正峰</t>
+          <t>迎輝</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>12.19999980926514</v>
+        <v>12.39999961853027</v>
       </c>
       <c r="G5" t="n">
-        <v>12.89499998092651</v>
+        <v>12.82749996185303</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>36.55404909991231</v>
+        <v>48.74658670686937</v>
       </c>
       <c r="J5" t="n">
-        <v>35.38920695637704</v>
+        <v>44.51019693037161</v>
       </c>
       <c r="K5" t="n">
-        <v>34.89998605763309</v>
+        <v>37.71440342086395</v>
       </c>
       <c r="L5" t="n">
-        <v>50582.6</v>
+        <v>172107</v>
       </c>
       <c r="M5" t="n">
-        <v>22370.4</v>
+        <v>51095.65</v>
       </c>
       <c r="N5" t="n">
-        <v>29351.825</v>
+        <v>40472.775</v>
       </c>
       <c r="O5" t="n">
-        <v>2.261139720344741</v>
+        <v>3.368329789326489</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.7132395143728978</v>
+        <v>-0.455176588593444</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.7662871133930196</v>
+        <v>-0.4985450554719721</v>
       </c>
       <c r="R5" t="n">
-        <v>0.05304759902012179</v>
+        <v>0.04336846687852813</v>
       </c>
       <c r="S5" t="n">
-        <v>0.05140381760834511</v>
+        <v>0.04526563362469704</v>
       </c>
       <c r="T5" t="n">
-        <v>0.06091183394929145</v>
+        <v>0.05191589189844181</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1170,31 +1170,31 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.022</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>-4.022</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.995000000000001</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
@@ -1213,63 +1213,63 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4558</t>
+          <t>1538</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>寶緯</t>
+          <t>正峰</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>19.45000076293945</v>
+        <v>12.19999980926514</v>
       </c>
       <c r="G6" t="n">
-        <v>19.42499990463257</v>
+        <v>12.89499998092651</v>
       </c>
       <c r="H6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>38.89548766809799</v>
+        <v>36.55404909991231</v>
       </c>
       <c r="J6" t="n">
-        <v>35.90554022605892</v>
+        <v>35.38920695637704</v>
       </c>
       <c r="K6" t="n">
-        <v>49.94440666336983</v>
+        <v>34.89998605763309</v>
       </c>
       <c r="L6" t="n">
-        <v>125260</v>
+        <v>50582.6</v>
       </c>
       <c r="M6" t="n">
-        <v>65615</v>
+        <v>22370.4</v>
       </c>
       <c r="N6" t="n">
-        <v>88309.89999999999</v>
+        <v>29351.825</v>
       </c>
       <c r="O6" t="n">
-        <v>1.909014707002972</v>
+        <v>2.261139720344741</v>
       </c>
       <c r="P6" t="n">
-        <v>0.04362516696046015</v>
+        <v>-0.7132395143728978</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.01235375325367065</v>
+        <v>-0.7662871133930196</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0559789202141308</v>
+        <v>0.05304759902012179</v>
       </c>
       <c r="S6" t="n">
-        <v>0.075981786659512</v>
+        <v>0.05140381760834511</v>
       </c>
       <c r="T6" t="n">
-        <v>0.05610579588288976</v>
+        <v>0.06091183394929145</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1316,31 +1316,31 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>-0.022</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-4.022</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>2.001</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6612</t>
+          <t>4558</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>奈米醫材</t>
+          <t>寶緯</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1373,49 +1373,49 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>67.80000305175781</v>
+        <v>19.45000076293945</v>
       </c>
       <c r="G7" t="n">
-        <v>68.54000015258789</v>
+        <v>19.42499990463257</v>
       </c>
       <c r="H7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>38.10164862527157</v>
+        <v>38.89548766809799</v>
       </c>
       <c r="J7" t="n">
-        <v>34.44611798354443</v>
+        <v>35.90554022605892</v>
       </c>
       <c r="K7" t="n">
-        <v>44.70522960945206</v>
+        <v>49.94440666336983</v>
       </c>
       <c r="L7" t="n">
-        <v>58444.8</v>
+        <v>125260</v>
       </c>
       <c r="M7" t="n">
-        <v>31052.15</v>
+        <v>65615</v>
       </c>
       <c r="N7" t="n">
-        <v>23670.925</v>
+        <v>88309.89999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>1.882149867239467</v>
+        <v>1.909014707002972</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4615906912318479</v>
+        <v>0.04362516696046015</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.3646952075721979</v>
+        <v>-0.01235375325367065</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.09689548365965001</v>
+        <v>0.0559789202141308</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1401967369944709</v>
+        <v>0.075981786659512</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.07042177855564036</v>
+        <v>0.05610579588288976</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4729</t>
+          <t>6612</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>熒茂</t>
+          <t>奈米醫材</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1519,49 +1519,49 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>20.04999923706055</v>
+        <v>67.80000305175781</v>
       </c>
       <c r="G8" t="n">
-        <v>20.11500005722046</v>
+        <v>68.54000015258789</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>40.03252914870374</v>
+        <v>38.10164862527157</v>
       </c>
       <c r="J8" t="n">
-        <v>35.48079451561392</v>
+        <v>34.44611798354443</v>
       </c>
       <c r="K8" t="n">
-        <v>48.39118698503333</v>
+        <v>44.70522960945206</v>
       </c>
       <c r="L8" t="n">
-        <v>746686</v>
+        <v>58444.8</v>
       </c>
       <c r="M8" t="n">
-        <v>408060.7</v>
+        <v>31052.15</v>
       </c>
       <c r="N8" t="n">
-        <v>286105.625</v>
+        <v>23670.925</v>
       </c>
       <c r="O8" t="n">
-        <v>1.829840511472925</v>
+        <v>1.882149867239467</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.001968290326107791</v>
+        <v>-0.4615906912318479</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.09126974622303025</v>
+        <v>-0.3646952075721979</v>
       </c>
       <c r="R8" t="n">
-        <v>0.08930145589692245</v>
+        <v>-0.09689548365965001</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1217865254905505</v>
+        <v>-0.1401967369944709</v>
       </c>
       <c r="T8" t="n">
-        <v>0.124354059723645</v>
+        <v>-0.07042177855564036</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1651,63 +1651,63 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>4729</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>熒茂</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>20.04999923706055</v>
       </c>
       <c r="G9" t="n">
-        <v>13.07749996185303</v>
+        <v>20.11500005722046</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>45.1279707796968</v>
+        <v>40.03252914870374</v>
       </c>
       <c r="J9" t="n">
-        <v>35.66039521645349</v>
+        <v>35.48079451561392</v>
       </c>
       <c r="K9" t="n">
-        <v>47.34339692506855</v>
+        <v>48.39118698503333</v>
       </c>
       <c r="L9" t="n">
-        <v>16672</v>
+        <v>746686</v>
       </c>
       <c r="M9" t="n">
-        <v>9904.450000000001</v>
+        <v>408060.7</v>
       </c>
       <c r="N9" t="n">
-        <v>8576.674999999999</v>
+        <v>286105.625</v>
       </c>
       <c r="O9" t="n">
-        <v>1.683283776484307</v>
+        <v>1.829840511472925</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3881676954178754</v>
+        <v>-0.001968290326107791</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.431135773024979</v>
+        <v>-0.09126974622303025</v>
       </c>
       <c r="R9" t="n">
-        <v>0.04296807760710353</v>
+        <v>0.08930145589692245</v>
       </c>
       <c r="S9" t="n">
-        <v>0.00374273470610087</v>
+        <v>0.1217865254905505</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.02217975833307273</v>
+        <v>0.124354059723645</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1751,34 +1751,34 @@
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0.6220000000000001</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>-3.622</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>-1.252</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>-4.252</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -747,16 +747,16 @@
         <v>9.938000000000001</v>
       </c>
       <c r="AJ2" t="n">
-        <v>16.2</v>
+        <v>21.2</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>60.738</v>
+        <v>59.998</v>
       </c>
       <c r="AM2" t="n">
-        <v>76.938</v>
+        <v>81.19800000000001</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
@@ -775,12 +775,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>鑫永銓</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,53 +789,53 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="G3" t="n">
-        <v>13.07749996185303</v>
+        <v>88.3950008392334</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>45.1279707796968</v>
+        <v>40.67502530054776</v>
       </c>
       <c r="J3" t="n">
-        <v>35.66039521645349</v>
+        <v>34.1890566601808</v>
       </c>
       <c r="K3" t="n">
-        <v>47.34339692506855</v>
+        <v>44.57368438769481</v>
       </c>
       <c r="L3" t="n">
-        <v>16672</v>
+        <v>78463</v>
       </c>
       <c r="M3" t="n">
-        <v>9904.450000000001</v>
+        <v>49637.35</v>
       </c>
       <c r="N3" t="n">
-        <v>8576.674999999999</v>
+        <v>40633.525</v>
       </c>
       <c r="O3" t="n">
-        <v>1.683283776484307</v>
+        <v>1.580724998413493</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3881676954178754</v>
+        <v>-0.1808840313655367</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.431135773024979</v>
+        <v>-0.1408225222788201</v>
       </c>
       <c r="R3" t="n">
-        <v>0.04296807760710353</v>
+        <v>-0.04006150908671657</v>
       </c>
       <c r="S3" t="n">
-        <v>0.00374273470610087</v>
+        <v>-0.05093762199336851</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.02217975833307273</v>
+        <v>-0.05194541608982742</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -855,12 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -869,40 +869,40 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.03</v>
+        <v>-11</v>
       </c>
       <c r="AF3" t="n">
-        <v>3</v>
+        <v>-15.5</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-1.207</v>
+        <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.793</v>
+        <v>-14.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3</v>
+        <v>20.886</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.2519999999999999</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.747999999999999</v>
+        <v>20.886</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
@@ -917,71 +917,71 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>3523</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>鑫永銓</t>
+          <t>迎輝</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>88</v>
+        <v>12.39999961853027</v>
       </c>
       <c r="G4" t="n">
-        <v>88.3950008392334</v>
+        <v>12.82749996185303</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>40.67502530054776</v>
+        <v>48.74658670686937</v>
       </c>
       <c r="J4" t="n">
-        <v>34.1890566601808</v>
+        <v>44.51019693037161</v>
       </c>
       <c r="K4" t="n">
-        <v>44.57368438769481</v>
+        <v>37.71440342086395</v>
       </c>
       <c r="L4" t="n">
-        <v>78463</v>
+        <v>172107</v>
       </c>
       <c r="M4" t="n">
-        <v>49637.35</v>
+        <v>51095.65</v>
       </c>
       <c r="N4" t="n">
-        <v>40633.525</v>
+        <v>40472.775</v>
       </c>
       <c r="O4" t="n">
-        <v>1.580724998413493</v>
+        <v>3.368329789326489</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1808840313655367</v>
+        <v>-0.455176588593444</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1408225222788201</v>
+        <v>-0.4985450554719721</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.04006150908671657</v>
+        <v>0.04336846687852813</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.05093762199336851</v>
+        <v>0.04526563362469704</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.05194541608982742</v>
+        <v>0.05191589189844181</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1024,31 +1024,31 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>-15.5</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>-14.5</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>11.886</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>10.886</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
@@ -1067,63 +1067,63 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3523</t>
+          <t>1538</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>迎輝</t>
+          <t>正峰</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>12.39999961853027</v>
+        <v>12.19999980926514</v>
       </c>
       <c r="G5" t="n">
-        <v>12.82749996185303</v>
+        <v>12.89499998092651</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>48.74658670686937</v>
+        <v>36.55404909991231</v>
       </c>
       <c r="J5" t="n">
-        <v>44.51019693037161</v>
+        <v>35.38920695637704</v>
       </c>
       <c r="K5" t="n">
-        <v>37.71440342086395</v>
+        <v>34.89998605763309</v>
       </c>
       <c r="L5" t="n">
-        <v>172107</v>
+        <v>50582.6</v>
       </c>
       <c r="M5" t="n">
-        <v>51095.65</v>
+        <v>22370.4</v>
       </c>
       <c r="N5" t="n">
-        <v>40472.775</v>
+        <v>29351.825</v>
       </c>
       <c r="O5" t="n">
-        <v>3.368329789326489</v>
+        <v>2.261139720344741</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.455176588593444</v>
+        <v>-0.7132395143728978</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.4985450554719721</v>
+        <v>-0.7662871133930196</v>
       </c>
       <c r="R5" t="n">
-        <v>0.04336846687852813</v>
+        <v>0.05304759902012179</v>
       </c>
       <c r="S5" t="n">
-        <v>0.04526563362469704</v>
+        <v>0.05140381760834511</v>
       </c>
       <c r="T5" t="n">
-        <v>0.05191589189844181</v>
+        <v>0.06091183394929145</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1170,31 +1170,31 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>-0.022</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-4.022</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.995000000000001</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
@@ -1213,63 +1213,63 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1538</t>
+          <t>4558</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>正峰</t>
+          <t>寶緯</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>12.19999980926514</v>
+        <v>19.45000076293945</v>
       </c>
       <c r="G6" t="n">
-        <v>12.89499998092651</v>
+        <v>19.42499990463257</v>
       </c>
       <c r="H6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>36.55404909991231</v>
+        <v>38.89548766809799</v>
       </c>
       <c r="J6" t="n">
-        <v>35.38920695637704</v>
+        <v>35.90554022605892</v>
       </c>
       <c r="K6" t="n">
-        <v>34.89998605763309</v>
+        <v>49.94440666336983</v>
       </c>
       <c r="L6" t="n">
-        <v>50582.6</v>
+        <v>125260</v>
       </c>
       <c r="M6" t="n">
-        <v>22370.4</v>
+        <v>65615</v>
       </c>
       <c r="N6" t="n">
-        <v>29351.825</v>
+        <v>88309.89999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>2.261139720344741</v>
+        <v>1.909014707002972</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7132395143728978</v>
+        <v>0.04362516696046015</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.7662871133930196</v>
+        <v>-0.01235375325367065</v>
       </c>
       <c r="R6" t="n">
-        <v>0.05304759902012179</v>
+        <v>0.0559789202141308</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05140381760834511</v>
+        <v>0.075981786659512</v>
       </c>
       <c r="T6" t="n">
-        <v>0.06091183394929145</v>
+        <v>0.05610579588288976</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1316,31 +1316,31 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.022</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>-4.022</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>2.001</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4558</t>
+          <t>6612</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>寶緯</t>
+          <t>奈米醫材</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1373,49 +1373,49 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>19.45000076293945</v>
+        <v>67.80000305175781</v>
       </c>
       <c r="G7" t="n">
-        <v>19.42499990463257</v>
+        <v>68.54000015258789</v>
       </c>
       <c r="H7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>38.89548766809799</v>
+        <v>38.10164862527157</v>
       </c>
       <c r="J7" t="n">
-        <v>35.90554022605892</v>
+        <v>34.44611798354443</v>
       </c>
       <c r="K7" t="n">
-        <v>49.94440666336983</v>
+        <v>44.70522960945206</v>
       </c>
       <c r="L7" t="n">
-        <v>125260</v>
+        <v>58444.8</v>
       </c>
       <c r="M7" t="n">
-        <v>65615</v>
+        <v>31052.15</v>
       </c>
       <c r="N7" t="n">
-        <v>88309.89999999999</v>
+        <v>23670.925</v>
       </c>
       <c r="O7" t="n">
-        <v>1.909014707002972</v>
+        <v>1.882149867239467</v>
       </c>
       <c r="P7" t="n">
-        <v>0.04362516696046015</v>
+        <v>-0.4615906912318479</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.01235375325367065</v>
+        <v>-0.3646952075721979</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0559789202141308</v>
+        <v>-0.09689548365965001</v>
       </c>
       <c r="S7" t="n">
-        <v>0.075981786659512</v>
+        <v>-0.1401967369944709</v>
       </c>
       <c r="T7" t="n">
-        <v>0.05610579588288976</v>
+        <v>-0.07042177855564036</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>6612</t>
+          <t>4729</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>奈米醫材</t>
+          <t>熒茂</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1519,49 +1519,49 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>67.80000305175781</v>
+        <v>20.04999923706055</v>
       </c>
       <c r="G8" t="n">
-        <v>68.54000015258789</v>
+        <v>20.11500005722046</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>38.10164862527157</v>
+        <v>40.03252914870374</v>
       </c>
       <c r="J8" t="n">
-        <v>34.44611798354443</v>
+        <v>35.48079451561392</v>
       </c>
       <c r="K8" t="n">
-        <v>44.70522960945206</v>
+        <v>48.39118698503333</v>
       </c>
       <c r="L8" t="n">
-        <v>58444.8</v>
+        <v>746686</v>
       </c>
       <c r="M8" t="n">
-        <v>31052.15</v>
+        <v>408060.7</v>
       </c>
       <c r="N8" t="n">
-        <v>23670.925</v>
+        <v>286105.625</v>
       </c>
       <c r="O8" t="n">
-        <v>1.882149867239467</v>
+        <v>1.829840511472925</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4615906912318479</v>
+        <v>-0.001968290326107791</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.3646952075721979</v>
+        <v>-0.09126974622303025</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.09689548365965001</v>
+        <v>0.08930145589692245</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1401967369944709</v>
+        <v>0.1217865254905505</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.07042177855564036</v>
+        <v>0.124354059723645</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1651,63 +1651,63 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4729</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>熒茂</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>20.04999923706055</v>
+        <v>13</v>
       </c>
       <c r="G9" t="n">
-        <v>20.11500005722046</v>
+        <v>13.07749996185303</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>40.03252914870374</v>
+        <v>45.1279707796968</v>
       </c>
       <c r="J9" t="n">
-        <v>35.48079451561392</v>
+        <v>35.66039521645349</v>
       </c>
       <c r="K9" t="n">
-        <v>48.39118698503333</v>
+        <v>47.34339692506855</v>
       </c>
       <c r="L9" t="n">
-        <v>746686</v>
+        <v>16672</v>
       </c>
       <c r="M9" t="n">
-        <v>408060.7</v>
+        <v>9904.450000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>286105.625</v>
+        <v>8576.674999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>1.829840511472925</v>
+        <v>1.683283776484307</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.001968290326107791</v>
+        <v>-0.3881676954178754</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.09126974622303025</v>
+        <v>-0.431135773024979</v>
       </c>
       <c r="R9" t="n">
-        <v>0.08930145589692245</v>
+        <v>0.04296807760710353</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1217865254905505</v>
+        <v>0.00374273470610087</v>
       </c>
       <c r="T9" t="n">
-        <v>0.124354059723645</v>
+        <v>-0.02217975833307273</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1751,34 +1751,34 @@
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>-0.6220000000000001</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>-3.622</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>-1.252</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>-4.252</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN10"/>
+  <dimension ref="A1:AN7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,12 +629,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8487</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>愛爾達-創</t>
+          <t>鑫永銓</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,53 +643,53 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G2" t="n">
-        <v>78.25499992370605</v>
+        <v>88.3950008392334</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>39.14775751377626</v>
+        <v>40.67502530054776</v>
       </c>
       <c r="J2" t="n">
-        <v>34.68911539348966</v>
+        <v>34.1890566601808</v>
       </c>
       <c r="K2" t="n">
-        <v>46.46770789658576</v>
+        <v>44.57368438769481</v>
       </c>
       <c r="L2" t="n">
-        <v>101436.2</v>
+        <v>78463</v>
       </c>
       <c r="M2" t="n">
-        <v>53907.3</v>
+        <v>49637.35</v>
       </c>
       <c r="N2" t="n">
-        <v>41043.65</v>
+        <v>40633.525</v>
       </c>
       <c r="O2" t="n">
-        <v>1.881678362670733</v>
+        <v>1.580724998413493</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.5441615464101801</v>
+        <v>-0.1808840313655367</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.6477499846452816</v>
+        <v>-0.1408225222788201</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1035884382351014</v>
+        <v>-0.04006150908671657</v>
       </c>
       <c r="S2" t="n">
-        <v>0.07736743790408696</v>
+        <v>-0.05093762199336851</v>
       </c>
       <c r="T2" t="n">
-        <v>0.07958822384735953</v>
+        <v>-0.05194541608982742</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -723,40 +723,40 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>-2</v>
+        <v>-11</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>2</v>
+        <v>-11</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.2</v>
+        <v>-15.5</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>7.738</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
-        <v>9.938000000000001</v>
+        <v>-14.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>21.2</v>
+        <v>20.886</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>59.998</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>81.19800000000001</v>
+        <v>20.886</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
@@ -771,71 +771,71 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>3523</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>鑫永銓</t>
+          <t>迎輝</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>88</v>
+        <v>12.39999961853027</v>
       </c>
       <c r="G3" t="n">
-        <v>88.3950008392334</v>
+        <v>12.82749996185303</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>40.67502530054776</v>
+        <v>48.74658670686937</v>
       </c>
       <c r="J3" t="n">
-        <v>34.1890566601808</v>
+        <v>44.51019693037161</v>
       </c>
       <c r="K3" t="n">
-        <v>44.57368438769481</v>
+        <v>37.71440342086395</v>
       </c>
       <c r="L3" t="n">
-        <v>78463</v>
+        <v>172107</v>
       </c>
       <c r="M3" t="n">
-        <v>49637.35</v>
+        <v>51095.65</v>
       </c>
       <c r="N3" t="n">
-        <v>40633.525</v>
+        <v>40472.775</v>
       </c>
       <c r="O3" t="n">
-        <v>1.580724998413493</v>
+        <v>3.368329789326489</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1808840313655367</v>
+        <v>-0.455176588593444</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1408225222788201</v>
+        <v>-0.4985450554719721</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.04006150908671657</v>
+        <v>0.04336846687852813</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.05093762199336851</v>
+        <v>0.04526563362469704</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.05194541608982742</v>
+        <v>0.05191589189844181</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -878,22 +878,22 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-15.5</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-14.5</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>20.886</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
@@ -902,7 +902,7 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>20.886</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
@@ -921,63 +921,63 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3523</t>
+          <t>1538</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>迎輝</t>
+          <t>正峰</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>12.39999961853027</v>
+        <v>12.19999980926514</v>
       </c>
       <c r="G4" t="n">
-        <v>12.82749996185303</v>
+        <v>12.89499998092651</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>48.74658670686937</v>
+        <v>36.55404909991231</v>
       </c>
       <c r="J4" t="n">
-        <v>44.51019693037161</v>
+        <v>35.38920695637704</v>
       </c>
       <c r="K4" t="n">
-        <v>37.71440342086395</v>
+        <v>34.89998605763309</v>
       </c>
       <c r="L4" t="n">
-        <v>172107</v>
+        <v>50582.6</v>
       </c>
       <c r="M4" t="n">
-        <v>51095.65</v>
+        <v>22370.4</v>
       </c>
       <c r="N4" t="n">
-        <v>40472.775</v>
+        <v>29351.825</v>
       </c>
       <c r="O4" t="n">
-        <v>3.368329789326489</v>
+        <v>2.261139720344741</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.455176588593444</v>
+        <v>-0.7132395143728978</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.4985450554719721</v>
+        <v>-0.7662871133930196</v>
       </c>
       <c r="R4" t="n">
-        <v>0.04336846687852813</v>
+        <v>0.05304759902012179</v>
       </c>
       <c r="S4" t="n">
-        <v>0.04526563362469704</v>
+        <v>0.05140381760834511</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05191589189844181</v>
+        <v>0.06091183394929145</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1024,31 +1024,31 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>-0.022</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-4.022</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.995000000000001</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
@@ -1067,63 +1067,63 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1538</t>
+          <t>6612</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>正峰</t>
+          <t>奈米醫材</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>12.19999980926514</v>
+        <v>67.80000305175781</v>
       </c>
       <c r="G5" t="n">
-        <v>12.89499998092651</v>
+        <v>68.48000030517578</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>36.55404909991231</v>
+        <v>42.73447310695188</v>
       </c>
       <c r="J5" t="n">
-        <v>35.38920695637704</v>
+        <v>37.20890302468025</v>
       </c>
       <c r="K5" t="n">
-        <v>34.89998605763309</v>
+        <v>44.70522960945206</v>
       </c>
       <c r="L5" t="n">
-        <v>50582.6</v>
+        <v>54836.6</v>
       </c>
       <c r="M5" t="n">
-        <v>22370.4</v>
+        <v>30455.1</v>
       </c>
       <c r="N5" t="n">
-        <v>29351.825</v>
+        <v>23146.25</v>
       </c>
       <c r="O5" t="n">
-        <v>2.261139720344741</v>
+        <v>1.800571989584667</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.7132395143728978</v>
+        <v>-0.441383731316165</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.7662871133930196</v>
+        <v>-0.3800329123209913</v>
       </c>
       <c r="R5" t="n">
-        <v>0.05304759902012179</v>
+        <v>-0.06135081899517369</v>
       </c>
       <c r="S5" t="n">
-        <v>0.05140381760834511</v>
+        <v>-0.09689548365965001</v>
       </c>
       <c r="T5" t="n">
-        <v>0.06091183394929145</v>
+        <v>-0.1401967369944709</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1170,35 +1170,35 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.022</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>-4.022</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.995000000000001</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4558</t>
+          <t>4729</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>寶緯</t>
+          <t>熒茂</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1227,49 +1227,49 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>19.45000076293945</v>
+        <v>20.10000038146973</v>
       </c>
       <c r="G6" t="n">
-        <v>19.42499990463257</v>
+        <v>20.12000007629394</v>
       </c>
       <c r="H6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>38.89548766809799</v>
+        <v>37.55792158876897</v>
       </c>
       <c r="J6" t="n">
-        <v>35.90554022605892</v>
+        <v>36.1731702066656</v>
       </c>
       <c r="K6" t="n">
-        <v>49.94440666336983</v>
+        <v>49.127746646583</v>
       </c>
       <c r="L6" t="n">
-        <v>125260</v>
+        <v>719039.6</v>
       </c>
       <c r="M6" t="n">
-        <v>65615</v>
+        <v>403212.25</v>
       </c>
       <c r="N6" t="n">
-        <v>88309.89999999999</v>
+        <v>281330.4</v>
       </c>
       <c r="O6" t="n">
-        <v>1.909014707002972</v>
+        <v>1.7832781618118</v>
       </c>
       <c r="P6" t="n">
-        <v>0.04362516696046015</v>
+        <v>-0.005917047706663681</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.01235375325367065</v>
+        <v>-0.07419920651975694</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0559789202141308</v>
+        <v>0.06828215881309325</v>
       </c>
       <c r="S6" t="n">
-        <v>0.075981786659512</v>
+        <v>0.08930145589692245</v>
       </c>
       <c r="T6" t="n">
-        <v>0.05610579588288976</v>
+        <v>0.1217865254905505</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
@@ -1359,63 +1359,63 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6612</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>奈米醫材</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>67.80000305175781</v>
+        <v>13</v>
       </c>
       <c r="G7" t="n">
-        <v>68.54000015258789</v>
+        <v>13.07749996185303</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>38.10164862527157</v>
+        <v>45.1279707796968</v>
       </c>
       <c r="J7" t="n">
-        <v>34.44611798354443</v>
+        <v>35.66039521645349</v>
       </c>
       <c r="K7" t="n">
-        <v>44.70522960945206</v>
+        <v>47.34339692506855</v>
       </c>
       <c r="L7" t="n">
-        <v>58444.8</v>
+        <v>16672</v>
       </c>
       <c r="M7" t="n">
-        <v>31052.15</v>
+        <v>9904.450000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>23670.925</v>
+        <v>8576.674999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>1.882149867239467</v>
+        <v>1.683283776484307</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4615906912318479</v>
+        <v>-0.3881676954178754</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.3646952075721979</v>
+        <v>-0.431135773024979</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.09689548365965001</v>
+        <v>0.04296807760710353</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1401967369944709</v>
+        <v>0.00374273470610087</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.07042177855564036</v>
+        <v>-0.02217975833307273</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1459,474 +1459,36 @@
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>-0.6220000000000001</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-3.622</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>-1.252</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>-4.252</v>
       </c>
       <c r="AN7" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>70</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>4729</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>熒茂</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>20.04999923706055</v>
-      </c>
-      <c r="G8" t="n">
-        <v>20.11500005722046</v>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>40.03252914870374</v>
-      </c>
-      <c r="J8" t="n">
-        <v>35.48079451561392</v>
-      </c>
-      <c r="K8" t="n">
-        <v>48.39118698503333</v>
-      </c>
-      <c r="L8" t="n">
-        <v>746686</v>
-      </c>
-      <c r="M8" t="n">
-        <v>408060.7</v>
-      </c>
-      <c r="N8" t="n">
-        <v>286105.625</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.829840511472925</v>
-      </c>
-      <c r="P8" t="n">
-        <v>-0.001968290326107791</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>-0.09126974622303025</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.08930145589692245</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.1217865254905505</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.124354059723645</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>70</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>8101</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>華冠</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>13</v>
-      </c>
-      <c r="G9" t="n">
-        <v>13.07749996185303</v>
-      </c>
-      <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>45.1279707796968</v>
-      </c>
-      <c r="J9" t="n">
-        <v>35.66039521645349</v>
-      </c>
-      <c r="K9" t="n">
-        <v>47.34339692506855</v>
-      </c>
-      <c r="L9" t="n">
-        <v>16672</v>
-      </c>
-      <c r="M9" t="n">
-        <v>9904.450000000001</v>
-      </c>
-      <c r="N9" t="n">
-        <v>8576.674999999999</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.683283776484307</v>
-      </c>
-      <c r="P9" t="n">
-        <v>-0.3881676954178754</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>-0.431135773024979</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.04296807760710353</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.00374273470610087</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-0.02217975833307273</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>-0.6220000000000001</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>-3.622</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>-1.252</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>-4.252</v>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>70</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>7738</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>東聯互動</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>177</v>
-      </c>
-      <c r="G10" t="n">
-        <v>180.325</v>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>36.68151509603008</v>
-      </c>
-      <c r="J10" t="n">
-        <v>33.03368499743637</v>
-      </c>
-      <c r="K10" t="n">
-        <v>44.95830643351373</v>
-      </c>
-      <c r="L10" t="n">
-        <v>76404</v>
-      </c>
-      <c r="M10" t="n">
-        <v>49927.35</v>
-      </c>
-      <c r="N10" t="n">
-        <v>48834.775</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.530303531030587</v>
-      </c>
-      <c r="P10" t="n">
-        <v>-1.528502331054284</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-0.9303190476927872</v>
-      </c>
-      <c r="R10" t="n">
-        <v>-0.5981832833614968</v>
-      </c>
-      <c r="S10" t="n">
-        <v>-0.6797005246170519</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-0.6397350141707487</v>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="inlineStr">
         <is>
           <t>2026-05-13</t>
         </is>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,202 +429,202 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>candidate_level</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>candidate_score</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>市場</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>MA20</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>是否站上 MA20</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>K 值</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>D 值</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA5</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA20</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA40</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>放量倍數</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>MACD_DIF</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>MACD_Signal</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>MACD_Histogram</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>MACD_Histogram_前1日</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>MACD_Histogram_前2日</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>MACD_綠柱趨緩接近翻紅</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>是否符合 KD 區間</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>是否符合 RSI 區間</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>是否明顯放量</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>MACD 是否綠柱趨緩接近翻紅</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>法人近 5 日是否合計買超</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>投信近 5 日是否買超</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>外資近 1 日買賣超張數</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>投信近 1 日買賣超張數</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>自營商近 1 日買賣超張數</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>三大法人近 1 日合計買賣超張數</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>外資近 5 日買賣超張數</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>投信近 5 日買賣超張數</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>自營商近 5 日買賣超張數</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>三大法人近 5 日合計買賣超張數</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>外資近 20 日買賣超張數</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>投信近 20 日買賣超張數</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>自營商近 20 日買賣超張數</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>三大法人近 20 日合計買賣超張數</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>最後更新日期</t>
         </is>
@@ -673,19 +685,19 @@
         <v>1.580724998413493</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1808840313655367</v>
+        <v>-0.1808840313655366</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1408225222788201</v>
+        <v>-0.14082252227882</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.04006150908671657</v>
+        <v>-0.0400615090867165</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.05093762199336851</v>
+        <v>-0.0509376219933685</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.05194541608982742</v>
+        <v>-0.0519454160898274</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -825,13 +837,13 @@
         <v>-0.4985450554719721</v>
       </c>
       <c r="R3" t="n">
-        <v>0.04336846687852813</v>
+        <v>0.0433684668785281</v>
       </c>
       <c r="S3" t="n">
-        <v>0.04526563362469704</v>
+        <v>0.045265633624697</v>
       </c>
       <c r="T3" t="n">
-        <v>0.05191589189844181</v>
+        <v>0.0519158918984418</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -971,13 +983,13 @@
         <v>-0.7662871133930196</v>
       </c>
       <c r="R4" t="n">
-        <v>0.05304759902012179</v>
+        <v>0.0530475990201217</v>
       </c>
       <c r="S4" t="n">
-        <v>0.05140381760834511</v>
+        <v>0.0514038176083451</v>
       </c>
       <c r="T4" t="n">
-        <v>0.06091183394929145</v>
+        <v>0.0609118339492914</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1117,7 +1129,7 @@
         <v>-0.3800329123209913</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.06135081899517369</v>
+        <v>-0.0613508189951736</v>
       </c>
       <c r="S5" t="n">
         <v>-0.09689548365965001</v>
@@ -1257,19 +1269,19 @@
         <v>1.7832781618118</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.005917047706663681</v>
+        <v>-0.0059170477066636</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.07419920651975694</v>
+        <v>-0.07419920651975689</v>
       </c>
       <c r="R6" t="n">
-        <v>0.06828215881309325</v>
+        <v>0.0682821588130932</v>
       </c>
       <c r="S6" t="n">
-        <v>0.08930145589692245</v>
+        <v>0.0893014558969224</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1217865254905505</v>
+        <v>0.1217865254905504</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1406,16 +1418,16 @@
         <v>-0.3881676954178754</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.431135773024979</v>
+        <v>-0.4311357730249789</v>
       </c>
       <c r="R7" t="n">
-        <v>0.04296807760710353</v>
+        <v>0.0429680776071035</v>
       </c>
       <c r="S7" t="n">
-        <v>0.00374273470610087</v>
+        <v>0.0037427347061008</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.02217975833307273</v>
+        <v>-0.0221797583330727</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,202 +417,202 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>candidate_level</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>candidate_score</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>市場</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>MA20</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>是否站上 MA20</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>K 值</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>D 值</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Volume_MA5</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Volume_MA20</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Volume_MA40</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>放量倍數</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>MACD_DIF</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>MACD_Signal</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>MACD_Histogram</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>MACD_Histogram_前1日</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>MACD_Histogram_前2日</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>MACD_綠柱趨緩接近翻紅</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>是否符合 KD 區間</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>是否符合 RSI 區間</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>是否明顯放量</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>MACD 是否綠柱趨緩接近翻紅</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>法人近 5 日是否合計買超</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>投信近 5 日是否買超</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>外資近 1 日買賣超張數</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>投信近 1 日買賣超張數</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>自營商近 1 日買賣超張數</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>三大法人近 1 日合計買賣超張數</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>外資近 5 日買賣超張數</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>投信近 5 日買賣超張數</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>自營商近 5 日買賣超張數</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>三大法人近 5 日合計買賣超張數</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>外資近 20 日買賣超張數</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>投信近 20 日買賣超張數</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>自營商近 20 日買賣超張數</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>三大法人近 20 日合計買賣超張數</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>最後更新日期</t>
         </is>
@@ -1400,7 +1388,7 @@
         <v>35.66039521645349</v>
       </c>
       <c r="K7" t="n">
-        <v>47.34339692506855</v>
+        <v>47.34339692506856</v>
       </c>
       <c r="L7" t="n">
         <v>16672</v>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN7"/>
+  <dimension ref="A1:AN6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,63 +629,63 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>2724</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>鑫永銓</t>
+          <t>藝舍-KY</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>88</v>
+        <v>14.44999980926514</v>
       </c>
       <c r="G2" t="n">
-        <v>88.3950008392334</v>
+        <v>15.38000016212463</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>40.67502530054776</v>
+        <v>42.67213120254623</v>
       </c>
       <c r="J2" t="n">
-        <v>34.1890566601808</v>
+        <v>30.26958718735749</v>
       </c>
       <c r="K2" t="n">
-        <v>44.57368438769481</v>
+        <v>32.99149193299974</v>
       </c>
       <c r="L2" t="n">
-        <v>78463</v>
+        <v>37133.8</v>
       </c>
       <c r="M2" t="n">
-        <v>49637.35</v>
+        <v>18709.75</v>
       </c>
       <c r="N2" t="n">
-        <v>40633.525</v>
+        <v>12545.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.580724998413493</v>
+        <v>1.984729886823715</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1808840313655366</v>
+        <v>-1.058124126066586</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.14082252227882</v>
+        <v>-1.055284221637127</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.0400615090867165</v>
+        <v>-0.002839904429459139</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0509376219933685</v>
+        <v>-0.06530930613997166</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0519454160898274</v>
+        <v>-0.1238112854771514</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -732,22 +732,22 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>-15.5</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>-14.5</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>20.886</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
@@ -756,11 +756,11 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>20.886</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
@@ -771,67 +771,67 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3523</t>
+          <t>2390</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>迎輝</t>
+          <t>云辰</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>12.39999961853027</v>
+        <v>9.739999771118164</v>
       </c>
       <c r="G3" t="n">
-        <v>12.82749996185303</v>
+        <v>9.823000001907349</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>48.74658670686937</v>
+        <v>44.51071759430096</v>
       </c>
       <c r="J3" t="n">
-        <v>44.51019693037161</v>
+        <v>30.78421215442959</v>
       </c>
       <c r="K3" t="n">
-        <v>37.71440342086395</v>
+        <v>46.15168541468909</v>
       </c>
       <c r="L3" t="n">
-        <v>172107</v>
+        <v>1100464.6</v>
       </c>
       <c r="M3" t="n">
-        <v>51095.65</v>
+        <v>726741.1</v>
       </c>
       <c r="N3" t="n">
-        <v>40472.775</v>
+        <v>828562</v>
       </c>
       <c r="O3" t="n">
-        <v>3.368329789326489</v>
+        <v>1.514245719693024</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.455176588593444</v>
+        <v>-0.1377415031682343</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.4985450554719721</v>
+        <v>-0.1496411237269726</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0433684668785281</v>
+        <v>0.01189962055873828</v>
       </c>
       <c r="S3" t="n">
-        <v>0.045265633624697</v>
+        <v>-0.0005952129791348959</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0519158918984418</v>
+        <v>-0.04473325155893929</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -869,44 +869,44 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>41.994</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>-0.852</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>41.142</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>166.049</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>-50.41</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>115.639</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>-293.988</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>-4.779000000000009</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>-298.7669999999999</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
@@ -921,63 +921,63 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1538</t>
+          <t>8931</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>正峰</t>
+          <t>大汽電</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>12.19999980926514</v>
+        <v>42.09999847412109</v>
       </c>
       <c r="G4" t="n">
-        <v>12.89499998092651</v>
+        <v>41.83499965667725</v>
       </c>
       <c r="H4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>36.55404909991231</v>
+        <v>39.49569833841275</v>
       </c>
       <c r="J4" t="n">
-        <v>35.38920695637704</v>
+        <v>38.76489537780827</v>
       </c>
       <c r="K4" t="n">
-        <v>34.89998605763309</v>
+        <v>46.935604253331</v>
       </c>
       <c r="L4" t="n">
-        <v>50582.6</v>
+        <v>136205.4</v>
       </c>
       <c r="M4" t="n">
-        <v>22370.4</v>
+        <v>56507.5</v>
       </c>
       <c r="N4" t="n">
-        <v>29351.825</v>
+        <v>45141.5</v>
       </c>
       <c r="O4" t="n">
-        <v>2.261139720344741</v>
+        <v>2.410395080299075</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7132395143728978</v>
+        <v>-0.3103870299002764</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.7662871133930196</v>
+        <v>-0.523598817787043</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0530475990201217</v>
+        <v>0.2132117878867665</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0514038176083451</v>
+        <v>0.2262672188035962</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0609118339492914</v>
+        <v>0.1856546054992838</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1024,35 +1024,35 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.022</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>-4.022</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.995000000000001</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
@@ -1067,63 +1067,63 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6612</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>奈米醫材</t>
+          <t>太設</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>67.80000305175781</v>
+        <v>8.600000381469727</v>
       </c>
       <c r="G5" t="n">
-        <v>68.48000030517578</v>
+        <v>8.761500072479247</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>42.73447310695188</v>
+        <v>34.14338373858578</v>
       </c>
       <c r="J5" t="n">
-        <v>37.20890302468025</v>
+        <v>30.08723873237084</v>
       </c>
       <c r="K5" t="n">
-        <v>44.70522960945206</v>
+        <v>34.51269896470778</v>
       </c>
       <c r="L5" t="n">
-        <v>54836.6</v>
+        <v>282327.4</v>
       </c>
       <c r="M5" t="n">
-        <v>30455.1</v>
+        <v>157687.7</v>
       </c>
       <c r="N5" t="n">
-        <v>23146.25</v>
+        <v>142343.775</v>
       </c>
       <c r="O5" t="n">
-        <v>1.800571989584667</v>
+        <v>1.790421193282672</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.441383731316165</v>
+        <v>-0.08595420701279899</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.3800329123209913</v>
+        <v>-0.06800980811202592</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.0613508189951736</v>
+        <v>-0.01794439890077307</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.09689548365965001</v>
+        <v>-0.02059879359000326</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1401967369944709</v>
+        <v>-0.02015056001327488</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>-86</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1182,10 +1182,10 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-86</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>91.976</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
@@ -1194,11 +1194,11 @@
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>91.976</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4729</t>
+          <t>5487</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>熒茂</t>
+          <t>通泰</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1227,49 +1227,49 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>20.10000038146973</v>
+        <v>27.20000076293945</v>
       </c>
       <c r="G6" t="n">
-        <v>20.12000007629394</v>
+        <v>28.59250001907349</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>37.55792158876897</v>
+        <v>38.39725647307002</v>
       </c>
       <c r="J6" t="n">
-        <v>36.1731702066656</v>
+        <v>32.95345180858228</v>
       </c>
       <c r="K6" t="n">
-        <v>49.127746646583</v>
+        <v>39.83738911306136</v>
       </c>
       <c r="L6" t="n">
-        <v>719039.6</v>
+        <v>96084.39999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>403212.25</v>
+        <v>56397.1</v>
       </c>
       <c r="N6" t="n">
-        <v>281330.4</v>
+        <v>41650.85</v>
       </c>
       <c r="O6" t="n">
-        <v>1.7832781618118</v>
+        <v>1.703711715673323</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.0059170477066636</v>
+        <v>-0.1927200419280091</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.07419920651975689</v>
+        <v>0.01602557002782572</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0682821588130932</v>
+        <v>-0.2087456119558348</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0893014558969224</v>
+        <v>-0.1851350073453385</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1217865254905504</v>
+        <v>-0.2246098410512202</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1344,153 +1344,7 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>70</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>8101</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>華冠</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>13</v>
-      </c>
-      <c r="G7" t="n">
-        <v>13.07749996185303</v>
-      </c>
-      <c r="H7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>45.1279707796968</v>
-      </c>
-      <c r="J7" t="n">
-        <v>35.66039521645349</v>
-      </c>
-      <c r="K7" t="n">
-        <v>47.34339692506856</v>
-      </c>
-      <c r="L7" t="n">
-        <v>16672</v>
-      </c>
-      <c r="M7" t="n">
-        <v>9904.450000000001</v>
-      </c>
-      <c r="N7" t="n">
-        <v>8576.674999999999</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.683283776484307</v>
-      </c>
-      <c r="P7" t="n">
-        <v>-0.3881676954178754</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>-0.4311357730249789</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.0429680776071035</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.0037427347061008</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-0.0221797583330727</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>-0.6220000000000001</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>-3.622</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>-1.252</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>-4.252</v>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN6"/>
+  <dimension ref="A1:AN5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,16 +661,16 @@
         <v>32.99149193299974</v>
       </c>
       <c r="L2" t="n">
-        <v>37133.8</v>
+        <v>37120.2</v>
       </c>
       <c r="M2" t="n">
-        <v>18709.75</v>
+        <v>18706.35</v>
       </c>
       <c r="N2" t="n">
-        <v>12545.4</v>
+        <v>12543.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1.984729886823715</v>
+        <v>1.984363598457208</v>
       </c>
       <c r="P2" t="n">
         <v>-1.058124126066586</v>
@@ -775,12 +775,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2390</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>云辰</t>
+          <t>太設</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,124 +789,124 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>9.739999771118164</v>
+        <v>8.619999885559082</v>
       </c>
       <c r="G3" t="n">
-        <v>9.823000001907349</v>
+        <v>8.743500089645385</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>44.51071759430096</v>
+        <v>39.04131699686465</v>
       </c>
       <c r="J3" t="n">
-        <v>30.78421215442959</v>
+        <v>33.07193148720211</v>
       </c>
       <c r="K3" t="n">
-        <v>46.15168541468909</v>
+        <v>36.63781246300921</v>
       </c>
       <c r="L3" t="n">
-        <v>1100464.6</v>
+        <v>272631</v>
       </c>
       <c r="M3" t="n">
-        <v>726741.1</v>
+        <v>158847.75</v>
       </c>
       <c r="N3" t="n">
-        <v>828562</v>
+        <v>143466.95</v>
       </c>
       <c r="O3" t="n">
-        <v>1.514245719693024</v>
+        <v>1.716303819223124</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1377415031682343</v>
+        <v>-0.08481436639267415</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1496411237269726</v>
+        <v>-0.07137071976815557</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01189962055873828</v>
+        <v>-0.01344364662451858</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0005952129791348959</v>
+        <v>-0.01794439890077307</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.04473325155893929</v>
+        <v>-0.02059879359000326</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
       <c r="AB3" t="n">
-        <v>41.994</v>
+        <v>20</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.852</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>41.142</v>
+        <v>20</v>
       </c>
       <c r="AF3" t="n">
-        <v>166.049</v>
+        <v>-8</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-50.41</v>
+        <v>7</v>
       </c>
       <c r="AI3" t="n">
-        <v>115.639</v>
+        <v>-1</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-293.988</v>
+        <v>142.976</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-4.779000000000009</v>
+        <v>2</v>
       </c>
       <c r="AM3" t="n">
-        <v>-298.7669999999999</v>
+        <v>144.976</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>8931</t>
+          <t>6875</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>大汽電</t>
+          <t>國邑*</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,49 +935,49 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>42.09999847412109</v>
+        <v>37.34999847412109</v>
       </c>
       <c r="G4" t="n">
-        <v>41.83499965667725</v>
+        <v>37.04750003814697</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>39.49569833841275</v>
+        <v>47.0417317923759</v>
       </c>
       <c r="J4" t="n">
-        <v>38.76489537780827</v>
+        <v>44.73777168522721</v>
       </c>
       <c r="K4" t="n">
-        <v>46.935604253331</v>
+        <v>49.84044643581586</v>
       </c>
       <c r="L4" t="n">
-        <v>136205.4</v>
+        <v>395341.8</v>
       </c>
       <c r="M4" t="n">
-        <v>56507.5</v>
+        <v>194463.3</v>
       </c>
       <c r="N4" t="n">
-        <v>45141.5</v>
+        <v>133830.3</v>
       </c>
       <c r="O4" t="n">
-        <v>2.410395080299075</v>
+        <v>2.032989258127369</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3103870299002764</v>
+        <v>-0.153959560660077</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.523598817787043</v>
+        <v>-0.4020915949718807</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2132117878867665</v>
+        <v>0.2481320343118038</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2262672188035962</v>
+        <v>0.2897393626503633</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1856546054992838</v>
+        <v>0.3233672377673575</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1067,63 +1067,63 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>4406</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>太設</t>
+          <t>新昕纖</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>8.600000381469727</v>
+        <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>8.761500072479247</v>
+        <v>10.04800000190735</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>34.14338373858578</v>
+        <v>47.14878085476353</v>
       </c>
       <c r="J5" t="n">
-        <v>30.08723873237084</v>
+        <v>32.11751728644181</v>
       </c>
       <c r="K5" t="n">
-        <v>34.51269896470778</v>
+        <v>48.50266147615626</v>
       </c>
       <c r="L5" t="n">
-        <v>282327.4</v>
+        <v>150000</v>
       </c>
       <c r="M5" t="n">
-        <v>157687.7</v>
+        <v>74855.55</v>
       </c>
       <c r="N5" t="n">
-        <v>142343.775</v>
+        <v>40878.3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.790421193282672</v>
+        <v>2.003859433268475</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.08595420701279899</v>
+        <v>-0.02218336626396145</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.06800980811202592</v>
+        <v>-0.01305900596304625</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.01794439890077307</v>
+        <v>-0.009124360300915194</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.02059879359000326</v>
+        <v>-0.01357035383179256</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.02015056001327488</v>
+        <v>-0.01020833778644447</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-86</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1182,10 +1182,10 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>-86</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>91.976</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
@@ -1194,157 +1194,11 @@
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>91.976</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>70</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>5487</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>通泰</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>27.20000076293945</v>
-      </c>
-      <c r="G6" t="n">
-        <v>28.59250001907349</v>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>38.39725647307002</v>
-      </c>
-      <c r="J6" t="n">
-        <v>32.95345180858228</v>
-      </c>
-      <c r="K6" t="n">
-        <v>39.83738911306136</v>
-      </c>
-      <c r="L6" t="n">
-        <v>96084.39999999999</v>
-      </c>
-      <c r="M6" t="n">
-        <v>56397.1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>41650.85</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.703711715673323</v>
-      </c>
-      <c r="P6" t="n">
-        <v>-0.1927200419280091</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.01602557002782572</v>
-      </c>
-      <c r="R6" t="n">
-        <v>-0.2087456119558348</v>
-      </c>
-      <c r="S6" t="n">
-        <v>-0.1851350073453385</v>
-      </c>
-      <c r="T6" t="n">
-        <v>-0.2246098410512202</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN5"/>
+  <dimension ref="A1:AN3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,91 +625,91 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2724</t>
+          <t>8488</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>藝舍-KY</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>14.44999980926514</v>
+        <v>10.10000038146973</v>
       </c>
       <c r="G2" t="n">
-        <v>15.38000016212463</v>
+        <v>10.12900009155273</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>42.67213120254623</v>
+        <v>35.47904578843965</v>
       </c>
       <c r="J2" t="n">
-        <v>30.26958718735749</v>
+        <v>32.24517665640881</v>
       </c>
       <c r="K2" t="n">
-        <v>32.99149193299974</v>
+        <v>49.24922399615909</v>
       </c>
       <c r="L2" t="n">
-        <v>37120.2</v>
+        <v>168136.6</v>
       </c>
       <c r="M2" t="n">
-        <v>18706.35</v>
+        <v>48484.2</v>
       </c>
       <c r="N2" t="n">
-        <v>12543.7</v>
+        <v>81392.47500000001</v>
       </c>
       <c r="O2" t="n">
-        <v>1.984363598457208</v>
+        <v>3.467863757677759</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.058124126066586</v>
+        <v>0.03279386168015286</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.055284221637127</v>
+        <v>0.01748721588416096</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.002839904429459139</v>
+        <v>0.0153066457959919</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.06530930613997166</v>
+        <v>0.02534233566404201</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1238112854771514</v>
+        <v>-0.03732805345743694</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>-127</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -732,10 +732,10 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>-127</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -744,23 +744,23 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>3.445</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>6.445</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
@@ -771,91 +771,91 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>6228</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>太設</t>
+          <t>全譜</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8.619999885559082</v>
+        <v>22.29999923706055</v>
       </c>
       <c r="G3" t="n">
-        <v>8.743500089645385</v>
+        <v>23.20999975204468</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>39.04131699686465</v>
+        <v>45.00655028047179</v>
       </c>
       <c r="J3" t="n">
-        <v>33.07193148720211</v>
+        <v>34.60500504052698</v>
       </c>
       <c r="K3" t="n">
-        <v>36.63781246300921</v>
+        <v>43.0897637715016</v>
       </c>
       <c r="L3" t="n">
-        <v>272631</v>
+        <v>38056</v>
       </c>
       <c r="M3" t="n">
-        <v>158847.75</v>
+        <v>17082.2</v>
       </c>
       <c r="N3" t="n">
-        <v>143466.95</v>
+        <v>11581.325</v>
       </c>
       <c r="O3" t="n">
-        <v>1.716303819223124</v>
+        <v>2.227816089262507</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.08481436639267415</v>
+        <v>-0.584619645386816</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.07137071976815557</v>
+        <v>-0.5011693517477165</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.01344364662451858</v>
+        <v>-0.0834502936390995</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.01794439890077307</v>
+        <v>-0.1238228748459481</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.02059879359000326</v>
+        <v>-0.1708931176448485</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -878,327 +878,35 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>142.976</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>144.976</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>70</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>6875</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>國邑*</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>37.34999847412109</v>
-      </c>
-      <c r="G4" t="n">
-        <v>37.04750003814697</v>
-      </c>
-      <c r="H4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>47.0417317923759</v>
-      </c>
-      <c r="J4" t="n">
-        <v>44.73777168522721</v>
-      </c>
-      <c r="K4" t="n">
-        <v>49.84044643581586</v>
-      </c>
-      <c r="L4" t="n">
-        <v>395341.8</v>
-      </c>
-      <c r="M4" t="n">
-        <v>194463.3</v>
-      </c>
-      <c r="N4" t="n">
-        <v>133830.3</v>
-      </c>
-      <c r="O4" t="n">
-        <v>2.032989258127369</v>
-      </c>
-      <c r="P4" t="n">
-        <v>-0.153959560660077</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-0.4020915949718807</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.2481320343118038</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.2897393626503633</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.3233672377673575</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>70</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>4406</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>新昕纖</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>10</v>
-      </c>
-      <c r="G5" t="n">
-        <v>10.04800000190735</v>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>47.14878085476353</v>
-      </c>
-      <c r="J5" t="n">
-        <v>32.11751728644181</v>
-      </c>
-      <c r="K5" t="n">
-        <v>48.50266147615626</v>
-      </c>
-      <c r="L5" t="n">
-        <v>150000</v>
-      </c>
-      <c r="M5" t="n">
-        <v>74855.55</v>
-      </c>
-      <c r="N5" t="n">
-        <v>40878.3</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.003859433268475</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-0.02218336626396145</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-0.01305900596304625</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-0.009124360300915194</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-0.01357035383179256</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-0.01020833778644447</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN3"/>
+  <dimension ref="A1:AN2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,63 +629,63 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8488</t>
+          <t>6228</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>全譜</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10.10000038146973</v>
+        <v>21.60000038146973</v>
       </c>
       <c r="G2" t="n">
-        <v>10.12900009155273</v>
+        <v>23.06499977111816</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>35.47904578843965</v>
+        <v>42.43374648058349</v>
       </c>
       <c r="J2" t="n">
-        <v>32.24517665640881</v>
+        <v>37.21458552054582</v>
       </c>
       <c r="K2" t="n">
-        <v>49.24922399615909</v>
+        <v>38.56338700021554</v>
       </c>
       <c r="L2" t="n">
-        <v>168136.6</v>
+        <v>33834.6</v>
       </c>
       <c r="M2" t="n">
-        <v>48484.2</v>
+        <v>17276.8</v>
       </c>
       <c r="N2" t="n">
-        <v>81392.47500000001</v>
+        <v>11591.1</v>
       </c>
       <c r="O2" t="n">
-        <v>3.467863757677759</v>
+        <v>1.958383496943878</v>
       </c>
       <c r="P2" t="n">
-        <v>0.03279386168015286</v>
+        <v>-0.6185120591497828</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01748721588416096</v>
+        <v>-0.5246378932281297</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0153066457959919</v>
+        <v>-0.0938741659216531</v>
       </c>
       <c r="S2" t="n">
-        <v>0.02534233566404201</v>
+        <v>-0.0834502936390995</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.03732805345743694</v>
+        <v>-0.1238228748459481</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>-127</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -732,10 +732,10 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-127</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -744,169 +744,23 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3.445</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>6.445</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>70</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>6228</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>全譜</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>22.29999923706055</v>
-      </c>
-      <c r="G3" t="n">
-        <v>23.20999975204468</v>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>45.00655028047179</v>
-      </c>
-      <c r="J3" t="n">
-        <v>34.60500504052698</v>
-      </c>
-      <c r="K3" t="n">
-        <v>43.0897637715016</v>
-      </c>
-      <c r="L3" t="n">
-        <v>38056</v>
-      </c>
-      <c r="M3" t="n">
-        <v>17082.2</v>
-      </c>
-      <c r="N3" t="n">
-        <v>11581.325</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2.227816089262507</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-0.584619645386816</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-0.5011693517477165</v>
-      </c>
-      <c r="R3" t="n">
-        <v>-0.0834502936390995</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-0.1238228748459481</v>
-      </c>
-      <c r="T3" t="n">
-        <v>-0.1708931176448485</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN2"/>
+  <dimension ref="A1:AN4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,142 +625,434 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>90</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>8466</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>美吉吉-KY</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>14.19999980926514</v>
+      </c>
+      <c r="G2" t="n">
+        <v>15.30999979972839</v>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>42.13181046393437</v>
+      </c>
+      <c r="J2" t="n">
+        <v>30.83314156353119</v>
+      </c>
+      <c r="K2" t="n">
+        <v>31.28330027070963</v>
+      </c>
+      <c r="L2" t="n">
+        <v>366853</v>
+      </c>
+      <c r="M2" t="n">
+        <v>152121.3</v>
+      </c>
+      <c r="N2" t="n">
+        <v>124873.3</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.411582072990436</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-0.9761969447120702</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-0.9494209026593134</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-0.02677604205275674</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-0.06131411371289652</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-0.0975775564652771</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>73.67099999999999</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>73.67099999999999</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>51.71599999999998</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>-0.05499999999999972</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>51.661</v>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>70</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>6228</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>全譜</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1470</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>大統新創</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>21.89999961853027</v>
+      </c>
+      <c r="G3" t="n">
+        <v>22.15749998092651</v>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>41.07675613252933</v>
+      </c>
+      <c r="J3" t="n">
+        <v>33.15909750003893</v>
+      </c>
+      <c r="K3" t="n">
+        <v>48.50901763370656</v>
+      </c>
+      <c r="L3" t="n">
+        <v>74523.60000000001</v>
+      </c>
+      <c r="M3" t="n">
+        <v>32638.8</v>
+      </c>
+      <c r="N3" t="n">
+        <v>22658.45</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.283282473620354</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-0.262759024748231</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-0.1859066261218339</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-0.07685239862639706</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-0.1222367683968527</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-0.1005429277426851</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.265</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.265</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.2629999999999999</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-9.737</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.264</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>9.864000000000001</v>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>70</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>8928</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>鉅明</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>21.60000038146973</v>
-      </c>
-      <c r="G2" t="n">
-        <v>23.06499977111816</v>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>42.43374648058349</v>
-      </c>
-      <c r="J2" t="n">
-        <v>37.21458552054582</v>
-      </c>
-      <c r="K2" t="n">
-        <v>38.56338700021554</v>
-      </c>
-      <c r="L2" t="n">
-        <v>33834.6</v>
-      </c>
-      <c r="M2" t="n">
-        <v>17276.8</v>
-      </c>
-      <c r="N2" t="n">
-        <v>11591.1</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.958383496943878</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-0.6185120591497828</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-0.5246378932281297</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-0.0938741659216531</v>
-      </c>
-      <c r="S2" t="n">
-        <v>-0.0834502936390995</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-0.1238228748459481</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="F4" t="n">
+        <v>21.54999923706055</v>
+      </c>
+      <c r="G4" t="n">
+        <v>21.5524998664856</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>47.63442062598287</v>
+      </c>
+      <c r="J4" t="n">
+        <v>45.86270597922287</v>
+      </c>
+      <c r="K4" t="n">
+        <v>43.99107676236491</v>
+      </c>
+      <c r="L4" t="n">
+        <v>59767.2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>36847.9</v>
+      </c>
+      <c r="N4" t="n">
+        <v>27521.075</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.621997454400386</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0.3269092506565379</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0.4475885844689923</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.1206793338124544</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.1254304691038278</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.1294693545270613</v>
+      </c>
+      <c r="U4" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN4"/>
+  <dimension ref="A1:AN6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,12 +629,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8466</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>雋揚</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,49 +643,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>14.19999980926514</v>
+        <v>25.89999961853027</v>
       </c>
       <c r="G2" t="n">
-        <v>15.30999979972839</v>
+        <v>26.15999994277954</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>42.13181046393437</v>
+        <v>42.25048934061301</v>
       </c>
       <c r="J2" t="n">
-        <v>30.83314156353119</v>
+        <v>33.8209021267991</v>
       </c>
       <c r="K2" t="n">
-        <v>31.28330027070963</v>
+        <v>40.95620997279505</v>
       </c>
       <c r="L2" t="n">
-        <v>366853</v>
+        <v>111610.4</v>
       </c>
       <c r="M2" t="n">
-        <v>152121.3</v>
+        <v>48540.5</v>
       </c>
       <c r="N2" t="n">
-        <v>124873.3</v>
+        <v>40700</v>
       </c>
       <c r="O2" t="n">
-        <v>2.411582072990436</v>
+        <v>2.299325305672582</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.9761969447120702</v>
+        <v>-0.4616985071880748</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9494209026593134</v>
+        <v>-0.4565687880106439</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.02677604205275674</v>
+        <v>-0.00512971917743088</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.06131411371289652</v>
+        <v>-0.04571732826271624</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0975775564652771</v>
+        <v>-0.07457249009275502</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>3</v>
+        <v>148</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -732,35 +732,35 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>3</v>
+        <v>148</v>
       </c>
       <c r="AF2" t="n">
-        <v>73.67099999999999</v>
+        <v>415</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AI2" t="n">
-        <v>73.67099999999999</v>
+        <v>411</v>
       </c>
       <c r="AJ2" t="n">
-        <v>51.71599999999998</v>
+        <v>386.6</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.05499999999999972</v>
+        <v>-9</v>
       </c>
       <c r="AM2" t="n">
-        <v>51.661</v>
+        <v>377.6</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
@@ -771,16 +771,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1470</t>
+          <t>8466</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>大統新創</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,124 +789,124 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>21.89999961853027</v>
+        <v>14.10000038146973</v>
       </c>
       <c r="G3" t="n">
-        <v>22.15749998092651</v>
+        <v>15.15999979972839</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>41.07675613252933</v>
+        <v>45.32925522092123</v>
       </c>
       <c r="J3" t="n">
-        <v>33.15909750003893</v>
+        <v>35.66517944932787</v>
       </c>
       <c r="K3" t="n">
-        <v>48.50901763370656</v>
+        <v>30.53820857086693</v>
       </c>
       <c r="L3" t="n">
-        <v>74523.60000000001</v>
+        <v>340900.2</v>
       </c>
       <c r="M3" t="n">
-        <v>32638.8</v>
+        <v>154533.1</v>
       </c>
       <c r="N3" t="n">
-        <v>22658.45</v>
+        <v>123429.2</v>
       </c>
       <c r="O3" t="n">
-        <v>2.283282473620354</v>
+        <v>2.206001173858545</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.262759024748231</v>
+        <v>-0.9512342079143821</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1859066261218339</v>
+        <v>-0.9497835637103272</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.07685239862639706</v>
+        <v>-0.00145064420405483</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1222367683968527</v>
+        <v>-0.02677604205275674</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1005429277426851</v>
+        <v>-0.06131411371289652</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.265</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.265</v>
+        <v>5</v>
       </c>
       <c r="AF3" t="n">
-        <v>-10</v>
+        <v>72.67099999999999</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.2629999999999999</v>
+        <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>-9.737</v>
+        <v>73.67099999999999</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8.6</v>
+        <v>50.71599999999999</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.264</v>
+        <v>0.9450000000000003</v>
       </c>
       <c r="AM3" t="n">
-        <v>9.864000000000001</v>
+        <v>51.66099999999999</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
@@ -917,142 +917,434 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>90</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1338</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>廣華-KY</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>15.85000038146973</v>
+      </c>
+      <c r="G4" t="n">
+        <v>16.06500005722046</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>40.96639887151434</v>
+      </c>
+      <c r="J4" t="n">
+        <v>34.83208920733619</v>
+      </c>
+      <c r="K4" t="n">
+        <v>46.96447334443889</v>
+      </c>
+      <c r="L4" t="n">
+        <v>284047.8</v>
+      </c>
+      <c r="M4" t="n">
+        <v>162919.6</v>
+      </c>
+      <c r="N4" t="n">
+        <v>211193.775</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.743484516289016</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0.1377624999455076</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0.1224406403031656</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-0.01532185964234199</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-0.02697333027718753</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.05176329180942127</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>31</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-182.4</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-192.4</v>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>80</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>8284</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>三竹</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>63.70999965667725</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>46.9281879473689</v>
+      </c>
+      <c r="J5" t="n">
+        <v>39.28982758557291</v>
+      </c>
+      <c r="K5" t="n">
+        <v>48.37248877635688</v>
+      </c>
+      <c r="L5" t="n">
+        <v>64857.6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>31778.7</v>
+      </c>
+      <c r="N5" t="n">
+        <v>21612.975</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.040914197245324</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.04453489507661601</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.001020539331432195</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-0.04351435574518382</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0.04895125700873677</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.07403858456839316</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>70</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>8928</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>鉅明</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>21.54999923706055</v>
-      </c>
-      <c r="G4" t="n">
-        <v>21.5524998664856</v>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>47.63442062598287</v>
-      </c>
-      <c r="J4" t="n">
-        <v>45.86270597922287</v>
-      </c>
-      <c r="K4" t="n">
-        <v>43.99107676236491</v>
-      </c>
-      <c r="L4" t="n">
-        <v>59767.2</v>
-      </c>
-      <c r="M4" t="n">
-        <v>36847.9</v>
-      </c>
-      <c r="N4" t="n">
-        <v>27521.075</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.621997454400386</v>
-      </c>
-      <c r="P4" t="n">
-        <v>-0.3269092506565379</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-0.4475885844689923</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.1206793338124544</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.1254304691038278</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.1294693545270613</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>5007</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>三星</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>56.79999923706055</v>
+      </c>
+      <c r="G6" t="n">
+        <v>57.42999992370606</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>34.76544788187115</v>
+      </c>
+      <c r="J6" t="n">
+        <v>32.55215950251866</v>
+      </c>
+      <c r="K6" t="n">
+        <v>46.51692770976436</v>
+      </c>
+      <c r="L6" t="n">
+        <v>119998</v>
+      </c>
+      <c r="M6" t="n">
+        <v>58591.75</v>
+      </c>
+      <c r="N6" t="n">
+        <v>78426.3</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.048035772954384</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.3593410605381848</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.1788533672942542</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-0.1804876932439306</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.2484300535012318</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.2730152763413677</v>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="AB6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-52</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-50</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-31.541</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-19</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-50.541</v>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -625,71 +625,71 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>4416</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>雋揚</t>
+          <t>三圓</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>25.89999961853027</v>
+        <v>12.30000019073486</v>
       </c>
       <c r="G2" t="n">
-        <v>26.15999994277954</v>
+        <v>12.24000000953674</v>
       </c>
       <c r="H2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>42.25048934061301</v>
+        <v>44.64817059534596</v>
       </c>
       <c r="J2" t="n">
-        <v>33.8209021267991</v>
+        <v>32.72429750926753</v>
       </c>
       <c r="K2" t="n">
-        <v>40.95620997279505</v>
+        <v>45.80255254903346</v>
       </c>
       <c r="L2" t="n">
-        <v>111610.4</v>
+        <v>610195</v>
       </c>
       <c r="M2" t="n">
-        <v>48540.5</v>
+        <v>335101.05</v>
       </c>
       <c r="N2" t="n">
-        <v>40700</v>
+        <v>423465.275</v>
       </c>
       <c r="O2" t="n">
-        <v>2.299325305672582</v>
+        <v>1.820928343853294</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4616985071880748</v>
+        <v>-0.6718695447384011</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.4565687880106439</v>
+        <v>-0.7288069036281095</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.00512971917743088</v>
+        <v>0.05693735888970841</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.04571732826271624</v>
+        <v>-0.019716350229117</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.07457249009275502</v>
+        <v>-0.01755694356024695</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -732,35 +732,35 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>415</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>411</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>386.6</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>377.6</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -771,16 +771,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8466</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>三星</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,53 +789,53 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>14.10000038146973</v>
+        <v>56.70000076293945</v>
       </c>
       <c r="G3" t="n">
-        <v>15.15999979972839</v>
+        <v>57.36499996185303</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>45.32925522092123</v>
+        <v>40.46092984155371</v>
       </c>
       <c r="J3" t="n">
-        <v>35.66517944932787</v>
+        <v>35.18841655518968</v>
       </c>
       <c r="K3" t="n">
-        <v>30.53820857086693</v>
+        <v>44.68760741735724</v>
       </c>
       <c r="L3" t="n">
-        <v>340900.2</v>
+        <v>102393.2</v>
       </c>
       <c r="M3" t="n">
-        <v>154533.1</v>
+        <v>57940.55</v>
       </c>
       <c r="N3" t="n">
-        <v>123429.2</v>
+        <v>78663.22500000001</v>
       </c>
       <c r="O3" t="n">
-        <v>2.206001173858545</v>
+        <v>1.767211391676468</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9512342079143821</v>
+        <v>-0.3451264166176458</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9497835637103272</v>
+        <v>-0.2118360253571538</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.00145064420405483</v>
+        <v>-0.133290391260492</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.02677604205275674</v>
+        <v>-0.1805930325518812</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.06131411371289652</v>
+        <v>-0.2485432059450666</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -855,12 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -869,19 +869,19 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE3" t="n">
         <v>1</v>
       </c>
-      <c r="AE3" t="n">
-        <v>5</v>
-      </c>
       <c r="AF3" t="n">
-        <v>72.67099999999999</v>
+        <v>-44</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -890,23 +890,23 @@
         <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>73.67099999999999</v>
+        <v>-43</v>
       </c>
       <c r="AJ3" t="n">
-        <v>50.71599999999999</v>
+        <v>-83</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.9450000000000003</v>
+        <v>-8</v>
       </c>
       <c r="AM3" t="n">
-        <v>51.66099999999999</v>
+        <v>-91</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -917,71 +917,71 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>廣華-KY</t>
+          <t>金穎生技</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>15.85000038146973</v>
+        <v>37.25</v>
       </c>
       <c r="G4" t="n">
-        <v>16.06500005722046</v>
+        <v>37.21249961853027</v>
       </c>
       <c r="H4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>40.96639887151434</v>
+        <v>41.8344008282433</v>
       </c>
       <c r="J4" t="n">
-        <v>34.83208920733619</v>
+        <v>33.04077912066366</v>
       </c>
       <c r="K4" t="n">
-        <v>46.96447334443889</v>
+        <v>48.59576832016765</v>
       </c>
       <c r="L4" t="n">
-        <v>284047.8</v>
+        <v>54110.2</v>
       </c>
       <c r="M4" t="n">
-        <v>162919.6</v>
+        <v>30672.8</v>
       </c>
       <c r="N4" t="n">
-        <v>211193.775</v>
+        <v>30189.125</v>
       </c>
       <c r="O4" t="n">
-        <v>1.743484516289016</v>
+        <v>1.764110221433974</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1377624999455076</v>
+        <v>-0.536264806187468</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1224406403031656</v>
+        <v>-0.6566094926352166</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.01532185964234199</v>
+        <v>0.1203446864477486</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.02697333027718753</v>
+        <v>0.0853015146392766</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.05176329180942127</v>
+        <v>-0.09502700830865307</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1001,12 +1001,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1024,35 +1024,35 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-182.4</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-192.4</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1063,71 +1063,71 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>8284</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>三竹</t>
+          <t>淘帝-KY</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>63.5</v>
+        <v>5.5</v>
       </c>
       <c r="G5" t="n">
-        <v>63.70999965667725</v>
+        <v>5.538500046730041</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>46.9281879473689</v>
+        <v>42.08062567950864</v>
       </c>
       <c r="J5" t="n">
-        <v>39.28982758557291</v>
+        <v>34.0015997178355</v>
       </c>
       <c r="K5" t="n">
-        <v>48.37248877635688</v>
+        <v>42.94226281497132</v>
       </c>
       <c r="L5" t="n">
-        <v>64857.6</v>
+        <v>680002.8</v>
       </c>
       <c r="M5" t="n">
-        <v>31778.7</v>
+        <v>416990.4</v>
       </c>
       <c r="N5" t="n">
-        <v>21612.975</v>
+        <v>348796.8</v>
       </c>
       <c r="O5" t="n">
-        <v>2.040914197245324</v>
+        <v>1.630739700482313</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.04453489507661601</v>
+        <v>-0.1596703951226299</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.001020539331432195</v>
+        <v>-0.2039178663066561</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.04351435574518382</v>
+        <v>0.04424747118402619</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.04895125700873677</v>
+        <v>0.04441883756943005</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.07403858456839316</v>
+        <v>0.02068600898707432</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1161,44 +1161,44 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>-61</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>25.991</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>-35.009</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>-387</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-361</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>-390.1990000000001</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-375.1990000000001</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1213,63 +1213,63 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>8450</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>三星</t>
+          <t>霹靂</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>56.79999923706055</v>
+        <v>15.85000038146973</v>
       </c>
       <c r="G6" t="n">
-        <v>57.42999992370606</v>
+        <v>16.13750004768372</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>34.76544788187115</v>
+        <v>48.24534972554505</v>
       </c>
       <c r="J6" t="n">
-        <v>32.55215950251866</v>
+        <v>38.93669762889417</v>
       </c>
       <c r="K6" t="n">
-        <v>46.51692770976436</v>
+        <v>38.30768259062744</v>
       </c>
       <c r="L6" t="n">
-        <v>119998</v>
+        <v>88713.39999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>58591.75</v>
+        <v>57813.6</v>
       </c>
       <c r="N6" t="n">
-        <v>78426.3</v>
+        <v>51844.425</v>
       </c>
       <c r="O6" t="n">
-        <v>2.048035772954384</v>
+        <v>1.53447285759752</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3593410605381848</v>
+        <v>-0.298682015794002</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1788533672942542</v>
+        <v>-0.319504763160583</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.1804876932439306</v>
+        <v>0.02082274736658102</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2484300535012318</v>
+        <v>0.01611677297109121</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2730152763413677</v>
+        <v>-0.003288970895070409</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1316,35 +1316,35 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>-52</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-31.541</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>-19</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>-50.541</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN6"/>
+  <dimension ref="A1:AN8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,71 +625,71 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4416</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>三圓</t>
+          <t>大宇</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>12.30000019073486</v>
+        <v>11.80000019073486</v>
       </c>
       <c r="G2" t="n">
-        <v>12.24000000953674</v>
+        <v>12.0875</v>
       </c>
       <c r="H2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>44.64817059534596</v>
+        <v>42.47778467331568</v>
       </c>
       <c r="J2" t="n">
-        <v>32.72429750926753</v>
+        <v>34.58741944929598</v>
       </c>
       <c r="K2" t="n">
-        <v>45.80255254903346</v>
+        <v>42.21817670212703</v>
       </c>
       <c r="L2" t="n">
-        <v>610195</v>
+        <v>155550.6</v>
       </c>
       <c r="M2" t="n">
-        <v>335101.05</v>
+        <v>90304.39999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>423465.275</v>
+        <v>85055.45</v>
       </c>
       <c r="O2" t="n">
-        <v>1.820928343853294</v>
+        <v>1.722514074618734</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.6718695447384011</v>
+        <v>-0.3068876676710826</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.7288069036281095</v>
+        <v>-0.3041763461140427</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05693735888970841</v>
+        <v>-0.002711321557039903</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.019716350229117</v>
+        <v>-0.02393894277098824</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.01755694356024695</v>
+        <v>-0.02593541208366917</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -723,44 +723,44 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>10.9</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>3.899999999999999</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
@@ -771,16 +771,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>2038</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>三星</t>
+          <t>海光</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,49 +789,49 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>56.70000076293945</v>
+        <v>13.75</v>
       </c>
       <c r="G3" t="n">
-        <v>57.36499996185303</v>
+        <v>13.7699999332428</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>40.46092984155371</v>
+        <v>40.82376659988958</v>
       </c>
       <c r="J3" t="n">
-        <v>35.18841655518968</v>
+        <v>33.16819858391899</v>
       </c>
       <c r="K3" t="n">
-        <v>44.68760741735724</v>
+        <v>45.53784848385995</v>
       </c>
       <c r="L3" t="n">
-        <v>102393.2</v>
+        <v>1559567</v>
       </c>
       <c r="M3" t="n">
-        <v>57940.55</v>
+        <v>676581.75</v>
       </c>
       <c r="N3" t="n">
-        <v>78663.22500000001</v>
+        <v>579945.125</v>
       </c>
       <c r="O3" t="n">
-        <v>1.767211391676468</v>
+        <v>2.305068086746354</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3451264166176458</v>
+        <v>-0.2472570287480096</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2118360253571538</v>
+        <v>-0.3396298094851591</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.133290391260492</v>
+        <v>0.0923727807371495</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1805930325518812</v>
+        <v>0.09592282222153192</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2485432059450666</v>
+        <v>0.06829461301527429</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -869,44 +869,44 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>-353.999</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE3" t="n">
-        <v>1</v>
+        <v>-348.999</v>
       </c>
       <c r="AF3" t="n">
-        <v>-44</v>
+        <v>115.623</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AI3" t="n">
-        <v>-43</v>
+        <v>127.623</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-83</v>
+        <v>-633.977</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-8</v>
+        <v>17.068</v>
       </c>
       <c r="AM3" t="n">
-        <v>-91</v>
+        <v>-616.909</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>4416</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>金穎生技</t>
+          <t>三圓</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,49 +935,49 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>37.25</v>
+        <v>10.75</v>
       </c>
       <c r="G4" t="n">
-        <v>37.21249961853027</v>
+        <v>12.04000005722046</v>
       </c>
       <c r="H4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>41.8344008282433</v>
+        <v>35.20235216610757</v>
       </c>
       <c r="J4" t="n">
-        <v>33.04077912066366</v>
+        <v>34.98206340225782</v>
       </c>
       <c r="K4" t="n">
-        <v>48.59576832016765</v>
+        <v>33.1029685571992</v>
       </c>
       <c r="L4" t="n">
-        <v>54110.2</v>
+        <v>1296178.8</v>
       </c>
       <c r="M4" t="n">
-        <v>30672.8</v>
+        <v>451597</v>
       </c>
       <c r="N4" t="n">
-        <v>30189.125</v>
+        <v>484863.25</v>
       </c>
       <c r="O4" t="n">
-        <v>1.764110221433974</v>
+        <v>2.870211272439808</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.536264806187468</v>
+        <v>-0.7117620793823836</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.6566094926352166</v>
+        <v>-0.7060587974606544</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1203446864477486</v>
+        <v>-0.005703281921729197</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0853015146392766</v>
+        <v>0.026968137215303</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.09502700830865307</v>
+        <v>0.05145118891417133</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>2515</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>淘帝-KY</t>
+          <t>中工</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1081,49 +1081,49 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5.5</v>
+        <v>12.85000038146973</v>
       </c>
       <c r="G5" t="n">
-        <v>5.538500046730041</v>
+        <v>12.99000010490417</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>42.08062567950864</v>
+        <v>47.20877887210785</v>
       </c>
       <c r="J5" t="n">
-        <v>34.0015997178355</v>
+        <v>46.92587293431302</v>
       </c>
       <c r="K5" t="n">
-        <v>42.94226281497132</v>
+        <v>46.35613028522617</v>
       </c>
       <c r="L5" t="n">
-        <v>680002.8</v>
+        <v>13771935.6</v>
       </c>
       <c r="M5" t="n">
-        <v>416990.4</v>
+        <v>7781868.45</v>
       </c>
       <c r="N5" t="n">
-        <v>348796.8</v>
+        <v>7521902.475</v>
       </c>
       <c r="O5" t="n">
-        <v>1.630739700482313</v>
+        <v>1.76974664741345</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1596703951226299</v>
+        <v>-0.1738124587912182</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2039178663066561</v>
+        <v>-0.2354940485949354</v>
       </c>
       <c r="R5" t="n">
-        <v>0.04424747118402619</v>
+        <v>0.06168158980371719</v>
       </c>
       <c r="S5" t="n">
-        <v>0.04441883756943005</v>
+        <v>0.07571777918981371</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02068600898707432</v>
+        <v>0.09542878630242324</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1161,44 +1161,44 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>-61</v>
+        <v>-648.591</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>25.991</v>
+        <v>-91.001</v>
       </c>
       <c r="AE5" t="n">
-        <v>-35.009</v>
+        <v>-739.592</v>
       </c>
       <c r="AF5" t="n">
-        <v>-387</v>
+        <v>-15758.515</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AH5" t="n">
-        <v>26</v>
+        <v>-43.71700000000001</v>
       </c>
       <c r="AI5" t="n">
-        <v>-361</v>
+        <v>-15804.232</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-390.1990000000001</v>
+        <v>-33714.833</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="AL5" t="n">
-        <v>15</v>
+        <v>-543.2929999999999</v>
       </c>
       <c r="AM5" t="n">
-        <v>-375.1990000000001</v>
+        <v>-34280.126</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>8450</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>霹靂</t>
+          <t>永捷</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1227,49 +1227,49 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>15.85000038146973</v>
+        <v>13.64999961853027</v>
       </c>
       <c r="G6" t="n">
-        <v>16.13750004768372</v>
+        <v>14.12750005722046</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>48.24534972554505</v>
+        <v>40.73995696987673</v>
       </c>
       <c r="J6" t="n">
-        <v>38.93669762889417</v>
+        <v>30.36201725484161</v>
       </c>
       <c r="K6" t="n">
-        <v>38.30768259062744</v>
+        <v>43.38091503751957</v>
       </c>
       <c r="L6" t="n">
-        <v>88713.39999999999</v>
+        <v>2193922</v>
       </c>
       <c r="M6" t="n">
-        <v>57813.6</v>
+        <v>1277304.6</v>
       </c>
       <c r="N6" t="n">
-        <v>51844.425</v>
+        <v>1617101.375</v>
       </c>
       <c r="O6" t="n">
-        <v>1.53447285759752</v>
+        <v>1.717618491313661</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.298682015794002</v>
+        <v>-0.382614578701455</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.319504763160583</v>
+        <v>-0.3855484701346324</v>
       </c>
       <c r="R6" t="n">
-        <v>0.02082274736658102</v>
+        <v>0.002933891433177405</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01611677297109121</v>
+        <v>-0.01342220986151338</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.003288970895070409</v>
+        <v>-0.09895827119237943</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1344,7 +1344,299 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>70</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>6167</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>久正</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>11.89999961853027</v>
+      </c>
+      <c r="G7" t="n">
+        <v>11.92749996185303</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>49.89608294742852</v>
+      </c>
+      <c r="J7" t="n">
+        <v>44.342445619861</v>
+      </c>
+      <c r="K7" t="n">
+        <v>45.50089618493725</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1171292.8</v>
+      </c>
+      <c r="M7" t="n">
+        <v>683918.95</v>
+      </c>
+      <c r="N7" t="n">
+        <v>822660.975</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.712619309641881</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0.2735697922370459</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.3859679688494501</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.1123981766124042</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.1233794293946632</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.1060578384622027</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>70</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>8424</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>惠普</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>73</v>
+      </c>
+      <c r="G8" t="n">
+        <v>73.57499923706055</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>36.13691463470187</v>
+      </c>
+      <c r="J8" t="n">
+        <v>30.76064634319857</v>
+      </c>
+      <c r="K8" t="n">
+        <v>33.40907078700683</v>
+      </c>
+      <c r="L8" t="n">
+        <v>34979.4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>22711.4</v>
+      </c>
+      <c r="N8" t="n">
+        <v>16180.75</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.540169254207138</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0.4125750067465361</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.3673783771893652</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-0.04519662955717096</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0.07018999777962898</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0.05828858234275314</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN8"/>
+  <dimension ref="A1:AN16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,16 +625,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>2038</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>大宇</t>
+          <t>海光</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,53 +643,53 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11.80000019073486</v>
+        <v>13.64999961853027</v>
       </c>
       <c r="G2" t="n">
-        <v>12.0875</v>
+        <v>13.73999991416931</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>42.47778467331568</v>
+        <v>37.06432432240711</v>
       </c>
       <c r="J2" t="n">
-        <v>34.58741944929598</v>
+        <v>34.46690716341503</v>
       </c>
       <c r="K2" t="n">
-        <v>42.21817670212703</v>
+        <v>44.22805854971687</v>
       </c>
       <c r="L2" t="n">
-        <v>155550.6</v>
+        <v>1635973.8</v>
       </c>
       <c r="M2" t="n">
-        <v>90304.39999999999</v>
+        <v>690601.35</v>
       </c>
       <c r="N2" t="n">
-        <v>85055.45</v>
+        <v>558182.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.722514074618734</v>
+        <v>2.368911963464885</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.3068876676710826</v>
+        <v>-0.2371049355818755</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.3041763461140427</v>
+        <v>-0.3191248347045024</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.002711321557039903</v>
+        <v>0.08201989912262686</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.02393894277098824</v>
+        <v>0.0923727807371495</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.02593541208366917</v>
+        <v>0.09592282222153192</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -723,44 +723,44 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>30</v>
+        <v>-85.98</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="AE2" t="n">
-        <v>27</v>
+        <v>-81.98</v>
       </c>
       <c r="AF2" t="n">
-        <v>75</v>
+        <v>337.642</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-3</v>
+        <v>23</v>
       </c>
       <c r="AI2" t="n">
-        <v>72</v>
+        <v>360.642</v>
       </c>
       <c r="AJ2" t="n">
-        <v>10.9</v>
+        <v>-31.95699999999998</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-7</v>
+        <v>21.068</v>
       </c>
       <c r="AM2" t="n">
-        <v>3.899999999999999</v>
+        <v>-10.889</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
@@ -775,12 +775,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>海光</t>
+          <t>中鴻</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,49 +789,49 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>13.75</v>
+        <v>17.85000038146973</v>
       </c>
       <c r="G3" t="n">
-        <v>13.7699999332428</v>
+        <v>17.70750007629395</v>
       </c>
       <c r="H3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>40.82376659988958</v>
+        <v>40.43792868685871</v>
       </c>
       <c r="J3" t="n">
-        <v>33.16819858391899</v>
+        <v>38.12183962843405</v>
       </c>
       <c r="K3" t="n">
-        <v>45.53784848385995</v>
+        <v>49.65195757131</v>
       </c>
       <c r="L3" t="n">
-        <v>1559567</v>
+        <v>16225369.6</v>
       </c>
       <c r="M3" t="n">
-        <v>676581.75</v>
+        <v>7543853.35</v>
       </c>
       <c r="N3" t="n">
-        <v>579945.125</v>
+        <v>6658272.975</v>
       </c>
       <c r="O3" t="n">
-        <v>2.305068086746354</v>
+        <v>2.150806603365374</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2472570287480096</v>
+        <v>-0.02864485870100708</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.3396298094851591</v>
+        <v>-0.1059979756138136</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0923727807371495</v>
+        <v>0.07735311691280651</v>
       </c>
       <c r="S3" t="n">
-        <v>0.09592282222153192</v>
+        <v>0.08637407264506108</v>
       </c>
       <c r="T3" t="n">
-        <v>0.06829461301527429</v>
+        <v>0.08009296848946459</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -869,44 +869,44 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>-353.999</v>
+        <v>251</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>-348.999</v>
+        <v>252</v>
       </c>
       <c r="AF3" t="n">
-        <v>115.623</v>
+        <v>7669.2</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>12</v>
+        <v>-187.808</v>
       </c>
       <c r="AI3" t="n">
-        <v>127.623</v>
+        <v>7481.391999999999</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-633.977</v>
+        <v>19744.345</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>17.068</v>
+        <v>-2185.709</v>
       </c>
       <c r="AM3" t="n">
-        <v>-616.909</v>
+        <v>17558.636</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
@@ -917,67 +917,67 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4416</t>
+          <t>1506</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>三圓</t>
+          <t>正道</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>10.75</v>
+        <v>10.44999980926514</v>
       </c>
       <c r="G4" t="n">
-        <v>12.04000005722046</v>
+        <v>10.39500002861023</v>
       </c>
       <c r="H4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>35.20235216610757</v>
+        <v>32.8102714025607</v>
       </c>
       <c r="J4" t="n">
-        <v>34.98206340225782</v>
+        <v>30.19899491454913</v>
       </c>
       <c r="K4" t="n">
-        <v>33.1029685571992</v>
+        <v>48.48807011997991</v>
       </c>
       <c r="L4" t="n">
-        <v>1296178.8</v>
+        <v>525304.8</v>
       </c>
       <c r="M4" t="n">
-        <v>451597</v>
+        <v>283812.8</v>
       </c>
       <c r="N4" t="n">
-        <v>484863.25</v>
+        <v>245164.95</v>
       </c>
       <c r="O4" t="n">
-        <v>2.870211272439808</v>
+        <v>1.850884808578049</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7117620793823836</v>
+        <v>-0.1708213808171095</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.7060587974606544</v>
+        <v>-0.2026428411904573</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.005703281921729197</v>
+        <v>0.03182146037334779</v>
       </c>
       <c r="S4" t="n">
-        <v>0.026968137215303</v>
+        <v>0.01608101913293472</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05145118891417133</v>
+        <v>0.02832245465700114</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1024,35 +1024,35 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>-5.138</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>81.86199999999999</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>5.862000000000002</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>168.862</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
@@ -1063,16 +1063,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2515</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>中工</t>
+          <t>東華</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1081,53 +1081,53 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>12.85000038146973</v>
+        <v>18</v>
       </c>
       <c r="G5" t="n">
-        <v>12.99000010490417</v>
+        <v>18.42249994277954</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>47.20877887210785</v>
+        <v>44.71616308800814</v>
       </c>
       <c r="J5" t="n">
-        <v>46.92587293431302</v>
+        <v>30.15604034701413</v>
       </c>
       <c r="K5" t="n">
-        <v>46.35613028522617</v>
+        <v>45.76355978601987</v>
       </c>
       <c r="L5" t="n">
-        <v>13771935.6</v>
+        <v>63560.8</v>
       </c>
       <c r="M5" t="n">
-        <v>7781868.45</v>
+        <v>36620.45</v>
       </c>
       <c r="N5" t="n">
-        <v>7521902.475</v>
+        <v>26902.15</v>
       </c>
       <c r="O5" t="n">
-        <v>1.76974664741345</v>
+        <v>1.735664089327138</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1738124587912182</v>
+        <v>-0.2158364213503425</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2354940485949354</v>
+        <v>-0.1969396490612297</v>
       </c>
       <c r="R5" t="n">
-        <v>0.06168158980371719</v>
+        <v>-0.0188967722891128</v>
       </c>
       <c r="S5" t="n">
-        <v>0.07571777918981371</v>
+        <v>-0.03147312073320929</v>
       </c>
       <c r="T5" t="n">
-        <v>0.09542878630242324</v>
+        <v>-0.1275644222485635</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1161,44 +1161,44 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>-648.591</v>
+        <v>4</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>-91.001</v>
+        <v>-2</v>
       </c>
       <c r="AE5" t="n">
-        <v>-739.592</v>
+        <v>2</v>
       </c>
       <c r="AF5" t="n">
-        <v>-15758.515</v>
+        <v>-1</v>
       </c>
       <c r="AG5" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-43.71700000000001</v>
+        <v>-5.267</v>
       </c>
       <c r="AI5" t="n">
-        <v>-15804.232</v>
+        <v>-6.267000000000001</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-33714.833</v>
+        <v>-25.699</v>
       </c>
       <c r="AK5" t="n">
-        <v>-22</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-543.2929999999999</v>
+        <v>-12.985</v>
       </c>
       <c r="AM5" t="n">
-        <v>-34280.126</v>
+        <v>-38.684</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
@@ -1209,67 +1209,67 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>永捷</t>
+          <t>大宇</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>13.64999961853027</v>
+        <v>11.60000038146973</v>
       </c>
       <c r="G6" t="n">
-        <v>14.12750005722046</v>
+        <v>12.03500003814697</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>40.73995696987673</v>
+        <v>40.43974837276122</v>
       </c>
       <c r="J6" t="n">
-        <v>30.36201725484161</v>
+        <v>36.53819575711773</v>
       </c>
       <c r="K6" t="n">
-        <v>43.38091503751957</v>
+        <v>39.26985468417678</v>
       </c>
       <c r="L6" t="n">
-        <v>2193922</v>
+        <v>148305.6</v>
       </c>
       <c r="M6" t="n">
-        <v>1277304.6</v>
+        <v>94206.89999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>1617101.375</v>
+        <v>87902.075</v>
       </c>
       <c r="O6" t="n">
-        <v>1.717618491313661</v>
+        <v>1.574254115144432</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.382614578701455</v>
+        <v>-0.3032445095854701</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.3855484701346324</v>
+        <v>-0.3039899788083282</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002933891433177405</v>
+        <v>0.0007454692228580639</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.01342220986151338</v>
+        <v>-0.002711321557039903</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.09895827119237943</v>
+        <v>-0.02393894277098824</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1316,35 +1316,35 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>2.899999999999999</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>4.899999999999999</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6167</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>久正</t>
+          <t>安力-KY</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1373,49 +1373,49 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>11.89999961853027</v>
+        <v>24.70000076293945</v>
       </c>
       <c r="G7" t="n">
-        <v>11.92749996185303</v>
+        <v>24.78499994277954</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>49.89608294742852</v>
+        <v>47.30914805061202</v>
       </c>
       <c r="J7" t="n">
-        <v>44.342445619861</v>
+        <v>45.24763001606233</v>
       </c>
       <c r="K7" t="n">
-        <v>45.50089618493725</v>
+        <v>45.09046186440769</v>
       </c>
       <c r="L7" t="n">
-        <v>1171292.8</v>
+        <v>108623</v>
       </c>
       <c r="M7" t="n">
-        <v>683918.95</v>
+        <v>49405.75</v>
       </c>
       <c r="N7" t="n">
-        <v>822660.975</v>
+        <v>42056.3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.712619309641881</v>
+        <v>2.198590245062569</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2735697922370459</v>
+        <v>-0.2177532192563518</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.3859679688494501</v>
+        <v>-0.4105495725599737</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1123981766124042</v>
+        <v>0.1927963533036218</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1233794293946632</v>
+        <v>0.2466742516142142</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1060578384622027</v>
+        <v>0.2372212919869191</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
@@ -1505,138 +1505,1306 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>8424</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>惠普</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>18.85000038146973</v>
+      </c>
+      <c r="G8" t="n">
+        <v>18.62750015258789</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>36.78294347926983</v>
+      </c>
+      <c r="J8" t="n">
+        <v>34.99228000058267</v>
+      </c>
+      <c r="K8" t="n">
+        <v>49.29289051489646</v>
+      </c>
+      <c r="L8" t="n">
+        <v>140694015.2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>65164176.45</v>
+      </c>
+      <c r="N8" t="n">
+        <v>54147265.4</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.159069950158174</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0.05491689396658828</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.1836129432981529</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.1286960493315646</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.1519513026657133</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.1540295217986903</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>-14546.608</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-41</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-729.047</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-15316.655</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-35212.105</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-93</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>3148.24</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-32156.865</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>-185413.215</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>667.614</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>2711.99</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-182033.611</v>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>70</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2474</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>可成</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>190.5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>197.35</v>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>40.69145846776003</v>
+      </c>
+      <c r="J9" t="n">
+        <v>32.19805899036803</v>
+      </c>
+      <c r="K9" t="n">
+        <v>45.19120346950121</v>
+      </c>
+      <c r="L9" t="n">
+        <v>14667469</v>
+      </c>
+      <c r="M9" t="n">
+        <v>6999621.3</v>
+      </c>
+      <c r="N9" t="n">
+        <v>6169971.075</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.095466079000588</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-3.026759413788255</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-3.062801350502224</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.03604193671396905</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.1617724618028551</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-1.439206634197134</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>-6968.368</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-2683.604</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-581.058</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-10233.03</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-7242.424</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-9002.038</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-470.9049999999999</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-16715.367</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>-14613.216</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-16146.388</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>-3486.014000000001</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-34245.618</v>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>70</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2516</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>12.64999961853027</v>
+      </c>
+      <c r="G10" t="n">
+        <v>12.94250001907349</v>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>44.55533206766395</v>
+      </c>
+      <c r="J10" t="n">
+        <v>33.544356206375</v>
+      </c>
+      <c r="K10" t="n">
+        <v>45.02520189988496</v>
+      </c>
+      <c r="L10" t="n">
+        <v>700694.4</v>
+      </c>
+      <c r="M10" t="n">
+        <v>382178.75</v>
+      </c>
+      <c r="N10" t="n">
+        <v>349034.2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.833420617969995</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.2033754851843597</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.253449333593969</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.05007384840960938</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.05839261049442485</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0.02607765625531294</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>-50</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-51.2</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-126</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>5.827999999999999</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-120.172</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>-36.001</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-28.172</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-64.17300000000003</v>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>70</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>燁興</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>7.409999847412109</v>
+      </c>
+      <c r="G11" t="n">
+        <v>7.252499961853028</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>45.58848471904841</v>
+      </c>
+      <c r="J11" t="n">
+        <v>39.35319691098555</v>
+      </c>
+      <c r="K11" t="n">
+        <v>49.2987337532826</v>
+      </c>
+      <c r="L11" t="n">
+        <v>885827.4</v>
+      </c>
+      <c r="M11" t="n">
+        <v>488975.8</v>
+      </c>
+      <c r="N11" t="n">
+        <v>418655.325</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.811597629166924</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0.09676719470703254</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-0.1733558700343924</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.07658867532735983</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.0769072826187216</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.07072883799939556</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-129</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-141</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>-71</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-6.999999999999998</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-78</v>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>70</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>5438</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>東友</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>73</v>
-      </c>
-      <c r="G8" t="n">
-        <v>73.57499923706055</v>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>36.13691463470187</v>
-      </c>
-      <c r="J8" t="n">
-        <v>30.76064634319857</v>
-      </c>
-      <c r="K8" t="n">
-        <v>33.40907078700683</v>
-      </c>
-      <c r="L8" t="n">
-        <v>34979.4</v>
-      </c>
-      <c r="M8" t="n">
-        <v>22711.4</v>
-      </c>
-      <c r="N8" t="n">
-        <v>16180.75</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.540169254207138</v>
-      </c>
-      <c r="P8" t="n">
-        <v>-0.4125750067465361</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>-0.3673783771893652</v>
-      </c>
-      <c r="R8" t="n">
-        <v>-0.04519662955717096</v>
-      </c>
-      <c r="S8" t="n">
-        <v>-0.07018999777962898</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-0.05828858234275314</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
+      <c r="F12" t="n">
+        <v>19.04999923706055</v>
+      </c>
+      <c r="G12" t="n">
+        <v>19.06999988555908</v>
+      </c>
+      <c r="H12" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>42.87948431351634</v>
+      </c>
+      <c r="J12" t="n">
+        <v>41.00472757780967</v>
+      </c>
+      <c r="K12" t="n">
+        <v>48.41222133080314</v>
+      </c>
+      <c r="L12" t="n">
+        <v>251328.6</v>
+      </c>
+      <c r="M12" t="n">
+        <v>140550.1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>119507.975</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.788178023352527</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0.08665289491082717</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-0.160365233260123</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.0737123383492958</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.08259122723798396</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.0669955455828061</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>70</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4714</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>永捷</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>13.44999980926514</v>
+      </c>
+      <c r="G13" t="n">
+        <v>14.04750003814697</v>
+      </c>
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>37.15996177650799</v>
+      </c>
+      <c r="J13" t="n">
+        <v>32.62799876206373</v>
+      </c>
+      <c r="K13" t="n">
+        <v>41.53314412589596</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2211934.6</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1297966.4</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1623257.75</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.704153975018152</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.3808194318426157</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0.3846026624762291</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.00378323063361341</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.002933891433177405</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-0.01342220986151338</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>70</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1731</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>美吾華</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>21.29999923706055</v>
+      </c>
+      <c r="G14" t="n">
+        <v>21.57999992370605</v>
+      </c>
+      <c r="H14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>30.05090527373818</v>
+      </c>
+      <c r="J14" t="n">
+        <v>30.00344493596688</v>
+      </c>
+      <c r="K14" t="n">
+        <v>31.98296355459915</v>
+      </c>
+      <c r="L14" t="n">
+        <v>210144.8</v>
+      </c>
+      <c r="M14" t="n">
+        <v>132109.8</v>
+      </c>
+      <c r="N14" t="n">
+        <v>120016.75</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.590682901646963</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.0887959463315724</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-0.06864013029407937</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-0.02015581603749303</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-0.01132840480300609</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0.005553953844507402</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-73</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-73</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>-238.89</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-235.89</v>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>70</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1903</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>士紙</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>49</v>
+      </c>
+      <c r="G15" t="n">
+        <v>48.78250026702881</v>
+      </c>
+      <c r="H15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>36.323963160391</v>
+      </c>
+      <c r="J15" t="n">
+        <v>35.38292307235453</v>
+      </c>
+      <c r="K15" t="n">
+        <v>49.92903591550309</v>
+      </c>
+      <c r="L15" t="n">
+        <v>392674</v>
+      </c>
+      <c r="M15" t="n">
+        <v>254128.65</v>
+      </c>
+      <c r="N15" t="n">
+        <v>237829</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.545178003345943</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0.1263184289876875</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-0.3025799553551881</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.1762615263675006</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.1963189855553158</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.1914879124595737</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>108</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>104</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-292</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>22.124</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-269.876</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>-434.421</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>-437.541</v>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>70</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3703</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>欣陸</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>20.04999923706055</v>
+      </c>
+      <c r="G16" t="n">
+        <v>20.35249986648559</v>
+      </c>
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>42.88307374506081</v>
+      </c>
+      <c r="J16" t="n">
+        <v>39.22230850150029</v>
+      </c>
+      <c r="K16" t="n">
+        <v>35.23972324993221</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2113965.2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1393661.15</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1259498.5</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.51684302888116</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0.33985353755088</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-0.3825435024040799</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.04268996485319987</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.04574548751355473</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.04742292855149544</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>49</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-3.678</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>45.322</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-1174</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>-692.796</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-1866.796</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>-3658</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>-811.3470000000001</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>-4471.347</v>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN16"/>
+  <dimension ref="A1:AN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,12 +629,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>海光</t>
+          <t>臺鹽</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,49 +643,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>13.64999961853027</v>
+        <v>31.54999923706055</v>
       </c>
       <c r="G2" t="n">
-        <v>13.73999991416931</v>
+        <v>31.52249975204468</v>
       </c>
       <c r="H2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>37.06432432240711</v>
+        <v>46.55742973697013</v>
       </c>
       <c r="J2" t="n">
-        <v>34.46690716341503</v>
+        <v>46.30698264779441</v>
       </c>
       <c r="K2" t="n">
-        <v>44.22805854971687</v>
+        <v>48.14240678331988</v>
       </c>
       <c r="L2" t="n">
-        <v>1635973.8</v>
+        <v>195453.6</v>
       </c>
       <c r="M2" t="n">
-        <v>690601.35</v>
+        <v>126654.35</v>
       </c>
       <c r="N2" t="n">
-        <v>558182.2</v>
+        <v>115137</v>
       </c>
       <c r="O2" t="n">
-        <v>2.368911963464885</v>
+        <v>1.543204793202918</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2371049355818755</v>
+        <v>-0.06022337836810721</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.3191248347045024</v>
+        <v>-0.07263727988112546</v>
       </c>
       <c r="R2" t="n">
-        <v>0.08201989912262686</v>
+        <v>0.01241390151301826</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0923727807371495</v>
+        <v>0.008390719317643971</v>
       </c>
       <c r="T2" t="n">
-        <v>0.09592282222153192</v>
+        <v>0.01255349227729624</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>-85.98</v>
+        <v>38</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -732,35 +732,35 @@
         <v>4</v>
       </c>
       <c r="AE2" t="n">
-        <v>-81.98</v>
+        <v>42</v>
       </c>
       <c r="AF2" t="n">
-        <v>337.642</v>
+        <v>99</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="AI2" t="n">
-        <v>360.642</v>
+        <v>103</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-31.95699999999998</v>
+        <v>-22.896</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>21.068</v>
+        <v>-10</v>
       </c>
       <c r="AM2" t="n">
-        <v>-10.889</v>
+        <v>-32.89599999999999</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
     </row>
@@ -771,16 +771,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2038</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>中鴻</t>
+          <t>海光</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,49 +789,49 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>17.85000038146973</v>
+        <v>13.80000019073486</v>
       </c>
       <c r="G3" t="n">
-        <v>17.70750007629395</v>
+        <v>13.72499990463257</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>40.43792868685871</v>
+        <v>36.83076561028683</v>
       </c>
       <c r="J3" t="n">
-        <v>38.12183962843405</v>
+        <v>35.25485997903896</v>
       </c>
       <c r="K3" t="n">
-        <v>49.65195757131</v>
+        <v>46.70432323756066</v>
       </c>
       <c r="L3" t="n">
-        <v>16225369.6</v>
+        <v>1642297</v>
       </c>
       <c r="M3" t="n">
-        <v>7543853.35</v>
+        <v>708044</v>
       </c>
       <c r="N3" t="n">
-        <v>6658272.975</v>
+        <v>553697.825</v>
       </c>
       <c r="O3" t="n">
-        <v>2.150806603365374</v>
+        <v>2.319484382326522</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.02864485870100708</v>
+        <v>-0.2144831082749139</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1059979756138136</v>
+        <v>-0.2981964894185847</v>
       </c>
       <c r="R3" t="n">
-        <v>0.07735311691280651</v>
+        <v>0.08371338114367077</v>
       </c>
       <c r="S3" t="n">
-        <v>0.08637407264506108</v>
+        <v>0.08201989912262686</v>
       </c>
       <c r="T3" t="n">
-        <v>0.08009296848946459</v>
+        <v>0.0923727807371495</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -869,44 +869,44 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>251</v>
+        <v>-86.739</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="AE3" t="n">
-        <v>252</v>
+        <v>-89.739</v>
       </c>
       <c r="AF3" t="n">
-        <v>7669.2</v>
+        <v>-183.1100000000001</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-187.808</v>
+        <v>15</v>
       </c>
       <c r="AI3" t="n">
-        <v>7481.391999999999</v>
+        <v>-168.1100000000001</v>
       </c>
       <c r="AJ3" t="n">
-        <v>19744.345</v>
+        <v>-652.6959999999999</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-2185.709</v>
+        <v>21.068</v>
       </c>
       <c r="AM3" t="n">
-        <v>17558.636</v>
+        <v>-631.628</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
     </row>
@@ -917,67 +917,67 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>5202</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>正道</t>
+          <t>力新</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>10.44999980926514</v>
+        <v>12.19999980926514</v>
       </c>
       <c r="G4" t="n">
-        <v>10.39500002861023</v>
+        <v>12.36750001907349</v>
       </c>
       <c r="H4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>32.8102714025607</v>
+        <v>47.63351387339981</v>
       </c>
       <c r="J4" t="n">
-        <v>30.19899491454913</v>
+        <v>30.94892728155128</v>
       </c>
       <c r="K4" t="n">
-        <v>48.48807011997991</v>
+        <v>45.12592321186386</v>
       </c>
       <c r="L4" t="n">
-        <v>525304.8</v>
+        <v>529932</v>
       </c>
       <c r="M4" t="n">
-        <v>283812.8</v>
+        <v>277845.55</v>
       </c>
       <c r="N4" t="n">
-        <v>245164.95</v>
+        <v>279366.875</v>
       </c>
       <c r="O4" t="n">
-        <v>1.850884808578049</v>
+        <v>1.907289859420099</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1708213808171095</v>
+        <v>-0.371845799091103</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2026428411904573</v>
+        <v>-0.3969991562283937</v>
       </c>
       <c r="R4" t="n">
-        <v>0.03182146037334779</v>
+        <v>0.02515335713729067</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01608101913293472</v>
+        <v>-0.009109374239265389</v>
       </c>
       <c r="T4" t="n">
-        <v>0.02832245465700114</v>
+        <v>-0.08260067533711835</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1024,35 +1024,35 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-5.138</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>81.86199999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>5.862000000000002</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>168.862</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
     </row>
@@ -1063,16 +1063,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>2516</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>東華</t>
+          <t>新建</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1081,53 +1081,53 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>18</v>
+        <v>12.75</v>
       </c>
       <c r="G5" t="n">
-        <v>18.42249994277954</v>
+        <v>12.89750003814697</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>44.71616308800814</v>
+        <v>43.4716667477668</v>
       </c>
       <c r="J5" t="n">
-        <v>30.15604034701413</v>
+        <v>36.85345972017227</v>
       </c>
       <c r="K5" t="n">
-        <v>45.76355978601987</v>
+        <v>46.36529894092313</v>
       </c>
       <c r="L5" t="n">
-        <v>63560.8</v>
+        <v>720637.4</v>
       </c>
       <c r="M5" t="n">
-        <v>36620.45</v>
+        <v>381444.8</v>
       </c>
       <c r="N5" t="n">
-        <v>26902.15</v>
+        <v>348241.45</v>
       </c>
       <c r="O5" t="n">
-        <v>1.735664089327138</v>
+        <v>1.889231154809294</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2158364213503425</v>
+        <v>-0.1897902141680454</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1969396490612297</v>
+        <v>-0.2407175097087843</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.0188967722891128</v>
+        <v>0.05092729554073891</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.03147312073320929</v>
+        <v>0.05007384840960938</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1275644222485635</v>
+        <v>0.05839261049442485</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1161,44 +1161,44 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>4</v>
+        <v>-7</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="AF5" t="n">
-        <v>-1</v>
+        <v>-98</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-5.267</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>-6.267000000000001</v>
+        <v>-98</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-25.699</v>
+        <v>-75.001</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-12.985</v>
+        <v>-28</v>
       </c>
       <c r="AM5" t="n">
-        <v>-38.684</v>
+        <v>-103.001</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
     </row>
@@ -1209,67 +1209,67 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>大宇</t>
+          <t>永捷</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>11.60000038146973</v>
+        <v>13.39999961853027</v>
       </c>
       <c r="G6" t="n">
-        <v>12.03500003814697</v>
+        <v>13.97750000953674</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>40.43974837276122</v>
+        <v>33.93996180201444</v>
       </c>
       <c r="J6" t="n">
-        <v>36.53819575711773</v>
+        <v>33.06531977538064</v>
       </c>
       <c r="K6" t="n">
-        <v>39.26985468417678</v>
+        <v>41.06225466269198</v>
       </c>
       <c r="L6" t="n">
-        <v>148305.6</v>
+        <v>2179717.2</v>
       </c>
       <c r="M6" t="n">
-        <v>94206.89999999999</v>
+        <v>1298587.55</v>
       </c>
       <c r="N6" t="n">
-        <v>87902.075</v>
+        <v>1624874.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.574254115144432</v>
+        <v>1.678529260503075</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3032445095854701</v>
+        <v>-0.3790617743697506</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.3039899788083282</v>
+        <v>-0.3834944848549334</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0007454692228580639</v>
+        <v>0.004432710485182789</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.002711321557039903</v>
+        <v>0.00378323063361341</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.02393894277098824</v>
+        <v>0.002933891433177405</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1316,35 +1316,35 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.899999999999999</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>4.899999999999999</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
     </row>
@@ -1359,63 +1359,63 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>安力-KY</t>
+          <t>中宇</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>24.70000076293945</v>
+        <v>49.40000152587891</v>
       </c>
       <c r="G7" t="n">
-        <v>24.78499994277954</v>
+        <v>49.64750003814697</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>47.30914805061202</v>
+        <v>40.05745395498474</v>
       </c>
       <c r="J7" t="n">
-        <v>45.24763001606233</v>
+        <v>31.56209367605711</v>
       </c>
       <c r="K7" t="n">
-        <v>45.09046186440769</v>
+        <v>42.04556815989769</v>
       </c>
       <c r="L7" t="n">
-        <v>108623</v>
+        <v>127505.8</v>
       </c>
       <c r="M7" t="n">
-        <v>49405.75</v>
+        <v>80692.95</v>
       </c>
       <c r="N7" t="n">
-        <v>42056.3</v>
+        <v>72476.72500000001</v>
       </c>
       <c r="O7" t="n">
-        <v>2.198590245062569</v>
+        <v>1.580135563267919</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2177532192563518</v>
+        <v>-0.5423286627876536</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.4105495725599737</v>
+        <v>-0.5888529162651661</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1927963533036218</v>
+        <v>0.04652425347751254</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2466742516142142</v>
+        <v>0.01391841173387343</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2372212919869191</v>
+        <v>0.01019492849113013</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1462,35 +1462,35 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>4.007000000000005</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>-4.318</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0.311000000000007</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>-149.093</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>-7.583</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>-156.676</v>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
     </row>
@@ -1505,63 +1505,63 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>9951</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>皇田</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>18.85000038146973</v>
+        <v>52.79999923706055</v>
       </c>
       <c r="G8" t="n">
-        <v>18.62750015258789</v>
+        <v>53.25499973297119</v>
       </c>
       <c r="H8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>36.78294347926983</v>
+        <v>41.18079766687108</v>
       </c>
       <c r="J8" t="n">
-        <v>34.99228000058267</v>
+        <v>30.81030347660208</v>
       </c>
       <c r="K8" t="n">
-        <v>49.29289051489646</v>
+        <v>44.84532134742219</v>
       </c>
       <c r="L8" t="n">
-        <v>140694015.2</v>
+        <v>219096.8</v>
       </c>
       <c r="M8" t="n">
-        <v>65164176.45</v>
+        <v>141389.05</v>
       </c>
       <c r="N8" t="n">
-        <v>54147265.4</v>
+        <v>103783.875</v>
       </c>
       <c r="O8" t="n">
-        <v>2.159069950158174</v>
+        <v>1.549602320688908</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.05491689396658828</v>
+        <v>-0.432168399957952</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1836129432981529</v>
+        <v>-0.3716556817552978</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1286960493315646</v>
+        <v>-0.06051271820265414</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1519513026657133</v>
+        <v>-0.1072262225717261</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1540295217986903</v>
+        <v>-0.1472379154868523</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1599,44 +1599,44 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>-14546.608</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>-41</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>-729.047</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-15316.655</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>-35212.105</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>-93</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>3148.24</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>-32156.865</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-185413.215</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>667.614</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>2711.99</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>-182033.611</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
     </row>
@@ -1651,12 +1651,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>美吾華</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1665,49 +1665,49 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>190.5</v>
+        <v>21.35000038146973</v>
       </c>
       <c r="G9" t="n">
-        <v>197.35</v>
+        <v>21.56499996185303</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>40.69145846776003</v>
+        <v>31.1450479602699</v>
       </c>
       <c r="J9" t="n">
-        <v>32.19805899036803</v>
+        <v>30.38397927740122</v>
       </c>
       <c r="K9" t="n">
-        <v>45.19120346950121</v>
+        <v>35.74836256695912</v>
       </c>
       <c r="L9" t="n">
-        <v>14667469</v>
+        <v>207724.8</v>
       </c>
       <c r="M9" t="n">
-        <v>6999621.3</v>
+        <v>135994.1</v>
       </c>
       <c r="N9" t="n">
-        <v>6169971.075</v>
+        <v>121690.325</v>
       </c>
       <c r="O9" t="n">
-        <v>2.095466079000588</v>
+        <v>1.527454499864332</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.026759413788255</v>
+        <v>-0.09465929280814933</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.062801350502224</v>
+        <v>-0.07384396279689336</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03604193671396905</v>
+        <v>-0.02081533001125598</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1617724618028551</v>
+        <v>-0.02015581603749303</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.439206634197134</v>
+        <v>-0.01132840480300609</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1745,44 +1745,44 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>-6968.368</v>
+        <v>-9</v>
       </c>
       <c r="AC9" t="n">
-        <v>-2683.604</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>-581.058</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
-        <v>-10233.03</v>
+        <v>-8</v>
       </c>
       <c r="AF9" t="n">
-        <v>-7242.424</v>
+        <v>-79</v>
       </c>
       <c r="AG9" t="n">
-        <v>-9002.038</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-470.9049999999999</v>
+        <v>2</v>
       </c>
       <c r="AI9" t="n">
-        <v>-16715.367</v>
+        <v>-77</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-14613.216</v>
+        <v>-231.89</v>
       </c>
       <c r="AK9" t="n">
-        <v>-16146.388</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>-3486.014000000001</v>
+        <v>-2</v>
       </c>
       <c r="AM9" t="n">
-        <v>-34245.618</v>
+        <v>-233.89</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
     </row>
@@ -1797,12 +1797,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2516</t>
+          <t>3703</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>新建</t>
+          <t>欣陸</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1811,49 +1811,49 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>12.64999961853027</v>
+        <v>20.20000076293945</v>
       </c>
       <c r="G10" t="n">
-        <v>12.94250001907349</v>
+        <v>20.32499990463257</v>
       </c>
       <c r="H10" t="b">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>44.55533206766395</v>
+        <v>47.63638677824609</v>
       </c>
       <c r="J10" t="n">
-        <v>33.544356206375</v>
+        <v>42.02700126041556</v>
       </c>
       <c r="K10" t="n">
-        <v>45.02520189988496</v>
+        <v>39.78166996987412</v>
       </c>
       <c r="L10" t="n">
-        <v>700694.4</v>
+        <v>2159966.8</v>
       </c>
       <c r="M10" t="n">
-        <v>382178.75</v>
+        <v>1423271</v>
       </c>
       <c r="N10" t="n">
-        <v>349034.2</v>
+        <v>1256239.625</v>
       </c>
       <c r="O10" t="n">
-        <v>1.833420617969995</v>
+        <v>1.51760753925289</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2033754851843597</v>
+        <v>-0.3180469186709018</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.253449333593969</v>
+        <v>-0.3696441856574443</v>
       </c>
       <c r="R10" t="n">
-        <v>0.05007384840960938</v>
+        <v>0.05159726698654243</v>
       </c>
       <c r="S10" t="n">
-        <v>0.05839261049442485</v>
+        <v>0.04268996485319987</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.02607765625531294</v>
+        <v>0.04574548751355473</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -1891,920 +1891,44 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>-50</v>
+        <v>-222</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD10" t="n">
-        <v>-1.2</v>
+        <v>18</v>
       </c>
       <c r="AE10" t="n">
-        <v>-51.2</v>
+        <v>-205</v>
       </c>
       <c r="AF10" t="n">
-        <v>-126</v>
+        <v>-577</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AH10" t="n">
-        <v>5.827999999999999</v>
+        <v>-2558.04</v>
       </c>
       <c r="AI10" t="n">
-        <v>-120.172</v>
+        <v>-3136.04</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-36.001</v>
+        <v>-5035</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AL10" t="n">
-        <v>-28.172</v>
+        <v>-2828.436</v>
       </c>
       <c r="AM10" t="n">
-        <v>-64.17300000000003</v>
+        <v>-7866.436</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>70</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>燁興</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>7.409999847412109</v>
-      </c>
-      <c r="G11" t="n">
-        <v>7.252499961853028</v>
-      </c>
-      <c r="H11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>45.58848471904841</v>
-      </c>
-      <c r="J11" t="n">
-        <v>39.35319691098555</v>
-      </c>
-      <c r="K11" t="n">
-        <v>49.2987337532826</v>
-      </c>
-      <c r="L11" t="n">
-        <v>885827.4</v>
-      </c>
-      <c r="M11" t="n">
-        <v>488975.8</v>
-      </c>
-      <c r="N11" t="n">
-        <v>418655.325</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.811597629166924</v>
-      </c>
-      <c r="P11" t="n">
-        <v>-0.09676719470703254</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>-0.1733558700343924</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.07658867532735983</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.0769072826187216</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.07072883799939556</v>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>-129</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>-12</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>-141</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>-71</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>-6.999999999999998</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>-78</v>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>70</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>5438</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>東友</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>19.04999923706055</v>
-      </c>
-      <c r="G12" t="n">
-        <v>19.06999988555908</v>
-      </c>
-      <c r="H12" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>42.87948431351634</v>
-      </c>
-      <c r="J12" t="n">
-        <v>41.00472757780967</v>
-      </c>
-      <c r="K12" t="n">
-        <v>48.41222133080314</v>
-      </c>
-      <c r="L12" t="n">
-        <v>251328.6</v>
-      </c>
-      <c r="M12" t="n">
-        <v>140550.1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>119507.975</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.788178023352527</v>
-      </c>
-      <c r="P12" t="n">
-        <v>-0.08665289491082717</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>-0.160365233260123</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.0737123383492958</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.08259122723798396</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0.0669955455828061</v>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>70</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>4714</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>永捷</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>13.44999980926514</v>
-      </c>
-      <c r="G13" t="n">
-        <v>14.04750003814697</v>
-      </c>
-      <c r="H13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>37.15996177650799</v>
-      </c>
-      <c r="J13" t="n">
-        <v>32.62799876206373</v>
-      </c>
-      <c r="K13" t="n">
-        <v>41.53314412589596</v>
-      </c>
-      <c r="L13" t="n">
-        <v>2211934.6</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1297966.4</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1623257.75</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.704153975018152</v>
-      </c>
-      <c r="P13" t="n">
-        <v>-0.3808194318426157</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>-0.3846026624762291</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.00378323063361341</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.002933891433177405</v>
-      </c>
-      <c r="T13" t="n">
-        <v>-0.01342220986151338</v>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>70</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1731</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>美吾華</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>21.29999923706055</v>
-      </c>
-      <c r="G14" t="n">
-        <v>21.57999992370605</v>
-      </c>
-      <c r="H14" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>30.05090527373818</v>
-      </c>
-      <c r="J14" t="n">
-        <v>30.00344493596688</v>
-      </c>
-      <c r="K14" t="n">
-        <v>31.98296355459915</v>
-      </c>
-      <c r="L14" t="n">
-        <v>210144.8</v>
-      </c>
-      <c r="M14" t="n">
-        <v>132109.8</v>
-      </c>
-      <c r="N14" t="n">
-        <v>120016.75</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.590682901646963</v>
-      </c>
-      <c r="P14" t="n">
-        <v>-0.0887959463315724</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>-0.06864013029407937</v>
-      </c>
-      <c r="R14" t="n">
-        <v>-0.02015581603749303</v>
-      </c>
-      <c r="S14" t="n">
-        <v>-0.01132840480300609</v>
-      </c>
-      <c r="T14" t="n">
-        <v>-0.005553953844507402</v>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB14" t="n">
-        <v>-55</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>-55</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>-73</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>-73</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>-238.89</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>-235.89</v>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>70</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1903</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>士紙</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>49</v>
-      </c>
-      <c r="G15" t="n">
-        <v>48.78250026702881</v>
-      </c>
-      <c r="H15" t="b">
-        <v>1</v>
-      </c>
-      <c r="I15" t="n">
-        <v>36.323963160391</v>
-      </c>
-      <c r="J15" t="n">
-        <v>35.38292307235453</v>
-      </c>
-      <c r="K15" t="n">
-        <v>49.92903591550309</v>
-      </c>
-      <c r="L15" t="n">
-        <v>392674</v>
-      </c>
-      <c r="M15" t="n">
-        <v>254128.65</v>
-      </c>
-      <c r="N15" t="n">
-        <v>237829</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.545178003345943</v>
-      </c>
-      <c r="P15" t="n">
-        <v>-0.1263184289876875</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>-0.3025799553551881</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.1762615263675006</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.1963189855553158</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.1914879124595737</v>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB15" t="n">
-        <v>108</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>104</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>-292</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>22.124</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>-269.876</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>-434.421</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>-3.12</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>-437.541</v>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>70</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>3703</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>欣陸</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>20.04999923706055</v>
-      </c>
-      <c r="G16" t="n">
-        <v>20.35249986648559</v>
-      </c>
-      <c r="H16" t="b">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>42.88307374506081</v>
-      </c>
-      <c r="J16" t="n">
-        <v>39.22230850150029</v>
-      </c>
-      <c r="K16" t="n">
-        <v>35.23972324993221</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2113965.2</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1393661.15</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1259498.5</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.51684302888116</v>
-      </c>
-      <c r="P16" t="n">
-        <v>-0.33985353755088</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>-0.3825435024040799</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.04268996485319987</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.04574548751355473</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.04742292855149544</v>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB16" t="n">
-        <v>49</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>-3.678</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>45.322</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>-1174</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>-692.796</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>-1866.796</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>-3658</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>-811.3470000000001</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>-4471.347</v>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -629,12 +629,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>臺鹽</t>
+          <t>中宇</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,49 +643,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>31.54999923706055</v>
+        <v>49.40000152587891</v>
       </c>
       <c r="G2" t="n">
-        <v>31.52249975204468</v>
+        <v>49.64750003814697</v>
       </c>
       <c r="H2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>46.55742973697013</v>
+        <v>40.05745395498474</v>
       </c>
       <c r="J2" t="n">
-        <v>46.30698264779441</v>
+        <v>31.56209367605711</v>
       </c>
       <c r="K2" t="n">
-        <v>48.14240678331988</v>
+        <v>42.04556815989769</v>
       </c>
       <c r="L2" t="n">
-        <v>195453.6</v>
+        <v>127400.2</v>
       </c>
       <c r="M2" t="n">
-        <v>126654.35</v>
+        <v>80666.55</v>
       </c>
       <c r="N2" t="n">
-        <v>115137</v>
+        <v>72463.52499999999</v>
       </c>
       <c r="O2" t="n">
-        <v>1.543204793202918</v>
+        <v>1.579343606488687</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.06022337836810721</v>
+        <v>-0.5423286627876536</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.07263727988112546</v>
+        <v>-0.5888529162651661</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01241390151301826</v>
+        <v>0.04652425347751254</v>
       </c>
       <c r="S2" t="n">
-        <v>0.008390719317643971</v>
+        <v>0.01391841173387343</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01255349227729624</v>
+        <v>0.01019492849113013</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -723,40 +723,40 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>38</v>
+        <v>48.7</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="AE2" t="n">
-        <v>42</v>
+        <v>47.7</v>
       </c>
       <c r="AF2" t="n">
-        <v>99</v>
+        <v>153.707</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>4</v>
+        <v>-3.318</v>
       </c>
       <c r="AI2" t="n">
-        <v>103</v>
+        <v>150.389</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-22.896</v>
+        <v>-94.39299999999999</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-10</v>
+        <v>-8.583</v>
       </c>
       <c r="AM2" t="n">
-        <v>-32.89599999999999</v>
+        <v>-102.976</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
@@ -771,16 +771,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>海光</t>
+          <t>臺鹽</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,49 +789,49 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>13.80000019073486</v>
+        <v>31.54999923706055</v>
       </c>
       <c r="G3" t="n">
-        <v>13.72499990463257</v>
+        <v>31.52249975204468</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>36.83076561028683</v>
+        <v>46.55742973697013</v>
       </c>
       <c r="J3" t="n">
-        <v>35.25485997903896</v>
+        <v>46.30698264779441</v>
       </c>
       <c r="K3" t="n">
-        <v>46.70432323756066</v>
+        <v>48.14240678331988</v>
       </c>
       <c r="L3" t="n">
-        <v>1642297</v>
+        <v>194994.4</v>
       </c>
       <c r="M3" t="n">
-        <v>708044</v>
+        <v>126539.55</v>
       </c>
       <c r="N3" t="n">
-        <v>553697.825</v>
+        <v>115079.6</v>
       </c>
       <c r="O3" t="n">
-        <v>2.319484382326522</v>
+        <v>1.540975924128069</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2144831082749139</v>
+        <v>-0.06022337836810721</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2981964894185847</v>
+        <v>-0.07263727988112546</v>
       </c>
       <c r="R3" t="n">
-        <v>0.08371338114367077</v>
+        <v>0.01241390151301826</v>
       </c>
       <c r="S3" t="n">
-        <v>0.08201989912262686</v>
+        <v>0.008390719317643971</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0923727807371495</v>
+        <v>0.01255349227729624</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -869,40 +869,40 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>-86.739</v>
+        <v>65</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-89.739</v>
+        <v>65</v>
       </c>
       <c r="AF3" t="n">
-        <v>-183.1100000000001</v>
+        <v>145</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>15</v>
+        <v>-1</v>
       </c>
       <c r="AI3" t="n">
-        <v>-168.1100000000001</v>
+        <v>144</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-652.6959999999999</v>
+        <v>48.105</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>21.068</v>
+        <v>-12</v>
       </c>
       <c r="AM3" t="n">
-        <v>-631.628</v>
+        <v>36.105</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
@@ -921,63 +921,63 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5202</t>
+          <t>2038</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>力新</t>
+          <t>海光</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>12.19999980926514</v>
+        <v>13.80000019073486</v>
       </c>
       <c r="G4" t="n">
-        <v>12.36750001907349</v>
+        <v>13.72499990463257</v>
       </c>
       <c r="H4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>47.63351387339981</v>
+        <v>36.83076561028683</v>
       </c>
       <c r="J4" t="n">
-        <v>30.94892728155128</v>
+        <v>35.25485997903896</v>
       </c>
       <c r="K4" t="n">
-        <v>45.12592321186386</v>
+        <v>46.70432323756066</v>
       </c>
       <c r="L4" t="n">
-        <v>529932</v>
+        <v>1640773.2</v>
       </c>
       <c r="M4" t="n">
-        <v>277845.55</v>
+        <v>707663.05</v>
       </c>
       <c r="N4" t="n">
-        <v>279366.875</v>
+        <v>553507.35</v>
       </c>
       <c r="O4" t="n">
-        <v>1.907289859420099</v>
+        <v>2.318579725195486</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.371845799091103</v>
+        <v>-0.2144831082749139</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.3969991562283937</v>
+        <v>-0.2981964894185847</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02515335713729067</v>
+        <v>0.08371338114367077</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.009109374239265389</v>
+        <v>0.08201989912262686</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.08260067533711835</v>
+        <v>0.0923727807371495</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1015,40 +1015,40 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>240.696</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>252.696</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>-106.5050000000001</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>6.945</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-99.56000000000006</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>-329</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>29.068</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>-299.932</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
@@ -1067,63 +1067,63 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2516</t>
+          <t>5202</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>新建</t>
+          <t>力新</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>12.75</v>
+        <v>12.19999980926514</v>
       </c>
       <c r="G5" t="n">
-        <v>12.89750003814697</v>
+        <v>12.36750001907349</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>43.4716667477668</v>
+        <v>47.63351387339981</v>
       </c>
       <c r="J5" t="n">
-        <v>36.85345972017227</v>
+        <v>30.94892728155128</v>
       </c>
       <c r="K5" t="n">
-        <v>46.36529894092313</v>
+        <v>45.12592321186386</v>
       </c>
       <c r="L5" t="n">
-        <v>720637.4</v>
+        <v>529263.2</v>
       </c>
       <c r="M5" t="n">
-        <v>381444.8</v>
+        <v>277678.35</v>
       </c>
       <c r="N5" t="n">
-        <v>348241.45</v>
+        <v>279283.275</v>
       </c>
       <c r="O5" t="n">
-        <v>1.889231154809294</v>
+        <v>1.906029764293831</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1897902141680454</v>
+        <v>-0.371845799091103</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2407175097087843</v>
+        <v>-0.3969991562283937</v>
       </c>
       <c r="R5" t="n">
-        <v>0.05092729554073891</v>
+        <v>0.02515335713729067</v>
       </c>
       <c r="S5" t="n">
-        <v>0.05007384840960938</v>
+        <v>-0.009109374239265389</v>
       </c>
       <c r="T5" t="n">
-        <v>0.05839261049442485</v>
+        <v>-0.08260067533711835</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1170,10 +1170,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-98</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1182,19 +1182,19 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>-98</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-75.001</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-28</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>-103.001</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
@@ -1213,63 +1213,63 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>2516</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>永捷</t>
+          <t>新建</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>13.39999961853027</v>
+        <v>12.75</v>
       </c>
       <c r="G6" t="n">
-        <v>13.97750000953674</v>
+        <v>12.89750003814697</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>33.93996180201444</v>
+        <v>43.4716667477668</v>
       </c>
       <c r="J6" t="n">
-        <v>33.06531977538064</v>
+        <v>36.85345972017227</v>
       </c>
       <c r="K6" t="n">
-        <v>41.06225466269198</v>
+        <v>46.36529894092313</v>
       </c>
       <c r="L6" t="n">
-        <v>2179717.2</v>
+        <v>720296</v>
       </c>
       <c r="M6" t="n">
-        <v>1298587.55</v>
+        <v>381359.45</v>
       </c>
       <c r="N6" t="n">
-        <v>1624874.1</v>
+        <v>348198.775</v>
       </c>
       <c r="O6" t="n">
-        <v>1.678529260503075</v>
+        <v>1.888758755027573</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3790617743697506</v>
+        <v>-0.1897902141680454</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.3834944848549334</v>
+        <v>-0.2407175097087843</v>
       </c>
       <c r="R6" t="n">
-        <v>0.004432710485182789</v>
+        <v>0.05092729554073891</v>
       </c>
       <c r="S6" t="n">
-        <v>0.00378323063361341</v>
+        <v>0.05007384840960938</v>
       </c>
       <c r="T6" t="n">
-        <v>0.002933891433177405</v>
+        <v>0.05839261049442485</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1316,31 +1316,31 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>-27</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-49.00000000000001</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>-114.001</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>-139.001</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
@@ -1359,63 +1359,63 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>中宇</t>
+          <t>永捷</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>49.40000152587891</v>
+        <v>13.39999961853027</v>
       </c>
       <c r="G7" t="n">
-        <v>49.64750003814697</v>
+        <v>13.97750000953674</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>40.05745395498474</v>
+        <v>33.93996180201444</v>
       </c>
       <c r="J7" t="n">
-        <v>31.56209367605711</v>
+        <v>33.06531977538064</v>
       </c>
       <c r="K7" t="n">
-        <v>42.04556815989769</v>
+        <v>41.06225466269198</v>
       </c>
       <c r="L7" t="n">
-        <v>127505.8</v>
+        <v>2179030.6</v>
       </c>
       <c r="M7" t="n">
-        <v>80692.95</v>
+        <v>1298415.9</v>
       </c>
       <c r="N7" t="n">
-        <v>72476.72500000001</v>
+        <v>1624788.275</v>
       </c>
       <c r="O7" t="n">
-        <v>1.580135563267919</v>
+        <v>1.67822236311185</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.5423286627876536</v>
+        <v>-0.3790617743697506</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.5888529162651661</v>
+        <v>-0.3834944848549334</v>
       </c>
       <c r="R7" t="n">
-        <v>0.04652425347751254</v>
+        <v>0.004432710485182789</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01391841173387343</v>
+        <v>0.00378323063361341</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01019492849113013</v>
+        <v>0.002933891433177405</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1462,31 +1462,31 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>4.007000000000005</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-4.318</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.311000000000007</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-149.093</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>-7.583</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>-156.676</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
@@ -1537,16 +1537,16 @@
         <v>44.84532134742219</v>
       </c>
       <c r="L8" t="n">
-        <v>219096.8</v>
+        <v>218803.8</v>
       </c>
       <c r="M8" t="n">
-        <v>141389.05</v>
+        <v>141315.8</v>
       </c>
       <c r="N8" t="n">
-        <v>103783.875</v>
+        <v>103747.25</v>
       </c>
       <c r="O8" t="n">
-        <v>1.549602320688908</v>
+        <v>1.548332175170788</v>
       </c>
       <c r="P8" t="n">
         <v>-0.432168399957952</v>
@@ -1683,16 +1683,16 @@
         <v>35.74836256695912</v>
       </c>
       <c r="L9" t="n">
-        <v>207724.8</v>
+        <v>207423.6</v>
       </c>
       <c r="M9" t="n">
-        <v>135994.1</v>
+        <v>135918.8</v>
       </c>
       <c r="N9" t="n">
-        <v>121690.325</v>
+        <v>121652.675</v>
       </c>
       <c r="O9" t="n">
-        <v>1.527454499864332</v>
+        <v>1.526084691742423</v>
       </c>
       <c r="P9" t="n">
         <v>-0.09465929280814933</v>
@@ -1745,31 +1745,31 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>-9</v>
+        <v>-27</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-8</v>
+        <v>-27</v>
       </c>
       <c r="AF9" t="n">
-        <v>-79</v>
+        <v>-104</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="AI9" t="n">
-        <v>-77</v>
+        <v>-111</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-231.89</v>
+        <v>-271.89</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1778,7 +1778,7 @@
         <v>-2</v>
       </c>
       <c r="AM9" t="n">
-        <v>-233.89</v>
+        <v>-273.89</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
@@ -1829,16 +1829,16 @@
         <v>39.78166996987412</v>
       </c>
       <c r="L10" t="n">
-        <v>2159966.8</v>
+        <v>2159268.2</v>
       </c>
       <c r="M10" t="n">
-        <v>1423271</v>
+        <v>1423096.35</v>
       </c>
       <c r="N10" t="n">
-        <v>1256239.625</v>
+        <v>1256152.3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.51760753925289</v>
+        <v>1.517302886765186</v>
       </c>
       <c r="P10" t="n">
         <v>-0.3180469186709018</v>
@@ -1891,40 +1891,40 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>-222</v>
+        <v>399</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
-        <v>-205</v>
+        <v>400</v>
       </c>
       <c r="AF10" t="n">
-        <v>-577</v>
+        <v>240</v>
       </c>
       <c r="AG10" t="n">
         <v>-1</v>
       </c>
       <c r="AH10" t="n">
-        <v>-2558.04</v>
+        <v>-1944.571</v>
       </c>
       <c r="AI10" t="n">
-        <v>-3136.04</v>
+        <v>-1705.571</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-5035</v>
+        <v>-3932</v>
       </c>
       <c r="AK10" t="n">
         <v>-3</v>
       </c>
       <c r="AL10" t="n">
-        <v>-2828.436</v>
+        <v>-2814.951</v>
       </c>
       <c r="AM10" t="n">
-        <v>-7866.436</v>
+        <v>-6749.951</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN10"/>
+  <dimension ref="A1:AN11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,16 +625,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>2539</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>中宇</t>
+          <t>櫻花建</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,49 +643,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>49.40000152587891</v>
+        <v>36</v>
       </c>
       <c r="G2" t="n">
-        <v>49.64750003814697</v>
+        <v>37.61749992370606</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>40.05745395498474</v>
+        <v>45.20323440042991</v>
       </c>
       <c r="J2" t="n">
-        <v>31.56209367605711</v>
+        <v>33.80373394691094</v>
       </c>
       <c r="K2" t="n">
-        <v>42.04556815989769</v>
+        <v>35.18149162459814</v>
       </c>
       <c r="L2" t="n">
-        <v>127400.2</v>
+        <v>3072168</v>
       </c>
       <c r="M2" t="n">
-        <v>80666.55</v>
+        <v>1979433.85</v>
       </c>
       <c r="N2" t="n">
-        <v>72463.52499999999</v>
+        <v>1541498.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.579343606488687</v>
+        <v>1.552043782619965</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.5423286627876536</v>
+        <v>-1.971332371910592</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.5888529162651661</v>
+        <v>-2.106413978055551</v>
       </c>
       <c r="R2" t="n">
-        <v>0.04652425347751254</v>
+        <v>0.1350816061449596</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01391841173387343</v>
+        <v>0.07806749118987355</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01019492849113013</v>
+        <v>-0.05956806909320544</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -719,48 +719,48 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>48.7</v>
+        <v>-340.964</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>9.002000000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>-1</v>
+        <v>-5.078</v>
       </c>
       <c r="AE2" t="n">
-        <v>47.7</v>
+        <v>-337.04</v>
       </c>
       <c r="AF2" t="n">
-        <v>153.707</v>
+        <v>189.019</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>18.888</v>
       </c>
       <c r="AH2" t="n">
-        <v>-3.318</v>
+        <v>-1.07800000000001</v>
       </c>
       <c r="AI2" t="n">
-        <v>150.389</v>
+        <v>206.829</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-94.39299999999999</v>
+        <v>-2161.332</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>-16.595</v>
       </c>
       <c r="AL2" t="n">
-        <v>-8.583</v>
+        <v>-6.040000000000012</v>
       </c>
       <c r="AM2" t="n">
-        <v>-102.976</v>
+        <v>-2183.967</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -775,12 +775,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>4994</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>臺鹽</t>
+          <t>傳奇</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,124 +789,124 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>31.54999923706055</v>
+        <v>87.30000305175781</v>
       </c>
       <c r="G3" t="n">
-        <v>31.52249975204468</v>
+        <v>92.7949993133545</v>
       </c>
       <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>36.96341438014584</v>
+      </c>
+      <c r="J3" t="n">
+        <v>33.79652345547542</v>
+      </c>
+      <c r="K3" t="n">
+        <v>35.11822940588451</v>
+      </c>
+      <c r="L3" t="n">
+        <v>132125.2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>48953.85</v>
+      </c>
+      <c r="N3" t="n">
+        <v>36671.975</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.698974646529333</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-2.104427947394626</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-1.841672887304255</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-0.2627550600903714</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-0.1265529096042373</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-0.1579220910237285</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.024</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.024</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>14.843</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
         <v>1</v>
       </c>
-      <c r="I3" t="n">
-        <v>46.55742973697013</v>
-      </c>
-      <c r="J3" t="n">
-        <v>46.30698264779441</v>
-      </c>
-      <c r="K3" t="n">
-        <v>48.14240678331988</v>
-      </c>
-      <c r="L3" t="n">
-        <v>194994.4</v>
-      </c>
-      <c r="M3" t="n">
-        <v>126539.55</v>
-      </c>
-      <c r="N3" t="n">
-        <v>115079.6</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.540975924128069</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-0.06022337836810721</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-0.07263727988112546</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.01241390151301826</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.008390719317643971</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.01255349227729624</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>65</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>145</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>-1</v>
-      </c>
       <c r="AI3" t="n">
-        <v>144</v>
+        <v>15.843</v>
       </c>
       <c r="AJ3" t="n">
-        <v>48.105</v>
+        <v>-26.92</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-12</v>
+        <v>-2</v>
       </c>
       <c r="AM3" t="n">
-        <v>36.105</v>
+        <v>-28.92</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -917,16 +917,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>2538</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>海光</t>
+          <t>基泰</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,49 +935,49 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>13.80000019073486</v>
+        <v>9.510000228881836</v>
       </c>
       <c r="G4" t="n">
-        <v>13.72499990463257</v>
+        <v>9.537000131607055</v>
       </c>
       <c r="H4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>36.83076561028683</v>
+        <v>45.31644239472193</v>
       </c>
       <c r="J4" t="n">
-        <v>35.25485997903896</v>
+        <v>36.46394732093216</v>
       </c>
       <c r="K4" t="n">
-        <v>46.70432323756066</v>
+        <v>45.5125132745632</v>
       </c>
       <c r="L4" t="n">
-        <v>1640773.2</v>
+        <v>1192150.2</v>
       </c>
       <c r="M4" t="n">
-        <v>707663.05</v>
+        <v>648301.95</v>
       </c>
       <c r="N4" t="n">
-        <v>553507.35</v>
+        <v>528546.6</v>
       </c>
       <c r="O4" t="n">
-        <v>2.318579725195486</v>
+        <v>1.838881095452513</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2144831082749139</v>
+        <v>-0.1275752552952252</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2981964894185847</v>
+        <v>-0.1556446171936194</v>
       </c>
       <c r="R4" t="n">
-        <v>0.08371338114367077</v>
+        <v>0.02806936189839421</v>
       </c>
       <c r="S4" t="n">
-        <v>0.08201989912262686</v>
+        <v>0.01990058435520706</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0923727807371495</v>
+        <v>-0.005667124593579098</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1015,44 +1015,44 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>240.696</v>
+        <v>-326</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE4" t="n">
-        <v>252.696</v>
+        <v>-313</v>
       </c>
       <c r="AF4" t="n">
-        <v>-106.5050000000001</v>
+        <v>260.926</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>6.945</v>
+        <v>36</v>
       </c>
       <c r="AI4" t="n">
-        <v>-99.56000000000006</v>
+        <v>296.926</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-329</v>
+        <v>151.09</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>29.068</v>
+        <v>25</v>
       </c>
       <c r="AM4" t="n">
-        <v>-299.932</v>
+        <v>176.09</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -1063,67 +1063,67 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5202</t>
+          <t>1515</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>力新</t>
+          <t>力山</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>12.19999980926514</v>
+        <v>22</v>
       </c>
       <c r="G5" t="n">
-        <v>12.36750001907349</v>
+        <v>22.33000011444092</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>47.63351387339981</v>
+        <v>33.16921853244855</v>
       </c>
       <c r="J5" t="n">
-        <v>30.94892728155128</v>
+        <v>32.38585710897432</v>
       </c>
       <c r="K5" t="n">
-        <v>45.12592321186386</v>
+        <v>43.28432885053579</v>
       </c>
       <c r="L5" t="n">
-        <v>529263.2</v>
+        <v>1177841</v>
       </c>
       <c r="M5" t="n">
-        <v>277678.35</v>
+        <v>694767.95</v>
       </c>
       <c r="N5" t="n">
-        <v>279283.275</v>
+        <v>502360.9</v>
       </c>
       <c r="O5" t="n">
-        <v>1.906029764293831</v>
+        <v>1.695301287285921</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.371845799091103</v>
+        <v>-0.2414931801069038</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.3969991562283937</v>
+        <v>-0.2538259444621432</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02515335713729067</v>
+        <v>0.01233276435523945</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.009109374239265389</v>
+        <v>0.0156325257795028</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.08260067533711835</v>
+        <v>0.01314470066320739</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1161,44 +1161,44 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>-73</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>0.155</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>-72.845</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>971</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.602</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>972.6020000000001</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>-329.874</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>-56.262</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-386.1359999999999</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -1209,16 +1209,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2516</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>新建</t>
+          <t>宏洲</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1227,49 +1227,49 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>12.75</v>
+        <v>9.489999771118164</v>
       </c>
       <c r="G6" t="n">
-        <v>12.89750003814697</v>
+        <v>9.476999998092651</v>
       </c>
       <c r="H6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>43.4716667477668</v>
+        <v>44.06908586705662</v>
       </c>
       <c r="J6" t="n">
-        <v>36.85345972017227</v>
+        <v>38.36321227365829</v>
       </c>
       <c r="K6" t="n">
-        <v>46.36529894092313</v>
+        <v>48.88661851819758</v>
       </c>
       <c r="L6" t="n">
-        <v>720296</v>
+        <v>51503.4</v>
       </c>
       <c r="M6" t="n">
-        <v>381359.45</v>
+        <v>33255.4</v>
       </c>
       <c r="N6" t="n">
-        <v>348198.775</v>
+        <v>27052.45</v>
       </c>
       <c r="O6" t="n">
-        <v>1.888758755027573</v>
+        <v>1.548722914173337</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1897902141680454</v>
+        <v>-0.07319304493855583</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2407175097087843</v>
+        <v>-0.07960789568196236</v>
       </c>
       <c r="R6" t="n">
-        <v>0.05092729554073891</v>
+        <v>0.00641485074340653</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05007384840960938</v>
+        <v>-0.003881253045467548</v>
       </c>
       <c r="T6" t="n">
-        <v>0.05839261049442485</v>
+        <v>-0.01167510333191731</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1316,35 +1316,35 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AF6" t="n">
-        <v>-27</v>
+        <v>33</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-22</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>-49.00000000000001</v>
+        <v>33</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-114.001</v>
+        <v>41.7</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>-139.001</v>
+        <v>41.7</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -1355,67 +1355,67 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>1466</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>永捷</t>
+          <t>聚隆</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>13.39999961853027</v>
+        <v>14.35000038146973</v>
       </c>
       <c r="G7" t="n">
-        <v>13.97750000953674</v>
+        <v>14.73249998092651</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>33.93996180201444</v>
+        <v>41.20604318586713</v>
       </c>
       <c r="J7" t="n">
-        <v>33.06531977538064</v>
+        <v>31.13059982799518</v>
       </c>
       <c r="K7" t="n">
-        <v>41.06225466269198</v>
+        <v>36.39533895836961</v>
       </c>
       <c r="L7" t="n">
-        <v>2179030.6</v>
+        <v>336068.2</v>
       </c>
       <c r="M7" t="n">
-        <v>1298415.9</v>
+        <v>221169</v>
       </c>
       <c r="N7" t="n">
-        <v>1624788.275</v>
+        <v>218448.125</v>
       </c>
       <c r="O7" t="n">
-        <v>1.67822236311185</v>
+        <v>1.519508611062129</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3790617743697506</v>
+        <v>-0.573905626857993</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.3834944848549334</v>
+        <v>-0.5970079782690267</v>
       </c>
       <c r="R7" t="n">
-        <v>0.004432710485182789</v>
+        <v>0.02310235141103378</v>
       </c>
       <c r="S7" t="n">
-        <v>0.00378323063361341</v>
+        <v>-0.009926435217106344</v>
       </c>
       <c r="T7" t="n">
-        <v>0.002933891433177405</v>
+        <v>-0.03775160553306045</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1453,44 +1453,44 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>248</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>147.825</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.003</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>148.828</v>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -1505,63 +1505,63 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>9951</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>皇田</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>52.79999923706055</v>
+        <v>33.79999923706055</v>
       </c>
       <c r="G8" t="n">
-        <v>53.25499973297119</v>
+        <v>34.30249996185303</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>41.18079766687108</v>
+        <v>41.21023063509114</v>
       </c>
       <c r="J8" t="n">
-        <v>30.81030347660208</v>
+        <v>30.1200923316572</v>
       </c>
       <c r="K8" t="n">
-        <v>44.84532134742219</v>
+        <v>44.29612725346669</v>
       </c>
       <c r="L8" t="n">
-        <v>218803.8</v>
+        <v>57776927</v>
       </c>
       <c r="M8" t="n">
-        <v>141315.8</v>
+        <v>22261260</v>
       </c>
       <c r="N8" t="n">
-        <v>103747.25</v>
+        <v>16091465.1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.548332175170788</v>
+        <v>2.595402371653716</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.432168399957952</v>
+        <v>-0.4317953710562747</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.3716556817552978</v>
+        <v>-0.3732166209333399</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.06051271820265414</v>
+        <v>-0.05857875012293484</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1072262225717261</v>
+        <v>-0.09970543074791227</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1472379154868523</v>
+        <v>-0.1517665888693578</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1599,44 +1599,44 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>-2196.307</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>-174.242</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>-2319.549</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>-19464.091</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>-4639.107</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>-273.627</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>-24376.825</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>-68279.43799999999</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>-8224.545999999998</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>-2821.215</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>-79325.19900000001</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -1651,63 +1651,63 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>美吾華</t>
+          <t>寶利徠</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>21.35000038146973</v>
+        <v>11.94999980926514</v>
       </c>
       <c r="G9" t="n">
-        <v>21.56499996185303</v>
+        <v>12.17249989509583</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>31.1450479602699</v>
+        <v>38.35151427820887</v>
       </c>
       <c r="J9" t="n">
-        <v>30.38397927740122</v>
+        <v>32.11158173408099</v>
       </c>
       <c r="K9" t="n">
-        <v>35.74836256695912</v>
+        <v>35.10323801404326</v>
       </c>
       <c r="L9" t="n">
-        <v>207423.6</v>
+        <v>86088.8</v>
       </c>
       <c r="M9" t="n">
-        <v>135918.8</v>
+        <v>42194.75</v>
       </c>
       <c r="N9" t="n">
-        <v>121652.675</v>
+        <v>41485.3</v>
       </c>
       <c r="O9" t="n">
-        <v>1.526084691742423</v>
+        <v>2.040272782751409</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.09465929280814933</v>
+        <v>-0.2044060707313999</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.07384396279689336</v>
+        <v>-0.2146608022676302</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.02081533001125598</v>
+        <v>0.01025473153623027</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.02015581603749303</v>
+        <v>0.009689949381130186</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.01132840480300609</v>
+        <v>0.01622899038064965</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>-27</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1754,35 +1754,35 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-27</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>-104</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>-111</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-271.89</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>-273.89</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -1797,12 +1797,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3703</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>欣陸</t>
+          <t>宅配通</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1811,49 +1811,49 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>20.20000076293945</v>
+        <v>20.95000076293945</v>
       </c>
       <c r="G10" t="n">
-        <v>20.32499990463257</v>
+        <v>20.83000020980835</v>
       </c>
       <c r="H10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>47.63638677824609</v>
+        <v>45.60657398558658</v>
       </c>
       <c r="J10" t="n">
-        <v>42.02700126041556</v>
+        <v>35.59730982739954</v>
       </c>
       <c r="K10" t="n">
-        <v>39.78166996987412</v>
+        <v>44.45086383883459</v>
       </c>
       <c r="L10" t="n">
-        <v>2159268.2</v>
+        <v>185327.6</v>
       </c>
       <c r="M10" t="n">
-        <v>1423096.35</v>
+        <v>117586.25</v>
       </c>
       <c r="N10" t="n">
-        <v>1256152.3</v>
+        <v>93536.72500000001</v>
       </c>
       <c r="O10" t="n">
-        <v>1.517302886765186</v>
+        <v>1.57609924629793</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3180469186709018</v>
+        <v>-0.3826446326499067</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.3696441856574443</v>
+        <v>-0.5179600461321803</v>
       </c>
       <c r="R10" t="n">
-        <v>0.05159726698654243</v>
+        <v>0.1353154134822736</v>
       </c>
       <c r="S10" t="n">
-        <v>0.04268996485319987</v>
+        <v>0.119262815324723</v>
       </c>
       <c r="T10" t="n">
-        <v>0.04574548751355473</v>
+        <v>0.09170293679351404</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -1891,44 +1891,190 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>399</v>
+        <v>-40</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>400</v>
+        <v>-40</v>
       </c>
       <c r="AF10" t="n">
-        <v>240</v>
+        <v>-47</v>
       </c>
       <c r="AG10" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-1944.571</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>-1705.571</v>
+        <v>-47</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-3932</v>
+        <v>15.82000000000002</v>
       </c>
       <c r="AK10" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>-2814.951</v>
+        <v>-2</v>
       </c>
       <c r="AM10" t="n">
-        <v>-6749.951</v>
+        <v>13.82000000000002</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>70</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>6212</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>理銘</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>27.60000038146973</v>
+      </c>
+      <c r="G11" t="n">
+        <v>28.10499992370605</v>
+      </c>
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>43.57138070905599</v>
+      </c>
+      <c r="J11" t="n">
+        <v>36.66695862971176</v>
+      </c>
+      <c r="K11" t="n">
+        <v>41.77909996415158</v>
+      </c>
+      <c r="L11" t="n">
+        <v>9400</v>
+      </c>
+      <c r="M11" t="n">
+        <v>6204.05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>6347.825</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.515139304164215</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0.323565514469955</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-0.3419142841919003</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.01834876972194532</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.01951116270790071</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.005771490204465768</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN11"/>
+  <dimension ref="A1:AN9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,16 +625,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2539</t>
+          <t>4994</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>櫻花建</t>
+          <t>傳奇</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,49 +643,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>36</v>
+        <v>87.19999694824219</v>
       </c>
       <c r="G2" t="n">
-        <v>37.61749992370606</v>
+        <v>92.2549991607666</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>45.20323440042991</v>
+        <v>38.86138388303814</v>
       </c>
       <c r="J2" t="n">
-        <v>33.80373394691094</v>
+        <v>35.48481029854787</v>
       </c>
       <c r="K2" t="n">
-        <v>35.18149162459814</v>
+        <v>34.7196750922876</v>
       </c>
       <c r="L2" t="n">
-        <v>3072168</v>
+        <v>136548.4</v>
       </c>
       <c r="M2" t="n">
-        <v>1979433.85</v>
+        <v>50109.65</v>
       </c>
       <c r="N2" t="n">
-        <v>1541498.1</v>
+        <v>37549.875</v>
       </c>
       <c r="O2" t="n">
-        <v>1.552043782619965</v>
+        <v>2.724992092341495</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.971332371910592</v>
+        <v>-2.250218355302778</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.106413978055551</v>
+        <v>-1.927954887452512</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1350816061449596</v>
+        <v>-0.322263467850266</v>
       </c>
       <c r="S2" t="n">
-        <v>0.07806749118987355</v>
+        <v>-0.2609453764034098</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.05956806909320544</v>
+        <v>-0.1246019529012119</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -719,48 +719,48 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>-340.964</v>
+        <v>1.024</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.002000000000001</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-5.078</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-337.04</v>
+        <v>1.024</v>
       </c>
       <c r="AF2" t="n">
-        <v>189.019</v>
+        <v>4.024000000000001</v>
       </c>
       <c r="AG2" t="n">
-        <v>18.888</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-1.07800000000001</v>
+        <v>2</v>
       </c>
       <c r="AI2" t="n">
-        <v>206.829</v>
+        <v>6.024000000000001</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-2161.332</v>
+        <v>-40.239</v>
       </c>
       <c r="AK2" t="n">
-        <v>-16.595</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-6.040000000000012</v>
+        <v>2</v>
       </c>
       <c r="AM2" t="n">
-        <v>-2183.967</v>
+        <v>-38.239</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
@@ -775,12 +775,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>7736</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>傳奇</t>
+          <t>虎山</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,49 +789,49 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>87.30000305175781</v>
+        <v>72.90000152587891</v>
       </c>
       <c r="G3" t="n">
-        <v>92.7949993133545</v>
+        <v>73.17000007629395</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>36.96341438014584</v>
+        <v>34.44455818895815</v>
       </c>
       <c r="J3" t="n">
-        <v>33.79652345547542</v>
+        <v>31.88079516414955</v>
       </c>
       <c r="K3" t="n">
-        <v>35.11822940588451</v>
+        <v>41.83082772490176</v>
       </c>
       <c r="L3" t="n">
-        <v>132125.2</v>
+        <v>59670.8</v>
       </c>
       <c r="M3" t="n">
-        <v>48953.85</v>
+        <v>38119.95</v>
       </c>
       <c r="N3" t="n">
-        <v>36671.975</v>
+        <v>40472.425</v>
       </c>
       <c r="O3" t="n">
-        <v>2.698974646529333</v>
+        <v>1.565343081509813</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.104427947394626</v>
+        <v>-1.059928923122769</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.841672887304255</v>
+        <v>-1.551257174909423</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.2627550600903714</v>
+        <v>0.491328251786654</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1265529096042373</v>
+        <v>0.5660891539341351</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1579220910237285</v>
+        <v>0.5503716810350561</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>1.024</v>
+        <v>1</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -878,35 +878,35 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.024</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>14.843</v>
+        <v>18</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1</v>
+        <v>-0.764</v>
       </c>
       <c r="AI3" t="n">
-        <v>15.843</v>
+        <v>17.236</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-26.92</v>
+        <v>64.99000000000001</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-2</v>
+        <v>-4.909000000000001</v>
       </c>
       <c r="AM3" t="n">
-        <v>-28.92</v>
+        <v>60.081</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
@@ -917,67 +917,67 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2538</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>基泰</t>
+          <t>寶利徠</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>9.510000228881836</v>
+        <v>12.14999961853027</v>
       </c>
       <c r="G4" t="n">
-        <v>9.537000131607055</v>
+        <v>12.15749988555908</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>45.31644239472193</v>
+        <v>47.23433013510484</v>
       </c>
       <c r="J4" t="n">
-        <v>36.46394732093216</v>
+        <v>37.1524978420543</v>
       </c>
       <c r="K4" t="n">
-        <v>45.5125132745632</v>
+        <v>44.3597505849934</v>
       </c>
       <c r="L4" t="n">
-        <v>1192150.2</v>
+        <v>99196</v>
       </c>
       <c r="M4" t="n">
-        <v>648301.95</v>
+        <v>48521.55</v>
       </c>
       <c r="N4" t="n">
-        <v>528546.6</v>
+        <v>44673.7</v>
       </c>
       <c r="O4" t="n">
-        <v>1.838881095452513</v>
+        <v>2.04436997581487</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1275752552952252</v>
+        <v>-0.183671179483202</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1556446171936194</v>
+        <v>-0.2084628777107446</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02806936189839421</v>
+        <v>0.0247916982275426</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01990058435520706</v>
+        <v>0.01025473153623027</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.005667124593579098</v>
+        <v>0.009689949381130186</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1015,44 +1015,44 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>-326</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-313</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>260.926</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>296.926</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>151.09</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>176.09</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
@@ -1063,67 +1063,67 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t>4528</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>力山</t>
+          <t>江興鍛</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>22</v>
+        <v>15.80000019073486</v>
       </c>
       <c r="G5" t="n">
-        <v>22.33000011444092</v>
+        <v>15.66499996185303</v>
       </c>
       <c r="H5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>33.16921853244855</v>
+        <v>42.07755207918906</v>
       </c>
       <c r="J5" t="n">
-        <v>32.38585710897432</v>
+        <v>33.0247417558672</v>
       </c>
       <c r="K5" t="n">
-        <v>43.28432885053579</v>
+        <v>48.22582672138932</v>
       </c>
       <c r="L5" t="n">
-        <v>1177841</v>
+        <v>84316.60000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>694767.95</v>
+        <v>43367.15</v>
       </c>
       <c r="N5" t="n">
-        <v>502360.9</v>
+        <v>51340.825</v>
       </c>
       <c r="O5" t="n">
-        <v>1.695301287285921</v>
+        <v>1.944250429184302</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2414931801069038</v>
+        <v>-0.2196511002551151</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2538259444621432</v>
+        <v>-0.2876179254879573</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01233276435523945</v>
+        <v>0.06796682523284214</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0156325257795028</v>
+        <v>0.04737655599010476</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01314470066320739</v>
+        <v>0.03535761696677675</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1161,44 +1161,44 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>-73</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.155</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-72.845</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>971</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.602</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>972.6020000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-329.874</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-56.262</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>-386.1359999999999</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
@@ -1209,67 +1209,67 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>8066</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>宏洲</t>
+          <t>來思達</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>9.489999771118164</v>
+        <v>16.25</v>
       </c>
       <c r="G6" t="n">
-        <v>9.476999998092651</v>
+        <v>16.38999991416931</v>
       </c>
       <c r="H6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>44.06908586705662</v>
+        <v>36.25260444814153</v>
       </c>
       <c r="J6" t="n">
-        <v>38.36321227365829</v>
+        <v>30.08452858714341</v>
       </c>
       <c r="K6" t="n">
-        <v>48.88661851819758</v>
+        <v>43.54373637022683</v>
       </c>
       <c r="L6" t="n">
-        <v>51503.4</v>
+        <v>162596.6</v>
       </c>
       <c r="M6" t="n">
-        <v>33255.4</v>
+        <v>95925.45</v>
       </c>
       <c r="N6" t="n">
-        <v>27052.45</v>
+        <v>78777.375</v>
       </c>
       <c r="O6" t="n">
-        <v>1.548722914173337</v>
+        <v>1.695030880751667</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.07319304493855583</v>
+        <v>-0.4709921565870268</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.07960789568196236</v>
+        <v>-0.5101045533192128</v>
       </c>
       <c r="R6" t="n">
-        <v>0.00641485074340653</v>
+        <v>0.03911239673218603</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.003881253045467548</v>
+        <v>0.006630423749433123</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.01167510333191731</v>
+        <v>-0.01273115727751484</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1316,10 +1316,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1328,10 +1328,10 @@
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>41.7</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
@@ -1340,11 +1340,11 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>41.7</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
@@ -1355,16 +1355,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1466</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>聚隆</t>
+          <t>宅配通</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1373,49 +1373,49 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>14.35000038146973</v>
+        <v>20.5</v>
       </c>
       <c r="G7" t="n">
-        <v>14.73249998092651</v>
+        <v>20.78250017166138</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>41.20604318586713</v>
+        <v>38.24751771268367</v>
       </c>
       <c r="J7" t="n">
-        <v>31.13059982799518</v>
+        <v>36.48071246826376</v>
       </c>
       <c r="K7" t="n">
-        <v>36.39533895836961</v>
+        <v>36.19111376764814</v>
       </c>
       <c r="L7" t="n">
-        <v>336068.2</v>
+        <v>202502.8</v>
       </c>
       <c r="M7" t="n">
-        <v>221169</v>
+        <v>122585.05</v>
       </c>
       <c r="N7" t="n">
-        <v>218448.125</v>
+        <v>98183.89999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>1.519508611062129</v>
+        <v>1.651937165257917</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.573905626857993</v>
+        <v>-0.3743769637956653</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.5970079782690267</v>
+        <v>-0.4883288448663143</v>
       </c>
       <c r="R7" t="n">
-        <v>0.02310235141103378</v>
+        <v>0.113951881070649</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.009926435217106344</v>
+        <v>0.1349534753642005</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.03775160553306045</v>
+        <v>0.1188726224956566</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1453,44 +1453,44 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>-13</v>
+        <v>-40</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-14</v>
+        <v>-40</v>
       </c>
       <c r="AF7" t="n">
-        <v>248</v>
+        <v>-85</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>251</v>
+        <v>-85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>147.825</v>
+        <v>-67.88</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.003</v>
+        <v>-4</v>
       </c>
       <c r="AM7" t="n">
-        <v>148.828</v>
+        <v>-71.88</v>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
@@ -1505,63 +1505,63 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>8424</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>惠普</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>33.79999923706055</v>
+        <v>72.90000152587891</v>
       </c>
       <c r="G8" t="n">
-        <v>34.30249996185303</v>
+        <v>73.2299991607666</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>41.21023063509114</v>
+        <v>44.9028534942532</v>
       </c>
       <c r="J8" t="n">
-        <v>30.1200923316572</v>
+        <v>42.4690674039125</v>
       </c>
       <c r="K8" t="n">
-        <v>44.29612725346669</v>
+        <v>31.63873333214448</v>
       </c>
       <c r="L8" t="n">
-        <v>57776927</v>
+        <v>54711.2</v>
       </c>
       <c r="M8" t="n">
-        <v>22261260</v>
+        <v>33623.55</v>
       </c>
       <c r="N8" t="n">
-        <v>16091465.1</v>
+        <v>21761.775</v>
       </c>
       <c r="O8" t="n">
-        <v>2.595402371653716</v>
+        <v>1.627169052643162</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4317953710562747</v>
+        <v>-0.3451830967678688</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.3732166209333399</v>
+        <v>-0.3663037154099061</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.05857875012293484</v>
+        <v>0.02112061864203729</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.09970543074791227</v>
+        <v>0.01350361045705606</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1517665888693578</v>
+        <v>0.005626483542915506</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1599,44 +1599,44 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>-2196.307</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>-174.242</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-2319.549</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>-19464.091</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>-4639.107</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>-273.627</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>-24376.825</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-68279.43799999999</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>-8224.545999999998</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>-2821.215</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>-79325.19900000001</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
@@ -1651,12 +1651,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>1788</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>寶利徠</t>
+          <t>杏昌</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1665,49 +1665,49 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>11.94999980926514</v>
+        <v>134.5</v>
       </c>
       <c r="G9" t="n">
-        <v>12.17249989509583</v>
+        <v>134.95</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>38.35151427820887</v>
+        <v>32.83597883495014</v>
       </c>
       <c r="J9" t="n">
-        <v>32.11158173408099</v>
+        <v>30.26599029962267</v>
       </c>
       <c r="K9" t="n">
-        <v>35.10323801404326</v>
+        <v>42.9530069021747</v>
       </c>
       <c r="L9" t="n">
-        <v>86088.8</v>
+        <v>75564.8</v>
       </c>
       <c r="M9" t="n">
-        <v>42194.75</v>
+        <v>47562.9</v>
       </c>
       <c r="N9" t="n">
-        <v>41485.3</v>
+        <v>37096.55</v>
       </c>
       <c r="O9" t="n">
-        <v>2.040272782751409</v>
+        <v>1.588734076349424</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2044060707313999</v>
+        <v>-0.424621828582076</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2146608022676302</v>
+        <v>-0.3632329470265668</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01025473153623027</v>
+        <v>-0.0613888815555092</v>
       </c>
       <c r="S9" t="n">
-        <v>0.009689949381130186</v>
+        <v>-0.09862728893130679</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01622899038064965</v>
+        <v>-0.09382140051007476</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1782,299 +1782,7 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>70</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2642</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>宅配通</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>20.95000076293945</v>
-      </c>
-      <c r="G10" t="n">
-        <v>20.83000020980835</v>
-      </c>
-      <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>45.60657398558658</v>
-      </c>
-      <c r="J10" t="n">
-        <v>35.59730982739954</v>
-      </c>
-      <c r="K10" t="n">
-        <v>44.45086383883459</v>
-      </c>
-      <c r="L10" t="n">
-        <v>185327.6</v>
-      </c>
-      <c r="M10" t="n">
-        <v>117586.25</v>
-      </c>
-      <c r="N10" t="n">
-        <v>93536.72500000001</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.57609924629793</v>
-      </c>
-      <c r="P10" t="n">
-        <v>-0.3826446326499067</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-0.5179600461321803</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.1353154134822736</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.119262815324723</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.09170293679351404</v>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB10" t="n">
-        <v>-40</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>-40</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>-47</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>-47</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>15.82000000000002</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>13.82000000000002</v>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>70</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>6212</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>理銘</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>27.60000038146973</v>
-      </c>
-      <c r="G11" t="n">
-        <v>28.10499992370605</v>
-      </c>
-      <c r="H11" t="b">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>43.57138070905599</v>
-      </c>
-      <c r="J11" t="n">
-        <v>36.66695862971176</v>
-      </c>
-      <c r="K11" t="n">
-        <v>41.77909996415158</v>
-      </c>
-      <c r="L11" t="n">
-        <v>9400</v>
-      </c>
-      <c r="M11" t="n">
-        <v>6204.05</v>
-      </c>
-      <c r="N11" t="n">
-        <v>6347.825</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.515139304164215</v>
-      </c>
-      <c r="P11" t="n">
-        <v>-0.323565514469955</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>-0.3419142841919003</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.01834876972194532</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.01951116270790071</v>
-      </c>
-      <c r="T11" t="n">
-        <v>-0.005771490204465768</v>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN9"/>
+  <dimension ref="A1:AN11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,12 +629,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>傳奇</t>
+          <t>佳格</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,49 +643,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>87.19999694824219</v>
+        <v>28.45000076293945</v>
       </c>
       <c r="G2" t="n">
-        <v>92.2549991607666</v>
+        <v>28.4</v>
       </c>
       <c r="H2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>38.86138388303814</v>
+        <v>42.70047904409716</v>
       </c>
       <c r="J2" t="n">
-        <v>35.48481029854787</v>
+        <v>30.45723882755896</v>
       </c>
       <c r="K2" t="n">
-        <v>34.7196750922876</v>
+        <v>47.89197630680934</v>
       </c>
       <c r="L2" t="n">
-        <v>136548.4</v>
+        <v>4127956.2</v>
       </c>
       <c r="M2" t="n">
-        <v>50109.65</v>
+        <v>1801661.75</v>
       </c>
       <c r="N2" t="n">
-        <v>37549.875</v>
+        <v>1414942.275</v>
       </c>
       <c r="O2" t="n">
-        <v>2.724992092341495</v>
+        <v>2.291193782628731</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.250218355302778</v>
+        <v>-0.2813860957459724</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.927954887452512</v>
+        <v>-0.3374831210657638</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.322263467850266</v>
+        <v>0.05609702531979138</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2609453764034098</v>
+        <v>0.03093974712155295</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1246019529012119</v>
+        <v>-0.001581374479297626</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -723,44 +723,44 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>1.024</v>
+        <v>1320.764</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>8.308</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.024</v>
+        <v>1329.072</v>
       </c>
       <c r="AF2" t="n">
-        <v>4.024000000000001</v>
+        <v>8088.138</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>-677</v>
       </c>
       <c r="AH2" t="n">
-        <v>2</v>
+        <v>-22.12</v>
       </c>
       <c r="AI2" t="n">
-        <v>6.024000000000001</v>
+        <v>7389.018</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-40.239</v>
+        <v>4001.300999999999</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>-670</v>
       </c>
       <c r="AL2" t="n">
-        <v>2</v>
+        <v>-16.735</v>
       </c>
       <c r="AM2" t="n">
-        <v>-38.239</v>
+        <v>3314.566</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -775,12 +775,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>7736</t>
+          <t>2430</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>燦坤</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,49 +789,49 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>72.90000152587891</v>
+        <v>19.10000038146973</v>
       </c>
       <c r="G3" t="n">
-        <v>73.17000007629395</v>
+        <v>18.74249973297119</v>
       </c>
       <c r="H3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>34.44455818895815</v>
+        <v>47.81152978685318</v>
       </c>
       <c r="J3" t="n">
-        <v>31.88079516414955</v>
+        <v>40.5060613118503</v>
       </c>
       <c r="K3" t="n">
-        <v>41.83082772490176</v>
+        <v>48.15055028184459</v>
       </c>
       <c r="L3" t="n">
-        <v>59670.8</v>
+        <v>368310.8</v>
       </c>
       <c r="M3" t="n">
-        <v>38119.95</v>
+        <v>209385.2</v>
       </c>
       <c r="N3" t="n">
-        <v>40472.425</v>
+        <v>174633.95</v>
       </c>
       <c r="O3" t="n">
-        <v>1.565343081509813</v>
+        <v>1.759010665510265</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.059928923122769</v>
+        <v>-0.4072404856727445</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.551257174909423</v>
+        <v>-0.605944285741004</v>
       </c>
       <c r="R3" t="n">
-        <v>0.491328251786654</v>
+        <v>0.1987038000682595</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5660891539341351</v>
+        <v>0.1845262566180147</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5503716810350561</v>
+        <v>0.08982804037501868</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -869,44 +869,44 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>1</v>
+        <v>-30.85</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AE3" t="n">
-        <v>1</v>
+        <v>-31.85</v>
       </c>
       <c r="AF3" t="n">
-        <v>18</v>
+        <v>134.15</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.764</v>
+        <v>-1.256</v>
       </c>
       <c r="AI3" t="n">
-        <v>17.236</v>
+        <v>132.894</v>
       </c>
       <c r="AJ3" t="n">
-        <v>64.99000000000001</v>
+        <v>29.94999999999998</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-4.909000000000001</v>
+        <v>-23.256</v>
       </c>
       <c r="AM3" t="n">
-        <v>60.081</v>
+        <v>6.694000000000006</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -921,63 +921,63 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>4994</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>寶利徠</t>
+          <t>傳奇</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>12.14999961853027</v>
+        <v>86.80000305175781</v>
       </c>
       <c r="G4" t="n">
-        <v>12.15749988555908</v>
+        <v>91.6699993133545</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>47.23433013510484</v>
+        <v>39.19431037919734</v>
       </c>
       <c r="J4" t="n">
-        <v>37.1524978420543</v>
+        <v>36.72131036570929</v>
       </c>
       <c r="K4" t="n">
-        <v>44.3597505849934</v>
+        <v>34.66494459709743</v>
       </c>
       <c r="L4" t="n">
-        <v>99196</v>
+        <v>136965.2</v>
       </c>
       <c r="M4" t="n">
-        <v>48521.55</v>
+        <v>50373.85</v>
       </c>
       <c r="N4" t="n">
-        <v>44673.7</v>
+        <v>37006.975</v>
       </c>
       <c r="O4" t="n">
-        <v>2.04436997581487</v>
+        <v>2.718974229684648</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.183671179483202</v>
+        <v>-2.367645831778376</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2084628777107446</v>
+        <v>-2.015893076317685</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0247916982275426</v>
+        <v>-0.3517527554606907</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01025473153623027</v>
+        <v>-0.322263467850266</v>
       </c>
       <c r="T4" t="n">
-        <v>0.009689949381130186</v>
+        <v>-0.2609453764034098</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1015,44 +1015,44 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>4.024000000000001</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-2.975999999999999</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>-46.92</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>-51.92</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -1067,63 +1067,63 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>1454</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>江興鍛</t>
+          <t>台富</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>15.80000019073486</v>
+        <v>12.94999980926514</v>
       </c>
       <c r="G5" t="n">
-        <v>15.66499996185303</v>
+        <v>13.02999992370605</v>
       </c>
       <c r="H5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>42.07755207918906</v>
+        <v>35.51799186917036</v>
       </c>
       <c r="J5" t="n">
-        <v>33.0247417558672</v>
+        <v>31.58959187776733</v>
       </c>
       <c r="K5" t="n">
-        <v>48.22582672138932</v>
+        <v>48.48860145952712</v>
       </c>
       <c r="L5" t="n">
-        <v>84316.60000000001</v>
+        <v>147533.6</v>
       </c>
       <c r="M5" t="n">
-        <v>43367.15</v>
+        <v>83153.45</v>
       </c>
       <c r="N5" t="n">
-        <v>51340.825</v>
+        <v>105154.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.944250429184302</v>
+        <v>1.774233059482198</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2196511002551151</v>
+        <v>-0.1008374039801723</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2876179254879573</v>
+        <v>-0.122255586615181</v>
       </c>
       <c r="R5" t="n">
-        <v>0.06796682523284214</v>
+        <v>0.02141818263500869</v>
       </c>
       <c r="S5" t="n">
-        <v>0.04737655599010476</v>
+        <v>0.017699903203477</v>
       </c>
       <c r="T5" t="n">
-        <v>0.03535761696677675</v>
+        <v>0.007052420709859453</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1161,44 +1161,44 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>-23</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>-34.88999999999999</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-39.89</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>6461</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>來思達</t>
+          <t>益得</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1227,49 +1227,49 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>16.25</v>
+        <v>16.5</v>
       </c>
       <c r="G6" t="n">
-        <v>16.38999991416931</v>
+        <v>16.17250003814697</v>
       </c>
       <c r="H6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>36.25260444814153</v>
+        <v>47.5401337616258</v>
       </c>
       <c r="J6" t="n">
-        <v>30.08452858714341</v>
+        <v>35.78311657627271</v>
       </c>
       <c r="K6" t="n">
-        <v>43.54373637022683</v>
+        <v>48.18327580940343</v>
       </c>
       <c r="L6" t="n">
-        <v>162596.6</v>
+        <v>404341.8</v>
       </c>
       <c r="M6" t="n">
-        <v>95925.45</v>
+        <v>234512.65</v>
       </c>
       <c r="N6" t="n">
-        <v>78777.375</v>
+        <v>245074.675</v>
       </c>
       <c r="O6" t="n">
-        <v>1.695030880751667</v>
+        <v>1.724179058144625</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4709921565870268</v>
+        <v>-0.4375292484602262</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.5101045533192128</v>
+        <v>-0.5971766713588368</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03911239673218603</v>
+        <v>0.1596474228986106</v>
       </c>
       <c r="S6" t="n">
-        <v>0.006630423749433123</v>
+        <v>0.1281589836302228</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.01273115727751484</v>
+        <v>0.08155943233396423</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -1359,63 +1359,63 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>4528</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>宅配通</t>
+          <t>江興鍛</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>20.5</v>
+        <v>15.80000019073486</v>
       </c>
       <c r="G7" t="n">
-        <v>20.78250017166138</v>
+        <v>15.67249999046326</v>
       </c>
       <c r="H7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>38.24751771268367</v>
+        <v>48.34155765968328</v>
       </c>
       <c r="J7" t="n">
-        <v>36.48071246826376</v>
+        <v>38.13034704286068</v>
       </c>
       <c r="K7" t="n">
-        <v>36.19111376764814</v>
+        <v>48.790469457928</v>
       </c>
       <c r="L7" t="n">
-        <v>202502.8</v>
+        <v>75104.39999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>122585.05</v>
+        <v>44668.45</v>
       </c>
       <c r="N7" t="n">
-        <v>98183.89999999999</v>
+        <v>51968.45</v>
       </c>
       <c r="O7" t="n">
-        <v>1.651937165257917</v>
+        <v>1.681374661534036</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3743769637956653</v>
+        <v>-0.1855324987710443</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.4883288448663143</v>
+        <v>-0.2644571031931351</v>
       </c>
       <c r="R7" t="n">
-        <v>0.113951881070649</v>
+        <v>0.07892460442209082</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1349534753642005</v>
+        <v>0.06688101778201871</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1188726224956566</v>
+        <v>0.046205984945208</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1462,10 +1462,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>-85</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1474,23 +1474,23 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>-85</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-67.88</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>-71.88</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>8424</t>
+          <t>8066</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>惠普</t>
+          <t>來思達</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1519,49 +1519,49 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>72.90000152587891</v>
+        <v>16</v>
       </c>
       <c r="G8" t="n">
-        <v>73.2299991607666</v>
+        <v>16.33499989509583</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>44.9028534942532</v>
+        <v>46.00748191220891</v>
       </c>
       <c r="J8" t="n">
-        <v>42.4690674039125</v>
+        <v>35.39217967646054</v>
       </c>
       <c r="K8" t="n">
-        <v>31.63873333214448</v>
+        <v>40.88986092758873</v>
       </c>
       <c r="L8" t="n">
-        <v>54711.2</v>
+        <v>146651.4</v>
       </c>
       <c r="M8" t="n">
-        <v>33623.55</v>
+        <v>91282.45</v>
       </c>
       <c r="N8" t="n">
-        <v>21761.775</v>
+        <v>79082.325</v>
       </c>
       <c r="O8" t="n">
-        <v>1.627169052643162</v>
+        <v>1.606567308392796</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3451830967678688</v>
+        <v>-0.4520961776443571</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.3663037154099061</v>
+        <v>-0.4980455770628352</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02112061864203729</v>
+        <v>0.04594939941847814</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01350361045705606</v>
+        <v>0.03893142422144868</v>
       </c>
       <c r="T8" t="n">
-        <v>0.005626483542915506</v>
+        <v>0.006435323613740551</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -1651,138 +1651,430 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>杏昌</t>
+          <t>宅配通</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>20.79999923706055</v>
+      </c>
+      <c r="G9" t="n">
+        <v>20.75000009536743</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>39.22382213932451</v>
+      </c>
+      <c r="J9" t="n">
+        <v>37.39508237934427</v>
+      </c>
+      <c r="K9" t="n">
+        <v>44.27696587086676</v>
+      </c>
+      <c r="L9" t="n">
+        <v>196725.6</v>
+      </c>
+      <c r="M9" t="n">
+        <v>127717.05</v>
+      </c>
+      <c r="N9" t="n">
+        <v>102327.9</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.540323707758674</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0.3374190812929569</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-0.4544885704016338</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.1170694891086768</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.1125041355017533</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.1333927114902366</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-66</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-65</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>-23.18</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-26.18</v>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>70</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1599</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>宏佳騰</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>134.5</v>
-      </c>
-      <c r="G9" t="n">
-        <v>134.95</v>
-      </c>
-      <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>32.83597883495014</v>
-      </c>
-      <c r="J9" t="n">
-        <v>30.26599029962267</v>
-      </c>
-      <c r="K9" t="n">
-        <v>42.9530069021747</v>
-      </c>
-      <c r="L9" t="n">
-        <v>75564.8</v>
-      </c>
-      <c r="M9" t="n">
-        <v>47562.9</v>
-      </c>
-      <c r="N9" t="n">
-        <v>37096.55</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.588734076349424</v>
-      </c>
-      <c r="P9" t="n">
-        <v>-0.424621828582076</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>-0.3632329470265668</v>
-      </c>
-      <c r="R9" t="n">
-        <v>-0.0613888815555092</v>
-      </c>
-      <c r="S9" t="n">
-        <v>-0.09862728893130679</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-0.09382140051007476</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="F10" t="n">
+        <v>23.79999923706055</v>
+      </c>
+      <c r="G10" t="n">
+        <v>23.75500011444092</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>47.7045159065304</v>
+      </c>
+      <c r="J10" t="n">
+        <v>38.10309742449107</v>
+      </c>
+      <c r="K10" t="n">
+        <v>45.0966480340583</v>
+      </c>
+      <c r="L10" t="n">
+        <v>88506.39999999999</v>
+      </c>
+      <c r="M10" t="n">
+        <v>57935.95</v>
+      </c>
+      <c r="N10" t="n">
+        <v>50397.8</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.527659423898288</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.3177555371091323</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.4233434055365411</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.1055878684274088</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.09719899678842436</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.05677269545327979</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>70</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>4205</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>中華食</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>72.69999694824219</v>
+      </c>
+      <c r="G11" t="n">
+        <v>72.94999923706055</v>
+      </c>
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>43.68951835042044</v>
+      </c>
+      <c r="J11" t="n">
+        <v>31.3488072515399</v>
+      </c>
+      <c r="K11" t="n">
+        <v>35.99822659093533</v>
+      </c>
+      <c r="L11" t="n">
+        <v>55972.2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>36975.75</v>
+      </c>
+      <c r="N11" t="n">
+        <v>36000.175</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.513754284902943</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0.6787686738851448</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-0.7840756720936249</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.1053069982084801</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.081920208678679</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.04954381224512627</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN11"/>
+  <dimension ref="A1:AN6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,12 +629,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>2430</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>佳格</t>
+          <t>燦坤</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,49 +643,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>28.45000076293945</v>
+        <v>18.89999961853027</v>
       </c>
       <c r="G2" t="n">
-        <v>28.4</v>
+        <v>18.69249973297119</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>42.70047904409716</v>
+        <v>43.93109423298996</v>
       </c>
       <c r="J2" t="n">
-        <v>30.45723882755896</v>
+        <v>41.64773893963157</v>
       </c>
       <c r="K2" t="n">
-        <v>47.89197630680934</v>
+        <v>45.53030500795521</v>
       </c>
       <c r="L2" t="n">
-        <v>4127956.2</v>
+        <v>371188.6</v>
       </c>
       <c r="M2" t="n">
-        <v>1801661.75</v>
+        <v>210457</v>
       </c>
       <c r="N2" t="n">
-        <v>1414942.275</v>
+        <v>177017.425</v>
       </c>
       <c r="O2" t="n">
-        <v>2.291193782628731</v>
+        <v>1.763726556968882</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2813860957459724</v>
+        <v>-0.3685263794508202</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.3374831210657638</v>
+        <v>-0.5584607044829673</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05609702531979138</v>
+        <v>0.189934325032147</v>
       </c>
       <c r="S2" t="n">
-        <v>0.03093974712155295</v>
+        <v>0.1987038000682595</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.001581374479297626</v>
+        <v>0.1845262566180147</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -723,44 +723,44 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>1320.764</v>
+        <v>-49.331</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>8.308</v>
+        <v>-2.744</v>
       </c>
       <c r="AE2" t="n">
-        <v>1329.072</v>
+        <v>-52.075</v>
       </c>
       <c r="AF2" t="n">
-        <v>8088.138</v>
+        <v>79.81899999999999</v>
       </c>
       <c r="AG2" t="n">
-        <v>-677</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-22.12</v>
+        <v>-4</v>
       </c>
       <c r="AI2" t="n">
-        <v>7389.018</v>
+        <v>75.81899999999999</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4001.300999999999</v>
+        <v>-49.38100000000001</v>
       </c>
       <c r="AK2" t="n">
-        <v>-670</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-16.735</v>
+        <v>-27</v>
       </c>
       <c r="AM2" t="n">
-        <v>3314.566</v>
+        <v>-76.38100000000001</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -775,12 +775,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2430</t>
+          <t>1453</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>燦坤</t>
+          <t>大將</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,49 +789,49 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>19.10000038146973</v>
+        <v>11.39999961853027</v>
       </c>
       <c r="G3" t="n">
-        <v>18.74249973297119</v>
+        <v>11.3300000667572</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>47.81152978685318</v>
+        <v>45.62387320097024</v>
       </c>
       <c r="J3" t="n">
-        <v>40.5060613118503</v>
+        <v>42.18376526765744</v>
       </c>
       <c r="K3" t="n">
-        <v>48.15055028184459</v>
+        <v>47.77687248417627</v>
       </c>
       <c r="L3" t="n">
-        <v>368310.8</v>
+        <v>114385.4</v>
       </c>
       <c r="M3" t="n">
-        <v>209385.2</v>
+        <v>72149.7</v>
       </c>
       <c r="N3" t="n">
-        <v>174633.95</v>
+        <v>80151.72500000001</v>
       </c>
       <c r="O3" t="n">
-        <v>1.759010665510265</v>
+        <v>1.585389821440699</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4072404856727445</v>
+        <v>-0.09546530821330457</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.605944285741004</v>
+        <v>-0.1521925027141774</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1987038000682595</v>
+        <v>0.05672719450087288</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1845262566180147</v>
+        <v>0.0613241628025227</v>
       </c>
       <c r="T3" t="n">
-        <v>0.08982804037501868</v>
+        <v>0.05576761961014465</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -869,44 +869,44 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>-30.85</v>
+        <v>7</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
         <v>-1</v>
       </c>
-      <c r="AE3" t="n">
-        <v>-31.85</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>134.15</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>-1.256</v>
-      </c>
       <c r="AI3" t="n">
-        <v>132.894</v>
+        <v>37</v>
       </c>
       <c r="AJ3" t="n">
-        <v>29.94999999999998</v>
+        <v>17.82</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-23.256</v>
+        <v>-5</v>
       </c>
       <c r="AM3" t="n">
-        <v>6.694000000000006</v>
+        <v>12.82</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -935,49 +935,49 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>86.80000305175781</v>
+        <v>87.59999847412109</v>
       </c>
       <c r="G4" t="n">
-        <v>91.6699993133545</v>
+        <v>91.15499916076661</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>39.19431037919734</v>
+        <v>41.28105217293556</v>
       </c>
       <c r="J4" t="n">
-        <v>36.72131036570929</v>
+        <v>38.24122434066709</v>
       </c>
       <c r="K4" t="n">
-        <v>34.66494459709743</v>
+        <v>36.32550472327315</v>
       </c>
       <c r="L4" t="n">
-        <v>136965.2</v>
+        <v>136404.8</v>
       </c>
       <c r="M4" t="n">
-        <v>50373.85</v>
+        <v>50613.75</v>
       </c>
       <c r="N4" t="n">
-        <v>37006.975</v>
+        <v>37066.925</v>
       </c>
       <c r="O4" t="n">
-        <v>2.718974229684648</v>
+        <v>2.695014694623497</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.367645831778376</v>
+        <v>-2.379702862500665</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.015893076317685</v>
+        <v>-2.102373753200013</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.3517527554606907</v>
+        <v>-0.277329109300652</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.322263467850266</v>
+        <v>-0.3463237043997833</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2609453764034098</v>
+        <v>-0.316410597741148</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1021,38 +1021,38 @@
         <v>0</v>
       </c>
       <c r="AD4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE4" t="n">
         <v>-3</v>
       </c>
-      <c r="AE4" t="n">
-        <v>-5</v>
-      </c>
       <c r="AF4" t="n">
-        <v>4.024000000000001</v>
+        <v>-4.975999999999999</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="AI4" t="n">
-        <v>-2.975999999999999</v>
+        <v>-12.976</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-46.92</v>
+        <v>-30.92</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="AM4" t="n">
-        <v>-51.92</v>
+        <v>-38.92</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -1067,63 +1067,63 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1454</t>
+          <t>5481</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>台富</t>
+          <t>新華</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>12.94999980926514</v>
+        <v>18.70000076293945</v>
       </c>
       <c r="G5" t="n">
-        <v>13.02999992370605</v>
+        <v>19.34250001907349</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>35.51799186917036</v>
+        <v>41.36787758903554</v>
       </c>
       <c r="J5" t="n">
-        <v>31.58959187776733</v>
+        <v>33.60453429983754</v>
       </c>
       <c r="K5" t="n">
-        <v>48.48860145952712</v>
+        <v>35.77837373465761</v>
       </c>
       <c r="L5" t="n">
-        <v>147533.6</v>
+        <v>370235.8</v>
       </c>
       <c r="M5" t="n">
-        <v>83153.45</v>
+        <v>178256.5</v>
       </c>
       <c r="N5" t="n">
-        <v>105154.2</v>
+        <v>191556.925</v>
       </c>
       <c r="O5" t="n">
-        <v>1.774233059482198</v>
+        <v>2.076983448008908</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1008374039801723</v>
+        <v>-0.657390527375977</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.122255586615181</v>
+        <v>-0.6645005984792816</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02141818263500869</v>
+        <v>0.007110071103304527</v>
       </c>
       <c r="S5" t="n">
-        <v>0.017699903203477</v>
+        <v>-0.02083435951813273</v>
       </c>
       <c r="T5" t="n">
-        <v>0.007052420709859453</v>
+        <v>-0.06416626306943773</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1161,44 +1161,44 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-23</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>-18</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-34.88999999999999</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>-39.89</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -1227,49 +1227,49 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>16.5</v>
+        <v>16.20000076293945</v>
       </c>
       <c r="G6" t="n">
-        <v>16.17250003814697</v>
+        <v>16.13500003814697</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>47.5401337616258</v>
+        <v>45.58232133271802</v>
       </c>
       <c r="J6" t="n">
-        <v>35.78311657627271</v>
+        <v>39.0495181985931</v>
       </c>
       <c r="K6" t="n">
-        <v>48.18327580940343</v>
+        <v>42.22898643483769</v>
       </c>
       <c r="L6" t="n">
-        <v>404341.8</v>
+        <v>396880</v>
       </c>
       <c r="M6" t="n">
-        <v>234512.65</v>
+        <v>242297.1</v>
       </c>
       <c r="N6" t="n">
-        <v>245074.675</v>
+        <v>250766.95</v>
       </c>
       <c r="O6" t="n">
-        <v>1.724179058144625</v>
+        <v>1.637989063839394</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4375292484602262</v>
+        <v>-0.3994488775174254</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.5971766713588368</v>
+        <v>-0.556259244114832</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1596474228986106</v>
+        <v>0.1568103665974065</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1281589836302228</v>
+        <v>0.1591045191732017</v>
       </c>
       <c r="T6" t="n">
-        <v>0.08155943233396423</v>
+        <v>0.1275736981077752</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1344,737 +1344,7 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>70</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>4528</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>江興鍛</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>15.80000019073486</v>
-      </c>
-      <c r="G7" t="n">
-        <v>15.67249999046326</v>
-      </c>
-      <c r="H7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>48.34155765968328</v>
-      </c>
-      <c r="J7" t="n">
-        <v>38.13034704286068</v>
-      </c>
-      <c r="K7" t="n">
-        <v>48.790469457928</v>
-      </c>
-      <c r="L7" t="n">
-        <v>75104.39999999999</v>
-      </c>
-      <c r="M7" t="n">
-        <v>44668.45</v>
-      </c>
-      <c r="N7" t="n">
-        <v>51968.45</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.681374661534036</v>
-      </c>
-      <c r="P7" t="n">
-        <v>-0.1855324987710443</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>-0.2644571031931351</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.07892460442209082</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.06688101778201871</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.046205984945208</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>70</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>8066</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>來思達</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>16</v>
-      </c>
-      <c r="G8" t="n">
-        <v>16.33499989509583</v>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>46.00748191220891</v>
-      </c>
-      <c r="J8" t="n">
-        <v>35.39217967646054</v>
-      </c>
-      <c r="K8" t="n">
-        <v>40.88986092758873</v>
-      </c>
-      <c r="L8" t="n">
-        <v>146651.4</v>
-      </c>
-      <c r="M8" t="n">
-        <v>91282.45</v>
-      </c>
-      <c r="N8" t="n">
-        <v>79082.325</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.606567308392796</v>
-      </c>
-      <c r="P8" t="n">
-        <v>-0.4520961776443571</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>-0.4980455770628352</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.04594939941847814</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.03893142422144868</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.006435323613740551</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>70</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2642</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>宅配通</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>20.79999923706055</v>
-      </c>
-      <c r="G9" t="n">
-        <v>20.75000009536743</v>
-      </c>
-      <c r="H9" t="b">
-        <v>1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>39.22382213932451</v>
-      </c>
-      <c r="J9" t="n">
-        <v>37.39508237934427</v>
-      </c>
-      <c r="K9" t="n">
-        <v>44.27696587086676</v>
-      </c>
-      <c r="L9" t="n">
-        <v>196725.6</v>
-      </c>
-      <c r="M9" t="n">
-        <v>127717.05</v>
-      </c>
-      <c r="N9" t="n">
-        <v>102327.9</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.540323707758674</v>
-      </c>
-      <c r="P9" t="n">
-        <v>-0.3374190812929569</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>-0.4544885704016338</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.1170694891086768</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.1125041355017533</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.1333927114902366</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>-66</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>-65</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>-23.18</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>-26.18</v>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>70</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1599</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>宏佳騰</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>23.79999923706055</v>
-      </c>
-      <c r="G10" t="n">
-        <v>23.75500011444092</v>
-      </c>
-      <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>47.7045159065304</v>
-      </c>
-      <c r="J10" t="n">
-        <v>38.10309742449107</v>
-      </c>
-      <c r="K10" t="n">
-        <v>45.0966480340583</v>
-      </c>
-      <c r="L10" t="n">
-        <v>88506.39999999999</v>
-      </c>
-      <c r="M10" t="n">
-        <v>57935.95</v>
-      </c>
-      <c r="N10" t="n">
-        <v>50397.8</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.527659423898288</v>
-      </c>
-      <c r="P10" t="n">
-        <v>-0.3177555371091323</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-0.4233434055365411</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.1055878684274088</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.09719899678842436</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.05677269545327979</v>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>70</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>4205</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>中華食</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>72.69999694824219</v>
-      </c>
-      <c r="G11" t="n">
-        <v>72.94999923706055</v>
-      </c>
-      <c r="H11" t="b">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>43.68951835042044</v>
-      </c>
-      <c r="J11" t="n">
-        <v>31.3488072515399</v>
-      </c>
-      <c r="K11" t="n">
-        <v>35.99822659093533</v>
-      </c>
-      <c r="L11" t="n">
-        <v>55972.2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>36975.75</v>
-      </c>
-      <c r="N11" t="n">
-        <v>36000.175</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.513754284902943</v>
-      </c>
-      <c r="P11" t="n">
-        <v>-0.6787686738851448</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>-0.7840756720936249</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.1053069982084801</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.081920208678679</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.04954381224512627</v>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN6"/>
+  <dimension ref="A1:AN7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,12 +629,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2430</t>
+          <t>6657</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>燦坤</t>
+          <t>華安</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,49 +643,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>18.89999961853027</v>
+        <v>37.25</v>
       </c>
       <c r="G2" t="n">
-        <v>18.69249973297119</v>
+        <v>39.11999969482422</v>
       </c>
       <c r="H2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>43.93109423298996</v>
+        <v>48.23392254485769</v>
       </c>
       <c r="J2" t="n">
-        <v>41.64773893963157</v>
+        <v>47.48763368841567</v>
       </c>
       <c r="K2" t="n">
-        <v>45.53030500795521</v>
+        <v>36.44513148295969</v>
       </c>
       <c r="L2" t="n">
-        <v>371188.6</v>
+        <v>454174.4</v>
       </c>
       <c r="M2" t="n">
-        <v>210457</v>
+        <v>269407.95</v>
       </c>
       <c r="N2" t="n">
-        <v>177017.425</v>
+        <v>324633.125</v>
       </c>
       <c r="O2" t="n">
-        <v>1.763726556968882</v>
+        <v>1.68582404491033</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.3685263794508202</v>
+        <v>-0.8386148065908827</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.5584607044829673</v>
+        <v>-0.8874776637612403</v>
       </c>
       <c r="R2" t="n">
-        <v>0.189934325032147</v>
+        <v>0.04886285717035754</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1987038000682595</v>
+        <v>0.1590998175318074</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1845262566180147</v>
+        <v>0.1871213546418596</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -723,19 +723,19 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>-49.331</v>
+        <v>23</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-2.744</v>
+        <v>-2</v>
       </c>
       <c r="AE2" t="n">
-        <v>-52.075</v>
+        <v>21</v>
       </c>
       <c r="AF2" t="n">
-        <v>79.81899999999999</v>
+        <v>211.875</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -744,23 +744,23 @@
         <v>-4</v>
       </c>
       <c r="AI2" t="n">
-        <v>75.81899999999999</v>
+        <v>207.875</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-49.38100000000001</v>
+        <v>626.833</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-27</v>
+        <v>-1.983</v>
       </c>
       <c r="AM2" t="n">
-        <v>-76.38100000000001</v>
+        <v>624.8499999999999</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -771,16 +771,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>4994</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>大將</t>
+          <t>傳奇</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,49 +789,49 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>11.39999961853027</v>
+        <v>90</v>
       </c>
       <c r="G3" t="n">
-        <v>11.3300000667572</v>
+        <v>90.7549991607666</v>
       </c>
       <c r="H3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>45.62387320097024</v>
+        <v>49.41418759015679</v>
       </c>
       <c r="J3" t="n">
-        <v>42.18376526765744</v>
+        <v>41.96554549092117</v>
       </c>
       <c r="K3" t="n">
-        <v>47.77687248417627</v>
+        <v>44.34730294585901</v>
       </c>
       <c r="L3" t="n">
-        <v>114385.4</v>
+        <v>136961.2</v>
       </c>
       <c r="M3" t="n">
-        <v>72149.7</v>
+        <v>52522.85</v>
       </c>
       <c r="N3" t="n">
-        <v>80151.72500000001</v>
+        <v>37896.475</v>
       </c>
       <c r="O3" t="n">
-        <v>1.585389821440699</v>
+        <v>2.607649813366944</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.09546530821330457</v>
+        <v>-2.135203226909098</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1521925027141774</v>
+        <v>-2.075843491889656</v>
       </c>
       <c r="R3" t="n">
-        <v>0.05672719450087288</v>
+        <v>-0.05935973501944236</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0613241628025227</v>
+        <v>-0.2904207141576243</v>
       </c>
       <c r="T3" t="n">
-        <v>0.05576761961014465</v>
+        <v>-0.3604362458452988</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -869,44 +869,44 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>8</v>
+        <v>-10</v>
       </c>
       <c r="AF3" t="n">
-        <v>38</v>
+        <v>-21.976</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-1</v>
+        <v>-9</v>
       </c>
       <c r="AI3" t="n">
-        <v>37</v>
+        <v>-30.976</v>
       </c>
       <c r="AJ3" t="n">
-        <v>17.82</v>
+        <v>-42.168</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="AM3" t="n">
-        <v>12.82</v>
+        <v>-50.168</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -921,63 +921,63 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>傳奇</t>
+          <t>佰研</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>87.59999847412109</v>
+        <v>53.40000152587891</v>
       </c>
       <c r="G4" t="n">
-        <v>91.15499916076661</v>
+        <v>53.83999977111817</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>41.28105217293556</v>
+        <v>41.89793101644387</v>
       </c>
       <c r="J4" t="n">
-        <v>38.24122434066709</v>
+        <v>37.8294484205405</v>
       </c>
       <c r="K4" t="n">
-        <v>36.32550472327315</v>
+        <v>45.97851845310236</v>
       </c>
       <c r="L4" t="n">
-        <v>136404.8</v>
+        <v>586123.2</v>
       </c>
       <c r="M4" t="n">
-        <v>50613.75</v>
+        <v>261432.45</v>
       </c>
       <c r="N4" t="n">
-        <v>37066.925</v>
+        <v>314059.25</v>
       </c>
       <c r="O4" t="n">
-        <v>2.695014694623497</v>
+        <v>2.241968049490413</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.379702862500665</v>
+        <v>-0.4387106464567765</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.102373753200013</v>
+        <v>-0.696168525937965</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.277329109300652</v>
+        <v>0.2574578794811885</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3463237043997833</v>
+        <v>0.3670618232023699</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.316410597741148</v>
+        <v>0.1455655534077085</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1015,44 +1015,44 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>-4.975999999999999</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>-12.976</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-30.92</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-38.92</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5481</t>
+          <t>6169</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>新華</t>
+          <t>昱泉</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1081,49 +1081,49 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>18.70000076293945</v>
+        <v>14.05000019073486</v>
       </c>
       <c r="G5" t="n">
-        <v>19.34250001907349</v>
+        <v>14.54749994277954</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>41.36787758903554</v>
+        <v>44.54185980338613</v>
       </c>
       <c r="J5" t="n">
-        <v>33.60453429983754</v>
+        <v>43.73706180874539</v>
       </c>
       <c r="K5" t="n">
-        <v>35.77837373465761</v>
+        <v>40.9055942433514</v>
       </c>
       <c r="L5" t="n">
-        <v>370235.8</v>
+        <v>140498.2</v>
       </c>
       <c r="M5" t="n">
-        <v>178256.5</v>
+        <v>65502.6</v>
       </c>
       <c r="N5" t="n">
-        <v>191556.925</v>
+        <v>46033.85</v>
       </c>
       <c r="O5" t="n">
-        <v>2.076983448008908</v>
+        <v>2.144925544940201</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.657390527375977</v>
+        <v>-0.4422985523167675</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.6645005984792816</v>
+        <v>-0.5278394198046646</v>
       </c>
       <c r="R5" t="n">
-        <v>0.007110071103304527</v>
+        <v>0.08554086748789713</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.02083435951813273</v>
+        <v>0.1156854337568125</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.06416626306943773</v>
+        <v>0.1264566266386838</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1213,138 +1213,284 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>7786</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>益得</t>
+          <t>東方風能</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>120</v>
+      </c>
+      <c r="G6" t="n">
+        <v>121.125</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>47.90338694890366</v>
+      </c>
+      <c r="J6" t="n">
+        <v>43.47284532781605</v>
+      </c>
+      <c r="K6" t="n">
+        <v>45.72741588468298</v>
+      </c>
+      <c r="L6" t="n">
+        <v>530752.4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>349408.1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>282007.525</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.519004281812586</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-3.066409311844339</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-4.0399462266611</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.9735369148167612</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.022041836492109</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.5671614509183183</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>-10.785</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-14.032</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-24.817</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-269.651</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-7.588000000000001</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-277.239</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-819.0269999999999</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>6.135999999999999</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-812.891</v>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>70</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>5516</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>雙喜</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>16.20000076293945</v>
-      </c>
-      <c r="G6" t="n">
-        <v>16.13500003814697</v>
-      </c>
-      <c r="H6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>45.58232133271802</v>
-      </c>
-      <c r="J6" t="n">
-        <v>39.0495181985931</v>
-      </c>
-      <c r="K6" t="n">
-        <v>42.22898643483769</v>
-      </c>
-      <c r="L6" t="n">
-        <v>396880</v>
-      </c>
-      <c r="M6" t="n">
-        <v>242297.1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>250766.95</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.637989063839394</v>
-      </c>
-      <c r="P6" t="n">
-        <v>-0.3994488775174254</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>-0.556259244114832</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.1568103665974065</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.1591045191732017</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.1275736981077752</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
+      <c r="F7" t="n">
+        <v>10.55000019073486</v>
+      </c>
+      <c r="G7" t="n">
+        <v>10.66749992370606</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>49.0821392126364</v>
+      </c>
+      <c r="J7" t="n">
+        <v>41.41519074093148</v>
+      </c>
+      <c r="K7" t="n">
+        <v>43.95793472736887</v>
+      </c>
+      <c r="L7" t="n">
+        <v>104872.2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>69848.55</v>
+      </c>
+      <c r="N7" t="n">
+        <v>62720</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.501422721015683</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0.2630757505814856</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.3501163636367127</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.08704061305522709</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.0931839266683403</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.07514630703918956</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN7"/>
+  <dimension ref="A1:AN8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,67 +625,67 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6657</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>華安</t>
+          <t>坤悅</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>37.25</v>
+        <v>22.70000076293945</v>
       </c>
       <c r="G2" t="n">
-        <v>39.11999969482422</v>
+        <v>22.51750030517578</v>
       </c>
       <c r="H2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>48.23392254485769</v>
+        <v>49.56208307089824</v>
       </c>
       <c r="J2" t="n">
-        <v>47.48763368841567</v>
+        <v>41.05015733609949</v>
       </c>
       <c r="K2" t="n">
-        <v>36.44513148295969</v>
+        <v>46.57882622184603</v>
       </c>
       <c r="L2" t="n">
-        <v>454174.4</v>
+        <v>405383.2</v>
       </c>
       <c r="M2" t="n">
-        <v>269407.95</v>
+        <v>168725.35</v>
       </c>
       <c r="N2" t="n">
-        <v>324633.125</v>
+        <v>183357.15</v>
       </c>
       <c r="O2" t="n">
-        <v>1.68582404491033</v>
+        <v>2.402621775566031</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.8386148065908827</v>
+        <v>-0.47634560205368</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.8874776637612403</v>
+        <v>-0.711479251691279</v>
       </c>
       <c r="R2" t="n">
-        <v>0.04886285717035754</v>
+        <v>0.235133649637599</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1590998175318074</v>
+        <v>0.2366879446668704</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1871213546418596</v>
+        <v>0.2000304764321771</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -723,44 +723,44 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>211.875</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>207.875</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>626.833</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-1.983</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>624.8499999999999</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -775,63 +775,63 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>傳奇</t>
+          <t>佰研</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>90</v>
+        <v>54.29999923706055</v>
       </c>
       <c r="G3" t="n">
-        <v>90.7549991607666</v>
+        <v>53.81499977111817</v>
       </c>
       <c r="H3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>49.41418759015679</v>
+        <v>39.62026784392873</v>
       </c>
       <c r="J3" t="n">
-        <v>41.96554549092117</v>
+        <v>38.42638822833658</v>
       </c>
       <c r="K3" t="n">
-        <v>44.34730294585901</v>
+        <v>49.00830804922018</v>
       </c>
       <c r="L3" t="n">
-        <v>136961.2</v>
+        <v>627466</v>
       </c>
       <c r="M3" t="n">
-        <v>52522.85</v>
+        <v>262975.3</v>
       </c>
       <c r="N3" t="n">
-        <v>37896.475</v>
+        <v>309528.65</v>
       </c>
       <c r="O3" t="n">
-        <v>2.607649813366944</v>
+        <v>2.386026368255878</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.135203226909098</v>
+        <v>-0.3973604379384881</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.075843491889656</v>
+        <v>-0.6364069083380697</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.05935973501944236</v>
+        <v>0.2390464703995816</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2904207141576243</v>
+        <v>0.2574578794811885</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3604362458452988</v>
+        <v>0.3670618232023699</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -878,35 +878,35 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-21.976</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-30.976</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-42.168</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-50.168</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3205</t>
+          <t>5489</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>佰研</t>
+          <t>彩富</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,49 +935,49 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>53.40000152587891</v>
+        <v>39.5</v>
       </c>
       <c r="G4" t="n">
-        <v>53.83999977111817</v>
+        <v>39.62250022888183</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>41.89793101644387</v>
+        <v>31.47206753430038</v>
       </c>
       <c r="J4" t="n">
-        <v>37.8294484205405</v>
+        <v>30.47203012706148</v>
       </c>
       <c r="K4" t="n">
-        <v>45.97851845310236</v>
+        <v>47.76473443296115</v>
       </c>
       <c r="L4" t="n">
-        <v>586123.2</v>
+        <v>179741.6</v>
       </c>
       <c r="M4" t="n">
-        <v>261432.45</v>
+        <v>84825.85000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>314059.25</v>
+        <v>72338.8</v>
       </c>
       <c r="O4" t="n">
-        <v>2.241968049490413</v>
+        <v>2.118948410183924</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4387106464567765</v>
+        <v>-0.1976992478151374</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.696168525937965</v>
+        <v>-0.2447703601888435</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2574578794811885</v>
+        <v>0.04707111237370612</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3670618232023699</v>
+        <v>0.04802760145645735</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1455655534077085</v>
+        <v>0.08490445447493489</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6169</t>
+          <t>8342</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>昱泉</t>
+          <t>益張</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1081,49 +1081,49 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>14.05000019073486</v>
+        <v>88.80000305175781</v>
       </c>
       <c r="G5" t="n">
-        <v>14.54749994277954</v>
+        <v>89.94000091552735</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>44.54185980338613</v>
+        <v>45.39323411482518</v>
       </c>
       <c r="J5" t="n">
-        <v>43.73706180874539</v>
+        <v>32.47156325564245</v>
       </c>
       <c r="K5" t="n">
-        <v>40.9055942433514</v>
+        <v>46.74278669232523</v>
       </c>
       <c r="L5" t="n">
-        <v>140498.2</v>
+        <v>8600.4</v>
       </c>
       <c r="M5" t="n">
-        <v>65502.6</v>
+        <v>4763.8</v>
       </c>
       <c r="N5" t="n">
-        <v>46033.85</v>
+        <v>3911</v>
       </c>
       <c r="O5" t="n">
-        <v>2.144925544940201</v>
+        <v>1.805365464545111</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4422985523167675</v>
+        <v>-0.2690607812624677</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.5278394198046646</v>
+        <v>0.03877321562990499</v>
       </c>
       <c r="R5" t="n">
-        <v>0.08554086748789713</v>
+        <v>-0.3078339968923727</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1156854337568125</v>
+        <v>-0.3695185833727235</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1264566266386838</v>
+        <v>-0.3776201865060355</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -1213,63 +1213,63 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>7786</t>
+          <t>6593</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>東方風能</t>
+          <t>台灣銘板</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>120</v>
+        <v>35</v>
       </c>
       <c r="G6" t="n">
-        <v>121.125</v>
+        <v>35.08999996185302</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>47.90338694890366</v>
+        <v>42.63984663852767</v>
       </c>
       <c r="J6" t="n">
-        <v>43.47284532781605</v>
+        <v>38.03311570625984</v>
       </c>
       <c r="K6" t="n">
-        <v>45.72741588468298</v>
+        <v>41.9571599325965</v>
       </c>
       <c r="L6" t="n">
-        <v>530752.4</v>
+        <v>144111.4</v>
       </c>
       <c r="M6" t="n">
-        <v>349408.1</v>
+        <v>85304</v>
       </c>
       <c r="N6" t="n">
-        <v>282007.525</v>
+        <v>82569.72500000001</v>
       </c>
       <c r="O6" t="n">
-        <v>1.519004281812586</v>
+        <v>1.689386195254619</v>
       </c>
       <c r="P6" t="n">
-        <v>-3.066409311844339</v>
+        <v>-0.3106740437898594</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.0399462266611</v>
+        <v>-0.3927849178286458</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9735369148167612</v>
+        <v>0.08211087403878642</v>
       </c>
       <c r="S6" t="n">
-        <v>1.022041836492109</v>
+        <v>0.08728499680721585</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5671614509183183</v>
+        <v>0.1044333577483981</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1307,44 +1307,44 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>-10.785</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>-14.032</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-24.817</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>-269.651</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-7.588000000000001</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>-277.239</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-819.0269999999999</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>6.135999999999999</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>-812.891</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5516</t>
+          <t>5364</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>雙喜</t>
+          <t>力麗店</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1373,49 +1373,49 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>10.55000019073486</v>
+        <v>8.699999809265137</v>
       </c>
       <c r="G7" t="n">
-        <v>10.66749992370606</v>
+        <v>8.925999927520753</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>49.0821392126364</v>
+        <v>48.33076973582943</v>
       </c>
       <c r="J7" t="n">
-        <v>41.41519074093148</v>
+        <v>45.85940416672328</v>
       </c>
       <c r="K7" t="n">
-        <v>43.95793472736887</v>
+        <v>33.74275475835844</v>
       </c>
       <c r="L7" t="n">
-        <v>104872.2</v>
+        <v>273972.4</v>
       </c>
       <c r="M7" t="n">
-        <v>69848.55</v>
+        <v>166171.1</v>
       </c>
       <c r="N7" t="n">
-        <v>62720</v>
+        <v>171907.575</v>
       </c>
       <c r="O7" t="n">
-        <v>1.501422721015683</v>
+        <v>1.648736753863939</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2630757505814856</v>
+        <v>-0.385542084249531</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.3501163636367127</v>
+        <v>-0.4410244291791163</v>
       </c>
       <c r="R7" t="n">
-        <v>0.08704061305522709</v>
+        <v>0.05548234492958531</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0931839266683403</v>
+        <v>0.0512932570265221</v>
       </c>
       <c r="T7" t="n">
-        <v>0.07514630703918956</v>
+        <v>0.06730004790648886</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1490,7 +1490,153 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>70</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>6547</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>高端疫苗</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>47.09999847412109</v>
+      </c>
+      <c r="G8" t="n">
+        <v>47.26750011444092</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>49.8791158416001</v>
+      </c>
+      <c r="J8" t="n">
+        <v>44.61777417371113</v>
+      </c>
+      <c r="K8" t="n">
+        <v>48.95917267427256</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3435026.2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2270195.35</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2455981.775</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.513097187869758</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0.2976810025627543</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.5655982026743352</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.2679172001115809</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.3301747850550898</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.2481811169154329</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN8"/>
+  <dimension ref="A1:AN4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,12 +629,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5206</t>
+          <t>5489</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>坤悅</t>
+          <t>彩富</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,49 +643,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>22.70000076293945</v>
+        <v>39.65000152587891</v>
       </c>
       <c r="G2" t="n">
-        <v>22.51750030517578</v>
+        <v>39.59500026702881</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>49.56208307089824</v>
+        <v>32.2263663972151</v>
       </c>
       <c r="J2" t="n">
-        <v>41.05015733609949</v>
+        <v>31.05680888110216</v>
       </c>
       <c r="K2" t="n">
-        <v>46.57882622184603</v>
+        <v>48.89330371494039</v>
       </c>
       <c r="L2" t="n">
-        <v>405383.2</v>
+        <v>175646.4</v>
       </c>
       <c r="M2" t="n">
-        <v>168725.35</v>
+        <v>85164.3</v>
       </c>
       <c r="N2" t="n">
-        <v>183357.15</v>
+        <v>71326.89999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>2.402621775566031</v>
+        <v>2.062441656891444</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.47634560205368</v>
+        <v>-0.1786281028242627</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.711479251691279</v>
+        <v>-0.2361148152645066</v>
       </c>
       <c r="R2" t="n">
-        <v>0.235133649637599</v>
+        <v>0.05748671244024395</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2366879446668704</v>
+        <v>0.04888079606067314</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2000304764321771</v>
+        <v>0.04997855815948915</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
@@ -775,12 +775,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3205</t>
+          <t>6593</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>佰研</t>
+          <t>台灣銘板</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,49 +789,49 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>54.29999923706055</v>
+        <v>34.34999847412109</v>
       </c>
       <c r="G3" t="n">
-        <v>53.81499977111817</v>
+        <v>35.04499988555908</v>
       </c>
       <c r="H3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>39.62026784392873</v>
+        <v>39.39146790193372</v>
       </c>
       <c r="J3" t="n">
-        <v>38.42638822833658</v>
+        <v>38.48589979755828</v>
       </c>
       <c r="K3" t="n">
-        <v>49.00830804922018</v>
+        <v>34.11489999848106</v>
       </c>
       <c r="L3" t="n">
-        <v>627466</v>
+        <v>156165</v>
       </c>
       <c r="M3" t="n">
-        <v>262975.3</v>
+        <v>89021.35000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>309528.65</v>
+        <v>84653.14999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>2.386026368255878</v>
+        <v>1.754242100350085</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3973604379384881</v>
+        <v>-0.3458709445145089</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.6364069083380697</v>
+        <v>-0.3820302372458474</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2390464703995816</v>
+        <v>0.03615929273133844</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2574578794811885</v>
+        <v>0.08156796340998118</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3670618232023699</v>
+        <v>0.08669970384246323</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5489</t>
+          <t>6547</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>彩富</t>
+          <t>高端疫苗</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,49 +935,49 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>39.5</v>
+        <v>47.15000152587891</v>
       </c>
       <c r="G4" t="n">
-        <v>39.62250022888183</v>
+        <v>47.23000011444092</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>31.47206753430038</v>
+        <v>46.44719753479642</v>
       </c>
       <c r="J4" t="n">
-        <v>30.47203012706148</v>
+        <v>45.22758191790395</v>
       </c>
       <c r="K4" t="n">
-        <v>47.76473443296115</v>
+        <v>48.28755624889432</v>
       </c>
       <c r="L4" t="n">
-        <v>179741.6</v>
+        <v>3422494</v>
       </c>
       <c r="M4" t="n">
-        <v>84825.85000000001</v>
+        <v>2280600.6</v>
       </c>
       <c r="N4" t="n">
-        <v>72338.8</v>
+        <v>2333143.25</v>
       </c>
       <c r="O4" t="n">
-        <v>2.118948410183924</v>
+        <v>1.500698544058964</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1976992478151374</v>
+        <v>-0.2992639710793767</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2447703601888435</v>
+        <v>-0.528336529275332</v>
       </c>
       <c r="R4" t="n">
-        <v>0.04707111237370612</v>
+        <v>0.2290725581959553</v>
       </c>
       <c r="S4" t="n">
-        <v>0.04802760145645735</v>
+        <v>0.2742510930159665</v>
       </c>
       <c r="T4" t="n">
-        <v>0.08490445447493489</v>
+        <v>0.3370031335157094</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1052,591 +1052,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>70</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>8342</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>益張</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>88.80000305175781</v>
-      </c>
-      <c r="G5" t="n">
-        <v>89.94000091552735</v>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>45.39323411482518</v>
-      </c>
-      <c r="J5" t="n">
-        <v>32.47156325564245</v>
-      </c>
-      <c r="K5" t="n">
-        <v>46.74278669232523</v>
-      </c>
-      <c r="L5" t="n">
-        <v>8600.4</v>
-      </c>
-      <c r="M5" t="n">
-        <v>4763.8</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3911</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.805365464545111</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-0.2690607812624677</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.03877321562990499</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-0.3078339968923727</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-0.3695185833727235</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-0.3776201865060355</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>70</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>6593</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>台灣銘板</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>35</v>
-      </c>
-      <c r="G6" t="n">
-        <v>35.08999996185302</v>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>42.63984663852767</v>
-      </c>
-      <c r="J6" t="n">
-        <v>38.03311570625984</v>
-      </c>
-      <c r="K6" t="n">
-        <v>41.9571599325965</v>
-      </c>
-      <c r="L6" t="n">
-        <v>144111.4</v>
-      </c>
-      <c r="M6" t="n">
-        <v>85304</v>
-      </c>
-      <c r="N6" t="n">
-        <v>82569.72500000001</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.689386195254619</v>
-      </c>
-      <c r="P6" t="n">
-        <v>-0.3106740437898594</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>-0.3927849178286458</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.08211087403878642</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.08728499680721585</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.1044333577483981</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>70</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>5364</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>力麗店</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>8.699999809265137</v>
-      </c>
-      <c r="G7" t="n">
-        <v>8.925999927520753</v>
-      </c>
-      <c r="H7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>48.33076973582943</v>
-      </c>
-      <c r="J7" t="n">
-        <v>45.85940416672328</v>
-      </c>
-      <c r="K7" t="n">
-        <v>33.74275475835844</v>
-      </c>
-      <c r="L7" t="n">
-        <v>273972.4</v>
-      </c>
-      <c r="M7" t="n">
-        <v>166171.1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>171907.575</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.648736753863939</v>
-      </c>
-      <c r="P7" t="n">
-        <v>-0.385542084249531</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>-0.4410244291791163</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.05548234492958531</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.0512932570265221</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.06730004790648886</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>70</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>6547</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>高端疫苗</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>47.09999847412109</v>
-      </c>
-      <c r="G8" t="n">
-        <v>47.26750011444092</v>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>49.8791158416001</v>
-      </c>
-      <c r="J8" t="n">
-        <v>44.61777417371113</v>
-      </c>
-      <c r="K8" t="n">
-        <v>48.95917267427256</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3435026.2</v>
-      </c>
-      <c r="M8" t="n">
-        <v>2270195.35</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2455981.775</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.513097187869758</v>
-      </c>
-      <c r="P8" t="n">
-        <v>-0.2976810025627543</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>-0.5655982026743352</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.2679172001115809</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.3301747850550898</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.2481811169154329</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN4"/>
+  <dimension ref="A1:AN3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,12 +629,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5489</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>彩富</t>
+          <t>鑫傳</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,49 +643,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>39.65000152587891</v>
+        <v>47.75</v>
       </c>
       <c r="G2" t="n">
-        <v>39.59500026702881</v>
+        <v>50.20500030517578</v>
       </c>
       <c r="H2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>32.2263663972151</v>
+        <v>32.51156942766821</v>
       </c>
       <c r="J2" t="n">
-        <v>31.05680888110216</v>
+        <v>30.51031957486133</v>
       </c>
       <c r="K2" t="n">
-        <v>48.89330371494039</v>
+        <v>35.56059160326961</v>
       </c>
       <c r="L2" t="n">
-        <v>175646.4</v>
+        <v>13678</v>
       </c>
       <c r="M2" t="n">
-        <v>85164.3</v>
+        <v>7925.6</v>
       </c>
       <c r="N2" t="n">
-        <v>71326.89999999999</v>
+        <v>7013.35</v>
       </c>
       <c r="O2" t="n">
-        <v>2.062441656891444</v>
+        <v>1.725799939436762</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1786281028242627</v>
+        <v>-0.8262017048961141</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2361148152645066</v>
+        <v>-0.5261117514327959</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05748671244024395</v>
+        <v>-0.3000899534633182</v>
       </c>
       <c r="S2" t="n">
-        <v>0.04888079606067314</v>
+        <v>-0.2980204193991607</v>
       </c>
       <c r="T2" t="n">
-        <v>0.04997855815948915</v>
+        <v>-0.2886864747842579</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
@@ -775,12 +775,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6593</t>
+          <t>7718</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>台灣銘板</t>
+          <t>友鋮</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,49 +789,49 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>34.34999847412109</v>
+        <v>47.5</v>
       </c>
       <c r="G3" t="n">
-        <v>35.04499988555908</v>
+        <v>48.86750030517578</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>39.39146790193372</v>
+        <v>39.15628437147686</v>
       </c>
       <c r="J3" t="n">
-        <v>38.48589979755828</v>
+        <v>38.90057916177011</v>
       </c>
       <c r="K3" t="n">
-        <v>34.11489999848106</v>
+        <v>41.82005727883203</v>
       </c>
       <c r="L3" t="n">
-        <v>156165</v>
+        <v>64715.8</v>
       </c>
       <c r="M3" t="n">
-        <v>89021.35000000001</v>
+        <v>38996.6</v>
       </c>
       <c r="N3" t="n">
-        <v>84653.14999999999</v>
+        <v>32582.275</v>
       </c>
       <c r="O3" t="n">
-        <v>1.754242100350085</v>
+        <v>1.659524163645036</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3458709445145089</v>
+        <v>-0.08762641522721282</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.3820302372458474</v>
+        <v>0.1457590297054071</v>
       </c>
       <c r="R3" t="n">
-        <v>0.03615929273133844</v>
+        <v>-0.2333854449326199</v>
       </c>
       <c r="S3" t="n">
-        <v>0.08156796340998118</v>
+        <v>-0.1976510199168298</v>
       </c>
       <c r="T3" t="n">
-        <v>0.08669970384246323</v>
+        <v>-0.08634893411821609</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -906,153 +906,7 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>70</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>6547</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>高端疫苗</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>47.15000152587891</v>
-      </c>
-      <c r="G4" t="n">
-        <v>47.23000011444092</v>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>46.44719753479642</v>
-      </c>
-      <c r="J4" t="n">
-        <v>45.22758191790395</v>
-      </c>
-      <c r="K4" t="n">
-        <v>48.28755624889432</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3422494</v>
-      </c>
-      <c r="M4" t="n">
-        <v>2280600.6</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2333143.25</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.500698544058964</v>
-      </c>
-      <c r="P4" t="n">
-        <v>-0.2992639710793767</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-0.528336529275332</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.2290725581959553</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.2742510930159665</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.3370031335157094</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -625,142 +625,142 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>鑫傳</t>
+          <t>安集</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>47.75</v>
+        <v>33.5</v>
       </c>
       <c r="G2" t="n">
-        <v>50.20500030517578</v>
+        <v>33.77999992370606</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>32.51156942766821</v>
+        <v>45.93094003822335</v>
       </c>
       <c r="J2" t="n">
-        <v>30.51031957486133</v>
+        <v>39.38220963413819</v>
       </c>
       <c r="K2" t="n">
-        <v>35.56059160326961</v>
+        <v>48.3553431899218</v>
       </c>
       <c r="L2" t="n">
-        <v>13678</v>
+        <v>1636587.8</v>
       </c>
       <c r="M2" t="n">
-        <v>7925.6</v>
+        <v>928309.15</v>
       </c>
       <c r="N2" t="n">
-        <v>7013.35</v>
+        <v>893872.375</v>
       </c>
       <c r="O2" t="n">
-        <v>1.725799939436762</v>
+        <v>1.762977128901509</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.8262017048961141</v>
+        <v>-0.3434542758359385</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.5261117514327959</v>
+        <v>-0.2989248497698769</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.3000899534633182</v>
+        <v>-0.04452942606606153</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2980204193991607</v>
+        <v>-0.08932201721597877</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2886864747842579</v>
+        <v>-0.1847661273012042</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>205.94</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>-1.478</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>204.462</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>104.265</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>-1.239</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>103.026</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>922.6650000000001</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>-3.2</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>919.4650000000001</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
@@ -775,12 +775,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>7718</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>友鋮</t>
+          <t>鑫傳</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,49 +789,49 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>47.5</v>
+        <v>47.84999847412109</v>
       </c>
       <c r="G3" t="n">
-        <v>48.86750030517578</v>
+        <v>50.16000022888183</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>39.15628437147686</v>
+        <v>34.00770277989817</v>
       </c>
       <c r="J3" t="n">
-        <v>38.90057916177011</v>
+        <v>31.67611398858777</v>
       </c>
       <c r="K3" t="n">
-        <v>41.82005727883203</v>
+        <v>36.36857870566983</v>
       </c>
       <c r="L3" t="n">
-        <v>64715.8</v>
+        <v>14800</v>
       </c>
       <c r="M3" t="n">
-        <v>38996.6</v>
+        <v>7656.1</v>
       </c>
       <c r="N3" t="n">
-        <v>32582.275</v>
+        <v>7028.55</v>
       </c>
       <c r="O3" t="n">
-        <v>1.659524163645036</v>
+        <v>1.933099097451705</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.08762641522721282</v>
+        <v>-0.869208947270117</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1457590297054071</v>
+        <v>-0.5947311906002601</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.2333854449326199</v>
+        <v>-0.2744777566698569</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1976510199168298</v>
+        <v>-0.3000899534633182</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.08634893411821609</v>
+        <v>-0.2980204193991607</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN3"/>
+  <dimension ref="A1:AN4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -646,46 +646,46 @@
         <v>33.5</v>
       </c>
       <c r="G2" t="n">
-        <v>33.77999992370606</v>
+        <v>33.75</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>45.93094003822335</v>
+        <v>48.8898639318913</v>
       </c>
       <c r="J2" t="n">
-        <v>39.38220963413819</v>
+        <v>42.5514278170123</v>
       </c>
       <c r="K2" t="n">
-        <v>48.3553431899218</v>
+        <v>48.80148103837539</v>
       </c>
       <c r="L2" t="n">
-        <v>1636587.8</v>
+        <v>1576696</v>
       </c>
       <c r="M2" t="n">
-        <v>928309.15</v>
+        <v>941582.3</v>
       </c>
       <c r="N2" t="n">
-        <v>893872.375</v>
+        <v>899536.425</v>
       </c>
       <c r="O2" t="n">
-        <v>1.762977128901509</v>
+        <v>1.674517458537613</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.3434542758359385</v>
+        <v>-0.3034886538637096</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2989248497698769</v>
+        <v>-0.2876090844994929</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.04452942606606153</v>
+        <v>-0.01587956936421669</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.08932201721597877</v>
+        <v>-0.04936443548768987</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1847661273012042</v>
+        <v>-0.09453369449432447</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -723,44 +723,44 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>205.94</v>
+        <v>-15.359</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-1.478</v>
+        <v>0.62</v>
       </c>
       <c r="AE2" t="n">
-        <v>204.462</v>
+        <v>-14.739</v>
       </c>
       <c r="AF2" t="n">
-        <v>104.265</v>
+        <v>400.581</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-1.239</v>
+        <v>1.086</v>
       </c>
       <c r="AI2" t="n">
-        <v>103.026</v>
+        <v>401.6669999999999</v>
       </c>
       <c r="AJ2" t="n">
-        <v>922.6650000000001</v>
+        <v>916.3059999999999</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-3.2</v>
+        <v>1.420000000000001</v>
       </c>
       <c r="AM2" t="n">
-        <v>919.4650000000001</v>
+        <v>917.7259999999999</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -771,142 +771,288 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>80</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2540</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>愛山林</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>53.825</v>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>49.42698243836027</v>
+      </c>
+      <c r="J3" t="n">
+        <v>44.19657487040523</v>
+      </c>
+      <c r="K3" t="n">
+        <v>49.74683975980418</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1899768.2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1117498.8</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1428361.125</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.700018111876272</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-0.1530275614791279</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-0.05984423606986143</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-0.09318332540926645</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-0.145192230627172</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-0.1645860205946665</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>258.575</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>35</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>293.575</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>323.978</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>18.99999999999999</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>342.978</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>-504.174</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>-510.244</v>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>70</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>6856</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>鑫傳</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>47.84999847412109</v>
-      </c>
-      <c r="G3" t="n">
-        <v>50.16000022888183</v>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>34.00770277989817</v>
-      </c>
-      <c r="J3" t="n">
-        <v>31.67611398858777</v>
-      </c>
-      <c r="K3" t="n">
-        <v>36.36857870566983</v>
-      </c>
-      <c r="L3" t="n">
-        <v>14800</v>
-      </c>
-      <c r="M3" t="n">
-        <v>7656.1</v>
-      </c>
-      <c r="N3" t="n">
-        <v>7028.55</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.933099097451705</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-0.869208947270117</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-0.5947311906002601</v>
-      </c>
-      <c r="R3" t="n">
-        <v>-0.2744777566698569</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-0.3000899534633182</v>
-      </c>
-      <c r="T3" t="n">
-        <v>-0.2980204193991607</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>8940</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>新天地</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>16.60000038146973</v>
+      </c>
+      <c r="G4" t="n">
+        <v>16.71000013351441</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>43.61168416887877</v>
+      </c>
+      <c r="J4" t="n">
+        <v>38.93331554199742</v>
+      </c>
+      <c r="K4" t="n">
+        <v>44.49113514683137</v>
+      </c>
+      <c r="L4" t="n">
+        <v>113447.2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>75101.45</v>
+      </c>
+      <c r="N4" t="n">
+        <v>74897.575</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.510586013985083</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0.2249054618111188</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0.26436561017806</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.03946014836694123</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.03812917346101502</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.02153279906338917</v>
+      </c>
+      <c r="U4" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
+      <c r="AB4" t="n">
+        <v>-27.42</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-25.42</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-61.42</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-62.42</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-1.420000000000002</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-11.42</v>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN4"/>
+  <dimension ref="A1:AN2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,67 +625,67 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>2947</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>安集</t>
+          <t>振宇五金</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>33.5</v>
+        <v>76.90000152587891</v>
       </c>
       <c r="G2" t="n">
-        <v>33.75</v>
+        <v>77.26000022888184</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>48.8898639318913</v>
+        <v>41.15883650652769</v>
       </c>
       <c r="J2" t="n">
-        <v>42.5514278170123</v>
+        <v>34.26154523170184</v>
       </c>
       <c r="K2" t="n">
-        <v>48.80148103837539</v>
+        <v>42.88715301291573</v>
       </c>
       <c r="L2" t="n">
-        <v>1576696</v>
+        <v>23371.4</v>
       </c>
       <c r="M2" t="n">
-        <v>941582.3</v>
+        <v>15459.3</v>
       </c>
       <c r="N2" t="n">
-        <v>899536.425</v>
+        <v>14493.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.674517458537613</v>
+        <v>1.511801957397813</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.3034886538637096</v>
+        <v>-0.3668452842943566</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2876090844994929</v>
+        <v>-0.3377881564643266</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.01587956936421669</v>
+        <v>-0.02905712783003001</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.04936443548768987</v>
+        <v>-0.06244463068346318</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.09453369449432447</v>
+        <v>-0.1158642748601105</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -723,336 +723,44 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>-15.359</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-14.739</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>400.581</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.086</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>401.6669999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>916.3059999999999</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.420000000000001</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>917.7259999999999</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>80</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2540</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>愛山林</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="G3" t="n">
-        <v>53.825</v>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>49.42698243836027</v>
-      </c>
-      <c r="J3" t="n">
-        <v>44.19657487040523</v>
-      </c>
-      <c r="K3" t="n">
-        <v>49.74683975980418</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1899768.2</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1117498.8</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1428361.125</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.700018111876272</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-0.1530275614791279</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-0.05984423606986143</v>
-      </c>
-      <c r="R3" t="n">
-        <v>-0.09318332540926645</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-0.145192230627172</v>
-      </c>
-      <c r="T3" t="n">
-        <v>-0.1645860205946665</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>258.575</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>35</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>293.575</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>323.978</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>18.99999999999999</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>342.978</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>-504.174</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>-6.07</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>-510.244</v>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>70</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>8940</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>新天地</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>16.60000038146973</v>
-      </c>
-      <c r="G4" t="n">
-        <v>16.71000013351441</v>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>43.61168416887877</v>
-      </c>
-      <c r="J4" t="n">
-        <v>38.93331554199742</v>
-      </c>
-      <c r="K4" t="n">
-        <v>44.49113514683137</v>
-      </c>
-      <c r="L4" t="n">
-        <v>113447.2</v>
-      </c>
-      <c r="M4" t="n">
-        <v>75101.45</v>
-      </c>
-      <c r="N4" t="n">
-        <v>74897.575</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.510586013985083</v>
-      </c>
-      <c r="P4" t="n">
-        <v>-0.2249054618111188</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-0.26436561017806</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.03946014836694123</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.03812917346101502</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.02153279906338917</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>-27.42</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-25.42</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>-61.42</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>-62.42</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>-1.420000000000002</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>-10</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>-11.42</v>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN2"/>
+  <dimension ref="A1:AN1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -615,152 +615,6 @@
       <c r="AN1" t="inlineStr">
         <is>
           <t>最後更新日期</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>80</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2947</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>振宇五金</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>76.90000152587891</v>
-      </c>
-      <c r="G2" t="n">
-        <v>77.26000022888184</v>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>41.15883650652769</v>
-      </c>
-      <c r="J2" t="n">
-        <v>34.26154523170184</v>
-      </c>
-      <c r="K2" t="n">
-        <v>42.88715301291573</v>
-      </c>
-      <c r="L2" t="n">
-        <v>23371.4</v>
-      </c>
-      <c r="M2" t="n">
-        <v>15459.3</v>
-      </c>
-      <c r="N2" t="n">
-        <v>14493.3</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.511801957397813</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-0.3668452842943566</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-0.3377881564643266</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-0.02905712783003001</v>
-      </c>
-      <c r="S2" t="n">
-        <v>-0.06244463068346318</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-0.1158642748601105</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN1"/>
+  <dimension ref="A1:AN3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -615,6 +615,298 @@
       <c r="AN1" t="inlineStr">
         <is>
           <t>最後更新日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1626</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>艾美特-KY</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>9.739999771118164</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10.01500000953674</v>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>43.86414856973533</v>
+      </c>
+      <c r="J2" t="n">
+        <v>42.46141370031113</v>
+      </c>
+      <c r="K2" t="n">
+        <v>35.76365726641802</v>
+      </c>
+      <c r="L2" t="n">
+        <v>400095.4</v>
+      </c>
+      <c r="M2" t="n">
+        <v>202083.55</v>
+      </c>
+      <c r="N2" t="n">
+        <v>154320.425</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.979851403045919</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-0.10226688565999</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-0.1090349690101657</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.006768083350175702</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.02701064825044457</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.03524001011999191</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>-37</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-39</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>243.201</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>241.201</v>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>70</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3010</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>華立</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>135.25</v>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>48.60103615971278</v>
+      </c>
+      <c r="J3" t="n">
+        <v>40.01355101611611</v>
+      </c>
+      <c r="K3" t="n">
+        <v>46.50857039583591</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2439945.8</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1557519.35</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1592513.025</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.566558900215268</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-1.067583853413282</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-0.3912328352364578</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-0.6763510181768244</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-0.8625500273763637</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-1.033341243135873</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>245.071</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-791</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-0.765</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-546.694</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-234.11</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-3344.357</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>19.998</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-3558.469</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1941.882</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-3940.896</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>-69.31999999999998</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>-2068.334</v>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN3"/>
+  <dimension ref="A1:AN2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,16 +625,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1626</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>艾美特-KY</t>
+          <t>華立</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,49 +643,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9.739999771118164</v>
+        <v>126.5</v>
       </c>
       <c r="G2" t="n">
-        <v>10.01500000953674</v>
+        <v>134.575</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>43.86414856973533</v>
+        <v>41.0963429470549</v>
       </c>
       <c r="J2" t="n">
-        <v>42.46141370031113</v>
+        <v>40.37448165976237</v>
       </c>
       <c r="K2" t="n">
-        <v>35.76365726641802</v>
+        <v>38.76999205217571</v>
       </c>
       <c r="L2" t="n">
-        <v>400095.4</v>
+        <v>2763540.4</v>
       </c>
       <c r="M2" t="n">
-        <v>202083.55</v>
+        <v>1622093.5</v>
       </c>
       <c r="N2" t="n">
-        <v>154320.425</v>
+        <v>1601868.725</v>
       </c>
       <c r="O2" t="n">
-        <v>1.979851403045919</v>
+        <v>1.703687487805111</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.10226688565999</v>
+        <v>-1.44087180086666</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1090349690101657</v>
+        <v>-0.6011606283624982</v>
       </c>
       <c r="R2" t="n">
-        <v>0.006768083350175702</v>
+        <v>-0.8397111725041615</v>
       </c>
       <c r="S2" t="n">
-        <v>0.02701064825044457</v>
+        <v>-0.6763510181768244</v>
       </c>
       <c r="T2" t="n">
-        <v>0.03524001011999191</v>
+        <v>-0.8625500273763637</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -723,190 +723,44 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>-37</v>
+        <v>361.061</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>-791</v>
       </c>
       <c r="AD2" t="n">
-        <v>-2</v>
+        <v>6.619</v>
       </c>
       <c r="AE2" t="n">
-        <v>-39</v>
+        <v>-423.3200000000001</v>
       </c>
       <c r="AF2" t="n">
-        <v>13</v>
+        <v>526.885</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>-3983.357</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>26.194</v>
       </c>
       <c r="AI2" t="n">
-        <v>13</v>
+        <v>-3430.278</v>
       </c>
       <c r="AJ2" t="n">
-        <v>243.201</v>
+        <v>1833.923</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>-4726.896</v>
       </c>
       <c r="AL2" t="n">
-        <v>-2</v>
+        <v>-71.85399999999998</v>
       </c>
       <c r="AM2" t="n">
-        <v>241.201</v>
+        <v>-2964.826999999999</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>70</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>3010</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>華立</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>131.5</v>
-      </c>
-      <c r="G3" t="n">
-        <v>135.25</v>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>48.60103615971278</v>
-      </c>
-      <c r="J3" t="n">
-        <v>40.01355101611611</v>
-      </c>
-      <c r="K3" t="n">
-        <v>46.50857039583591</v>
-      </c>
-      <c r="L3" t="n">
-        <v>2439945.8</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1557519.35</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1592513.025</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.566558900215268</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-1.067583853413282</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-0.3912328352364578</v>
-      </c>
-      <c r="R3" t="n">
-        <v>-0.6763510181768244</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-0.8625500273763637</v>
-      </c>
-      <c r="T3" t="n">
-        <v>-1.033341243135873</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>245.071</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-791</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>-0.765</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>-546.694</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>-234.11</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>-3344.357</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>19.998</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>-3558.469</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1941.882</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>-3940.896</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>-69.31999999999998</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>-2068.334</v>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN2"/>
+  <dimension ref="A1:AN4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,138 +629,430 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3010</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>華立</t>
+          <t>鑫傳</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>45.95000076293945</v>
+      </c>
+      <c r="G2" t="n">
+        <v>48.20499973297119</v>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>33.95151972105479</v>
+      </c>
+      <c r="J2" t="n">
+        <v>33.35924283431917</v>
+      </c>
+      <c r="K2" t="n">
+        <v>34.08459195908574</v>
+      </c>
+      <c r="L2" t="n">
+        <v>36034.8</v>
+      </c>
+      <c r="M2" t="n">
+        <v>16859.95</v>
+      </c>
+      <c r="N2" t="n">
+        <v>11832.9</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.13730171204541</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-1.311620327883062</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-1.062406663708308</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-0.2492136641747544</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-0.3097425256823452</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-0.3658608780645324</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>70</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1626</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>艾美特-KY</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>126.5</v>
-      </c>
-      <c r="G2" t="n">
-        <v>134.575</v>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>41.0963429470549</v>
-      </c>
-      <c r="J2" t="n">
-        <v>40.37448165976237</v>
-      </c>
-      <c r="K2" t="n">
-        <v>38.76999205217571</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2763540.4</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1622093.5</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1601868.725</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.703687487805111</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-1.44087180086666</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-0.6011606283624982</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-0.8397111725041615</v>
-      </c>
-      <c r="S2" t="n">
-        <v>-0.6763510181768244</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-0.8625500273763637</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
+      <c r="F3" t="n">
+        <v>9.859999656677246</v>
+      </c>
+      <c r="G3" t="n">
+        <v>10.00000004768372</v>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>43.49517544987539</v>
+      </c>
+      <c r="J3" t="n">
+        <v>42.53519486599292</v>
+      </c>
+      <c r="K3" t="n">
+        <v>41.55475034237789</v>
+      </c>
+      <c r="L3" t="n">
+        <v>405441</v>
+      </c>
+      <c r="M3" t="n">
+        <v>204160.35</v>
+      </c>
+      <c r="N3" t="n">
+        <v>151490.075</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.985894910544579</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-0.1137616932464773</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-0.1111469467774085</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-0.002614746469068813</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-0.003170637129906145</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.00697837464015072</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>361.061</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-791</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>6.619</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-423.3200000000001</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>526.885</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-3983.357</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>26.194</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-3430.278</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1833.923</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-4726.896</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-71.85399999999998</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-2964.826999999999</v>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-39</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-41</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>187.701</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>185.701</v>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>70</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>6843</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>進典</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>40.20000076293945</v>
+      </c>
+      <c r="G4" t="n">
+        <v>40.73250045776367</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>32.49357934914509</v>
+      </c>
+      <c r="J4" t="n">
+        <v>30.37047399689968</v>
+      </c>
+      <c r="K4" t="n">
+        <v>40.5616696805584</v>
+      </c>
+      <c r="L4" t="n">
+        <v>75368.39999999999</v>
+      </c>
+      <c r="M4" t="n">
+        <v>45805.15</v>
+      </c>
+      <c r="N4" t="n">
+        <v>32306.875</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.645413234101405</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0.934375678514229</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-1.101593407975757</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.1672177294615285</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.1656109749964423</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.1607367814589606</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -625,105 +625,105 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>鑫傳</t>
+          <t>艾美特-KY</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>45.95000076293945</v>
+        <v>9.850000381469727</v>
       </c>
       <c r="G2" t="n">
-        <v>48.20499973297119</v>
+        <v>9.99000005722046</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>33.95151972105479</v>
+        <v>44.55235614621216</v>
       </c>
       <c r="J2" t="n">
-        <v>33.35924283431917</v>
+        <v>43.2075820179977</v>
       </c>
       <c r="K2" t="n">
-        <v>34.08459195908574</v>
+        <v>40.17293592193362</v>
       </c>
       <c r="L2" t="n">
-        <v>36034.8</v>
+        <v>376062.6</v>
       </c>
       <c r="M2" t="n">
-        <v>16859.95</v>
+        <v>192316.3</v>
       </c>
       <c r="N2" t="n">
-        <v>11832.9</v>
+        <v>151818.05</v>
       </c>
       <c r="O2" t="n">
-        <v>2.13730171204541</v>
+        <v>1.955437994595362</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.311620327883062</v>
+        <v>-0.113730193876977</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.062406663708308</v>
+        <v>-0.11215708240841</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.2492136641747544</v>
+        <v>-0.001573111468567062</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3097425256823452</v>
+        <v>-0.002419650054535177</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3658608780645324</v>
+        <v>-0.00296034583993178</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -732,35 +732,35 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>-64</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>-69</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>149.201</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>147.201</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
@@ -771,16 +771,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1626</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>艾美特-KY</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,49 +789,49 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>9.859999656677246</v>
+        <v>221</v>
       </c>
       <c r="G3" t="n">
-        <v>10.00000004768372</v>
+        <v>221.775</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>43.49517544987539</v>
+        <v>41.2847654100989</v>
       </c>
       <c r="J3" t="n">
-        <v>42.53519486599292</v>
+        <v>36.25664396664991</v>
       </c>
       <c r="K3" t="n">
-        <v>41.55475034237789</v>
+        <v>47.40521727989535</v>
       </c>
       <c r="L3" t="n">
-        <v>405441</v>
+        <v>5519525.8</v>
       </c>
       <c r="M3" t="n">
-        <v>204160.35</v>
+        <v>3169366.35</v>
       </c>
       <c r="N3" t="n">
-        <v>151490.075</v>
+        <v>2928729.7</v>
       </c>
       <c r="O3" t="n">
-        <v>1.985894910544579</v>
+        <v>1.741523443637243</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1137616932464773</v>
+        <v>-0.9956640915312107</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1111469467774085</v>
+        <v>-0.5141556913639472</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.002614746469068813</v>
+        <v>-0.4815084001672635</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.003170637129906145</v>
+        <v>-0.847180189651653</v>
       </c>
       <c r="T3" t="n">
-        <v>0.00697837464015072</v>
+        <v>-0.9467374220480388</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -860,53 +860,53 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
       <c r="AB3" t="n">
-        <v>15.5</v>
+        <v>2757.191</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>-1519.329</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>99.604</v>
       </c>
       <c r="AE3" t="n">
-        <v>15.5</v>
+        <v>1337.466</v>
       </c>
       <c r="AF3" t="n">
-        <v>-39</v>
+        <v>11918.669</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>-8524.519999999999</v>
       </c>
       <c r="AH3" t="n">
-        <v>-2</v>
+        <v>111.72</v>
       </c>
       <c r="AI3" t="n">
-        <v>-41</v>
+        <v>3505.869000000002</v>
       </c>
       <c r="AJ3" t="n">
-        <v>187.701</v>
+        <v>12747.814</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>-9424.659</v>
       </c>
       <c r="AL3" t="n">
-        <v>-2</v>
+        <v>210.466</v>
       </c>
       <c r="AM3" t="n">
-        <v>185.701</v>
+        <v>3533.621000000001</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6843</t>
+          <t>7747</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>進典</t>
+          <t>昕奇雲端</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,49 +935,49 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>40.20000076293945</v>
+        <v>126.5</v>
       </c>
       <c r="G4" t="n">
-        <v>40.73250045776367</v>
+        <v>127.5</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>32.49357934914509</v>
+        <v>48.19581283401691</v>
       </c>
       <c r="J4" t="n">
-        <v>30.37047399689968</v>
+        <v>41.32633806673255</v>
       </c>
       <c r="K4" t="n">
-        <v>40.5616696805584</v>
+        <v>45.36215680836818</v>
       </c>
       <c r="L4" t="n">
-        <v>75368.39999999999</v>
+        <v>74423</v>
       </c>
       <c r="M4" t="n">
-        <v>45805.15</v>
+        <v>23517.7</v>
       </c>
       <c r="N4" t="n">
-        <v>32306.875</v>
+        <v>14685</v>
       </c>
       <c r="O4" t="n">
-        <v>1.645413234101405</v>
+        <v>3.164552656084566</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.934375678514229</v>
+        <v>-0.3790571428254026</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.101593407975757</v>
+        <v>-0.1752060398541185</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1672177294615285</v>
+        <v>-0.2038511029712841</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1656109749964423</v>
+        <v>-0.2391556418141103</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1607367814589606</v>
+        <v>-0.2227640549018121</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN4"/>
+  <dimension ref="A1:AN9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,12 +629,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1626</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>艾美特-KY</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,53 +643,53 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9.850000381469727</v>
+        <v>216</v>
       </c>
       <c r="G2" t="n">
-        <v>9.99000005722046</v>
+        <v>221.7</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>44.55235614621216</v>
+        <v>39.28788282534036</v>
       </c>
       <c r="J2" t="n">
-        <v>43.2075820179977</v>
+        <v>37.26705697310731</v>
       </c>
       <c r="K2" t="n">
-        <v>40.17293592193362</v>
+        <v>45.66666742471189</v>
       </c>
       <c r="L2" t="n">
-        <v>376062.6</v>
+        <v>5248520.6</v>
       </c>
       <c r="M2" t="n">
-        <v>192316.3</v>
+        <v>3190787.75</v>
       </c>
       <c r="N2" t="n">
-        <v>151818.05</v>
+        <v>2951282.475</v>
       </c>
       <c r="O2" t="n">
-        <v>1.955437994595362</v>
+        <v>1.644898066316069</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.113730193876977</v>
+        <v>-1.019111664119492</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.11215708240841</v>
+        <v>-0.3980137813325751</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.001573111468567062</v>
+        <v>-0.6210978827869172</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.002419650054535177</v>
+        <v>-0.5673504951006927</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.00296034583993178</v>
+        <v>-0.9397080042745439</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -723,44 +723,44 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>-14</v>
+        <v>-692.676</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>37.016</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>62.668</v>
       </c>
       <c r="AE2" t="n">
-        <v>-14</v>
+        <v>-592.9920000000001</v>
       </c>
       <c r="AF2" t="n">
-        <v>-64</v>
+        <v>8393.762000000001</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>-6331.043</v>
       </c>
       <c r="AH2" t="n">
-        <v>-5</v>
+        <v>199.357</v>
       </c>
       <c r="AI2" t="n">
-        <v>-69</v>
+        <v>2262.076000000001</v>
       </c>
       <c r="AJ2" t="n">
-        <v>149.201</v>
+        <v>10968.377</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>-10146.285</v>
       </c>
       <c r="AL2" t="n">
-        <v>-2</v>
+        <v>226.7410000000001</v>
       </c>
       <c r="AM2" t="n">
-        <v>147.201</v>
+        <v>1048.833000000001</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
     </row>
@@ -771,67 +771,67 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>7747</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>昕奇雲端</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>221</v>
+        <v>125</v>
       </c>
       <c r="G3" t="n">
-        <v>221.775</v>
+        <v>127.375</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>41.2847654100989</v>
+        <v>45.46387522236502</v>
       </c>
       <c r="J3" t="n">
-        <v>36.25664396664991</v>
+        <v>42.70551711287312</v>
       </c>
       <c r="K3" t="n">
-        <v>47.40521727989535</v>
+        <v>39.86747534352981</v>
       </c>
       <c r="L3" t="n">
-        <v>5519525.8</v>
+        <v>73651</v>
       </c>
       <c r="M3" t="n">
-        <v>3169366.35</v>
+        <v>23524.7</v>
       </c>
       <c r="N3" t="n">
-        <v>2928729.7</v>
+        <v>14613.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.741523443637243</v>
+        <v>3.130794441586928</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9956640915312107</v>
+        <v>-0.498850473389723</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.5141556913639472</v>
+        <v>-0.2300652399893083</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.4815084001672635</v>
+        <v>-0.2687852334004147</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.847180189651653</v>
+        <v>-0.2077530163773583</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9467374220480388</v>
+        <v>-0.2433614515697038</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -869,44 +869,44 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>2757.191</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1519.329</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>99.604</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1337.466</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>11918.669</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>-8524.519999999999</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>111.72</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>3505.869000000002</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>12747.814</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-9424.659</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>210.466</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>3533.621000000001</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>7747</t>
+          <t>4609</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>唐鋒</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,49 +935,49 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>126.5</v>
+        <v>4.909999847412109</v>
       </c>
       <c r="G4" t="n">
-        <v>127.5</v>
+        <v>5.41000006198883</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>48.19581283401691</v>
+        <v>33.69347665863555</v>
       </c>
       <c r="J4" t="n">
-        <v>41.32633806673255</v>
+        <v>31.08188979822615</v>
       </c>
       <c r="K4" t="n">
-        <v>45.36215680836818</v>
+        <v>44.76132897182725</v>
       </c>
       <c r="L4" t="n">
-        <v>74423</v>
+        <v>56235</v>
       </c>
       <c r="M4" t="n">
-        <v>23517.7</v>
+        <v>24811.55</v>
       </c>
       <c r="N4" t="n">
-        <v>14685</v>
+        <v>24039</v>
       </c>
       <c r="O4" t="n">
-        <v>3.164552656084566</v>
+        <v>2.266484762136989</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3790571428254026</v>
+        <v>-0.09858047730009023</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1752060398541185</v>
+        <v>-0.01165262539956409</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.2038511029712841</v>
+        <v>-0.08692785190052614</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2391556418141103</v>
+        <v>-0.08898465364791064</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2227640549018121</v>
+        <v>-0.1226432072121286</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1052,7 +1052,737 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>5603</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>陸海</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>14.85000038146973</v>
+      </c>
+      <c r="G5" t="n">
+        <v>15.14000000953674</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>35.73880075628365</v>
+      </c>
+      <c r="J5" t="n">
+        <v>31.19372956976095</v>
+      </c>
+      <c r="K5" t="n">
+        <v>35.64893735146021</v>
+      </c>
+      <c r="L5" t="n">
+        <v>718914.6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>363318.6</v>
+      </c>
+      <c r="N5" t="n">
+        <v>273110.125</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.978744275685308</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.2257887488406496</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.2279467279210073</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.002157979080357753</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.003141132016776349</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.002411328976094668</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>70</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1626</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>艾美特-KY</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>9.819999694824219</v>
+      </c>
+      <c r="G6" t="n">
+        <v>9.982500028610229</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>43.9237794244708</v>
+      </c>
+      <c r="J6" t="n">
+        <v>43.44631451386736</v>
+      </c>
+      <c r="K6" t="n">
+        <v>40.23341814503665</v>
+      </c>
+      <c r="L6" t="n">
+        <v>334622.8</v>
+      </c>
+      <c r="M6" t="n">
+        <v>184610.65</v>
+      </c>
+      <c r="N6" t="n">
+        <v>147984.35</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.812586651961845</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.113300289793747</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.1109052746646763</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-0.002395015129070616</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.002158396991014055</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.003050519913483069</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>-21</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-21</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-92.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-94.5</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>77.70099999999999</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>72.70099999999999</v>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>70</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>6877</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>鏵友益</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>126</v>
+      </c>
+      <c r="G7" t="n">
+        <v>140.325</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>40.13314862091228</v>
+      </c>
+      <c r="J7" t="n">
+        <v>38.99086726577946</v>
+      </c>
+      <c r="K7" t="n">
+        <v>38.03013118716348</v>
+      </c>
+      <c r="L7" t="n">
+        <v>667846.2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>373161.3</v>
+      </c>
+      <c r="N7" t="n">
+        <v>509917.925</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.789698449437281</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-6.728648676174885</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-6.514697244276862</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-0.2139514318980229</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.06359375351806129</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0.626751223516119</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>70</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>8234</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>新漢</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>65.69999694824219</v>
+      </c>
+      <c r="G8" t="n">
+        <v>67.11499996185303</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>45.81075127370538</v>
+      </c>
+      <c r="J8" t="n">
+        <v>43.34682079316966</v>
+      </c>
+      <c r="K8" t="n">
+        <v>47.61805764857557</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2419894.8</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1371085.7</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1586663.425</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.764947880354963</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0.4465129087681703</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.6731480174863729</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.2266351087182026</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.3314511768984876</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.0946650480798632</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>70</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>8917</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>欣泰</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>52.29999923706055</v>
+      </c>
+      <c r="G9" t="n">
+        <v>52.26999988555908</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>42.94721807491817</v>
+      </c>
+      <c r="J9" t="n">
+        <v>35.33252242285303</v>
+      </c>
+      <c r="K9" t="n">
+        <v>48.71006899262635</v>
+      </c>
+      <c r="L9" t="n">
+        <v>50255.4</v>
+      </c>
+      <c r="M9" t="n">
+        <v>31225.65</v>
+      </c>
+      <c r="N9" t="n">
+        <v>26688</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.60942686541353</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0.02605784056438409</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-0.1154068133154568</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.0893489727510727</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.1222059065902618</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.09513753835054276</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN3"/>
+  <dimension ref="A1:AN2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,12 +629,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>2756</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>雄順</t>
+          <t>聯發國際</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,49 +643,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>26.10000038146973</v>
+        <v>59.70000076293945</v>
       </c>
       <c r="G2" t="n">
-        <v>26.04250020980835</v>
+        <v>60.01999988555908</v>
       </c>
       <c r="H2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>32.96758622802362</v>
+        <v>47.87330915245003</v>
       </c>
       <c r="J2" t="n">
-        <v>32.83921566488988</v>
+        <v>46.95488765956902</v>
       </c>
       <c r="K2" t="n">
-        <v>49.46447116107288</v>
+        <v>42.9527502263377</v>
       </c>
       <c r="L2" t="n">
-        <v>26804.6</v>
+        <v>133704.8</v>
       </c>
       <c r="M2" t="n">
-        <v>8651.35</v>
+        <v>61838.4</v>
       </c>
       <c r="N2" t="n">
-        <v>6635.175</v>
+        <v>45739.725</v>
       </c>
       <c r="O2" t="n">
-        <v>3.098314135944101</v>
+        <v>2.162164609692359</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1341016700005291</v>
+        <v>-0.6840245166553274</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01764936897374835</v>
+        <v>-0.8286633935943704</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1164523010267807</v>
+        <v>0.144638876939043</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1739645843597489</v>
+        <v>0.1481447680853475</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1647943044180916</v>
+        <v>0.1641092648588223</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -760,153 +760,7 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>70</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>4609</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>唐鋒</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>5.090000152587891</v>
-      </c>
-      <c r="G3" t="n">
-        <v>5.367000079154968</v>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>38.07078457540857</v>
-      </c>
-      <c r="J3" t="n">
-        <v>33.41152126578527</v>
-      </c>
-      <c r="K3" t="n">
-        <v>47.45844207353672</v>
-      </c>
-      <c r="L3" t="n">
-        <v>47435</v>
-      </c>
-      <c r="M3" t="n">
-        <v>22861.55</v>
-      </c>
-      <c r="N3" t="n">
-        <v>23813.875</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2.074881186971137</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-0.09921277346166413</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-0.03004787501717855</v>
-      </c>
-      <c r="R3" t="n">
-        <v>-0.06916489844448558</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-0.08657923159856946</v>
-      </c>
-      <c r="T3" t="n">
-        <v>-0.08860898140962817</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN2"/>
+  <dimension ref="A1:AN5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,142 +625,580 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1410</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>南染</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>25.39999961853027</v>
+      </c>
+      <c r="G2" t="n">
+        <v>25.16000003814697</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>49.9712591959256</v>
+      </c>
+      <c r="J2" t="n">
+        <v>47.57033549404488</v>
+      </c>
+      <c r="K2" t="n">
+        <v>47.51711073046896</v>
+      </c>
+      <c r="L2" t="n">
+        <v>133836.6</v>
+      </c>
+      <c r="M2" t="n">
+        <v>88318.89999999999</v>
+      </c>
+      <c r="N2" t="n">
+        <v>90696.85000000001</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.515378927953134</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-0.4731045493781814</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-0.6418813189049328</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.1687767695267515</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.1371510298571388</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.1462639235281982</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>-6.411</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>-11.411</v>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>70</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>2756</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>聯發國際</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="F3" t="n">
         <v>59.70000076293945</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G3" t="n">
         <v>60.01999988555908</v>
       </c>
-      <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>47.87330915245003</v>
-      </c>
-      <c r="J2" t="n">
-        <v>46.95488765956902</v>
-      </c>
-      <c r="K2" t="n">
-        <v>42.9527502263377</v>
-      </c>
-      <c r="L2" t="n">
-        <v>133704.8</v>
-      </c>
-      <c r="M2" t="n">
-        <v>61838.4</v>
-      </c>
-      <c r="N2" t="n">
-        <v>45739.725</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2.162164609692359</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-0.6840245166553274</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-0.8286633935943704</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.144638876939043</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.1481447680853475</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.1641092648588223</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>47.87330916210781</v>
+      </c>
+      <c r="J3" t="n">
+        <v>46.95488783473514</v>
+      </c>
+      <c r="K3" t="n">
+        <v>42.15714175174454</v>
+      </c>
+      <c r="L3" t="n">
+        <v>133682</v>
+      </c>
+      <c r="M3" t="n">
+        <v>61832.7</v>
+      </c>
+      <c r="N3" t="n">
+        <v>45736.875</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.161995190247232</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-0.6649674564238381</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-0.8008045284649451</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.135837072041107</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.1386591104144295</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.153888670667425</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="inlineStr">
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="inlineStr">
         <is>
           <t>2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>70</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>世坤</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="G4" t="n">
+        <v>44.07500019073486</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>39.22549705364277</v>
+      </c>
+      <c r="J4" t="n">
+        <v>38.91913205247299</v>
+      </c>
+      <c r="K4" t="n">
+        <v>39.3522937025385</v>
+      </c>
+      <c r="L4" t="n">
+        <v>25510.4</v>
+      </c>
+      <c r="M4" t="n">
+        <v>13584.5</v>
+      </c>
+      <c r="N4" t="n">
+        <v>9417.299999999999</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.877904965217712</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.03040781682047111</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.04775362037774277</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-0.01734580355727166</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.1199047472280472</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.00227743204057022</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>5013</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>強新</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>27.60000038146973</v>
+      </c>
+      <c r="G5" t="n">
+        <v>27.53999986648559</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>41.1276314466816</v>
+      </c>
+      <c r="J5" t="n">
+        <v>40.0366786515841</v>
+      </c>
+      <c r="K5" t="n">
+        <v>47.9193244607883</v>
+      </c>
+      <c r="L5" t="n">
+        <v>14801</v>
+      </c>
+      <c r="M5" t="n">
+        <v>8671.200000000001</v>
+      </c>
+      <c r="N5" t="n">
+        <v>10179.275</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.706914844542854</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.2283561106393286</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.2196741186631742</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-0.008681991976154435</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0.05183216569497417</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.04190475865194773</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN5"/>
+  <dimension ref="A1:AN2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,67 +625,67 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>4174</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>南染</t>
+          <t>浩鼎</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>25.39999961853027</v>
+        <v>28.79999923706055</v>
       </c>
       <c r="G2" t="n">
-        <v>25.16000003814697</v>
+        <v>28.51249990463257</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>49.9712591959256</v>
+        <v>49.70961840063196</v>
       </c>
       <c r="J2" t="n">
-        <v>47.57033549404488</v>
+        <v>44.00584248115617</v>
       </c>
       <c r="K2" t="n">
-        <v>47.51711073046896</v>
+        <v>48.32085737865016</v>
       </c>
       <c r="L2" t="n">
-        <v>133836.6</v>
+        <v>952105</v>
       </c>
       <c r="M2" t="n">
-        <v>88318.89999999999</v>
+        <v>625319.4</v>
       </c>
       <c r="N2" t="n">
-        <v>90696.85000000001</v>
+        <v>552736.35</v>
       </c>
       <c r="O2" t="n">
-        <v>1.515378927953134</v>
+        <v>1.522589895659722</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4731045493781814</v>
+        <v>-0.4537135838638306</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.6418813189049328</v>
+        <v>-0.7663782789001069</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1687767695267515</v>
+        <v>0.3126646950362763</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1371510298571388</v>
+        <v>0.3499328945287461</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1462639235281982</v>
+        <v>0.3415006900334704</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -735,470 +735,32 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-6.411</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-11.411</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>70</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2756</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>聯發國際</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>59.70000076293945</v>
-      </c>
-      <c r="G3" t="n">
-        <v>60.01999988555908</v>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>47.87330916210781</v>
-      </c>
-      <c r="J3" t="n">
-        <v>46.95488783473514</v>
-      </c>
-      <c r="K3" t="n">
-        <v>42.15714175174454</v>
-      </c>
-      <c r="L3" t="n">
-        <v>133682</v>
-      </c>
-      <c r="M3" t="n">
-        <v>61832.7</v>
-      </c>
-      <c r="N3" t="n">
-        <v>45736.875</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2.161995190247232</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-0.6649674564238381</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-0.8008045284649451</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.135837072041107</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.1386591104144295</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.153888670667425</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>70</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>4305</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>世坤</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>42.75</v>
-      </c>
-      <c r="G4" t="n">
-        <v>44.07500019073486</v>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>39.22549705364277</v>
-      </c>
-      <c r="J4" t="n">
-        <v>38.91913205247299</v>
-      </c>
-      <c r="K4" t="n">
-        <v>39.3522937025385</v>
-      </c>
-      <c r="L4" t="n">
-        <v>25510.4</v>
-      </c>
-      <c r="M4" t="n">
-        <v>13584.5</v>
-      </c>
-      <c r="N4" t="n">
-        <v>9417.299999999999</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.877904965217712</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.03040781682047111</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.04775362037774277</v>
-      </c>
-      <c r="R4" t="n">
-        <v>-0.01734580355727166</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.1199047472280472</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.00227743204057022</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>70</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>5013</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>強新</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>27.60000038146973</v>
-      </c>
-      <c r="G5" t="n">
-        <v>27.53999986648559</v>
-      </c>
-      <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>41.1276314466816</v>
-      </c>
-      <c r="J5" t="n">
-        <v>40.0366786515841</v>
-      </c>
-      <c r="K5" t="n">
-        <v>47.9193244607883</v>
-      </c>
-      <c r="L5" t="n">
-        <v>14801</v>
-      </c>
-      <c r="M5" t="n">
-        <v>8671.200000000001</v>
-      </c>
-      <c r="N5" t="n">
-        <v>10179.275</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.706914844542854</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-0.2283561106393286</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-0.2196741186631742</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-0.008681991976154435</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-0.05183216569497417</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-0.04190475865194773</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN2"/>
+  <dimension ref="A1:AN3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,142 +625,288 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>8450</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>霹靂</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>15.44999980926514</v>
+      </c>
+      <c r="G2" t="n">
+        <v>15.59999990463257</v>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>34.37687930642133</v>
+      </c>
+      <c r="J2" t="n">
+        <v>31.26866488661812</v>
+      </c>
+      <c r="K2" t="n">
+        <v>46.59724852495236</v>
+      </c>
+      <c r="L2" t="n">
+        <v>133617.8</v>
+      </c>
+      <c r="M2" t="n">
+        <v>68897.35000000001</v>
+      </c>
+      <c r="N2" t="n">
+        <v>65782.77499999999</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.939375026760826</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-0.2185521728203614</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-0.1829089729718713</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-0.03564319984849013</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-0.07014368433316515</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-0.07606296003171517</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>70</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>4174</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>浩鼎</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3115</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>富榮綱</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>28.79999923706055</v>
-      </c>
-      <c r="G2" t="n">
-        <v>28.51249990463257</v>
-      </c>
-      <c r="H2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>49.70961840063196</v>
-      </c>
-      <c r="J2" t="n">
-        <v>44.00584248115617</v>
-      </c>
-      <c r="K2" t="n">
-        <v>48.32085737865016</v>
-      </c>
-      <c r="L2" t="n">
-        <v>952105</v>
-      </c>
-      <c r="M2" t="n">
-        <v>625319.4</v>
-      </c>
-      <c r="N2" t="n">
-        <v>552736.35</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.522589895659722</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-0.4537135838638306</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-0.7663782789001069</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.3126646950362763</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.3499328945287461</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.3415006900334704</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="F3" t="n">
+        <v>8.579999923706055</v>
+      </c>
+      <c r="G3" t="n">
+        <v>8.995999956130982</v>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>40.98558670741475</v>
+      </c>
+      <c r="J3" t="n">
+        <v>38.36295907580185</v>
+      </c>
+      <c r="K3" t="n">
+        <v>44.0437734100771</v>
+      </c>
+      <c r="L3" t="n">
+        <v>33586.8</v>
+      </c>
+      <c r="M3" t="n">
+        <v>11497.65</v>
+      </c>
+      <c r="N3" t="n">
+        <v>22333.725</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.921188242814837</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-0.1787608236343914</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-0.1055365557968285</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-0.07322426783756286</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-0.09369949048059052</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-0.08671581178113176</v>
+      </c>
+      <c r="U3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN3"/>
+  <dimension ref="A1:AN7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,71 +625,71 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8450</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>霹靂</t>
+          <t>宏全</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>15.44999980926514</v>
+        <v>124</v>
       </c>
       <c r="G2" t="n">
-        <v>15.59999990463257</v>
+        <v>128.975</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>34.37687930642133</v>
+        <v>35.55311650268472</v>
       </c>
       <c r="J2" t="n">
-        <v>31.26866488661812</v>
+        <v>30.92431087096434</v>
       </c>
       <c r="K2" t="n">
-        <v>46.59724852495236</v>
+        <v>45.19255891960536</v>
       </c>
       <c r="L2" t="n">
-        <v>133617.8</v>
+        <v>3495844.2</v>
       </c>
       <c r="M2" t="n">
-        <v>68897.35000000001</v>
+        <v>1991251.95</v>
       </c>
       <c r="N2" t="n">
-        <v>65782.77499999999</v>
+        <v>1930008.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.939375026760826</v>
+        <v>1.755601143290783</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2185521728203614</v>
+        <v>-0.3375412074621522</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1829089729718713</v>
+        <v>1.077263154233868</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.03564319984849013</v>
+        <v>-1.414804361696021</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.07014368433316515</v>
+        <v>-1.573823524427469</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.07606296003171517</v>
+        <v>-1.513080155573713</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -709,58 +709,58 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1223.156</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>-0.877</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>-29.053</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1193.226</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>-81.80199999999991</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>403.377</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>231.8679999999999</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>553.4429999999998</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>-525.0369999999998</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>453.2599999999999</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>-57.37999999999999</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>-129.1570000000006</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
@@ -771,142 +771,726 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>80</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>5516</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>雙喜</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>10.79750003814697</v>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>40.04557287711476</v>
+      </c>
+      <c r="J3" t="n">
+        <v>39.33483918746707</v>
+      </c>
+      <c r="K3" t="n">
+        <v>45.39025583568738</v>
+      </c>
+      <c r="L3" t="n">
+        <v>162806.2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>84516.05</v>
+      </c>
+      <c r="N3" t="n">
+        <v>79158.27499999999</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.926334702106878</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-0.1024300309600079</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-0.06484761131800151</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-0.0375824196420064</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-0.03813394310960774</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-0.04519977178383136</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>80</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>8101</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>華冠</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>13.30000019073486</v>
+      </c>
+      <c r="G4" t="n">
+        <v>14.26250009536743</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>43.92481632301463</v>
+      </c>
+      <c r="J4" t="n">
+        <v>33.85696351426461</v>
+      </c>
+      <c r="K4" t="n">
+        <v>44.04638453121034</v>
+      </c>
+      <c r="L4" t="n">
+        <v>21185.8</v>
+      </c>
+      <c r="M4" t="n">
+        <v>11448.45</v>
+      </c>
+      <c r="N4" t="n">
+        <v>14198.875</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.850538719215265</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0.2916671407076894</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0.1371203090916325</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-0.1545468316160569</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-0.1818262748111724</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.2392550832367228</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-0.043</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.269</v>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>80</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>8450</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>霹靂</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>15.58999991416931</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>41.01316386093288</v>
+      </c>
+      <c r="J5" t="n">
+        <v>34.51683121138971</v>
+      </c>
+      <c r="K5" t="n">
+        <v>48.02110596297022</v>
+      </c>
+      <c r="L5" t="n">
+        <v>111191.2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>68077.89999999999</v>
+      </c>
+      <c r="N5" t="n">
+        <v>64486.1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.633293623922007</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.1920240324341531</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.1847319848643277</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-0.007292047569825433</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0.03564319984849013</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.07014368433316515</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>70</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>3115</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>富榮綱</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>6637</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>醫影</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>8.579999923706055</v>
-      </c>
-      <c r="G3" t="n">
-        <v>8.995999956130982</v>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>40.98558670741475</v>
-      </c>
-      <c r="J3" t="n">
-        <v>38.36295907580185</v>
-      </c>
-      <c r="K3" t="n">
-        <v>44.0437734100771</v>
-      </c>
-      <c r="L3" t="n">
-        <v>33586.8</v>
-      </c>
-      <c r="M3" t="n">
-        <v>11497.65</v>
-      </c>
-      <c r="N3" t="n">
-        <v>22333.725</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2.921188242814837</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-0.1787608236343914</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-0.1055365557968285</v>
-      </c>
-      <c r="R3" t="n">
-        <v>-0.07322426783756286</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-0.09369949048059052</v>
-      </c>
-      <c r="T3" t="n">
-        <v>-0.08671581178113176</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
+      <c r="F6" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>63.36500015258789</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>45.95136941443828</v>
+      </c>
+      <c r="J6" t="n">
+        <v>37.64253644805724</v>
+      </c>
+      <c r="K6" t="n">
+        <v>45.32804769142915</v>
+      </c>
+      <c r="L6" t="n">
+        <v>78542.60000000001</v>
+      </c>
+      <c r="M6" t="n">
+        <v>50692.25</v>
+      </c>
+      <c r="N6" t="n">
+        <v>50507.85</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.549400549393645</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.8988321734958618</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-1.100616747046652</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.2017845735507906</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.1662651141310256</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.09206864050918728</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>70</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1213</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>大飲</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>7.579999923706055</v>
+      </c>
+      <c r="G7" t="n">
+        <v>8.13600001335144</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>36.58879790144034</v>
+      </c>
+      <c r="J7" t="n">
+        <v>33.34579693794905</v>
+      </c>
+      <c r="K7" t="n">
+        <v>37.12032318820651</v>
+      </c>
+      <c r="L7" t="n">
+        <v>40564.6</v>
+      </c>
+      <c r="M7" t="n">
+        <v>26723.1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>23122</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.517960116902605</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0.2107706486948642</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.184875964689597</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-0.0258946840052672</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.01293760193141663</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0.02117000566756405</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>-0.383</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-0.383</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-0.383</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-0.383</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>-0.383</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>-0.383</v>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -625,67 +625,67 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>4175</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>宏全</t>
+          <t>杏一</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>124</v>
+        <v>51.59999847412109</v>
       </c>
       <c r="G2" t="n">
-        <v>128.975</v>
+        <v>53.075</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>35.55311650268472</v>
+        <v>45.59357396379542</v>
       </c>
       <c r="J2" t="n">
-        <v>30.92431087096434</v>
+        <v>44.51042227126292</v>
       </c>
       <c r="K2" t="n">
-        <v>45.19255891960536</v>
+        <v>35.13178869947899</v>
       </c>
       <c r="L2" t="n">
-        <v>3495844.2</v>
+        <v>86331</v>
       </c>
       <c r="M2" t="n">
-        <v>1991251.95</v>
+        <v>36325.4</v>
       </c>
       <c r="N2" t="n">
-        <v>1930008.1</v>
+        <v>34494.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1.755601143290783</v>
+        <v>2.376601496473542</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.3375412074621522</v>
+        <v>-0.2386009587126665</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.077263154233868</v>
+        <v>-0.2000254094757478</v>
       </c>
       <c r="R2" t="n">
-        <v>-1.414804361696021</v>
+        <v>-0.03857554923691869</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.573823524427469</v>
+        <v>0.06674743061449082</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.513080155573713</v>
+        <v>0.03851743014076947</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -714,53 +714,53 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>1223.156</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.877</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-29.053</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1193.226</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>-81.80199999999991</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>403.377</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>231.8679999999999</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>553.4429999999998</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-525.0369999999998</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>453.2599999999999</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-57.37999999999999</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-129.1570000000006</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
@@ -771,71 +771,71 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5516</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>雙喜</t>
+          <t>興泰</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>10.5</v>
+        <v>36.40000152587891</v>
       </c>
       <c r="G3" t="n">
-        <v>10.79750003814697</v>
+        <v>37.26000061035156</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>40.04557287711476</v>
+        <v>49.06056618815266</v>
       </c>
       <c r="J3" t="n">
-        <v>39.33483918746707</v>
+        <v>45.77597609776794</v>
       </c>
       <c r="K3" t="n">
-        <v>45.39025583568738</v>
+        <v>44.36661179844324</v>
       </c>
       <c r="L3" t="n">
-        <v>162806.2</v>
+        <v>77803.60000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>84516.05</v>
+        <v>36405.55</v>
       </c>
       <c r="N3" t="n">
-        <v>79158.27499999999</v>
+        <v>35521.775</v>
       </c>
       <c r="O3" t="n">
-        <v>1.926334702106878</v>
+        <v>2.13713568398225</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1024300309600079</v>
+        <v>-0.7653192391011814</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.06484761131800151</v>
+        <v>-0.8434530853931773</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.0375824196420064</v>
+        <v>0.07813384629199593</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.03813394310960774</v>
+        <v>0.09652534531997459</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.04519977178383136</v>
+        <v>0.07943855784371512</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -869,44 +869,44 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>-1.100000000000001</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>-7.100000000000001</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
@@ -917,16 +917,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>2239</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>英利-KY</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,49 +935,49 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>13.30000019073486</v>
+        <v>22.20000076293945</v>
       </c>
       <c r="G4" t="n">
-        <v>14.26250009536743</v>
+        <v>22.53500013351441</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>43.92481632301463</v>
+        <v>42.97524675654</v>
       </c>
       <c r="J4" t="n">
-        <v>33.85696351426461</v>
+        <v>37.53743599193009</v>
       </c>
       <c r="K4" t="n">
-        <v>44.04638453121034</v>
+        <v>45.41253612353341</v>
       </c>
       <c r="L4" t="n">
-        <v>21185.8</v>
+        <v>217350.8</v>
       </c>
       <c r="M4" t="n">
-        <v>11448.45</v>
+        <v>102870.9</v>
       </c>
       <c r="N4" t="n">
-        <v>14198.875</v>
+        <v>109836.875</v>
       </c>
       <c r="O4" t="n">
-        <v>1.850538719215265</v>
+        <v>2.112850184065659</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2916671407076894</v>
+        <v>-0.1253266343887312</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1371203090916325</v>
+        <v>-0.1486635227214449</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.1545468316160569</v>
+        <v>0.02333688833271375</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1818262748111724</v>
+        <v>0.05131162908453471</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2392550832367228</v>
+        <v>0.01753614186684882</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1015,44 +1015,44 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>-31.25</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.66</v>
+        <v>1.173</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.66</v>
+        <v>-30.077</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>-44</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.312</v>
+        <v>8.744999999999999</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.312</v>
+        <v>-35.255</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.043</v>
+        <v>-160</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.312</v>
+        <v>5.711000000000002</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.269</v>
+        <v>-154.289</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
@@ -1063,16 +1063,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>8450</t>
+          <t>6294</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>霹靂</t>
+          <t>智基</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1081,53 +1081,53 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>15.5</v>
+        <v>28.04999923706055</v>
       </c>
       <c r="G5" t="n">
-        <v>15.58999991416931</v>
+        <v>28.0625</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>41.01316386093288</v>
+        <v>41.30815367765913</v>
       </c>
       <c r="J5" t="n">
-        <v>34.51683121138971</v>
+        <v>34.57802331191167</v>
       </c>
       <c r="K5" t="n">
-        <v>48.02110596297022</v>
+        <v>47.63303856810301</v>
       </c>
       <c r="L5" t="n">
-        <v>111191.2</v>
+        <v>166527.2</v>
       </c>
       <c r="M5" t="n">
-        <v>68077.89999999999</v>
+        <v>82715.64999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>64486.1</v>
+        <v>71652.3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.633293623922007</v>
+        <v>2.013249004269446</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1920240324341531</v>
+        <v>-0.2777380403944711</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1847319848643277</v>
+        <v>-0.5336548862925504</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.007292047569825433</v>
+        <v>0.2559168458980793</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.03564319984849013</v>
+        <v>0.2998735666425318</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.07014368433316515</v>
+        <v>0.29761692497512</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
@@ -1213,63 +1213,63 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>6637</t>
+          <t>3543</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>醫影</t>
+          <t>州巧</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>63.5</v>
+        <v>31.54999923706055</v>
       </c>
       <c r="G6" t="n">
-        <v>63.36500015258789</v>
+        <v>30.58249988555908</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>45.95136941443828</v>
+        <v>49.27028923857191</v>
       </c>
       <c r="J6" t="n">
-        <v>37.64253644805724</v>
+        <v>32.79468215229966</v>
       </c>
       <c r="K6" t="n">
-        <v>45.32804769142915</v>
+        <v>49.36554137457335</v>
       </c>
       <c r="L6" t="n">
-        <v>78542.60000000001</v>
+        <v>1584407.6</v>
       </c>
       <c r="M6" t="n">
-        <v>50692.25</v>
+        <v>900472.65</v>
       </c>
       <c r="N6" t="n">
-        <v>50507.85</v>
+        <v>934677.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.549400549393645</v>
+        <v>1.759528842991511</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.8988321734958618</v>
+        <v>-1.402574152813557</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.100616747046652</v>
+        <v>-1.826556802380806</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2017845735507906</v>
+        <v>0.423982649567249</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1662651141310256</v>
+        <v>0.2907726001687596</v>
       </c>
       <c r="T6" t="n">
-        <v>0.09206864050918728</v>
+        <v>0.0413052843760835</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1307,44 +1307,44 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>-1785.8</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>-1.747</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>-1787.547</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>-1722.572</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-1723.572</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>-808.058</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>-807.058</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
@@ -1359,63 +1359,63 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1213</t>
+          <t>5013</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>大飲</t>
+          <t>強新</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>7.579999923706055</v>
+        <v>27.20000076293945</v>
       </c>
       <c r="G7" t="n">
-        <v>8.13600001335144</v>
+        <v>27.31749992370606</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>36.58879790144034</v>
+        <v>32.20948773321642</v>
       </c>
       <c r="J7" t="n">
-        <v>33.34579693794905</v>
+        <v>30.62459836305036</v>
       </c>
       <c r="K7" t="n">
-        <v>37.12032318820651</v>
+        <v>45.84022134257293</v>
       </c>
       <c r="L7" t="n">
-        <v>40564.6</v>
+        <v>20043.4</v>
       </c>
       <c r="M7" t="n">
-        <v>26723.1</v>
+        <v>12024.45</v>
       </c>
       <c r="N7" t="n">
-        <v>23122</v>
+        <v>10634.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.517960116902605</v>
+        <v>1.666887050966988</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2107706486948642</v>
+        <v>-0.2565413064790256</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.184875964689597</v>
+        <v>-0.2404943081077845</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.0258946840052672</v>
+        <v>-0.01604699837124116</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01293760193141663</v>
+        <v>-0.04369635436004168</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.02117000566756405</v>
+        <v>-0.03489703506346811</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>-0.383</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1462,10 +1462,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.383</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.383</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1474,10 +1474,10 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.383</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.383</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
@@ -1486,11 +1486,11 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.383</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN7"/>
+  <dimension ref="A1:AN4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,12 +629,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4175</t>
+          <t>3323</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>杏一</t>
+          <t>加百裕</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,49 +643,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>51.59999847412109</v>
+        <v>34.90000152587891</v>
       </c>
       <c r="G2" t="n">
-        <v>53.075</v>
+        <v>34.63500003814697</v>
       </c>
       <c r="H2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>45.59357396379542</v>
+        <v>43.64392592295077</v>
       </c>
       <c r="J2" t="n">
-        <v>44.51042227126292</v>
+        <v>39.32276159230851</v>
       </c>
       <c r="K2" t="n">
-        <v>35.13178869947899</v>
+        <v>49.33174613075063</v>
       </c>
       <c r="L2" t="n">
-        <v>86331</v>
+        <v>3039973.6</v>
       </c>
       <c r="M2" t="n">
-        <v>36325.4</v>
+        <v>1335657.15</v>
       </c>
       <c r="N2" t="n">
-        <v>34494.7</v>
+        <v>2164778.925</v>
       </c>
       <c r="O2" t="n">
-        <v>2.376601496473542</v>
+        <v>2.27601342155807</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2386009587126665</v>
+        <v>-0.1843189524529265</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2000254094757478</v>
+        <v>-0.3344504589998054</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.03857554923691869</v>
+        <v>0.1501315065468788</v>
       </c>
       <c r="S2" t="n">
-        <v>0.06674743061449082</v>
+        <v>0.168207105709609</v>
       </c>
       <c r="T2" t="n">
-        <v>0.03851743014076947</v>
+        <v>0.1374792476873302</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
@@ -775,63 +775,63 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>6294</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>興泰</t>
+          <t>智基</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>36.40000152587891</v>
+        <v>28.04999923706055</v>
       </c>
       <c r="G3" t="n">
-        <v>37.26000061035156</v>
+        <v>28.02499990463257</v>
       </c>
       <c r="H3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>49.06056618815266</v>
+        <v>37.0926320645009</v>
       </c>
       <c r="J3" t="n">
-        <v>45.77597609776794</v>
+        <v>36.74546546106941</v>
       </c>
       <c r="K3" t="n">
-        <v>44.36661179844324</v>
+        <v>47.666484462272</v>
       </c>
       <c r="L3" t="n">
-        <v>77803.60000000001</v>
+        <v>164564.6</v>
       </c>
       <c r="M3" t="n">
-        <v>36405.55</v>
+        <v>76060.55</v>
       </c>
       <c r="N3" t="n">
-        <v>35521.775</v>
+        <v>64042.6</v>
       </c>
       <c r="O3" t="n">
-        <v>2.13713568398225</v>
+        <v>2.163599921378428</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.7653192391011814</v>
+        <v>-0.2351857043439765</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.8434530853931773</v>
+        <v>-0.4387072690658372</v>
       </c>
       <c r="R3" t="n">
-        <v>0.07813384629199593</v>
+        <v>0.2035215647218608</v>
       </c>
       <c r="S3" t="n">
-        <v>0.09652534531997459</v>
+        <v>0.2404765529567162</v>
       </c>
       <c r="T3" t="n">
-        <v>0.07943855784371512</v>
+        <v>0.2609907020877072</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -869,44 +869,44 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-1.100000000000001</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-7.100000000000001</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2239</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>英利-KY</t>
+          <t>勝悅-KY</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,49 +935,49 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>22.20000076293945</v>
+        <v>5.5</v>
       </c>
       <c r="G4" t="n">
-        <v>22.53500013351441</v>
+        <v>5.568499994277954</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>42.97524675654</v>
+        <v>42.56862010460016</v>
       </c>
       <c r="J4" t="n">
-        <v>37.53743599193009</v>
+        <v>42.41762768190476</v>
       </c>
       <c r="K4" t="n">
-        <v>45.41253612353341</v>
+        <v>46.45540100512667</v>
       </c>
       <c r="L4" t="n">
-        <v>217350.8</v>
+        <v>433262</v>
       </c>
       <c r="M4" t="n">
-        <v>102870.9</v>
+        <v>236891.4</v>
       </c>
       <c r="N4" t="n">
-        <v>109836.875</v>
+        <v>313240.775</v>
       </c>
       <c r="O4" t="n">
-        <v>2.112850184065659</v>
+        <v>1.828947779446616</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1253266343887312</v>
+        <v>-0.006840247274499944</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1486635227214449</v>
+        <v>-0.03314411335607093</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02333688833271375</v>
+        <v>0.02630386608157099</v>
       </c>
       <c r="S4" t="n">
-        <v>0.05131162908453471</v>
+        <v>0.04014591616941846</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01753614186684882</v>
+        <v>0.03705038743591253</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1015,482 +1015,44 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>-31.25</v>
+        <v>-55</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.173</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
-        <v>-30.077</v>
+        <v>-39</v>
       </c>
       <c r="AF4" t="n">
-        <v>-44</v>
+        <v>-177.25</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>8.744999999999999</v>
+        <v>-8</v>
       </c>
       <c r="AI4" t="n">
-        <v>-35.255</v>
+        <v>-185.25</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-160</v>
+        <v>-17.881</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>5.711000000000002</v>
+        <v>14</v>
       </c>
       <c r="AM4" t="n">
-        <v>-154.289</v>
+        <v>-3.881000000000014</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>70</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>6294</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>智基</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>28.04999923706055</v>
-      </c>
-      <c r="G5" t="n">
-        <v>28.0625</v>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>41.30815367765913</v>
-      </c>
-      <c r="J5" t="n">
-        <v>34.57802331191167</v>
-      </c>
-      <c r="K5" t="n">
-        <v>47.63303856810301</v>
-      </c>
-      <c r="L5" t="n">
-        <v>166527.2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>82715.64999999999</v>
-      </c>
-      <c r="N5" t="n">
-        <v>71652.3</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.013249004269446</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-0.2777380403944711</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-0.5336548862925504</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.2559168458980793</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.2998735666425318</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.29761692497512</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>70</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>3543</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>州巧</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>31.54999923706055</v>
-      </c>
-      <c r="G6" t="n">
-        <v>30.58249988555908</v>
-      </c>
-      <c r="H6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>49.27028923857191</v>
-      </c>
-      <c r="J6" t="n">
-        <v>32.79468215229966</v>
-      </c>
-      <c r="K6" t="n">
-        <v>49.36554137457335</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1584407.6</v>
-      </c>
-      <c r="M6" t="n">
-        <v>900472.65</v>
-      </c>
-      <c r="N6" t="n">
-        <v>934677.2</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.759528842991511</v>
-      </c>
-      <c r="P6" t="n">
-        <v>-1.402574152813557</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>-1.826556802380806</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.423982649567249</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.2907726001687596</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.0413052843760835</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>-1785.8</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>-1.747</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>-1787.547</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>-1722.572</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>-1723.572</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>-808.058</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>-807.058</v>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>70</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>5013</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>強新</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>27.20000076293945</v>
-      </c>
-      <c r="G7" t="n">
-        <v>27.31749992370606</v>
-      </c>
-      <c r="H7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>32.20948773321642</v>
-      </c>
-      <c r="J7" t="n">
-        <v>30.62459836305036</v>
-      </c>
-      <c r="K7" t="n">
-        <v>45.84022134257293</v>
-      </c>
-      <c r="L7" t="n">
-        <v>20043.4</v>
-      </c>
-      <c r="M7" t="n">
-        <v>12024.45</v>
-      </c>
-      <c r="N7" t="n">
-        <v>10634.5</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.666887050966988</v>
-      </c>
-      <c r="P7" t="n">
-        <v>-0.2565413064790256</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>-0.2404943081077845</v>
-      </c>
-      <c r="R7" t="n">
-        <v>-0.01604699837124116</v>
-      </c>
-      <c r="S7" t="n">
-        <v>-0.04369635436004168</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-0.03489703506346811</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN4"/>
+  <dimension ref="A1:AN1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -615,444 +615,6 @@
       <c r="AN1" t="inlineStr">
         <is>
           <t>最後更新日期</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>70</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>3323</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>加百裕</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>34.90000152587891</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.63500003814697</v>
-      </c>
-      <c r="H2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>43.64392592295077</v>
-      </c>
-      <c r="J2" t="n">
-        <v>39.32276159230851</v>
-      </c>
-      <c r="K2" t="n">
-        <v>49.33174613075063</v>
-      </c>
-      <c r="L2" t="n">
-        <v>3039973.6</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1335657.15</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2164778.925</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2.27601342155807</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-0.1843189524529265</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-0.3344504589998054</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.1501315065468788</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.168207105709609</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.1374792476873302</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>70</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>6294</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>智基</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>28.04999923706055</v>
-      </c>
-      <c r="G3" t="n">
-        <v>28.02499990463257</v>
-      </c>
-      <c r="H3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>37.0926320645009</v>
-      </c>
-      <c r="J3" t="n">
-        <v>36.74546546106941</v>
-      </c>
-      <c r="K3" t="n">
-        <v>47.666484462272</v>
-      </c>
-      <c r="L3" t="n">
-        <v>164564.6</v>
-      </c>
-      <c r="M3" t="n">
-        <v>76060.55</v>
-      </c>
-      <c r="N3" t="n">
-        <v>64042.6</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2.163599921378428</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-0.2351857043439765</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-0.4387072690658372</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.2035215647218608</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.2404765529567162</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.2609907020877072</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>70</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1340</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>勝悅-KY</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G4" t="n">
-        <v>5.568499994277954</v>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>42.56862010460016</v>
-      </c>
-      <c r="J4" t="n">
-        <v>42.41762768190476</v>
-      </c>
-      <c r="K4" t="n">
-        <v>46.45540100512667</v>
-      </c>
-      <c r="L4" t="n">
-        <v>433262</v>
-      </c>
-      <c r="M4" t="n">
-        <v>236891.4</v>
-      </c>
-      <c r="N4" t="n">
-        <v>313240.775</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.828947779446616</v>
-      </c>
-      <c r="P4" t="n">
-        <v>-0.006840247274499944</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-0.03314411335607093</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.02630386608157099</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.04014591616941846</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.03705038743591253</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>-55</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-39</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>-177.25</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>-185.25</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>-17.881</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>-3.881000000000014</v>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN1"/>
+  <dimension ref="A1:AN2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -615,6 +615,152 @@
       <c r="AN1" t="inlineStr">
         <is>
           <t>最後更新日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>70</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2235</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>謚源</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.10249986648559</v>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>32.36196866560461</v>
+      </c>
+      <c r="J2" t="n">
+        <v>31.65241255163256</v>
+      </c>
+      <c r="K2" t="n">
+        <v>34.19746995871115</v>
+      </c>
+      <c r="L2" t="n">
+        <v>21449</v>
+      </c>
+      <c r="M2" t="n">
+        <v>11115</v>
+      </c>
+      <c r="N2" t="n">
+        <v>13354.425</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.929734592892488</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-0.1851556401382162</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-0.1412927157493716</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-0.04386292438884462</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.07983922536489227</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.02805498769514908</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -625,67 +625,67 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2235</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>謚源</t>
+          <t>福壽</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>28.5</v>
+        <v>12.19999980926514</v>
       </c>
       <c r="G2" t="n">
-        <v>30.10249986648559</v>
+        <v>12.34249997138977</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>32.36196866560461</v>
+        <v>41.48372377772002</v>
       </c>
       <c r="J2" t="n">
-        <v>31.65241255163256</v>
+        <v>37.54753475894721</v>
       </c>
       <c r="K2" t="n">
-        <v>34.19746995871115</v>
+        <v>41.38159472582386</v>
       </c>
       <c r="L2" t="n">
-        <v>21449</v>
+        <v>1123315.2</v>
       </c>
       <c r="M2" t="n">
-        <v>11115</v>
+        <v>687040.15</v>
       </c>
       <c r="N2" t="n">
-        <v>13354.425</v>
+        <v>602091.375</v>
       </c>
       <c r="O2" t="n">
-        <v>1.929734592892488</v>
+        <v>1.635006629525217</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1851556401382162</v>
+        <v>-0.1759197956009295</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1412927157493716</v>
+        <v>-0.1550536515883049</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.04386292438884462</v>
+        <v>-0.0208661440126246</v>
       </c>
       <c r="S2" t="n">
-        <v>0.07983922536489227</v>
+        <v>-0.04023156328161681</v>
       </c>
       <c r="T2" t="n">
-        <v>0.02805498769514908</v>
+        <v>-0.02485670498199957</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -714,53 +714,53 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>415.955</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>425.955</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>362.33</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>389.33</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1336.296</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1354.296</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -629,12 +629,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>6674</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>福壽</t>
+          <t>鋐寶科技</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,49 +643,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>12.19999980926514</v>
+        <v>16.89999961853027</v>
       </c>
       <c r="G2" t="n">
-        <v>12.34249997138977</v>
+        <v>16.97999982833862</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>41.48372377772002</v>
+        <v>41.10283958737589</v>
       </c>
       <c r="J2" t="n">
-        <v>37.54753475894721</v>
+        <v>31.87846819853402</v>
       </c>
       <c r="K2" t="n">
-        <v>41.38159472582386</v>
+        <v>47.43121053801215</v>
       </c>
       <c r="L2" t="n">
-        <v>1123315.2</v>
+        <v>49504.8</v>
       </c>
       <c r="M2" t="n">
-        <v>687040.15</v>
+        <v>32634</v>
       </c>
       <c r="N2" t="n">
-        <v>602091.375</v>
+        <v>37855</v>
       </c>
       <c r="O2" t="n">
-        <v>1.635006629525217</v>
+        <v>1.516970031255746</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1759197956009295</v>
+        <v>-0.3026152362249022</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1550536515883049</v>
+        <v>-0.2754055074394725</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.0208661440126246</v>
+        <v>-0.02720972878542971</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.04023156328161681</v>
+        <v>-0.07416697186902477</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.02485670498199957</v>
+        <v>-0.05242961575199001</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -723,44 +723,44 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>415.955</v>
+        <v>24</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>425.955</v>
+        <v>24</v>
       </c>
       <c r="AF2" t="n">
-        <v>362.33</v>
+        <v>13</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
-        <v>389.33</v>
+        <v>14</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1336.296</v>
+        <v>5.02</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>18</v>
+        <v>-1</v>
       </c>
       <c r="AM2" t="n">
-        <v>1354.296</v>
+        <v>4.02</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN2"/>
+  <dimension ref="A1:AN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,142 +625,1310 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>90</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2915</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>潤泰全</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>50.90000152587891</v>
+      </c>
+      <c r="G2" t="n">
+        <v>51.97999992370605</v>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>43.96556625729465</v>
+      </c>
+      <c r="J2" t="n">
+        <v>41.28004151630677</v>
+      </c>
+      <c r="K2" t="n">
+        <v>49.17508024821407</v>
+      </c>
+      <c r="L2" t="n">
+        <v>5485663.4</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3080833.7</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4059600.55</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.780577575479001</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.6447365948127697</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.9379745660029184</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-0.2932379711901487</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-0.2348681135178832</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-0.3302620425494081</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>1138.912</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-206</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>933.912</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>943.498</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-197.192</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>747.306</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>943.498</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>-197.192</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>747.306</v>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>80</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>6674</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>鋐寶科技</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>8488</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>吉源-KY</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>16.89999961853027</v>
-      </c>
-      <c r="G2" t="n">
-        <v>16.97999982833862</v>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>41.10283958737589</v>
-      </c>
-      <c r="J2" t="n">
-        <v>31.87846819853402</v>
-      </c>
-      <c r="K2" t="n">
-        <v>47.43121053801215</v>
-      </c>
-      <c r="L2" t="n">
-        <v>49504.8</v>
-      </c>
-      <c r="M2" t="n">
-        <v>32634</v>
-      </c>
-      <c r="N2" t="n">
-        <v>37855</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.516970031255746</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-0.3026152362249022</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-0.2754055074394725</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-0.02720972878542971</v>
-      </c>
-      <c r="S2" t="n">
-        <v>-0.07416697186902477</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-0.05242961575199001</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
+      <c r="F3" t="n">
+        <v>10.10000038146973</v>
+      </c>
+      <c r="G3" t="n">
+        <v>10.13850002288818</v>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>31.47254751285316</v>
+      </c>
+      <c r="J3" t="n">
+        <v>30.28885682189199</v>
+      </c>
+      <c r="K3" t="n">
+        <v>49.34747231487543</v>
+      </c>
+      <c r="L3" t="n">
+        <v>57200</v>
+      </c>
+      <c r="M3" t="n">
+        <v>20706.85</v>
+      </c>
+      <c r="N3" t="n">
+        <v>24054.225</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.762370906246001</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.001097800291079309</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.002286796892751103</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-0.001188996601671793</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.00136214216313927</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-0.009991831072176587</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>80</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2722</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>夏都</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>22.14999961853027</v>
+      </c>
+      <c r="G4" t="n">
+        <v>22.82000017166138</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>32.74071444412025</v>
+      </c>
+      <c r="J4" t="n">
+        <v>32.41814766711555</v>
+      </c>
+      <c r="K4" t="n">
+        <v>36.10198599878144</v>
+      </c>
+      <c r="L4" t="n">
+        <v>99706.8</v>
+      </c>
+      <c r="M4" t="n">
+        <v>62801.15</v>
+      </c>
+      <c r="N4" t="n">
+        <v>58298.075</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.587658824718974</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0.136476464662767</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0.08084565895806742</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-0.05563080570469955</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-0.02737201230550095</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.009569024401515719</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
         <v>1</v>
       </c>
-      <c r="AI2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
+      <c r="AI4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2719</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>燦星旅</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>23.85000038146973</v>
+      </c>
+      <c r="G5" t="n">
+        <v>24.34249992370605</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>47.22204311134021</v>
+      </c>
+      <c r="J5" t="n">
+        <v>38.06232094664399</v>
+      </c>
+      <c r="K5" t="n">
+        <v>46.3122854825125</v>
+      </c>
+      <c r="L5" t="n">
+        <v>264231</v>
+      </c>
+      <c r="M5" t="n">
+        <v>80859.64999999999</v>
+      </c>
+      <c r="N5" t="n">
+        <v>50523.95</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3.267773234239822</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.3553823225595742</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.4288098556036111</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.07342753304403682</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.0923793656805677</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.1076967866318565</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>70</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>7814</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>海昌生技</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>37.04999923706055</v>
+      </c>
+      <c r="G6" t="n">
+        <v>37.41999988555908</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>41.23538940926738</v>
+      </c>
+      <c r="J6" t="n">
+        <v>34.7683542418866</v>
+      </c>
+      <c r="K6" t="n">
+        <v>48.98673821564214</v>
+      </c>
+      <c r="L6" t="n">
+        <v>465427.4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>164244.25</v>
+      </c>
+      <c r="N6" t="n">
+        <v>119827.2</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.833751562079038</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-1.05779693946657</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.91339479358194</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-0.1444021458846301</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.3205389848969071</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.110011898157009</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>70</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>8068</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>全達</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="G7" t="n">
+        <v>18.88500022888184</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>39.60754141610299</v>
+      </c>
+      <c r="J7" t="n">
+        <v>39.4903133702184</v>
+      </c>
+      <c r="K7" t="n">
+        <v>40.9458860096721</v>
+      </c>
+      <c r="L7" t="n">
+        <v>878513.4</v>
+      </c>
+      <c r="M7" t="n">
+        <v>379437.5</v>
+      </c>
+      <c r="N7" t="n">
+        <v>371037.475</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.315304628562016</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0.2664129499493768</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.3579550813990965</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.09154213144971968</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.1524060986647203</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.1303045609272203</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>70</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>8933</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>愛地雅</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>4.449999809265137</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4.571500015258789</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>49.92448965727685</v>
+      </c>
+      <c r="J8" t="n">
+        <v>42.48194169888203</v>
+      </c>
+      <c r="K8" t="n">
+        <v>43.98098275647298</v>
+      </c>
+      <c r="L8" t="n">
+        <v>384027.4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>200101.95</v>
+      </c>
+      <c r="N8" t="n">
+        <v>279903.6</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.919158708848165</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0.07569136795231213</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.09288203449117542</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.01719066653886329</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.02571533590901076</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.00192428509572061</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>70</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>6542</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>隆中</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>45.56249980926513</v>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>34.67897829469975</v>
+      </c>
+      <c r="J9" t="n">
+        <v>30.27584861126526</v>
+      </c>
+      <c r="K9" t="n">
+        <v>43.5821936122754</v>
+      </c>
+      <c r="L9" t="n">
+        <v>12404.2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>6515.05</v>
+      </c>
+      <c r="N9" t="n">
+        <v>9269.025</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.903930131004367</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0.8137346633778009</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-0.708488392438575</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-0.1052462709392259</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0.1648962814724353</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.2007150562847051</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>70</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2734</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>易飛網</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>15.10000038146973</v>
+      </c>
+      <c r="G10" t="n">
+        <v>15.32250003814697</v>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>31.17042736227403</v>
+      </c>
+      <c r="J10" t="n">
+        <v>30.96456659141846</v>
+      </c>
+      <c r="K10" t="n">
+        <v>45.29687659004249</v>
+      </c>
+      <c r="L10" t="n">
+        <v>198067</v>
+      </c>
+      <c r="M10" t="n">
+        <v>113104.1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>113840.075</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.751192043436091</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.03668867513153096</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.05813745009063982</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.02144877495910887</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.04397790298854817</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.02116765968602456</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN10"/>
+  <dimension ref="A1:AN5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,67 +625,67 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2915</t>
+          <t>8084</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>潤泰全</t>
+          <t>巨虹</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>50.90000152587891</v>
+        <v>45.90000152587891</v>
       </c>
       <c r="G2" t="n">
-        <v>51.97999992370605</v>
+        <v>48.05750007629395</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>43.96556625729465</v>
+        <v>35.8756218050211</v>
       </c>
       <c r="J2" t="n">
-        <v>41.28004151630677</v>
+        <v>30.75987147849812</v>
       </c>
       <c r="K2" t="n">
-        <v>49.17508024821407</v>
+        <v>44.5272808177666</v>
       </c>
       <c r="L2" t="n">
-        <v>5485663.4</v>
+        <v>485337.6</v>
       </c>
       <c r="M2" t="n">
-        <v>3080833.7</v>
+        <v>218895.9</v>
       </c>
       <c r="N2" t="n">
-        <v>4059600.55</v>
+        <v>183709.025</v>
       </c>
       <c r="O2" t="n">
-        <v>1.780577575479001</v>
+        <v>2.21720735746992</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6447365948127697</v>
+        <v>-0.5551940754673197</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9379745660029184</v>
+        <v>-0.07487438581296391</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.2932379711901487</v>
+        <v>-0.4803196896543558</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2348681135178832</v>
+        <v>-0.565319447727012</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3302620425494081</v>
+        <v>-0.5626724512850105</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -714,53 +714,53 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>1138.912</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-206</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>933.912</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>943.498</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-197.192</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>747.306</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>943.498</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-197.192</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>747.306</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -771,67 +771,67 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8488</t>
+          <t>8933</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>愛地雅</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>10.10000038146973</v>
+        <v>4.489999771118164</v>
       </c>
       <c r="G3" t="n">
-        <v>10.13850002288818</v>
+        <v>4.560500001907348</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>31.47254751285316</v>
+        <v>49.41201296049547</v>
       </c>
       <c r="J3" t="n">
-        <v>30.28885682189199</v>
+        <v>44.79196549558879</v>
       </c>
       <c r="K3" t="n">
-        <v>49.34747231487543</v>
+        <v>45.44137093093048</v>
       </c>
       <c r="L3" t="n">
-        <v>57200</v>
+        <v>369411.2</v>
       </c>
       <c r="M3" t="n">
-        <v>20706.85</v>
+        <v>194784.15</v>
       </c>
       <c r="N3" t="n">
-        <v>24054.225</v>
+        <v>262158.325</v>
       </c>
       <c r="O3" t="n">
-        <v>2.762370906246001</v>
+        <v>1.896515707258522</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001097800291079309</v>
+        <v>-0.07437075474111676</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.002286796892751103</v>
+        <v>-0.0884481098300979</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.001188996601671793</v>
+        <v>0.01407735508898114</v>
       </c>
       <c r="S3" t="n">
-        <v>0.00136214216313927</v>
+        <v>0.01690111569923582</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.009991831072176587</v>
+        <v>0.02540318127363995</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -869,44 +869,44 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -917,67 +917,67 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>8426</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>夏都</t>
+          <t>紅木-KY</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>22.14999961853027</v>
+        <v>20.29999923706055</v>
       </c>
       <c r="G4" t="n">
-        <v>22.82000017166138</v>
+        <v>20.2125</v>
       </c>
       <c r="H4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>32.74071444412025</v>
+        <v>40.9688606408851</v>
       </c>
       <c r="J4" t="n">
-        <v>32.41814766711555</v>
+        <v>31.46703282413474</v>
       </c>
       <c r="K4" t="n">
-        <v>36.10198599878144</v>
+        <v>47.14458915944083</v>
       </c>
       <c r="L4" t="n">
-        <v>99706.8</v>
+        <v>87504.39999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>62801.15</v>
+        <v>55704.8</v>
       </c>
       <c r="N4" t="n">
-        <v>58298.075</v>
+        <v>47456.65</v>
       </c>
       <c r="O4" t="n">
-        <v>1.587658824718974</v>
+        <v>1.57085924372765</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.136476464662767</v>
+        <v>-0.3334119032471357</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.08084565895806742</v>
+        <v>-0.4091098781738601</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.05563080570469955</v>
+        <v>0.07569797492672448</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.02737201230550095</v>
+        <v>0.0475986263288366</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.009569024401515719</v>
+        <v>0.02028505979641304</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1015,44 +1015,44 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2719</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>燦星旅</t>
+          <t>大車隊</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1081,49 +1081,49 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>23.85000038146973</v>
+        <v>145.5</v>
       </c>
       <c r="G5" t="n">
-        <v>24.34249992370605</v>
+        <v>155.65</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>47.22204311134021</v>
+        <v>41.27404993797341</v>
       </c>
       <c r="J5" t="n">
-        <v>38.06232094664399</v>
+        <v>40.52157756083262</v>
       </c>
       <c r="K5" t="n">
-        <v>46.3122854825125</v>
+        <v>34.32135061995112</v>
       </c>
       <c r="L5" t="n">
-        <v>264231</v>
+        <v>83221.2</v>
       </c>
       <c r="M5" t="n">
-        <v>80859.64999999999</v>
+        <v>53606.8</v>
       </c>
       <c r="N5" t="n">
-        <v>50523.95</v>
+        <v>43205.05</v>
       </c>
       <c r="O5" t="n">
-        <v>3.267773234239822</v>
+        <v>1.55243737734765</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3553823225595742</v>
+        <v>-1.099771171544603</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.4288098556036111</v>
+        <v>-0.8383830026452952</v>
       </c>
       <c r="R5" t="n">
-        <v>0.07342753304403682</v>
+        <v>-0.2613881688993078</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0923793656805677</v>
+        <v>0.6317946971398203</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1076967866318565</v>
+        <v>0.4370486908930771</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1198,737 +1198,7 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>70</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>7814</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>海昌生技</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>37.04999923706055</v>
-      </c>
-      <c r="G6" t="n">
-        <v>37.41999988555908</v>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>41.23538940926738</v>
-      </c>
-      <c r="J6" t="n">
-        <v>34.7683542418866</v>
-      </c>
-      <c r="K6" t="n">
-        <v>48.98673821564214</v>
-      </c>
-      <c r="L6" t="n">
-        <v>465427.4</v>
-      </c>
-      <c r="M6" t="n">
-        <v>164244.25</v>
-      </c>
-      <c r="N6" t="n">
-        <v>119827.2</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2.833751562079038</v>
-      </c>
-      <c r="P6" t="n">
-        <v>-1.05779693946657</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>-0.91339479358194</v>
-      </c>
-      <c r="R6" t="n">
-        <v>-0.1444021458846301</v>
-      </c>
-      <c r="S6" t="n">
-        <v>-0.3205389848969071</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.110011898157009</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>70</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>8068</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>全達</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>18.25</v>
-      </c>
-      <c r="G7" t="n">
-        <v>18.88500022888184</v>
-      </c>
-      <c r="H7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>39.60754141610299</v>
-      </c>
-      <c r="J7" t="n">
-        <v>39.4903133702184</v>
-      </c>
-      <c r="K7" t="n">
-        <v>40.9458860096721</v>
-      </c>
-      <c r="L7" t="n">
-        <v>878513.4</v>
-      </c>
-      <c r="M7" t="n">
-        <v>379437.5</v>
-      </c>
-      <c r="N7" t="n">
-        <v>371037.475</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.315304628562016</v>
-      </c>
-      <c r="P7" t="n">
-        <v>-0.2664129499493768</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>-0.3579550813990965</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.09154213144971968</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.1524060986647203</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.1303045609272203</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>70</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>8933</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>愛地雅</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>4.449999809265137</v>
-      </c>
-      <c r="G8" t="n">
-        <v>4.571500015258789</v>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>49.92448965727685</v>
-      </c>
-      <c r="J8" t="n">
-        <v>42.48194169888203</v>
-      </c>
-      <c r="K8" t="n">
-        <v>43.98098275647298</v>
-      </c>
-      <c r="L8" t="n">
-        <v>384027.4</v>
-      </c>
-      <c r="M8" t="n">
-        <v>200101.95</v>
-      </c>
-      <c r="N8" t="n">
-        <v>279903.6</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.919158708848165</v>
-      </c>
-      <c r="P8" t="n">
-        <v>-0.07569136795231213</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>-0.09288203449117542</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.01719066653886329</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.02571533590901076</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.00192428509572061</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>70</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>6542</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>隆中</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="G9" t="n">
-        <v>45.56249980926513</v>
-      </c>
-      <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>34.67897829469975</v>
-      </c>
-      <c r="J9" t="n">
-        <v>30.27584861126526</v>
-      </c>
-      <c r="K9" t="n">
-        <v>43.5821936122754</v>
-      </c>
-      <c r="L9" t="n">
-        <v>12404.2</v>
-      </c>
-      <c r="M9" t="n">
-        <v>6515.05</v>
-      </c>
-      <c r="N9" t="n">
-        <v>9269.025</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.903930131004367</v>
-      </c>
-      <c r="P9" t="n">
-        <v>-0.8137346633778009</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>-0.708488392438575</v>
-      </c>
-      <c r="R9" t="n">
-        <v>-0.1052462709392259</v>
-      </c>
-      <c r="S9" t="n">
-        <v>-0.1648962814724353</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-0.2007150562847051</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>70</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2734</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>易飛網</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>15.10000038146973</v>
-      </c>
-      <c r="G10" t="n">
-        <v>15.32250003814697</v>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>31.17042736227403</v>
-      </c>
-      <c r="J10" t="n">
-        <v>30.96456659141846</v>
-      </c>
-      <c r="K10" t="n">
-        <v>45.29687659004249</v>
-      </c>
-      <c r="L10" t="n">
-        <v>198067</v>
-      </c>
-      <c r="M10" t="n">
-        <v>113104.1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>113840.075</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.751192043436091</v>
-      </c>
-      <c r="P10" t="n">
-        <v>-0.03668867513153096</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-0.05813745009063982</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.02144877495910887</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.04397790298854817</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.02116765968602456</v>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN5"/>
+  <dimension ref="A1:AN4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,67 +625,67 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8084</t>
+          <t>8467</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>巨虹</t>
+          <t>波力-KY</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>45.90000152587891</v>
+        <v>106</v>
       </c>
       <c r="G2" t="n">
-        <v>48.05750007629395</v>
+        <v>112.4</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>35.8756218050211</v>
+        <v>32.85788319506868</v>
       </c>
       <c r="J2" t="n">
-        <v>30.75987147849812</v>
+        <v>30.61865168324583</v>
       </c>
       <c r="K2" t="n">
-        <v>44.5272808177666</v>
+        <v>35.04929709375592</v>
       </c>
       <c r="L2" t="n">
-        <v>485337.6</v>
+        <v>28205.6</v>
       </c>
       <c r="M2" t="n">
-        <v>218895.9</v>
+        <v>18504.85</v>
       </c>
       <c r="N2" t="n">
-        <v>183709.025</v>
+        <v>17663.025</v>
       </c>
       <c r="O2" t="n">
-        <v>2.21720735746992</v>
+        <v>1.524227432267757</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.5551940754673197</v>
+        <v>-5.570279770373674</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.07487438581296391</v>
+        <v>-5.153685636937238</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.4803196896543558</v>
+        <v>-0.4165941334364351</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.565319447727012</v>
+        <v>-0.6843547234775578</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5626724512850105</v>
+        <v>-0.5735970937548034</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -714,16 +714,16 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -732,35 +732,35 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>45.685</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>46.685</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>89.87400000000001</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>90.28400000000001</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -775,12 +775,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8933</t>
+          <t>8084</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>愛地雅</t>
+          <t>巨虹</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,49 +789,49 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.489999771118164</v>
+        <v>45.15000152587891</v>
       </c>
       <c r="G3" t="n">
-        <v>4.560500001907348</v>
+        <v>47.81500015258789</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>49.41201296049547</v>
+        <v>36.27912058499222</v>
       </c>
       <c r="J3" t="n">
-        <v>44.79196549558879</v>
+        <v>32.59962117763402</v>
       </c>
       <c r="K3" t="n">
-        <v>45.44137093093048</v>
+        <v>41.21223163195423</v>
       </c>
       <c r="L3" t="n">
-        <v>369411.2</v>
+        <v>436560</v>
       </c>
       <c r="M3" t="n">
-        <v>194784.15</v>
+        <v>221001.5</v>
       </c>
       <c r="N3" t="n">
-        <v>262158.325</v>
+        <v>186386.825</v>
       </c>
       <c r="O3" t="n">
-        <v>1.896515707258522</v>
+        <v>1.975371207887729</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.07437075474111676</v>
+        <v>-0.6379896738800923</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.0884481098300979</v>
+        <v>-0.1897838967006697</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01407735508898114</v>
+        <v>-0.4482057771794226</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01690111569923582</v>
+        <v>-0.4794148478108629</v>
       </c>
       <c r="T3" t="n">
-        <v>0.02540318127363995</v>
+        <v>-0.5643439693754845</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -935,49 +935,49 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>20.29999923706055</v>
+        <v>20.20000076293945</v>
       </c>
       <c r="G4" t="n">
-        <v>20.2125</v>
+        <v>20.20500001907349</v>
       </c>
       <c r="H4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>40.9688606408851</v>
+        <v>42.7597463885152</v>
       </c>
       <c r="J4" t="n">
-        <v>31.46703282413474</v>
+        <v>35.23127071541781</v>
       </c>
       <c r="K4" t="n">
-        <v>47.14458915944083</v>
+        <v>45.7454586387714</v>
       </c>
       <c r="L4" t="n">
-        <v>87504.39999999999</v>
+        <v>83823.60000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>55704.8</v>
+        <v>55487.2</v>
       </c>
       <c r="N4" t="n">
-        <v>47456.65</v>
+        <v>46322.85</v>
       </c>
       <c r="O4" t="n">
-        <v>1.57085924372765</v>
+        <v>1.51068354503381</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3334119032471357</v>
+        <v>-0.2993001283403061</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.4091098781738601</v>
+        <v>-0.3853187760542733</v>
       </c>
       <c r="R4" t="n">
-        <v>0.07569797492672448</v>
+        <v>0.08601864771396722</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0475986263288366</v>
+        <v>0.07497410559398004</v>
       </c>
       <c r="T4" t="n">
-        <v>0.02028505979641304</v>
+        <v>0.04681824811301544</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1052,153 +1052,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>70</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2640</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>大車隊</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>145.5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>155.65</v>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>41.27404993797341</v>
-      </c>
-      <c r="J5" t="n">
-        <v>40.52157756083262</v>
-      </c>
-      <c r="K5" t="n">
-        <v>34.32135061995112</v>
-      </c>
-      <c r="L5" t="n">
-        <v>83221.2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>53606.8</v>
-      </c>
-      <c r="N5" t="n">
-        <v>43205.05</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.55243737734765</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-1.099771171544603</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-0.8383830026452952</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-0.2613881688993078</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.6317946971398203</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.4370486908930771</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN4"/>
+  <dimension ref="A1:AN5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,67 +625,67 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8467</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>波力-KY</t>
+          <t>邑昇</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>106</v>
+        <v>55.5</v>
       </c>
       <c r="G2" t="n">
-        <v>112.4</v>
+        <v>55.83000011444092</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>32.85788319506868</v>
+        <v>49.26529001912529</v>
       </c>
       <c r="J2" t="n">
-        <v>30.61865168324583</v>
+        <v>35.1975473129655</v>
       </c>
       <c r="K2" t="n">
-        <v>35.04929709375592</v>
+        <v>44.39500964519441</v>
       </c>
       <c r="L2" t="n">
-        <v>28205.6</v>
+        <v>1302234.8</v>
       </c>
       <c r="M2" t="n">
-        <v>18504.85</v>
+        <v>627856.4</v>
       </c>
       <c r="N2" t="n">
-        <v>17663.025</v>
+        <v>667935.975</v>
       </c>
       <c r="O2" t="n">
-        <v>1.524227432267757</v>
+        <v>2.07409656093336</v>
       </c>
       <c r="P2" t="n">
-        <v>-5.570279770373674</v>
+        <v>-2.918690412826969</v>
       </c>
       <c r="Q2" t="n">
-        <v>-5.153685636937238</v>
+        <v>-3.055934626252182</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.4165941334364351</v>
+        <v>0.1372442134252134</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6843547234775578</v>
+        <v>-0.1611412945466038</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5735970937548034</v>
+        <v>-0.4158665740165679</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -732,35 +732,35 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>45.685</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>46.685</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>89.87400000000001</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>90.28400000000001</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -775,63 +775,63 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8084</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>巨虹</t>
+          <t>華友聯</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>45.15000152587891</v>
+        <v>45.29999923706055</v>
       </c>
       <c r="G3" t="n">
-        <v>47.81500015258789</v>
+        <v>45.03500003814698</v>
       </c>
       <c r="H3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>36.27912058499222</v>
+        <v>38.0633537962413</v>
       </c>
       <c r="J3" t="n">
-        <v>32.59962117763402</v>
+        <v>35.41369255004497</v>
       </c>
       <c r="K3" t="n">
-        <v>41.21223163195423</v>
+        <v>49.03393807751447</v>
       </c>
       <c r="L3" t="n">
-        <v>436560</v>
+        <v>845410.2</v>
       </c>
       <c r="M3" t="n">
-        <v>221001.5</v>
+        <v>440905.1</v>
       </c>
       <c r="N3" t="n">
-        <v>186386.825</v>
+        <v>452494.05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.975371207887729</v>
+        <v>1.917442551696499</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.6379896738800923</v>
+        <v>-0.2430312662000063</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1897838967006697</v>
+        <v>-0.3030944666828437</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.4482057771794226</v>
+        <v>0.06006320048283742</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4794148478108629</v>
+        <v>0.02987557570830524</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5643439693754845</v>
+        <v>0.03984088877664077</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -869,44 +869,44 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>-589</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>-593</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>-858.0250000000001</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>-51</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>-905.0250000000001</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>-509.0120000000002</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>-53</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>-560.0120000000002</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -938,46 +938,46 @@
         <v>20.20000076293945</v>
       </c>
       <c r="G4" t="n">
-        <v>20.20500001907349</v>
+        <v>20.17250003814697</v>
       </c>
       <c r="H4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>42.7597463885152</v>
+        <v>43.95367022039003</v>
       </c>
       <c r="J4" t="n">
-        <v>35.23127071541781</v>
+        <v>38.1387372558313</v>
       </c>
       <c r="K4" t="n">
-        <v>45.7454586387714</v>
+        <v>45.64962671899151</v>
       </c>
       <c r="L4" t="n">
-        <v>83823.60000000001</v>
+        <v>77415.60000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>55487.2</v>
+        <v>45835.2</v>
       </c>
       <c r="N4" t="n">
-        <v>46322.85</v>
+        <v>45421.8</v>
       </c>
       <c r="O4" t="n">
-        <v>1.51068354503381</v>
+        <v>1.688998848046916</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2993001283403061</v>
+        <v>-0.2689405201200223</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.3853187760542733</v>
+        <v>-0.3602139552702887</v>
       </c>
       <c r="R4" t="n">
-        <v>0.08601864771396722</v>
+        <v>0.09127343515026631</v>
       </c>
       <c r="S4" t="n">
-        <v>0.07497410559398004</v>
+        <v>0.08529477147782127</v>
       </c>
       <c r="T4" t="n">
-        <v>0.04681824811301544</v>
+        <v>0.07419371993584029</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1052,7 +1052,153 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>8084</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>巨虹</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>47.47000007629394</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>34.20939538696949</v>
+      </c>
+      <c r="J5" t="n">
+        <v>33.13621256361159</v>
+      </c>
+      <c r="K5" t="n">
+        <v>39.26466357509607</v>
+      </c>
+      <c r="L5" t="n">
+        <v>365122.2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>228057.05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>189364.525</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.601012553657079</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.7368637651379686</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.2877676040166894</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-0.4490961611212791</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0.4527299863968442</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.4842922395684474</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN5"/>
+  <dimension ref="A1:AN4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,16 +625,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5291</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>邑昇</t>
+          <t>唐榮公司</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,85 +643,85 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>55.5</v>
+        <v>27.14999961853027</v>
       </c>
       <c r="G2" t="n">
-        <v>55.83000011444092</v>
+        <v>27.5149998664856</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>49.26529001912529</v>
+        <v>49.83306999249291</v>
       </c>
       <c r="J2" t="n">
-        <v>35.1975473129655</v>
+        <v>47.64194429267808</v>
       </c>
       <c r="K2" t="n">
-        <v>44.39500964519441</v>
+        <v>39.1739330435076</v>
       </c>
       <c r="L2" t="n">
-        <v>1302234.8</v>
+        <v>16196.8</v>
       </c>
       <c r="M2" t="n">
-        <v>627856.4</v>
+        <v>6976.8</v>
       </c>
       <c r="N2" t="n">
-        <v>667935.975</v>
+        <v>9117.075000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>2.07409656093336</v>
+        <v>2.321522761151244</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.918690412826969</v>
+        <v>-0.1865601932667609</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.055934626252182</v>
+        <v>-0.1441891173971516</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1372442134252134</v>
+        <v>-0.04237107586960931</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1611412945466038</v>
+        <v>-0.04758554020620895</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4158665740165679</v>
+        <v>-0.04998187987610092</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
@@ -760,7 +760,7 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
@@ -775,63 +775,63 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1436</t>
+          <t>2751</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>華友聯</t>
+          <t>王座</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>45.29999923706055</v>
+        <v>52.09999847412109</v>
       </c>
       <c r="G3" t="n">
-        <v>45.03500003814698</v>
+        <v>52.55499992370606</v>
       </c>
       <c r="H3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>38.0633537962413</v>
+        <v>39.34790204908366</v>
       </c>
       <c r="J3" t="n">
-        <v>35.41369255004497</v>
+        <v>36.25546211227984</v>
       </c>
       <c r="K3" t="n">
-        <v>49.03393807751447</v>
+        <v>46.80559264960826</v>
       </c>
       <c r="L3" t="n">
-        <v>845410.2</v>
+        <v>15405.2</v>
       </c>
       <c r="M3" t="n">
-        <v>440905.1</v>
+        <v>9373.200000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>452494.05</v>
+        <v>11182.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.917442551696499</v>
+        <v>1.643536892416677</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2430312662000063</v>
+        <v>-0.2110553018158257</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.3030944666828437</v>
+        <v>-0.09728628642002171</v>
       </c>
       <c r="R3" t="n">
-        <v>0.06006320048283742</v>
+        <v>-0.1137690153958039</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02987557570830524</v>
+        <v>-0.1404200220469684</v>
       </c>
       <c r="T3" t="n">
-        <v>0.03984088877664077</v>
+        <v>-0.1396495271129342</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -869,44 +869,44 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>-589</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-593</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-858.0250000000001</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>-51</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-905.0250000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-509.0120000000002</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-53</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-560.0120000000002</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
@@ -935,49 +935,49 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>20.20000076293945</v>
+        <v>20.35000038146973</v>
       </c>
       <c r="G4" t="n">
-        <v>20.17250003814697</v>
+        <v>20.15500001907349</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>43.95367022039003</v>
+        <v>47.18863853545523</v>
       </c>
       <c r="J4" t="n">
-        <v>38.1387372558313</v>
+        <v>41.1553710285566</v>
       </c>
       <c r="K4" t="n">
-        <v>45.64962671899151</v>
+        <v>48.31259158620566</v>
       </c>
       <c r="L4" t="n">
-        <v>77415.60000000001</v>
+        <v>73879</v>
       </c>
       <c r="M4" t="n">
-        <v>45835.2</v>
+        <v>46951.05</v>
       </c>
       <c r="N4" t="n">
-        <v>45421.8</v>
+        <v>45679.725</v>
       </c>
       <c r="O4" t="n">
-        <v>1.688998848046916</v>
+        <v>1.573532434311906</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2689405201200223</v>
+        <v>-0.2295390422657952</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.3602139552702887</v>
+        <v>-0.3317925193951066</v>
       </c>
       <c r="R4" t="n">
-        <v>0.09127343515026631</v>
+        <v>0.1022534771293113</v>
       </c>
       <c r="S4" t="n">
-        <v>0.08529477147782127</v>
+        <v>0.09036859330678348</v>
       </c>
       <c r="T4" t="n">
-        <v>0.07419371993584029</v>
+        <v>0.08431929312630621</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1052,153 +1052,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>70</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>8084</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>巨虹</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>47.47000007629394</v>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>34.20939538696949</v>
-      </c>
-      <c r="J5" t="n">
-        <v>33.13621256361159</v>
-      </c>
-      <c r="K5" t="n">
-        <v>39.26466357509607</v>
-      </c>
-      <c r="L5" t="n">
-        <v>365122.2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>228057.05</v>
-      </c>
-      <c r="N5" t="n">
-        <v>189364.525</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.601012553657079</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-0.7368637651379686</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-0.2877676040166894</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-0.4490961611212791</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-0.4527299863968442</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-0.4842922395684474</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN4"/>
+  <dimension ref="A1:AN3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -652,25 +652,25 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>49.83306999249291</v>
+        <v>49.8330699905806</v>
       </c>
       <c r="J2" t="n">
-        <v>47.64194429267808</v>
+        <v>47.64194425698173</v>
       </c>
       <c r="K2" t="n">
-        <v>39.1739330435076</v>
+        <v>37.94624845723428</v>
       </c>
       <c r="L2" t="n">
-        <v>16196.8</v>
+        <v>16000.4</v>
       </c>
       <c r="M2" t="n">
-        <v>6976.8</v>
+        <v>6927.7</v>
       </c>
       <c r="N2" t="n">
-        <v>9117.075000000001</v>
+        <v>9092.525</v>
       </c>
       <c r="O2" t="n">
-        <v>2.321522761151244</v>
+        <v>2.309626571589416</v>
       </c>
       <c r="P2" t="n">
         <v>-0.1865601932667609</v>
@@ -789,49 +789,49 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>52.09999847412109</v>
+        <v>52.5</v>
       </c>
       <c r="G3" t="n">
-        <v>52.55499992370606</v>
+        <v>52.58999996185302</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>39.34790204908366</v>
+        <v>47.06526306718108</v>
       </c>
       <c r="J3" t="n">
-        <v>36.25546211227984</v>
+        <v>39.85872912545572</v>
       </c>
       <c r="K3" t="n">
-        <v>46.80559264960826</v>
+        <v>49.12045611022323</v>
       </c>
       <c r="L3" t="n">
-        <v>15405.2</v>
+        <v>14029.2</v>
       </c>
       <c r="M3" t="n">
-        <v>9373.200000000001</v>
+        <v>8479.200000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>11182.5</v>
+        <v>10785.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.643536892416677</v>
+        <v>1.654542881403906</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2110553018158257</v>
+        <v>-0.1774209384618715</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.09728628642002171</v>
+        <v>-0.1123986494740864</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.1137690153958039</v>
+        <v>-0.06502228898778503</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1404200220469684</v>
+        <v>-0.1141309466104727</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1396495271129342</v>
+        <v>-0.1408102074337269</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -906,153 +906,7 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>70</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>8426</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>紅木-KY</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>20.35000038146973</v>
-      </c>
-      <c r="G4" t="n">
-        <v>20.15500001907349</v>
-      </c>
-      <c r="H4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>47.18863853545523</v>
-      </c>
-      <c r="J4" t="n">
-        <v>41.1553710285566</v>
-      </c>
-      <c r="K4" t="n">
-        <v>48.31259158620566</v>
-      </c>
-      <c r="L4" t="n">
-        <v>73879</v>
-      </c>
-      <c r="M4" t="n">
-        <v>46951.05</v>
-      </c>
-      <c r="N4" t="n">
-        <v>45679.725</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.573532434311906</v>
-      </c>
-      <c r="P4" t="n">
-        <v>-0.2295390422657952</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-0.3317925193951066</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.1022534771293113</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.09036859330678348</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.08431929312630621</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN3"/>
+  <dimension ref="A1:AN4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,91 +625,91 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>3652</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>唐榮公司</t>
+          <t>精聯</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>27.14999961853027</v>
+        <v>31.39999961853027</v>
       </c>
       <c r="G2" t="n">
-        <v>27.5149998664856</v>
+        <v>33.6875</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>49.8330699905806</v>
+        <v>44.13013348865657</v>
       </c>
       <c r="J2" t="n">
-        <v>47.64194425698173</v>
+        <v>39.91344157871029</v>
       </c>
       <c r="K2" t="n">
-        <v>37.94624845723428</v>
+        <v>42.71148934424366</v>
       </c>
       <c r="L2" t="n">
-        <v>16000.4</v>
+        <v>1350530.6</v>
       </c>
       <c r="M2" t="n">
-        <v>6927.7</v>
+        <v>609163.3</v>
       </c>
       <c r="N2" t="n">
-        <v>9092.525</v>
+        <v>808351.85</v>
       </c>
       <c r="O2" t="n">
-        <v>2.309626571589416</v>
+        <v>2.217025549635049</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1865601932667609</v>
+        <v>-1.127652833777312</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1441891173971516</v>
+        <v>-1.006228062944556</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.04237107586960931</v>
+        <v>-0.1214247708327556</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.04758554020620895</v>
+        <v>-0.1318384217320637</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.04998187987610092</v>
+        <v>-0.2199590984878159</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -723,44 +723,44 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>-29</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>3.944</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>-25.056</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>-257</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>-32.057</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>-289.057</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>-270.9559999999999</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>-3.999999999999998</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>-274.9559999999999</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -775,63 +775,63 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2751</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>王座</t>
+          <t>生達</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>52.5</v>
+        <v>57.40000152587891</v>
       </c>
       <c r="G3" t="n">
-        <v>52.58999996185302</v>
+        <v>57.77727165222168</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>47.06526306718108</v>
+        <v>36.57801494350952</v>
       </c>
       <c r="J3" t="n">
-        <v>39.85872912545572</v>
+        <v>35.20106079383939</v>
       </c>
       <c r="K3" t="n">
-        <v>49.12045611022323</v>
+        <v>49.21019473898105</v>
       </c>
       <c r="L3" t="n">
-        <v>14029.2</v>
+        <v>602525.2</v>
       </c>
       <c r="M3" t="n">
-        <v>8479.200000000001</v>
+        <v>334634.55</v>
       </c>
       <c r="N3" t="n">
-        <v>10785.5</v>
+        <v>318407.975</v>
       </c>
       <c r="O3" t="n">
-        <v>1.654542881403906</v>
+        <v>1.800546895112892</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1774209384618715</v>
+        <v>-0.003754820233730527</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1123986494740864</v>
+        <v>0.1910387308674334</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.06502228898778503</v>
+        <v>-0.1947935511011639</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1141309466104727</v>
+        <v>-0.2353559295928513</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1408102074337269</v>
+        <v>-0.1922376129839459</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -869,44 +869,190 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.994</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>161.994</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>-444.877</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
+        <v>-9.893000000000004</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-454.77</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>-127.665</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>12.935</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>-110.7299999999999</v>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>70</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>4977</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>眾達-KY</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>133.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>147.025</v>
+      </c>
+      <c r="H4" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="I4" t="n">
+        <v>45.39117077898095</v>
+      </c>
+      <c r="J4" t="n">
+        <v>38.09574202949952</v>
+      </c>
+      <c r="K4" t="n">
+        <v>34.27596285977708</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3589132.4</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2015423.9</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2496313.85</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.780832508734267</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-12.57111785485813</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-13.07597140553331</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.504853550675179</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.3181876274074771</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.3742096456516855</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>-117.376</v>
+      </c>
+      <c r="AC4" t="n">
         <v>0</v>
       </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
+      <c r="AD4" t="n">
+        <v>-16.152</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-133.528</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-1310.282</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-76</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>63.00700000000001</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-1323.275</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1103.046</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-133</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-90.22200000000001</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>879.8240000000003</v>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN4"/>
+  <dimension ref="A1:AN5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,16 +625,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3652</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>精聯</t>
+          <t>興農</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,124 +643,124 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>31.39999961853027</v>
+        <v>39.34999847412109</v>
       </c>
       <c r="G2" t="n">
-        <v>33.6875</v>
+        <v>39.56999969482422</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>44.13013348865657</v>
+        <v>42.72070132877298</v>
       </c>
       <c r="J2" t="n">
-        <v>39.91344157871029</v>
+        <v>41.65731820839675</v>
       </c>
       <c r="K2" t="n">
-        <v>42.71148934424366</v>
+        <v>48.54670661032442</v>
       </c>
       <c r="L2" t="n">
-        <v>1350530.6</v>
+        <v>1401621.6</v>
       </c>
       <c r="M2" t="n">
-        <v>609163.3</v>
+        <v>850898.8</v>
       </c>
       <c r="N2" t="n">
-        <v>808351.85</v>
+        <v>814850.65</v>
       </c>
       <c r="O2" t="n">
-        <v>2.217025549635049</v>
+        <v>1.64722479335968</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.127652833777312</v>
+        <v>-0.1004435415026492</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.006228062944556</v>
+        <v>-0.08245384584511388</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.1214247708327556</v>
+        <v>-0.01798969565753535</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1318384217320637</v>
+        <v>-0.02580571645444142</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2199590984878159</v>
+        <v>-0.03498361448523332</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>-29</v>
+        <v>246.563</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>-11.551</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.944</v>
+        <v>11.671</v>
       </c>
       <c r="AE2" t="n">
-        <v>-25.056</v>
+        <v>246.683</v>
       </c>
       <c r="AF2" t="n">
-        <v>-257</v>
+        <v>-2074.436</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>425.713</v>
       </c>
       <c r="AH2" t="n">
-        <v>-32.057</v>
+        <v>-8.450000000000003</v>
       </c>
       <c r="AI2" t="n">
-        <v>-289.057</v>
+        <v>-1657.173</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-270.9559999999999</v>
+        <v>-2305.689</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1677.163</v>
       </c>
       <c r="AL2" t="n">
-        <v>-3.999999999999998</v>
+        <v>-13.546</v>
       </c>
       <c r="AM2" t="n">
-        <v>-274.9559999999999</v>
+        <v>-642.072</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -771,142 +771,142 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1720</t>
+          <t>8916</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>生達</t>
+          <t>光隆</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>57.40000152587891</v>
+        <v>42.25</v>
       </c>
       <c r="G3" t="n">
-        <v>57.77727165222168</v>
+        <v>43.00500011444092</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>36.57801494350952</v>
+        <v>44.21288509338461</v>
       </c>
       <c r="J3" t="n">
-        <v>35.20106079383939</v>
+        <v>31.35177985213548</v>
       </c>
       <c r="K3" t="n">
-        <v>49.21019473898105</v>
+        <v>36.24235597766285</v>
       </c>
       <c r="L3" t="n">
-        <v>602525.2</v>
+        <v>223499.4</v>
       </c>
       <c r="M3" t="n">
-        <v>334634.55</v>
+        <v>133408.95</v>
       </c>
       <c r="N3" t="n">
-        <v>318407.975</v>
+        <v>145992.175</v>
       </c>
       <c r="O3" t="n">
-        <v>1.800546895112892</v>
+        <v>1.675295398097354</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.003754820233730527</v>
+        <v>-0.6068734813551089</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1910387308674334</v>
+        <v>-0.584549679306668</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.1947935511011639</v>
+        <v>-0.02232380204844087</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2353559295928513</v>
+        <v>-0.05267192304641011</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1922376129839459</v>
+        <v>-0.09335515061116761</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
       <c r="AB3" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.994</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>161.994</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-444.877</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-9.893000000000004</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-454.77</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-127.665</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>12.935</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-110.7299999999999</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -921,138 +921,284 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4977</t>
+          <t>6649</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>眾達-KY</t>
+          <t>台生材</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>37.15000152587891</v>
+      </c>
+      <c r="G4" t="n">
+        <v>38.34000034332276</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>44.16968006862696</v>
+      </c>
+      <c r="J4" t="n">
+        <v>39.32159634174506</v>
+      </c>
+      <c r="K4" t="n">
+        <v>41.94161939774651</v>
+      </c>
+      <c r="L4" t="n">
+        <v>109675.6</v>
+      </c>
+      <c r="M4" t="n">
+        <v>62505.35</v>
+      </c>
+      <c r="N4" t="n">
+        <v>49886.225</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.754659401155261</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0.3034357607818023</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0.1448958706477065</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-0.1585398901340958</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-0.1521015714460309</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.1937588218205099</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1720</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>生達</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>133.5</v>
-      </c>
-      <c r="G4" t="n">
-        <v>147.025</v>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>45.39117077898095</v>
-      </c>
-      <c r="J4" t="n">
-        <v>38.09574202949952</v>
-      </c>
-      <c r="K4" t="n">
-        <v>34.27596285977708</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3589132.4</v>
-      </c>
-      <c r="M4" t="n">
-        <v>2015423.9</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2496313.85</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.780832508734267</v>
-      </c>
-      <c r="P4" t="n">
-        <v>-12.57111785485813</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-13.07597140553331</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.504853550675179</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.3181876274074771</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-0.3742096456516855</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="F5" t="n">
+        <v>57.29999923706055</v>
+      </c>
+      <c r="G5" t="n">
+        <v>57.76499900817871</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>42.54838324347861</v>
+      </c>
+      <c r="J5" t="n">
+        <v>37.65016827276895</v>
+      </c>
+      <c r="K5" t="n">
+        <v>48.76280474245878</v>
+      </c>
+      <c r="L5" t="n">
+        <v>594362</v>
+      </c>
+      <c r="M5" t="n">
+        <v>343774.35</v>
+      </c>
+      <c r="N5" t="n">
+        <v>318551.2</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.728930619751008</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.01740592068224345</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.1501812634852412</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-0.1675871841674847</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0.1951225945400948</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.2357106598185792</v>
+      </c>
+      <c r="U5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AB4" t="n">
-        <v>-117.376</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>-16.152</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-133.528</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>-1310.282</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-76</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>63.00700000000001</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>-1323.275</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1103.046</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>-133</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>-90.22200000000001</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>879.8240000000003</v>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
+      <c r="AB5" t="n">
+        <v>131</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>146</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-306.407</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>9.106999999999999</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-297.3</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-35.66499999999995</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>27.935</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-4.729999999999947</v>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN5"/>
+  <dimension ref="A1:AN2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,91 +625,91 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1712</t>
+          <t>4577</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>興農</t>
+          <t>達航科技</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>39.34999847412109</v>
+        <v>69.59999847412109</v>
       </c>
       <c r="G2" t="n">
-        <v>39.56999969482422</v>
+        <v>78.35000038146973</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>42.72070132877298</v>
+        <v>38.33487739958224</v>
       </c>
       <c r="J2" t="n">
-        <v>41.65731820839675</v>
+        <v>32.41159915147696</v>
       </c>
       <c r="K2" t="n">
-        <v>48.54670661032442</v>
+        <v>34.208523285109</v>
       </c>
       <c r="L2" t="n">
-        <v>1401621.6</v>
+        <v>1126782</v>
       </c>
       <c r="M2" t="n">
-        <v>850898.8</v>
+        <v>575945.3</v>
       </c>
       <c r="N2" t="n">
-        <v>814850.65</v>
+        <v>706902.725</v>
       </c>
       <c r="O2" t="n">
-        <v>1.64722479335968</v>
+        <v>1.956404540500634</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1004435415026492</v>
+        <v>-7.293168775345393</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.08245384584511388</v>
+        <v>-7.988726484222813</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.01798969565753535</v>
+        <v>0.6955577088774199</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.02580571645444142</v>
+        <v>0.7595214804822987</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.03498361448523332</v>
+        <v>0.1327776485277106</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -719,486 +719,48 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>246.563</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-11.551</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>11.671</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>246.683</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>-2074.436</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>425.713</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-8.450000000000003</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>-1657.173</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-2305.689</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1677.163</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-13.546</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-642.072</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>80</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>8916</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>光隆</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>42.25</v>
-      </c>
-      <c r="G3" t="n">
-        <v>43.00500011444092</v>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>44.21288509338461</v>
-      </c>
-      <c r="J3" t="n">
-        <v>31.35177985213548</v>
-      </c>
-      <c r="K3" t="n">
-        <v>36.24235597766285</v>
-      </c>
-      <c r="L3" t="n">
-        <v>223499.4</v>
-      </c>
-      <c r="M3" t="n">
-        <v>133408.95</v>
-      </c>
-      <c r="N3" t="n">
-        <v>145992.175</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.675295398097354</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-0.6068734813551089</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-0.584549679306668</v>
-      </c>
-      <c r="R3" t="n">
-        <v>-0.02232380204844087</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-0.05267192304641011</v>
-      </c>
-      <c r="T3" t="n">
-        <v>-0.09335515061116761</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>70</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>6649</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>台生材</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>37.15000152587891</v>
-      </c>
-      <c r="G4" t="n">
-        <v>38.34000034332276</v>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>44.16968006862696</v>
-      </c>
-      <c r="J4" t="n">
-        <v>39.32159634174506</v>
-      </c>
-      <c r="K4" t="n">
-        <v>41.94161939774651</v>
-      </c>
-      <c r="L4" t="n">
-        <v>109675.6</v>
-      </c>
-      <c r="M4" t="n">
-        <v>62505.35</v>
-      </c>
-      <c r="N4" t="n">
-        <v>49886.225</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.754659401155261</v>
-      </c>
-      <c r="P4" t="n">
-        <v>-0.3034357607818023</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-0.1448958706477065</v>
-      </c>
-      <c r="R4" t="n">
-        <v>-0.1585398901340958</v>
-      </c>
-      <c r="S4" t="n">
-        <v>-0.1521015714460309</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-0.1937588218205099</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>70</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1720</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>生達</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>57.29999923706055</v>
-      </c>
-      <c r="G5" t="n">
-        <v>57.76499900817871</v>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>42.54838324347861</v>
-      </c>
-      <c r="J5" t="n">
-        <v>37.65016827276895</v>
-      </c>
-      <c r="K5" t="n">
-        <v>48.76280474245878</v>
-      </c>
-      <c r="L5" t="n">
-        <v>594362</v>
-      </c>
-      <c r="M5" t="n">
-        <v>343774.35</v>
-      </c>
-      <c r="N5" t="n">
-        <v>318551.2</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.728930619751008</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-0.01740592068224345</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.1501812634852412</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-0.1675871841674847</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-0.1951225945400948</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-0.2357106598185792</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>131</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>146</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-306.407</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>9.106999999999999</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-297.3</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>-35.66499999999995</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>27.935</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>-4.729999999999947</v>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN2"/>
+  <dimension ref="A1:AN6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,138 +629,722 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4577</t>
+          <t>4976</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>達航科技</t>
+          <t>佳凌</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>33.95000076293945</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.26500015258789</v>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>47.93055846826567</v>
+      </c>
+      <c r="J2" t="n">
+        <v>37.44693596324654</v>
+      </c>
+      <c r="K2" t="n">
+        <v>47.3470508715186</v>
+      </c>
+      <c r="L2" t="n">
+        <v>9827387</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3662809.35</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4782514.1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.683018978315101</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-0.6080242143534775</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-0.639508366949287</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.0314841525958095</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.03093964680166039</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-0.3449185211009841</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>63.051</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>25.672</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>88.723</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-73.43299999999999</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>23.597</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-49.836</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>-1129.709</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>96.08500000000002</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>-1033.624</v>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>70</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3504</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>揚明光</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>62.29999923706055</v>
+      </c>
+      <c r="G3" t="n">
+        <v>69.67499961853028</v>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>35.05914720958852</v>
+      </c>
+      <c r="J3" t="n">
+        <v>30.72013709628708</v>
+      </c>
+      <c r="K3" t="n">
+        <v>40.04124041782145</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5062645.4</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2042147.95</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2701877.9</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.479078658331293</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-4.024179035534061</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-3.732453267681879</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-0.2917257678521823</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-0.286339942443782</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-0.8420237306644358</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>112.265</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-19.2</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>93.065</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-693.8860000000001</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>46.24</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-647.6460000000001</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>-1366.246</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>47.015</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>-1319.231</v>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>70</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>6668</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>中揚光</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>33.45000076293945</v>
+      </c>
+      <c r="G4" t="n">
+        <v>36.02000045776367</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>34.98295083556545</v>
+      </c>
+      <c r="J4" t="n">
+        <v>32.05205440633399</v>
+      </c>
+      <c r="K4" t="n">
+        <v>39.96829280187428</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1994398.2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>849035.15</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1454013.8</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.349017234445476</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-1.253559240789265</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-1.235001667422441</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-0.0185575733668244</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.04719267149380535</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.2106839967888852</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>-441</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-10.256</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-451.256</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-450.86</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-441.86</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-1176.934</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-1167.934</v>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3362</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>先進光</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>69.59999847412109</v>
-      </c>
-      <c r="G2" t="n">
-        <v>78.35000038146973</v>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>38.33487739958224</v>
-      </c>
-      <c r="J2" t="n">
-        <v>32.41159915147696</v>
-      </c>
-      <c r="K2" t="n">
-        <v>34.208523285109</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1126782</v>
-      </c>
-      <c r="M2" t="n">
-        <v>575945.3</v>
-      </c>
-      <c r="N2" t="n">
-        <v>706902.725</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.956404540500634</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-7.293168775345393</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-7.988726484222813</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.6955577088774199</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.7595214804822987</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.1327776485277106</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
+      <c r="F5" t="n">
+        <v>156.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>166.325</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>48.11954056480939</v>
+      </c>
+      <c r="J5" t="n">
+        <v>41.32630902274443</v>
+      </c>
+      <c r="K5" t="n">
+        <v>46.41697117073114</v>
+      </c>
+      <c r="L5" t="n">
+        <v>16150780.2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>6887759.25</v>
+      </c>
+      <c r="N5" t="n">
+        <v>7904251.15</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.344852602099877</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-2.330188132775504</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-1.137737576462119</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-1.192450556313385</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-1.027540058034051</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-2.397189504563602</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>70</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>7736</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>虎山</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>70.30000305175781</v>
+      </c>
+      <c r="G6" t="n">
+        <v>70.56000099182128</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>42.63244602991772</v>
+      </c>
+      <c r="J6" t="n">
+        <v>33.72584740295127</v>
+      </c>
+      <c r="K6" t="n">
+        <v>43.73986908984457</v>
+      </c>
+      <c r="L6" t="n">
+        <v>106734</v>
+      </c>
+      <c r="M6" t="n">
+        <v>49335.55</v>
+      </c>
+      <c r="N6" t="n">
+        <v>39106.825</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.163429818862868</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.3724422166457941</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.4431130542417397</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.07067083759594561</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.07579418211935146</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.09451380093351103</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-19.7</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-14.7</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>30.621</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>34.621</v>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN6"/>
+  <dimension ref="A1:AN7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,16 +625,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4976</t>
+          <t>6226</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>佳凌</t>
+          <t>光鼎</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,49 +643,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>33.95000076293945</v>
+        <v>19.60000038146973</v>
       </c>
       <c r="G2" t="n">
-        <v>35.26500015258789</v>
+        <v>22.40749979019165</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>47.93055846826567</v>
+        <v>36.62543547705081</v>
       </c>
       <c r="J2" t="n">
-        <v>37.44693596324654</v>
+        <v>32.17428295812243</v>
       </c>
       <c r="K2" t="n">
-        <v>47.3470508715186</v>
+        <v>47.65781818601891</v>
       </c>
       <c r="L2" t="n">
-        <v>9827387</v>
+        <v>24115229.2</v>
       </c>
       <c r="M2" t="n">
-        <v>3662809.35</v>
+        <v>10728857</v>
       </c>
       <c r="N2" t="n">
-        <v>4782514.1</v>
+        <v>8614053.6</v>
       </c>
       <c r="O2" t="n">
-        <v>2.683018978315101</v>
+        <v>2.247697886177437</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.6080242143534775</v>
+        <v>0.219447890353937</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.639508366949287</v>
+        <v>0.8038565960360959</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0314841525958095</v>
+        <v>-0.584408705682159</v>
       </c>
       <c r="S2" t="n">
-        <v>0.03093964680166039</v>
+        <v>-0.6023636329421964</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3449185211009841</v>
+        <v>-0.665720592302341</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -719,48 +719,48 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>63.051</v>
+        <v>-956.48</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>25.672</v>
+        <v>2</v>
       </c>
       <c r="AE2" t="n">
-        <v>88.723</v>
+        <v>-946.48</v>
       </c>
       <c r="AF2" t="n">
-        <v>-73.43299999999999</v>
+        <v>-736.039</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH2" t="n">
-        <v>23.597</v>
+        <v>-61.16</v>
       </c>
       <c r="AI2" t="n">
-        <v>-49.836</v>
+        <v>-782.199</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-1129.709</v>
+        <v>-3009.125999999999</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>303</v>
       </c>
       <c r="AL2" t="n">
-        <v>96.08500000000002</v>
+        <v>182.832</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1033.624</v>
+        <v>-2523.294</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
@@ -789,50 +789,50 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>62.29999923706055</v>
+        <v>68.5</v>
       </c>
       <c r="G3" t="n">
-        <v>69.67499961853028</v>
+        <v>69.16999969482421</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>35.05914720958852</v>
+        <v>39.91777419416688</v>
       </c>
       <c r="J3" t="n">
-        <v>30.72013709628708</v>
+        <v>33.78601612891368</v>
       </c>
       <c r="K3" t="n">
-        <v>40.04124041782145</v>
+        <v>48.05982285185477</v>
       </c>
       <c r="L3" t="n">
-        <v>5062645.4</v>
+        <v>5403568.6</v>
       </c>
       <c r="M3" t="n">
-        <v>2042147.95</v>
+        <v>2122876.9</v>
       </c>
       <c r="N3" t="n">
-        <v>2701877.9</v>
+        <v>2708841.2</v>
       </c>
       <c r="O3" t="n">
-        <v>2.479078658331293</v>
+        <v>2.545398934813413</v>
       </c>
       <c r="P3" t="n">
-        <v>-4.024179035534061</v>
+        <v>-3.545092172350891</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.732453267681879</v>
+        <v>-3.694981048615682</v>
       </c>
       <c r="R3" t="n">
+        <v>0.1498888762647903</v>
+      </c>
+      <c r="S3" t="n">
         <v>-0.2917257678521823</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>-0.286339942443782</v>
       </c>
-      <c r="T3" t="n">
-        <v>-0.8420237306644358</v>
-      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>否</t>
@@ -869,44 +869,44 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>112.265</v>
+        <v>69.001</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>-19.2</v>
+        <v>60.994</v>
       </c>
       <c r="AE3" t="n">
-        <v>93.065</v>
+        <v>129.995</v>
       </c>
       <c r="AF3" t="n">
-        <v>-693.8860000000001</v>
+        <v>-512.9349999999999</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>46.24</v>
+        <v>108.021</v>
       </c>
       <c r="AI3" t="n">
-        <v>-647.6460000000001</v>
+        <v>-404.914</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-1366.246</v>
+        <v>-1368.825</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>47.015</v>
+        <v>107.853</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1319.231</v>
+        <v>-1260.972</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
@@ -935,50 +935,50 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>33.45000076293945</v>
+        <v>35.54999923706055</v>
       </c>
       <c r="G4" t="n">
-        <v>36.02000045776367</v>
+        <v>35.80250034332276</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>34.98295083556545</v>
+        <v>35.82196154707592</v>
       </c>
       <c r="J4" t="n">
-        <v>32.05205440633399</v>
+        <v>33.30869011991463</v>
       </c>
       <c r="K4" t="n">
-        <v>39.96829280187428</v>
+        <v>47.59537604715646</v>
       </c>
       <c r="L4" t="n">
-        <v>1994398.2</v>
+        <v>2229286.4</v>
       </c>
       <c r="M4" t="n">
-        <v>849035.15</v>
+        <v>886358.7</v>
       </c>
       <c r="N4" t="n">
-        <v>1454013.8</v>
+        <v>1476373.075</v>
       </c>
       <c r="O4" t="n">
-        <v>2.349017234445476</v>
+        <v>2.515106355925654</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.253559240789265</v>
+        <v>-1.126900996535973</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.235001667422441</v>
+        <v>-1.213381533245147</v>
       </c>
       <c r="R4" t="n">
+        <v>0.08648053670917433</v>
+      </c>
+      <c r="S4" t="n">
         <v>-0.0185575733668244</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>0.04719267149380535</v>
       </c>
-      <c r="T4" t="n">
-        <v>-0.2106839967888852</v>
-      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>否</t>
@@ -1015,31 +1015,31 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>-441</v>
+        <v>304.292</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>-10.256</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-451.256</v>
+        <v>304.292</v>
       </c>
       <c r="AF4" t="n">
-        <v>-450.86</v>
+        <v>-47.56800000000004</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI4" t="n">
-        <v>-441.86</v>
+        <v>-39.56800000000001</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-1176.934</v>
+        <v>-872.8380000000001</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
@@ -1048,11 +1048,11 @@
         <v>9</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1167.934</v>
+        <v>-863.8380000000001</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
@@ -1067,63 +1067,63 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>7736</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>先進光</t>
+          <t>虎山</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>156.5</v>
+        <v>70.40000152587891</v>
       </c>
       <c r="G5" t="n">
-        <v>166.325</v>
+        <v>70.54000091552734</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>48.11954056480939</v>
+        <v>46.8426921240584</v>
       </c>
       <c r="J5" t="n">
-        <v>41.32630902274443</v>
+        <v>38.09812897665365</v>
       </c>
       <c r="K5" t="n">
-        <v>46.41697117073114</v>
+        <v>44.60036753320436</v>
       </c>
       <c r="L5" t="n">
-        <v>16150780.2</v>
+        <v>107526.6</v>
       </c>
       <c r="M5" t="n">
-        <v>6887759.25</v>
+        <v>49183.7</v>
       </c>
       <c r="N5" t="n">
-        <v>7904251.15</v>
+        <v>39205.85</v>
       </c>
       <c r="O5" t="n">
-        <v>2.344852602099877</v>
+        <v>2.186224297887308</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.330188132775504</v>
+        <v>-0.3503925685467664</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.137737576462119</v>
+        <v>-0.4245689571027451</v>
       </c>
       <c r="R5" t="n">
-        <v>-1.192450556313385</v>
+        <v>0.07417638855597875</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.027540058034051</v>
+        <v>0.07067083759594561</v>
       </c>
       <c r="T5" t="n">
-        <v>-2.397189504563602</v>
+        <v>0.07579418211935146</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1161,44 +1161,44 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>-24.7</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-18.7</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>20.371</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>25.371</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
@@ -1213,63 +1213,63 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>7736</t>
+          <t>4735</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>豪展</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>70.30000305175781</v>
+        <v>30.5</v>
       </c>
       <c r="G6" t="n">
-        <v>70.56000099182128</v>
+        <v>30.72500009536743</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>42.63244602991772</v>
+        <v>42.84388750179928</v>
       </c>
       <c r="J6" t="n">
-        <v>33.72584740295127</v>
+        <v>41.61980227051176</v>
       </c>
       <c r="K6" t="n">
-        <v>43.73986908984457</v>
+        <v>47.13344086363259</v>
       </c>
       <c r="L6" t="n">
-        <v>106734</v>
+        <v>37384.6</v>
       </c>
       <c r="M6" t="n">
-        <v>49335.55</v>
+        <v>20263.75</v>
       </c>
       <c r="N6" t="n">
-        <v>39106.825</v>
+        <v>28350.325</v>
       </c>
       <c r="O6" t="n">
-        <v>2.163429818862868</v>
+        <v>1.844900376287706</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3724422166457941</v>
+        <v>-0.1938792732861643</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.4431130542417397</v>
+        <v>-0.1172691511852368</v>
       </c>
       <c r="R6" t="n">
-        <v>0.07067083759594561</v>
+        <v>-0.07661012210092746</v>
       </c>
       <c r="S6" t="n">
-        <v>0.07579418211935146</v>
+        <v>-0.1091694968988856</v>
       </c>
       <c r="T6" t="n">
-        <v>0.09451380093351103</v>
+        <v>-0.09964971792175989</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1307,44 +1307,190 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>-19.7</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>-14.7</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>30.621</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>34.621</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>70</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>6620</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>漢達</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>87.90000152587891</v>
+      </c>
+      <c r="G7" t="n">
+        <v>91.83500022888184</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>49.14927365749683</v>
+      </c>
+      <c r="J7" t="n">
+        <v>42.88658061201052</v>
+      </c>
+      <c r="K7" t="n">
+        <v>48.65218966539008</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1834675</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1027751.85</v>
+      </c>
+      <c r="N7" t="n">
+        <v>996152.175</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.785134222818475</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.1560569350604055</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.5698562005197393</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-0.4137992654593338</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.3706034881346115</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-1.135757085457627</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -625,16 +625,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6226</t>
+          <t>6120</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>光鼎</t>
+          <t>達運</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,49 +643,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>19.60000038146973</v>
+        <v>12.80000019073486</v>
       </c>
       <c r="G2" t="n">
-        <v>22.40749979019165</v>
+        <v>13.29999990463257</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>36.62543547705081</v>
+        <v>42.33135216187949</v>
       </c>
       <c r="J2" t="n">
-        <v>32.17428295812243</v>
+        <v>31.6651154384789</v>
       </c>
       <c r="K2" t="n">
-        <v>47.65781818601891</v>
+        <v>45.29263225868609</v>
       </c>
       <c r="L2" t="n">
-        <v>24115229.2</v>
+        <v>5037117.2</v>
       </c>
       <c r="M2" t="n">
-        <v>10728857</v>
+        <v>3231510.85</v>
       </c>
       <c r="N2" t="n">
-        <v>8614053.6</v>
+        <v>3490623.075</v>
       </c>
       <c r="O2" t="n">
-        <v>2.247697886177437</v>
+        <v>1.558749895579029</v>
       </c>
       <c r="P2" t="n">
-        <v>0.219447890353937</v>
+        <v>-0.4554028000951078</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.8038565960360959</v>
+        <v>-0.3804415527933548</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.584408705682159</v>
+        <v>-0.07496124730175302</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6023636329421964</v>
+        <v>-0.1270825237848813</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.665720592302341</v>
+        <v>-0.1790770366005925</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -723,44 +723,44 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>-956.48</v>
+        <v>389</v>
       </c>
       <c r="AC2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>2</v>
+        <v>-21.728</v>
       </c>
       <c r="AE2" t="n">
-        <v>-946.48</v>
+        <v>367.272</v>
       </c>
       <c r="AF2" t="n">
-        <v>-736.039</v>
+        <v>323.27</v>
       </c>
       <c r="AG2" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="AH2" t="n">
-        <v>-61.16</v>
+        <v>-129.645</v>
       </c>
       <c r="AI2" t="n">
-        <v>-782.199</v>
+        <v>243.625</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-3009.125999999999</v>
+        <v>-6500.682000000002</v>
       </c>
       <c r="AK2" t="n">
-        <v>303</v>
+        <v>62</v>
       </c>
       <c r="AL2" t="n">
-        <v>182.832</v>
+        <v>57.973</v>
       </c>
       <c r="AM2" t="n">
-        <v>-2523.294</v>
+        <v>-6380.709</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -771,71 +771,71 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>8401</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>揚明光</t>
+          <t>白紗科</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>68.5</v>
+        <v>22.79999923706055</v>
       </c>
       <c r="G3" t="n">
-        <v>69.16999969482421</v>
+        <v>22.84500017166138</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>39.91777419416688</v>
+        <v>44.08328502987079</v>
       </c>
       <c r="J3" t="n">
-        <v>33.78601612891368</v>
+        <v>40.05893307682037</v>
       </c>
       <c r="K3" t="n">
-        <v>48.05982285185477</v>
+        <v>47.41969507175438</v>
       </c>
       <c r="L3" t="n">
-        <v>5403568.6</v>
+        <v>52293.2</v>
       </c>
       <c r="M3" t="n">
-        <v>2122876.9</v>
+        <v>34417.6</v>
       </c>
       <c r="N3" t="n">
-        <v>2708841.2</v>
+        <v>36695.45</v>
       </c>
       <c r="O3" t="n">
-        <v>2.545398934813413</v>
+        <v>1.519373808749012</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.545092172350891</v>
+        <v>-0.09810222317744532</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.694981048615682</v>
+        <v>-0.08055795476760359</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1498888762647903</v>
+        <v>-0.01754426840984173</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2917257678521823</v>
+        <v>-0.03452981394650623</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.286339942443782</v>
+        <v>-0.03727005713282294</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -869,44 +869,44 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>69.001</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>60.994</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>129.995</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-512.9349999999999</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>108.021</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-404.914</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-1368.825</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>107.853</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1260.972</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6668</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>遠見</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,49 +935,49 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>35.54999923706055</v>
+        <v>35.5</v>
       </c>
       <c r="G4" t="n">
-        <v>35.80250034332276</v>
+        <v>36.89750003814697</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>35.82196154707592</v>
+        <v>34.33006505796435</v>
       </c>
       <c r="J4" t="n">
-        <v>33.30869011991463</v>
+        <v>30.17996637751223</v>
       </c>
       <c r="K4" t="n">
-        <v>47.59537604715646</v>
+        <v>36.62840232716795</v>
       </c>
       <c r="L4" t="n">
-        <v>2229286.4</v>
+        <v>569366.8</v>
       </c>
       <c r="M4" t="n">
-        <v>886358.7</v>
+        <v>247793.3</v>
       </c>
       <c r="N4" t="n">
-        <v>1476373.075</v>
+        <v>243769.275</v>
       </c>
       <c r="O4" t="n">
-        <v>2.515106355925654</v>
+        <v>2.297748970613814</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.126900996535973</v>
+        <v>-0.7930240598325824</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.213381533245147</v>
+        <v>-0.622671318256344</v>
       </c>
       <c r="R4" t="n">
-        <v>0.08648053670917433</v>
+        <v>-0.1703527415762384</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0185575733668244</v>
+        <v>-0.2149610716353583</v>
       </c>
       <c r="T4" t="n">
-        <v>0.04719267149380535</v>
+        <v>-0.2088064084876293</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1015,44 +1015,44 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>304.292</v>
+        <v>-9</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="AE4" t="n">
-        <v>304.292</v>
+        <v>-21</v>
       </c>
       <c r="AF4" t="n">
-        <v>-47.56800000000004</v>
+        <v>-84.69</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="AI4" t="n">
-        <v>-39.56800000000001</v>
+        <v>-85.69</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-872.8380000000001</v>
+        <v>26.47200000000002</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>-69</v>
       </c>
       <c r="AL4" t="n">
-        <v>9</v>
+        <v>0.870000000000001</v>
       </c>
       <c r="AM4" t="n">
-        <v>-863.8380000000001</v>
+        <v>-41.65799999999999</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -1067,63 +1067,63 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>7736</t>
+          <t>2596</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>綠意</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>70.40000152587891</v>
+        <v>30.45000076293945</v>
       </c>
       <c r="G5" t="n">
-        <v>70.54000091552734</v>
+        <v>31.14499988555908</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>46.8426921240584</v>
+        <v>44.61409189864928</v>
       </c>
       <c r="J5" t="n">
-        <v>38.09812897665365</v>
+        <v>41.51426663006859</v>
       </c>
       <c r="K5" t="n">
-        <v>44.60036753320436</v>
+        <v>46.72528127742809</v>
       </c>
       <c r="L5" t="n">
-        <v>107526.6</v>
+        <v>69602</v>
       </c>
       <c r="M5" t="n">
-        <v>49183.7</v>
+        <v>35770.55</v>
       </c>
       <c r="N5" t="n">
-        <v>39205.85</v>
+        <v>49501.675</v>
       </c>
       <c r="O5" t="n">
-        <v>2.186224297887308</v>
+        <v>1.945790601486418</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3503925685467664</v>
+        <v>-0.09147148411916106</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.4245689571027451</v>
+        <v>0.1293458201737093</v>
       </c>
       <c r="R5" t="n">
-        <v>0.07417638855597875</v>
+        <v>-0.2208173042928703</v>
       </c>
       <c r="S5" t="n">
-        <v>0.07067083759594561</v>
+        <v>-0.2565721395063139</v>
       </c>
       <c r="T5" t="n">
-        <v>0.07579418211935146</v>
+        <v>-0.2337520109429989</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1161,44 +1161,44 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-24.7</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>-18.7</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>20.371</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>25.371</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -1213,63 +1213,63 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4735</t>
+          <t>6918</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>豪展</t>
+          <t>愛派司</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>30.5</v>
+        <v>70.40000152587891</v>
       </c>
       <c r="G6" t="n">
-        <v>30.72500009536743</v>
+        <v>72.48500022888183</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>42.84388750179928</v>
+        <v>40.50243692196086</v>
       </c>
       <c r="J6" t="n">
-        <v>41.61980227051176</v>
+        <v>35.48603865639201</v>
       </c>
       <c r="K6" t="n">
-        <v>47.13344086363259</v>
+        <v>40.41541391979185</v>
       </c>
       <c r="L6" t="n">
-        <v>37384.6</v>
+        <v>53823.6</v>
       </c>
       <c r="M6" t="n">
-        <v>20263.75</v>
+        <v>30829.2</v>
       </c>
       <c r="N6" t="n">
-        <v>28350.325</v>
+        <v>33868.425</v>
       </c>
       <c r="O6" t="n">
-        <v>1.844900376287706</v>
+        <v>1.745864310458916</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1938792732861643</v>
+        <v>-0.7934821195665478</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1172691511852368</v>
+        <v>-0.5455544661677592</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.07661012210092746</v>
+        <v>-0.2479276533987886</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1091694968988856</v>
+        <v>-0.2618584847206888</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.09964971792175989</v>
+        <v>-0.3773313262967564</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1307,44 +1307,44 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>-29</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>-56.452</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-55.452</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>-76.352</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>-75.352</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -1359,63 +1359,63 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6620</t>
+          <t>6165</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>漢達</t>
+          <t>浪凡</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>87.90000152587891</v>
+        <v>47.70000076293945</v>
       </c>
       <c r="G7" t="n">
-        <v>91.83500022888184</v>
+        <v>49.63250007629394</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>49.14927365749683</v>
+        <v>33.95205835109324</v>
       </c>
       <c r="J7" t="n">
-        <v>42.88658061201052</v>
+        <v>30.32372384910375</v>
       </c>
       <c r="K7" t="n">
-        <v>48.65218966539008</v>
+        <v>42.44824815230131</v>
       </c>
       <c r="L7" t="n">
-        <v>1834675</v>
+        <v>1567356.2</v>
       </c>
       <c r="M7" t="n">
-        <v>1027751.85</v>
+        <v>979904.55</v>
       </c>
       <c r="N7" t="n">
-        <v>996152.175</v>
+        <v>760398.725</v>
       </c>
       <c r="O7" t="n">
-        <v>1.785134222818475</v>
+        <v>1.599498849148113</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1560569350604055</v>
+        <v>-0.3384735607669356</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5698562005197393</v>
+        <v>-0.0500839478011512</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.4137992654593338</v>
+        <v>-0.2883896129657844</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3706034881346115</v>
+        <v>-0.2827137560542428</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.135757085457627</v>
+        <v>-0.3368785287377477</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1453,44 +1453,44 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>-611</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>-619</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>-6348.49</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-6353.49</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>-5885.228999999999</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>-5884.228999999999</v>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -625,16 +625,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>6668</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>達運</t>
+          <t>中揚光</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,49 +643,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>12.80000019073486</v>
+        <v>35.34999847412109</v>
       </c>
       <c r="G2" t="n">
-        <v>13.29999990463257</v>
+        <v>35.48500022888184</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>42.33135216187949</v>
+        <v>33.38117736529256</v>
       </c>
       <c r="J2" t="n">
-        <v>31.6651154384789</v>
+        <v>33.28814276664231</v>
       </c>
       <c r="K2" t="n">
-        <v>45.29263225868609</v>
+        <v>47.49574981448293</v>
       </c>
       <c r="L2" t="n">
-        <v>5037117.2</v>
+        <v>2105449.6</v>
       </c>
       <c r="M2" t="n">
-        <v>3231510.85</v>
+        <v>883595.35</v>
       </c>
       <c r="N2" t="n">
-        <v>3490623.075</v>
+        <v>1485019.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.558749895579029</v>
+        <v>2.382821050382395</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4554028000951078</v>
+        <v>-0.9702463810749791</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.3804415527933548</v>
+        <v>-1.146286932466751</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.07496124730175302</v>
+        <v>0.1760405513917718</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1270825237848813</v>
+        <v>0.126235659329561</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1790770366005925</v>
+        <v>0.0891659466014727</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -719,48 +719,48 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>389</v>
+        <v>28.198</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-21.728</v>
+        <v>-7</v>
       </c>
       <c r="AE2" t="n">
-        <v>367.272</v>
+        <v>21.198</v>
       </c>
       <c r="AF2" t="n">
-        <v>323.27</v>
+        <v>49.62999999999994</v>
       </c>
       <c r="AG2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-129.645</v>
+        <v>-21</v>
       </c>
       <c r="AI2" t="n">
-        <v>243.625</v>
+        <v>28.62999999999997</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-6500.682000000002</v>
+        <v>-783.4440000000001</v>
       </c>
       <c r="AK2" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>57.973</v>
+        <v>-5</v>
       </c>
       <c r="AM2" t="n">
-        <v>-6380.709</v>
+        <v>-788.4440000000001</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
@@ -792,47 +792,47 @@
         <v>22.79999923706055</v>
       </c>
       <c r="G3" t="n">
-        <v>22.84500017166138</v>
+        <v>22.83750009536743</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>44.08328502987079</v>
+        <v>48.43646275903527</v>
       </c>
       <c r="J3" t="n">
-        <v>40.05893307682037</v>
+        <v>42.851442970892</v>
       </c>
       <c r="K3" t="n">
         <v>47.41969507175438</v>
       </c>
       <c r="L3" t="n">
-        <v>52293.2</v>
+        <v>49258</v>
       </c>
       <c r="M3" t="n">
-        <v>34417.6</v>
+        <v>32069.3</v>
       </c>
       <c r="N3" t="n">
-        <v>36695.45</v>
+        <v>35320.3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.519373808749012</v>
+        <v>1.535986130037138</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.09810222317744532</v>
+        <v>-0.08711286288651721</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.08055795476760359</v>
+        <v>-0.08186893639138632</v>
       </c>
       <c r="R3" t="n">
+        <v>-0.005243926495130891</v>
+      </c>
+      <c r="S3" t="n">
         <v>-0.01754426840984173</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>-0.03452981394650623</v>
       </c>
-      <c r="T3" t="n">
-        <v>-0.03727005713282294</v>
-      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>是</t>
@@ -906,7 +906,7 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
@@ -921,63 +921,63 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>6904</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>遠見</t>
+          <t>伯鑫</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>35.5</v>
+        <v>121.5</v>
       </c>
       <c r="G4" t="n">
-        <v>36.89750003814697</v>
+        <v>123.875</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>34.33006505796435</v>
+        <v>45.75795912840606</v>
       </c>
       <c r="J4" t="n">
-        <v>30.17996637751223</v>
+        <v>36.86442406043227</v>
       </c>
       <c r="K4" t="n">
-        <v>36.62840232716795</v>
+        <v>47.05204398065318</v>
       </c>
       <c r="L4" t="n">
-        <v>569366.8</v>
+        <v>5222.2</v>
       </c>
       <c r="M4" t="n">
-        <v>247793.3</v>
+        <v>2255.6</v>
       </c>
       <c r="N4" t="n">
-        <v>243769.275</v>
+        <v>2039.15</v>
       </c>
       <c r="O4" t="n">
-        <v>2.297748970613814</v>
+        <v>2.315215463734705</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7930240598325824</v>
+        <v>-1.421631322803563</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.622671318256344</v>
+        <v>-0.5785285999922377</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.1703527415762384</v>
+        <v>-0.8431027228113254</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2149610716353583</v>
+        <v>-1.22110771833564</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2088064084876293</v>
+        <v>-1.411264818653543</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1015,44 +1015,44 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-21</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>-84.69</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>-85.69</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>26.47200000000002</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>-69</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.870000000000001</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-41.65799999999999</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2596</t>
+          <t>7708</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>綠意</t>
+          <t>全家餐飲</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1081,49 +1081,49 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>30.45000076293945</v>
+        <v>92.30000305175781</v>
       </c>
       <c r="G5" t="n">
-        <v>31.14499988555908</v>
+        <v>93.28500022888184</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>44.61409189864928</v>
+        <v>40.58175936415407</v>
       </c>
       <c r="J5" t="n">
-        <v>41.51426663006859</v>
+        <v>40.36127571030261</v>
       </c>
       <c r="K5" t="n">
-        <v>46.72528127742809</v>
+        <v>46.03718131215449</v>
       </c>
       <c r="L5" t="n">
-        <v>69602</v>
+        <v>37586.8</v>
       </c>
       <c r="M5" t="n">
-        <v>35770.55</v>
+        <v>19104.7</v>
       </c>
       <c r="N5" t="n">
-        <v>49501.675</v>
+        <v>15153.925</v>
       </c>
       <c r="O5" t="n">
-        <v>1.945790601486418</v>
+        <v>1.967411160604459</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.09147148411916106</v>
+        <v>-0.5963495027604182</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1293458201737093</v>
+        <v>-0.1943004577221422</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.2208173042928703</v>
+        <v>-0.402049045038276</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2565721395063139</v>
+        <v>-0.5427948313962744</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2337520109429989</v>
+        <v>-0.4864046292412975</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>6918</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>愛派司</t>
+          <t>遠見</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1227,49 +1227,49 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>70.40000152587891</v>
+        <v>35.79999923706055</v>
       </c>
       <c r="G6" t="n">
-        <v>72.48500022888183</v>
+        <v>36.82250003814697</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>40.50243692196086</v>
+        <v>42.05337034748079</v>
       </c>
       <c r="J6" t="n">
-        <v>35.48603865639201</v>
+        <v>34.13776770083508</v>
       </c>
       <c r="K6" t="n">
-        <v>40.41541391979185</v>
+        <v>39.90611086587025</v>
       </c>
       <c r="L6" t="n">
-        <v>53823.6</v>
+        <v>433845.6</v>
       </c>
       <c r="M6" t="n">
-        <v>30829.2</v>
+        <v>246812.4</v>
       </c>
       <c r="N6" t="n">
-        <v>33868.425</v>
+        <v>240776.7</v>
       </c>
       <c r="O6" t="n">
-        <v>1.745864310458916</v>
+        <v>1.757794989230687</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7934821195665478</v>
+        <v>-0.7584724511148764</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.5455544661677592</v>
+        <v>-0.6498315448280505</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.2479276533987886</v>
+        <v>-0.1086409062868259</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2618584847206888</v>
+        <v>-0.1703527415762384</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3773313262967564</v>
+        <v>-0.2149610716353583</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>-29</v>
+        <v>-18</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1316,35 +1316,35 @@
         <v>-1</v>
       </c>
       <c r="AE6" t="n">
-        <v>-30</v>
+        <v>-19</v>
       </c>
       <c r="AF6" t="n">
-        <v>-56.452</v>
+        <v>-105.79</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1</v>
+        <v>-26</v>
       </c>
       <c r="AI6" t="n">
-        <v>-55.452</v>
+        <v>-131.79</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-76.352</v>
+        <v>-11.528</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>-69</v>
       </c>
       <c r="AL6" t="n">
-        <v>1</v>
+        <v>-0.129999999999999</v>
       </c>
       <c r="AM6" t="n">
-        <v>-75.352</v>
+        <v>-80.658</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6165</t>
+          <t>6918</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>浪凡</t>
+          <t>愛派司</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1373,49 +1373,49 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>47.70000076293945</v>
+        <v>70.40000152587891</v>
       </c>
       <c r="G7" t="n">
-        <v>49.63250007629394</v>
+        <v>72.29000015258789</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>33.95205835109324</v>
+        <v>41.28734631474168</v>
       </c>
       <c r="J7" t="n">
-        <v>30.32372384910375</v>
+        <v>37.4198078758419</v>
       </c>
       <c r="K7" t="n">
-        <v>42.44824815230131</v>
+        <v>40.41541391979185</v>
       </c>
       <c r="L7" t="n">
-        <v>1567356.2</v>
+        <v>51688</v>
       </c>
       <c r="M7" t="n">
-        <v>979904.55</v>
+        <v>30845.45</v>
       </c>
       <c r="N7" t="n">
-        <v>760398.725</v>
+        <v>33001.55</v>
       </c>
       <c r="O7" t="n">
-        <v>1.599498849148113</v>
+        <v>1.675709059196737</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3384735607669356</v>
+        <v>-0.8220864474280205</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.0500839478011512</v>
+        <v>-0.6008608624198114</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.2883896129657844</v>
+        <v>-0.2212255850082091</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2827137560542428</v>
+        <v>-0.2479276533987886</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3368785287377477</v>
+        <v>-0.2618584847206888</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1453,44 +1453,44 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>-611</v>
+        <v>-3</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="AE7" t="n">
-        <v>-619</v>
+        <v>-9</v>
       </c>
       <c r="AF7" t="n">
-        <v>-6348.49</v>
+        <v>-48.452</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="AI7" t="n">
-        <v>-6353.49</v>
+        <v>-55.452</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-5885.228999999999</v>
+        <v>-118.352</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="AM7" t="n">
-        <v>-5884.228999999999</v>
+        <v>-122.352</v>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN7"/>
+  <dimension ref="A1:AN5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,12 +629,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6668</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>全友</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,49 +643,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>35.34999847412109</v>
+        <v>29.35000038146973</v>
       </c>
       <c r="G2" t="n">
-        <v>35.48500022888184</v>
+        <v>32.80749988555908</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>33.38117736529256</v>
+        <v>45.84520430639039</v>
       </c>
       <c r="J2" t="n">
-        <v>33.28814276664231</v>
+        <v>38.00557185250278</v>
       </c>
       <c r="K2" t="n">
-        <v>47.49574981448293</v>
+        <v>43.69860817496826</v>
       </c>
       <c r="L2" t="n">
-        <v>2105449.6</v>
+        <v>10102000</v>
       </c>
       <c r="M2" t="n">
-        <v>883595.35</v>
+        <v>6678952.05</v>
       </c>
       <c r="N2" t="n">
-        <v>1485019.2</v>
+        <v>6485149.05</v>
       </c>
       <c r="O2" t="n">
-        <v>2.382821050382395</v>
+        <v>1.512512730196948</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.9702463810749791</v>
+        <v>-0.7178514536320968</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.146286932466751</v>
+        <v>-0.2150002960714241</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1760405513917718</v>
+        <v>-0.5028511575606727</v>
       </c>
       <c r="S2" t="n">
-        <v>0.126235659329561</v>
+        <v>-0.4865648681582398</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0891659466014727</v>
+        <v>-0.7494964867929885</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -714,53 +714,53 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>28.198</v>
+        <v>-2336.863</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-7</v>
+        <v>-0.284</v>
       </c>
       <c r="AE2" t="n">
-        <v>21.198</v>
+        <v>-2337.147</v>
       </c>
       <c r="AF2" t="n">
-        <v>49.62999999999994</v>
+        <v>-2249.371</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AH2" t="n">
-        <v>-21</v>
+        <v>-54.044</v>
       </c>
       <c r="AI2" t="n">
-        <v>28.62999999999997</v>
+        <v>-2293.415</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-783.4440000000001</v>
+        <v>-7728.912999999999</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="AL2" t="n">
-        <v>-5</v>
+        <v>-128.73</v>
       </c>
       <c r="AM2" t="n">
-        <v>-788.4440000000001</v>
+        <v>-7638.643</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -775,67 +775,67 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8401</t>
+          <t>6931</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>白紗科</t>
+          <t>青松健康</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>22.79999923706055</v>
+        <v>37.70000076293945</v>
       </c>
       <c r="G3" t="n">
-        <v>22.83750009536743</v>
+        <v>38.73000011444092</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>48.43646275903527</v>
+        <v>40.54464501036516</v>
       </c>
       <c r="J3" t="n">
-        <v>42.851442970892</v>
+        <v>31.37967330946126</v>
       </c>
       <c r="K3" t="n">
-        <v>47.41969507175438</v>
+        <v>38.56670774003936</v>
       </c>
       <c r="L3" t="n">
-        <v>49258</v>
+        <v>73733.39999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>32069.3</v>
+        <v>48781.5</v>
       </c>
       <c r="N3" t="n">
-        <v>35320.3</v>
+        <v>53127.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.535986130037138</v>
+        <v>1.511503336305771</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.08711286288651721</v>
+        <v>-0.7093227113687561</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.08186893639138632</v>
+        <v>-0.621722234900823</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.005243926495130891</v>
+        <v>-0.08760047646793312</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.01754426840984173</v>
+        <v>-0.1227362297519339</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.03452981394650623</v>
+        <v>-0.1496217785483372</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -855,12 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -878,35 +878,35 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>15.325</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>7.324999999999996</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6904</t>
+          <t>5514</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>伯鑫</t>
+          <t>三豐</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,49 +935,49 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>121.5</v>
+        <v>13.75</v>
       </c>
       <c r="G4" t="n">
-        <v>123.875</v>
+        <v>13.60500001907349</v>
       </c>
       <c r="H4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>45.75795912840606</v>
+        <v>40.42530688710323</v>
       </c>
       <c r="J4" t="n">
-        <v>36.86442406043227</v>
+        <v>40.04579909960366</v>
       </c>
       <c r="K4" t="n">
-        <v>47.05204398065318</v>
+        <v>48.84101366717996</v>
       </c>
       <c r="L4" t="n">
-        <v>5222.2</v>
+        <v>128000.6</v>
       </c>
       <c r="M4" t="n">
-        <v>2255.6</v>
+        <v>77731.25</v>
       </c>
       <c r="N4" t="n">
-        <v>2039.15</v>
+        <v>87106.85000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>2.315215463734705</v>
+        <v>1.646707083701857</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.421631322803563</v>
+        <v>-0.03372419818536088</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.5785285999922377</v>
+        <v>-0.09167074458125869</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.8431027228113254</v>
+        <v>0.05794654639589782</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.22110771833564</v>
+        <v>0.06535556568732963</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.411264818653543</v>
+        <v>0.08343618172071056</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>7708</t>
+          <t>7792</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>全家餐飲</t>
+          <t>安葆</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1081,49 +1081,49 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>92.30000305175781</v>
+        <v>203.5</v>
       </c>
       <c r="G5" t="n">
-        <v>93.28500022888184</v>
+        <v>212.5</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>40.58175936415407</v>
+        <v>47.75830471268464</v>
       </c>
       <c r="J5" t="n">
-        <v>40.36127571030261</v>
+        <v>34.70817210201501</v>
       </c>
       <c r="K5" t="n">
-        <v>46.03718131215449</v>
+        <v>40.3876075349619</v>
       </c>
       <c r="L5" t="n">
-        <v>37586.8</v>
+        <v>218571.4</v>
       </c>
       <c r="M5" t="n">
-        <v>19104.7</v>
+        <v>145319.05</v>
       </c>
       <c r="N5" t="n">
-        <v>15153.925</v>
+        <v>130514.775</v>
       </c>
       <c r="O5" t="n">
-        <v>1.967411160604459</v>
+        <v>1.50407947203068</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5963495027604182</v>
+        <v>-14.97019817897078</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1943004577221422</v>
+        <v>-15.73898809108571</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.402049045038276</v>
+        <v>0.7687899121149364</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5427948313962744</v>
+        <v>-0.1855170146401584</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4864046292412975</v>
+        <v>-0.9008280346424087</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1198,299 +1198,7 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>70</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>3040</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>遠見</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>35.79999923706055</v>
-      </c>
-      <c r="G6" t="n">
-        <v>36.82250003814697</v>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>42.05337034748079</v>
-      </c>
-      <c r="J6" t="n">
-        <v>34.13776770083508</v>
-      </c>
-      <c r="K6" t="n">
-        <v>39.90611086587025</v>
-      </c>
-      <c r="L6" t="n">
-        <v>433845.6</v>
-      </c>
-      <c r="M6" t="n">
-        <v>246812.4</v>
-      </c>
-      <c r="N6" t="n">
-        <v>240776.7</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.757794989230687</v>
-      </c>
-      <c r="P6" t="n">
-        <v>-0.7584724511148764</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>-0.6498315448280505</v>
-      </c>
-      <c r="R6" t="n">
-        <v>-0.1086409062868259</v>
-      </c>
-      <c r="S6" t="n">
-        <v>-0.1703527415762384</v>
-      </c>
-      <c r="T6" t="n">
-        <v>-0.2149610716353583</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>-18</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>-19</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>-105.79</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>-26</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>-131.79</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>-11.528</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>-69</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>-0.129999999999999</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>-80.658</v>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>70</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>6918</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>愛派司</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>70.40000152587891</v>
-      </c>
-      <c r="G7" t="n">
-        <v>72.29000015258789</v>
-      </c>
-      <c r="H7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>41.28734631474168</v>
-      </c>
-      <c r="J7" t="n">
-        <v>37.4198078758419</v>
-      </c>
-      <c r="K7" t="n">
-        <v>40.41541391979185</v>
-      </c>
-      <c r="L7" t="n">
-        <v>51688</v>
-      </c>
-      <c r="M7" t="n">
-        <v>30845.45</v>
-      </c>
-      <c r="N7" t="n">
-        <v>33001.55</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.675709059196737</v>
-      </c>
-      <c r="P7" t="n">
-        <v>-0.8220864474280205</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>-0.6008608624198114</v>
-      </c>
-      <c r="R7" t="n">
-        <v>-0.2212255850082091</v>
-      </c>
-      <c r="S7" t="n">
-        <v>-0.2479276533987886</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-0.2618584847206888</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>-6</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>-9</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>-48.452</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>-7</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>-55.452</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>-118.352</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>-122.352</v>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -629,12 +629,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>士紙</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,49 +643,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>29.35000038146973</v>
+        <v>47.04999923706055</v>
       </c>
       <c r="G2" t="n">
-        <v>32.80749988555908</v>
+        <v>48.16000003814698</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>45.84520430639039</v>
+        <v>33.2568252353181</v>
       </c>
       <c r="J2" t="n">
-        <v>38.00557185250278</v>
+        <v>33.00362698764248</v>
       </c>
       <c r="K2" t="n">
-        <v>43.69860817496826</v>
+        <v>39.85588158127809</v>
       </c>
       <c r="L2" t="n">
-        <v>10102000</v>
+        <v>284921.4</v>
       </c>
       <c r="M2" t="n">
-        <v>6678952.05</v>
+        <v>160526.45</v>
       </c>
       <c r="N2" t="n">
-        <v>6485149.05</v>
+        <v>209499.025</v>
       </c>
       <c r="O2" t="n">
-        <v>1.512512730196948</v>
+        <v>1.77491871277288</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.7178514536320968</v>
+        <v>-0.3577707790451683</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2150002960714241</v>
+        <v>-0.1636361275491548</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.5028511575606727</v>
+        <v>-0.1941346514960135</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4865648681582398</v>
+        <v>-0.2143024078998034</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7494964867929885</v>
+        <v>-0.2065177406978525</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -714,53 +714,53 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>-2336.863</v>
+        <v>-11</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.284</v>
+        <v>-1.171</v>
       </c>
       <c r="AE2" t="n">
-        <v>-2337.147</v>
+        <v>-12.171</v>
       </c>
       <c r="AF2" t="n">
-        <v>-2249.371</v>
+        <v>117.304</v>
       </c>
       <c r="AG2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-54.044</v>
+        <v>-12.544</v>
       </c>
       <c r="AI2" t="n">
-        <v>-2293.415</v>
+        <v>104.76</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-7728.912999999999</v>
+        <v>452.756</v>
       </c>
       <c r="AK2" t="n">
-        <v>219</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-128.73</v>
+        <v>-13.334</v>
       </c>
       <c r="AM2" t="n">
-        <v>-7638.643</v>
+        <v>439.422</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -771,67 +771,67 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6931</t>
+          <t>6997</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>青松健康</t>
+          <t>博弘</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>37.70000076293945</v>
+        <v>70.90000152587891</v>
       </c>
       <c r="G3" t="n">
-        <v>38.73000011444092</v>
+        <v>72.18999977111817</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>40.54464501036516</v>
+        <v>47.66168487102966</v>
       </c>
       <c r="J3" t="n">
-        <v>31.37967330946126</v>
+        <v>42.02852585155565</v>
       </c>
       <c r="K3" t="n">
-        <v>38.56670774003936</v>
+        <v>46.43032904575413</v>
       </c>
       <c r="L3" t="n">
-        <v>73733.39999999999</v>
+        <v>8543.799999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>48781.5</v>
+        <v>4251.45</v>
       </c>
       <c r="N3" t="n">
-        <v>53127.25</v>
+        <v>4530.375</v>
       </c>
       <c r="O3" t="n">
-        <v>1.511503336305771</v>
+        <v>2.009620247209775</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.7093227113687561</v>
+        <v>-0.320042250013671</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.621722234900823</v>
+        <v>-0.4728080904402532</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.08760047646793312</v>
+        <v>0.1527658404265821</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1227362297519339</v>
+        <v>0.2620784008276047</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1496217785483372</v>
+        <v>0.2081770320410818</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -878,35 +878,35 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>15.325</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>7.324999999999996</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5514</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>三豐</t>
+          <t>笙科</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,49 +935,49 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>13.75</v>
+        <v>18.25</v>
       </c>
       <c r="G4" t="n">
-        <v>13.60500001907349</v>
+        <v>18.50499992370606</v>
       </c>
       <c r="H4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>40.42530688710323</v>
+        <v>48.66687155623913</v>
       </c>
       <c r="J4" t="n">
-        <v>40.04579909960366</v>
+        <v>36.58991669747623</v>
       </c>
       <c r="K4" t="n">
-        <v>48.84101366717996</v>
+        <v>43.85248316395936</v>
       </c>
       <c r="L4" t="n">
-        <v>128000.6</v>
+        <v>269713.8</v>
       </c>
       <c r="M4" t="n">
-        <v>77731.25</v>
+        <v>152121.3</v>
       </c>
       <c r="N4" t="n">
-        <v>87106.85000000001</v>
+        <v>171924.85</v>
       </c>
       <c r="O4" t="n">
-        <v>1.646707083701857</v>
+        <v>1.773017979730649</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.03372419818536088</v>
+        <v>-0.8695218043059292</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.09167074458125869</v>
+        <v>-0.9290690034796358</v>
       </c>
       <c r="R4" t="n">
-        <v>0.05794654639589782</v>
+        <v>0.05954719917370666</v>
       </c>
       <c r="S4" t="n">
-        <v>0.06535556568732963</v>
+        <v>-0.02471941754734241</v>
       </c>
       <c r="T4" t="n">
-        <v>0.08343618172071056</v>
+        <v>-0.06700162943708321</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -1067,63 +1067,63 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>7792</t>
+          <t>6176</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>安葆</t>
+          <t>瑞儀</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>203.5</v>
+        <v>84.30000305175781</v>
       </c>
       <c r="G5" t="n">
-        <v>212.5</v>
+        <v>86.28999977111816</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>47.75830471268464</v>
+        <v>47.07452521518069</v>
       </c>
       <c r="J5" t="n">
-        <v>34.70817210201501</v>
+        <v>46.94833830193848</v>
       </c>
       <c r="K5" t="n">
-        <v>40.3876075349619</v>
+        <v>42.21515088937006</v>
       </c>
       <c r="L5" t="n">
-        <v>218571.4</v>
+        <v>8509085</v>
       </c>
       <c r="M5" t="n">
-        <v>145319.05</v>
+        <v>5308963.25</v>
       </c>
       <c r="N5" t="n">
-        <v>130514.775</v>
+        <v>6454420.225</v>
       </c>
       <c r="O5" t="n">
-        <v>1.50407947203068</v>
+        <v>1.602777152394114</v>
       </c>
       <c r="P5" t="n">
-        <v>-14.97019817897078</v>
+        <v>-1.562278805099112</v>
       </c>
       <c r="Q5" t="n">
-        <v>-15.73898809108571</v>
+        <v>-1.711248250505878</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7687899121149364</v>
+        <v>0.1489694454067665</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1855170146401584</v>
+        <v>0.1854037664359471</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9008280346424087</v>
+        <v>0.2229141749624426</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1161,44 +1161,44 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>855.861</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>-13.583</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>839.278</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>-2354.051</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-439.961</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>-160.323</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-2954.335</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>-326.3999999999999</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-874.4300000000001</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>-144.911</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-1345.741000000001</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -625,67 +625,67 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>2924</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>士紙</t>
+          <t>宏太-KY</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>47.04999923706055</v>
+        <v>16.95000076293945</v>
       </c>
       <c r="G2" t="n">
-        <v>48.16000003814698</v>
+        <v>17.75750026702881</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>33.2568252353181</v>
+        <v>33.8746774840877</v>
       </c>
       <c r="J2" t="n">
-        <v>33.00362698764248</v>
+        <v>31.59798086994646</v>
       </c>
       <c r="K2" t="n">
-        <v>39.85588158127809</v>
+        <v>42.23619311937473</v>
       </c>
       <c r="L2" t="n">
-        <v>284921.4</v>
+        <v>9400</v>
       </c>
       <c r="M2" t="n">
-        <v>160526.45</v>
+        <v>3500</v>
       </c>
       <c r="N2" t="n">
-        <v>209499.025</v>
+        <v>2650.225</v>
       </c>
       <c r="O2" t="n">
-        <v>1.77491871277288</v>
+        <v>2.685714285714285</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.3577707790451683</v>
+        <v>-0.2807486511806339</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1636361275491548</v>
+        <v>-0.1014026008143576</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.1941346514960135</v>
+        <v>-0.1793460503662763</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2143024078998034</v>
+        <v>-0.2032022130786675</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2065177406978525</v>
+        <v>-0.2285365940752357</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -723,44 +723,44 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-1.171</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-12.171</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>117.304</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-12.544</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>104.76</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>452.756</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-13.334</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>439.422</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -792,46 +792,46 @@
         <v>70.90000152587891</v>
       </c>
       <c r="G3" t="n">
-        <v>72.18999977111817</v>
+        <v>72.11499977111816</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>47.66168487102966</v>
+        <v>43.01477456776662</v>
       </c>
       <c r="J3" t="n">
-        <v>42.02852585155565</v>
+        <v>42.35727544212428</v>
       </c>
       <c r="K3" t="n">
-        <v>46.43032904575413</v>
+        <v>46.75998984829111</v>
       </c>
       <c r="L3" t="n">
-        <v>8543.799999999999</v>
+        <v>9052.799999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>4251.45</v>
+        <v>4378.7</v>
       </c>
       <c r="N3" t="n">
-        <v>4530.375</v>
+        <v>4366.775</v>
       </c>
       <c r="O3" t="n">
-        <v>2.009620247209775</v>
+        <v>2.06746294562313</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.320042250013671</v>
+        <v>-0.3603230468936687</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.4728080904402532</v>
+        <v>-0.4353924520613081</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1527658404265821</v>
+        <v>0.07506940516763938</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2620784008276047</v>
+        <v>0.1468515542734078</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2081770320410818</v>
+        <v>0.2557005411289625</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -921,63 +921,63 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>2480</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>笙科</t>
+          <t>敦陽科</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>18.25</v>
+        <v>156.5</v>
       </c>
       <c r="G4" t="n">
-        <v>18.50499992370606</v>
+        <v>157.725</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>48.66687155623913</v>
+        <v>36.36176642842103</v>
       </c>
       <c r="J4" t="n">
-        <v>36.58991669747623</v>
+        <v>36.14972784117293</v>
       </c>
       <c r="K4" t="n">
-        <v>43.85248316395936</v>
+        <v>49.77487416670158</v>
       </c>
       <c r="L4" t="n">
-        <v>269713.8</v>
+        <v>723742.8</v>
       </c>
       <c r="M4" t="n">
-        <v>152121.3</v>
+        <v>429327.85</v>
       </c>
       <c r="N4" t="n">
-        <v>171924.85</v>
+        <v>466864.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.773017979730649</v>
+        <v>1.685757865463422</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.8695218043059292</v>
+        <v>-0.4650480593059569</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9290690034796358</v>
+        <v>0.08839763887868593</v>
       </c>
       <c r="R4" t="n">
-        <v>0.05954719917370666</v>
+        <v>-0.5534456981846428</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.02471941754734241</v>
+        <v>-0.747633593540566</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.06700162943708321</v>
+        <v>-0.8964023305939953</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1015,44 +1015,44 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>189.261</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>-0.217</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>184.044</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>-1208.287</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>-11.081</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>-32.918</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-1252.286</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>190.516</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>17.223</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>-38.07400000000001</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>169.6649999999999</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -1067,63 +1067,63 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6176</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>瑞儀</t>
+          <t>台聯電</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>84.30000305175781</v>
+        <v>66.59999847412109</v>
       </c>
       <c r="G5" t="n">
-        <v>86.28999977111816</v>
+        <v>66.45500030517579</v>
       </c>
       <c r="H5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>47.07452521518069</v>
+        <v>42.56614707111585</v>
       </c>
       <c r="J5" t="n">
-        <v>46.94833830193848</v>
+        <v>35.36333718139034</v>
       </c>
       <c r="K5" t="n">
-        <v>42.21515088937006</v>
+        <v>46.9290702681687</v>
       </c>
       <c r="L5" t="n">
-        <v>8509085</v>
+        <v>16014.6</v>
       </c>
       <c r="M5" t="n">
-        <v>5308963.25</v>
+        <v>10125.3</v>
       </c>
       <c r="N5" t="n">
-        <v>6454420.225</v>
+        <v>11508.475</v>
       </c>
       <c r="O5" t="n">
-        <v>1.602777152394114</v>
+        <v>1.581642025421469</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.562278805099112</v>
+        <v>-1.102646012440687</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.711248250505878</v>
+        <v>-1.403734674589655</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1489694454067665</v>
+        <v>0.3010886621489681</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1854037664359471</v>
+        <v>0.2326854803674052</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2229141749624426</v>
+        <v>0.2172396913856074</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1161,44 +1161,44 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>855.861</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>-13.583</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>839.278</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-2354.051</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>-439.961</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-160.323</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>-2954.335</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-326.3999999999999</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>-874.4300000000001</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-144.911</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>-1345.741000000001</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN5"/>
+  <dimension ref="A1:AN7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,67 +625,67 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2924</t>
+          <t>6666</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>宏太-KY</t>
+          <t>羅麗芬-KY</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>16.95000076293945</v>
+        <v>43.25</v>
       </c>
       <c r="G2" t="n">
-        <v>17.75750026702881</v>
+        <v>44.17750015258789</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>33.8746774840877</v>
+        <v>48.75397005828239</v>
       </c>
       <c r="J2" t="n">
-        <v>31.59798086994646</v>
+        <v>47.68228495784494</v>
       </c>
       <c r="K2" t="n">
-        <v>42.23619311937473</v>
+        <v>45.12206783289117</v>
       </c>
       <c r="L2" t="n">
-        <v>9400</v>
+        <v>85878</v>
       </c>
       <c r="M2" t="n">
-        <v>3500</v>
+        <v>45283.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2650.225</v>
+        <v>43124.75</v>
       </c>
       <c r="O2" t="n">
-        <v>2.685714285714285</v>
+        <v>1.896469102159525</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2807486511806339</v>
+        <v>-0.1780415823689268</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1014026008143576</v>
+        <v>0.116499700555742</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.1793460503662763</v>
+        <v>-0.2945412829246687</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2032022130786675</v>
+        <v>-0.3530644307056108</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2285365940752357</v>
+        <v>-0.3433083916794591</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -723,44 +723,44 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>30.6</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>0.1779999999999999</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>30.778</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
@@ -775,12 +775,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6997</t>
+          <t>2924</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>博弘</t>
+          <t>宏太-KY</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,49 +789,49 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>70.90000152587891</v>
+        <v>17.45000076293945</v>
       </c>
       <c r="G3" t="n">
-        <v>72.11499977111816</v>
+        <v>17.7375002861023</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>43.01477456776662</v>
+        <v>43.34815060237614</v>
       </c>
       <c r="J3" t="n">
-        <v>42.35727544212428</v>
+        <v>35.51470415636368</v>
       </c>
       <c r="K3" t="n">
-        <v>46.75998984829111</v>
+        <v>43.42792539235343</v>
       </c>
       <c r="L3" t="n">
-        <v>9052.799999999999</v>
+        <v>9600</v>
       </c>
       <c r="M3" t="n">
-        <v>4378.7</v>
+        <v>3500</v>
       </c>
       <c r="N3" t="n">
-        <v>4366.775</v>
+        <v>2625.225</v>
       </c>
       <c r="O3" t="n">
-        <v>2.06746294562313</v>
+        <v>2.742857142857143</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3603230468936687</v>
+        <v>-0.2541007925255094</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.4353924520613081</v>
+        <v>-0.131942239156588</v>
       </c>
       <c r="R3" t="n">
-        <v>0.07506940516763938</v>
+        <v>-0.1221585533689215</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1468515542734078</v>
+        <v>-0.1793460503662763</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2557005411289625</v>
+        <v>-0.2032022130786675</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
@@ -921,63 +921,63 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2480</t>
+          <t>6997</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>敦陽科</t>
+          <t>博弘</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>156.5</v>
+        <v>70.90000152587891</v>
       </c>
       <c r="G4" t="n">
-        <v>157.725</v>
+        <v>72.11499977111816</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>36.36176642842103</v>
+        <v>43.01477457144476</v>
       </c>
       <c r="J4" t="n">
-        <v>36.14972784117293</v>
+        <v>42.35727551251875</v>
       </c>
       <c r="K4" t="n">
-        <v>49.77487416670158</v>
+        <v>46.7573638896474</v>
       </c>
       <c r="L4" t="n">
-        <v>723742.8</v>
+        <v>9006.799999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>429327.85</v>
+        <v>4367.2</v>
       </c>
       <c r="N4" t="n">
-        <v>466864.3</v>
+        <v>4361.025</v>
       </c>
       <c r="O4" t="n">
-        <v>1.685757865463422</v>
+        <v>2.062374061183367</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4650480593059569</v>
+        <v>-0.3888651892560517</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.08839763887868593</v>
+        <v>-0.4771723764116743</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.5534456981846428</v>
+        <v>0.08830718715562258</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.747633593540566</v>
+        <v>0.1611246532381454</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8964023305939953</v>
+        <v>0.2710875365546079</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1015,40 +1015,40 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>189.261</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.217</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>184.044</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>-1208.287</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>-11.081</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-32.918</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>-1252.286</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>190.516</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>17.223</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>-38.07400000000001</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>169.6649999999999</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4905</t>
+          <t>6590</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>台聯電</t>
+          <t>普鴻</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1081,49 +1081,49 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>66.59999847412109</v>
+        <v>64.40000152587891</v>
       </c>
       <c r="G5" t="n">
-        <v>66.45500030517579</v>
+        <v>65.72499923706054</v>
       </c>
       <c r="H5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>42.56614707111585</v>
+        <v>47.72838278174051</v>
       </c>
       <c r="J5" t="n">
-        <v>35.36333718139034</v>
+        <v>40.30942196338319</v>
       </c>
       <c r="K5" t="n">
-        <v>46.9290702681687</v>
+        <v>40.48632810260321</v>
       </c>
       <c r="L5" t="n">
-        <v>16014.6</v>
+        <v>23721.2</v>
       </c>
       <c r="M5" t="n">
-        <v>10125.3</v>
+        <v>11882.45</v>
       </c>
       <c r="N5" t="n">
-        <v>11508.475</v>
+        <v>11286.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.581642025421469</v>
+        <v>1.996322307268282</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.102646012440687</v>
+        <v>-0.7413363540170508</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.403734674589655</v>
+        <v>-0.5513059103467409</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3010886621489681</v>
+        <v>-0.1900304436703099</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2326854803674052</v>
+        <v>-0.2389833332707245</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2172396913856074</v>
+        <v>-0.1574058241798794</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1198,7 +1198,299 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>70</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>5475</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>德宏</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>125</v>
+      </c>
+      <c r="G6" t="n">
+        <v>137.275</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>47.23058698038506</v>
+      </c>
+      <c r="J6" t="n">
+        <v>38.85959150421822</v>
+      </c>
+      <c r="K6" t="n">
+        <v>34.63624245764224</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5987851.2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3457555.9</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2861715.85</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.731816165286005</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-24.2944598573788</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-28.11262833618673</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3.81816847880793</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.243433352717481</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.630723091404253</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>70</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>7811</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>民盛</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>71.09999847412109</v>
+      </c>
+      <c r="G7" t="n">
+        <v>71.43999977111817</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>36.41787983405452</v>
+      </c>
+      <c r="J7" t="n">
+        <v>30.38974059579695</v>
+      </c>
+      <c r="K7" t="n">
+        <v>31.51942855059735</v>
+      </c>
+      <c r="L7" t="n">
+        <v>28646</v>
+      </c>
+      <c r="M7" t="n">
+        <v>17115.75</v>
+      </c>
+      <c r="N7" t="n">
+        <v>14710.275</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.673663146517097</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-1.496101692220009</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-1.703263588519433</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.2071618962994239</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.1749126241475578</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.1343593795597433</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN7"/>
+  <dimension ref="A1:AN4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,12 +629,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6666</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>羅麗芬-KY</t>
+          <t>聯發</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,49 +643,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>43.25</v>
+        <v>13.69999980926514</v>
       </c>
       <c r="G2" t="n">
-        <v>44.17750015258789</v>
+        <v>14.84333333969116</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>48.75397005828239</v>
+        <v>31.9289342271843</v>
       </c>
       <c r="J2" t="n">
-        <v>47.68228495784494</v>
+        <v>31.46602696278818</v>
       </c>
       <c r="K2" t="n">
-        <v>45.12206783289117</v>
+        <v>36.57986594470437</v>
       </c>
       <c r="L2" t="n">
-        <v>85878</v>
+        <v>247632</v>
       </c>
       <c r="M2" t="n">
-        <v>45283.1</v>
+        <v>111208.25</v>
       </c>
       <c r="N2" t="n">
-        <v>43124.75</v>
+        <v>124365.625</v>
       </c>
       <c r="O2" t="n">
-        <v>1.896469102159525</v>
+        <v>2.226741271443441</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1780415823689268</v>
+        <v>-0.6286710517731873</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.116499700555742</v>
+        <v>-0.4513136467663639</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.2945412829246687</v>
+        <v>-0.1773574050068234</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3530644307056108</v>
+        <v>-0.2355695179471785</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3433083916794591</v>
+        <v>-0.3333679681228651</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -723,44 +723,44 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>4</v>
+        <v>13.552</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-2</v>
+        <v>48</v>
       </c>
       <c r="AE2" t="n">
-        <v>2</v>
+        <v>61.552</v>
       </c>
       <c r="AF2" t="n">
-        <v>7</v>
+        <v>-24.145</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-3</v>
+        <v>31</v>
       </c>
       <c r="AI2" t="n">
-        <v>4</v>
+        <v>6.854999999999986</v>
       </c>
       <c r="AJ2" t="n">
-        <v>30.6</v>
+        <v>66.18299999999999</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.1779999999999999</v>
+        <v>28</v>
       </c>
       <c r="AM2" t="n">
-        <v>30.778</v>
+        <v>94.18299999999999</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -775,12 +775,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2924</t>
+          <t>7811</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>宏太-KY</t>
+          <t>民盛</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,49 +789,49 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>17.45000076293945</v>
+        <v>71.09999847412109</v>
       </c>
       <c r="G3" t="n">
-        <v>17.7375002861023</v>
+        <v>71.40499954223633</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>43.34815060237614</v>
+        <v>39.66312670025113</v>
       </c>
       <c r="J3" t="n">
-        <v>35.51470415636368</v>
+        <v>33.48086929728168</v>
       </c>
       <c r="K3" t="n">
-        <v>43.42792539235343</v>
+        <v>31.51942855059735</v>
       </c>
       <c r="L3" t="n">
-        <v>9600</v>
+        <v>33607.4</v>
       </c>
       <c r="M3" t="n">
-        <v>3500</v>
+        <v>18006.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2625.225</v>
+        <v>15430.45</v>
       </c>
       <c r="O3" t="n">
-        <v>2.742857142857143</v>
+        <v>1.866445260217371</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2541007925255094</v>
+        <v>-1.413208994267791</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.131942239156588</v>
+        <v>-1.645252669669104</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.1221585533689215</v>
+        <v>0.2320436754013135</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1793460503662763</v>
+        <v>0.2071618962994239</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2032022130786675</v>
+        <v>0.1749126241475578</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6997</t>
+          <t>6020</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>博弘</t>
+          <t>大展證</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,49 +935,49 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>70.90000152587891</v>
+        <v>21</v>
       </c>
       <c r="G4" t="n">
-        <v>72.11499977111816</v>
+        <v>21.24249992370606</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>43.01477457144476</v>
+        <v>39.74465932118099</v>
       </c>
       <c r="J4" t="n">
-        <v>42.35727551251875</v>
+        <v>38.52343680122007</v>
       </c>
       <c r="K4" t="n">
-        <v>46.7573638896474</v>
+        <v>42.63290209735876</v>
       </c>
       <c r="L4" t="n">
-        <v>9006.799999999999</v>
+        <v>87200</v>
       </c>
       <c r="M4" t="n">
-        <v>4367.2</v>
+        <v>48860.55</v>
       </c>
       <c r="N4" t="n">
-        <v>4361.025</v>
+        <v>56112.55</v>
       </c>
       <c r="O4" t="n">
-        <v>2.062374061183367</v>
+        <v>1.784670864327151</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3888651892560517</v>
+        <v>-0.3934653812201105</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.4771723764116743</v>
+        <v>-0.40118978333647</v>
       </c>
       <c r="R4" t="n">
-        <v>0.08830718715562258</v>
+        <v>0.007724402116359497</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1611246532381454</v>
+        <v>-0.01905354656901703</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2710875365546079</v>
+        <v>-0.008501141175759286</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1052,445 +1052,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>70</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>6590</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>普鴻</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>64.40000152587891</v>
-      </c>
-      <c r="G5" t="n">
-        <v>65.72499923706054</v>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>47.72838278174051</v>
-      </c>
-      <c r="J5" t="n">
-        <v>40.30942196338319</v>
-      </c>
-      <c r="K5" t="n">
-        <v>40.48632810260321</v>
-      </c>
-      <c r="L5" t="n">
-        <v>23721.2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>11882.45</v>
-      </c>
-      <c r="N5" t="n">
-        <v>11286.6</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.996322307268282</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-0.7413363540170508</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-0.5513059103467409</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-0.1900304436703099</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-0.2389833332707245</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-0.1574058241798794</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>70</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>5475</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>德宏</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>125</v>
-      </c>
-      <c r="G6" t="n">
-        <v>137.275</v>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>47.23058698038506</v>
-      </c>
-      <c r="J6" t="n">
-        <v>38.85959150421822</v>
-      </c>
-      <c r="K6" t="n">
-        <v>34.63624245764224</v>
-      </c>
-      <c r="L6" t="n">
-        <v>5987851.2</v>
-      </c>
-      <c r="M6" t="n">
-        <v>3457555.9</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2861715.85</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.731816165286005</v>
-      </c>
-      <c r="P6" t="n">
-        <v>-24.2944598573788</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>-28.11262833618673</v>
-      </c>
-      <c r="R6" t="n">
-        <v>3.81816847880793</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.243433352717481</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.630723091404253</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>70</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>7811</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>民盛</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>71.09999847412109</v>
-      </c>
-      <c r="G7" t="n">
-        <v>71.43999977111817</v>
-      </c>
-      <c r="H7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>36.41787983405452</v>
-      </c>
-      <c r="J7" t="n">
-        <v>30.38974059579695</v>
-      </c>
-      <c r="K7" t="n">
-        <v>31.51942855059735</v>
-      </c>
-      <c r="L7" t="n">
-        <v>28646</v>
-      </c>
-      <c r="M7" t="n">
-        <v>17115.75</v>
-      </c>
-      <c r="N7" t="n">
-        <v>14710.275</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.673663146517097</v>
-      </c>
-      <c r="P7" t="n">
-        <v>-1.496101692220009</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>-1.703263588519433</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.2071618962994239</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.1749126241475578</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.1343593795597433</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN4"/>
+  <dimension ref="A1:AN6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,12 +629,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1459</t>
+          <t>8467</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>聯發</t>
+          <t>波力-KY</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,49 +643,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>13.69999980926514</v>
+        <v>102.5</v>
       </c>
       <c r="G2" t="n">
-        <v>14.84333333969116</v>
+        <v>101.85</v>
       </c>
       <c r="H2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>31.9289342271843</v>
+        <v>41.91358626901736</v>
       </c>
       <c r="J2" t="n">
-        <v>31.46602696278818</v>
+        <v>35.30562308662936</v>
       </c>
       <c r="K2" t="n">
-        <v>36.57986594470437</v>
+        <v>44.08463996678195</v>
       </c>
       <c r="L2" t="n">
-        <v>247632</v>
+        <v>40565.6</v>
       </c>
       <c r="M2" t="n">
-        <v>111208.25</v>
+        <v>23092.25</v>
       </c>
       <c r="N2" t="n">
-        <v>124365.625</v>
+        <v>19372.975</v>
       </c>
       <c r="O2" t="n">
-        <v>2.226741271443441</v>
+        <v>1.756675941062478</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.6286710517731873</v>
+        <v>-3.019199855882519</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.4513136467663639</v>
+        <v>-4.186681843865005</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.1773574050068234</v>
+        <v>1.167481987982486</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2355695179471785</v>
+        <v>1.165029003592418</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3333679681228651</v>
+        <v>0.7724555322457869</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -723,44 +723,44 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>13.552</v>
+        <v>8</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>61.552</v>
+        <v>8</v>
       </c>
       <c r="AF2" t="n">
-        <v>-24.145</v>
+        <v>16</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>31</v>
+        <v>-1</v>
       </c>
       <c r="AI2" t="n">
-        <v>6.854999999999986</v>
+        <v>15</v>
       </c>
       <c r="AJ2" t="n">
-        <v>66.18299999999999</v>
+        <v>94.05199999999999</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>28</v>
+        <v>-1.059</v>
       </c>
       <c r="AM2" t="n">
-        <v>94.18299999999999</v>
+        <v>92.99299999999999</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -775,63 +775,63 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>7811</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>民盛</t>
+          <t>聯發</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>71.09999847412109</v>
+        <v>14.44999980926514</v>
       </c>
       <c r="G3" t="n">
-        <v>71.40499954223633</v>
+        <v>14.77916669845581</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>39.66312670025113</v>
+        <v>41.18645139852207</v>
       </c>
       <c r="J3" t="n">
-        <v>33.48086929728168</v>
+        <v>34.70616845545042</v>
       </c>
       <c r="K3" t="n">
-        <v>31.51942855059735</v>
+        <v>47.27479554238437</v>
       </c>
       <c r="L3" t="n">
-        <v>33607.4</v>
+        <v>302876.2</v>
       </c>
       <c r="M3" t="n">
-        <v>18006.1</v>
+        <v>130273.8</v>
       </c>
       <c r="N3" t="n">
-        <v>15430.45</v>
+        <v>135719.425</v>
       </c>
       <c r="O3" t="n">
-        <v>1.866445260217371</v>
+        <v>2.324920283280291</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.413208994267791</v>
+        <v>-0.5503948588949186</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.645252669669104</v>
+        <v>-0.4706064219333512</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2320436754013135</v>
+        <v>-0.07978843696156734</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2071618962994239</v>
+        <v>-0.1775649264232301</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1749126241475578</v>
+        <v>-0.2357933053061301</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -869,44 +869,44 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>-38.894</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.001</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>-36.893</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>-37.717</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>33.001</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>-4.716000000000001</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>-30.71100000000001</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>31.001</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>0.2900000000000098</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6020</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>大展證</t>
+          <t>建錩</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,49 +935,49 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>21</v>
+        <v>10.25</v>
       </c>
       <c r="G4" t="n">
-        <v>21.24249992370606</v>
+        <v>10.90499997138977</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>39.74465932118099</v>
+        <v>44.57044597726546</v>
       </c>
       <c r="J4" t="n">
-        <v>38.52343680122007</v>
+        <v>42.76755594393747</v>
       </c>
       <c r="K4" t="n">
-        <v>42.63290209735876</v>
+        <v>38.39067067939058</v>
       </c>
       <c r="L4" t="n">
-        <v>87200</v>
+        <v>1097485</v>
       </c>
       <c r="M4" t="n">
-        <v>48860.55</v>
+        <v>521714.05</v>
       </c>
       <c r="N4" t="n">
-        <v>56112.55</v>
+        <v>391770.325</v>
       </c>
       <c r="O4" t="n">
-        <v>1.784670864327151</v>
+        <v>2.10361403914654</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3934653812201105</v>
+        <v>-0.0785288164789435</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.40118978333647</v>
+        <v>-0.05402145330111599</v>
       </c>
       <c r="R4" t="n">
-        <v>0.007724402116359497</v>
+        <v>-0.02450736317782751</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.01905354656901703</v>
+        <v>0.01783662699169236</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.008501141175759286</v>
+        <v>-0.01721878494978284</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1052,7 +1052,299 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>8929</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>富堡</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>13.5074999332428</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>41.14447904302897</v>
+      </c>
+      <c r="J5" t="n">
+        <v>36.16073190371743</v>
+      </c>
+      <c r="K5" t="n">
+        <v>47.81943988695995</v>
+      </c>
+      <c r="L5" t="n">
+        <v>40548.8</v>
+      </c>
+      <c r="M5" t="n">
+        <v>22910.75</v>
+      </c>
+      <c r="N5" t="n">
+        <v>29953.725</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.769859127265585</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.2057093339052631</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.2294001577721035</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.02369082386684035</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.002424394214406128</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.02319418862706873</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>70</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>7811</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>民盛</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>71.19999694824219</v>
+      </c>
+      <c r="G6" t="n">
+        <v>71.36499938964843</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>44.39068203127532</v>
+      </c>
+      <c r="J6" t="n">
+        <v>37.11747354898837</v>
+      </c>
+      <c r="K6" t="n">
+        <v>34.52930668260103</v>
+      </c>
+      <c r="L6" t="n">
+        <v>33431.4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>20112.1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>16383.45</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.662253071534052</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-1.321078949080402</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-1.576491973528077</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.2554130244476751</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.230487285558302</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.2054835135160917</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -625,16 +625,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8467</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>波力-KY</t>
+          <t>聯發</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,53 +643,53 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>102.5</v>
+        <v>14.05000019073486</v>
       </c>
       <c r="G2" t="n">
-        <v>101.85</v>
+        <v>14.70166668891907</v>
       </c>
       <c r="H2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>41.91358626901736</v>
+        <v>47.97045666053594</v>
       </c>
       <c r="J2" t="n">
-        <v>35.30562308662936</v>
+        <v>39.12759787686358</v>
       </c>
       <c r="K2" t="n">
-        <v>44.08463996678195</v>
+        <v>42.80125841840046</v>
       </c>
       <c r="L2" t="n">
-        <v>40565.6</v>
+        <v>334099.4</v>
       </c>
       <c r="M2" t="n">
-        <v>23092.25</v>
+        <v>142974.35</v>
       </c>
       <c r="N2" t="n">
-        <v>19372.975</v>
+        <v>142274.6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.756675941062478</v>
+        <v>2.33677859000583</v>
       </c>
       <c r="P2" t="n">
-        <v>-3.019199855882519</v>
+        <v>-0.5158815492146616</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.186681843865005</v>
+        <v>-0.4807083744189036</v>
       </c>
       <c r="R2" t="n">
-        <v>1.167481987982486</v>
+        <v>-0.03517317479575793</v>
       </c>
       <c r="S2" t="n">
-        <v>1.165029003592418</v>
+        <v>-0.07937339709733227</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7724555322457869</v>
+        <v>-0.177117354906587</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -723,44 +723,44 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>8</v>
+        <v>33.568</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="AE2" t="n">
-        <v>8</v>
+        <v>33.567</v>
       </c>
       <c r="AF2" t="n">
-        <v>16</v>
+        <v>45.868</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-1</v>
+        <v>32</v>
       </c>
       <c r="AI2" t="n">
-        <v>15</v>
+        <v>77.86799999999999</v>
       </c>
       <c r="AJ2" t="n">
-        <v>94.05199999999999</v>
+        <v>-18.14300000000001</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-1.059</v>
+        <v>28</v>
       </c>
       <c r="AM2" t="n">
-        <v>92.99299999999999</v>
+        <v>9.85699999999999</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -771,16 +771,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1459</t>
+          <t>8467</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>聯發</t>
+          <t>波力-KY</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,49 +789,49 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>14.44999980926514</v>
+        <v>103.5</v>
       </c>
       <c r="G3" t="n">
-        <v>14.77916669845581</v>
+        <v>101.7</v>
       </c>
       <c r="H3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>41.18645139852207</v>
+        <v>41.04918546502896</v>
       </c>
       <c r="J3" t="n">
-        <v>34.70616845545042</v>
+        <v>37.22014389351349</v>
       </c>
       <c r="K3" t="n">
-        <v>47.27479554238437</v>
+        <v>46.08586657416575</v>
       </c>
       <c r="L3" t="n">
-        <v>302876.2</v>
+        <v>40520.2</v>
       </c>
       <c r="M3" t="n">
-        <v>130273.8</v>
+        <v>23030.9</v>
       </c>
       <c r="N3" t="n">
-        <v>135719.425</v>
+        <v>19592.3</v>
       </c>
       <c r="O3" t="n">
-        <v>2.324920283280291</v>
+        <v>1.759384131753427</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.5503948588949186</v>
+        <v>-2.658907661689057</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.4706064219333512</v>
+        <v>-3.861497247313278</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.07978843696156734</v>
+        <v>1.202589585624222</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1775649264232301</v>
+        <v>1.159700038767443</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2357933053061301</v>
+        <v>1.156637089675833</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -869,44 +869,44 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>-38.894</v>
+        <v>1</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.001</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-36.893</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>-37.717</v>
+        <v>9</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>33.001</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-4.716000000000001</v>
+        <v>9</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-30.71100000000001</v>
+        <v>97.05199999999999</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>31.001</v>
+        <v>-1.059</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.2900000000000098</v>
+        <v>95.99299999999999</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5014</t>
+          <t>6020</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>建錩</t>
+          <t>大展證</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,49 +935,49 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>10.25</v>
+        <v>20.64999961853027</v>
       </c>
       <c r="G4" t="n">
-        <v>10.90499997138977</v>
+        <v>21.16249990463257</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>44.57044597726546</v>
+        <v>47.30063412423931</v>
       </c>
       <c r="J4" t="n">
-        <v>42.76755594393747</v>
+        <v>44.10983428112775</v>
       </c>
       <c r="K4" t="n">
-        <v>38.39067067939058</v>
+        <v>38.90783684475243</v>
       </c>
       <c r="L4" t="n">
-        <v>1097485</v>
+        <v>114404</v>
       </c>
       <c r="M4" t="n">
-        <v>521714.05</v>
+        <v>52411.55</v>
       </c>
       <c r="N4" t="n">
-        <v>391770.325</v>
+        <v>56384.3</v>
       </c>
       <c r="O4" t="n">
-        <v>2.10361403914654</v>
+        <v>2.18280131001659</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.0785288164789435</v>
+        <v>-0.3541664574205825</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.05402145330111599</v>
+        <v>-0.3738599196238003</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.02450736317782751</v>
+        <v>0.01969346220321783</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01783662699169236</v>
+        <v>0.02974251528031374</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.01721878494978284</v>
+        <v>0.002979082424031165</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -1081,49 +1081,49 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>13.5</v>
+        <v>13.44999980926514</v>
       </c>
       <c r="G5" t="n">
-        <v>13.5074999332428</v>
+        <v>13.45999994277954</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>41.14447904302897</v>
+        <v>38.18233954465142</v>
       </c>
       <c r="J5" t="n">
-        <v>36.16073190371743</v>
+        <v>36.83460112557794</v>
       </c>
       <c r="K5" t="n">
-        <v>47.81943988695995</v>
+        <v>44.55253100806173</v>
       </c>
       <c r="L5" t="n">
-        <v>40548.8</v>
+        <v>40499.6</v>
       </c>
       <c r="M5" t="n">
-        <v>22910.75</v>
+        <v>22745.95</v>
       </c>
       <c r="N5" t="n">
-        <v>29953.725</v>
+        <v>29520.075</v>
       </c>
       <c r="O5" t="n">
-        <v>1.769859127265585</v>
+        <v>1.780519169346631</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2057093339052631</v>
+        <v>-0.1882241743919622</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2294001577721035</v>
+        <v>-0.2239131305076552</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02369082386684035</v>
+        <v>0.03568895611569309</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002424394214406128</v>
+        <v>0.024780297944378</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.02319418862706873</v>
+        <v>0.00359926344323161</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -1227,49 +1227,49 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>71.19999694824219</v>
+        <v>71</v>
       </c>
       <c r="G6" t="n">
-        <v>71.36499938964843</v>
+        <v>71.31499938964843</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>44.39068203127532</v>
+        <v>42.41427074573702</v>
       </c>
       <c r="J6" t="n">
-        <v>37.11747354898837</v>
+        <v>38.88307262489973</v>
       </c>
       <c r="K6" t="n">
-        <v>34.52930668260103</v>
+        <v>31.92329749824945</v>
       </c>
       <c r="L6" t="n">
-        <v>33431.4</v>
+        <v>31967.4</v>
       </c>
       <c r="M6" t="n">
-        <v>20112.1</v>
+        <v>21296.1</v>
       </c>
       <c r="N6" t="n">
-        <v>16383.45</v>
+        <v>16698.975</v>
       </c>
       <c r="O6" t="n">
-        <v>1.662253071534052</v>
+        <v>1.501091749193515</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.321078949080402</v>
+        <v>-1.258008372619415</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.576491973528077</v>
+        <v>-1.519861978969336</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2554130244476751</v>
+        <v>0.2618536063499217</v>
       </c>
       <c r="S6" t="n">
-        <v>0.230487285558302</v>
+        <v>0.2582145309148196</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2054835135160917</v>
+        <v>0.2335083796902859</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN6"/>
+  <dimension ref="A1:AN5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,16 +625,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1459</t>
+          <t>8467</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>聯發</t>
+          <t>波力-KY</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,124 +643,124 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>14.05000019073486</v>
+        <v>101.5</v>
       </c>
       <c r="G2" t="n">
-        <v>14.70166668891907</v>
+        <v>101.65</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>47.97045666053594</v>
+        <v>37.23667206776477</v>
       </c>
       <c r="J2" t="n">
-        <v>39.12759787686358</v>
+        <v>37.22565329518393</v>
       </c>
       <c r="K2" t="n">
-        <v>42.80125841840046</v>
+        <v>42.55488443910907</v>
       </c>
       <c r="L2" t="n">
-        <v>334099.4</v>
+        <v>43666.6</v>
       </c>
       <c r="M2" t="n">
-        <v>142974.35</v>
+        <v>22617.5</v>
       </c>
       <c r="N2" t="n">
-        <v>142274.6</v>
+        <v>19960.6</v>
       </c>
       <c r="O2" t="n">
-        <v>2.33677859000583</v>
+        <v>1.930655465900298</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.5158815492146616</v>
+        <v>-2.500376453504416</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.4807083744189036</v>
+        <v>-3.565717376411674</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.03517317479575793</v>
+        <v>1.065340922907258</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.07937339709733227</v>
+        <v>1.193251246566158</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.177117354906587</v>
+        <v>1.149629742067528</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>33.568</v>
+        <v>1</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>33.567</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="n">
-        <v>45.868</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>77.86799999999999</v>
+        <v>1</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-18.14300000000001</v>
+        <v>1</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>9.85699999999999</v>
+        <v>1</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -771,16 +771,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8467</t>
+          <t>6988</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>波力-KY</t>
+          <t>威力暘-創</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,49 +789,49 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>103.5</v>
+        <v>12.5</v>
       </c>
       <c r="G3" t="n">
-        <v>101.7</v>
+        <v>12.55</v>
       </c>
       <c r="H3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>41.04918546502896</v>
+        <v>45.87114106856269</v>
       </c>
       <c r="J3" t="n">
-        <v>37.22014389351349</v>
+        <v>44.07927794204367</v>
       </c>
       <c r="K3" t="n">
-        <v>46.08586657416575</v>
+        <v>47.44649627369037</v>
       </c>
       <c r="L3" t="n">
-        <v>40520.2</v>
+        <v>54800</v>
       </c>
       <c r="M3" t="n">
-        <v>23030.9</v>
+        <v>32600.2</v>
       </c>
       <c r="N3" t="n">
-        <v>19592.3</v>
+        <v>34902.35</v>
       </c>
       <c r="O3" t="n">
-        <v>1.759384131753427</v>
+        <v>1.680971282384771</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.658907661689057</v>
+        <v>-0.2262184506843976</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.861497247313278</v>
+        <v>-0.3174875435626409</v>
       </c>
       <c r="R3" t="n">
-        <v>1.202589585624222</v>
+        <v>0.09126909287824325</v>
       </c>
       <c r="S3" t="n">
-        <v>1.159700038767443</v>
+        <v>0.1022516246019843</v>
       </c>
       <c r="T3" t="n">
-        <v>1.156637089675833</v>
+        <v>0.1161716889477103</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -869,44 +869,44 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>1</v>
+        <v>-14</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AE3" t="n">
-        <v>1</v>
+        <v>-16</v>
       </c>
       <c r="AF3" t="n">
-        <v>9</v>
+        <v>-14</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AI3" t="n">
-        <v>9</v>
+        <v>-16</v>
       </c>
       <c r="AJ3" t="n">
-        <v>97.05199999999999</v>
+        <v>-14</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-1.059</v>
+        <v>-2</v>
       </c>
       <c r="AM3" t="n">
-        <v>95.99299999999999</v>
+        <v>-16</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -921,63 +921,63 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6020</t>
+          <t>1465</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>大展證</t>
+          <t>偉全</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>20.64999961853027</v>
+        <v>12.14999961853027</v>
       </c>
       <c r="G4" t="n">
-        <v>21.16249990463257</v>
+        <v>12.52249999046326</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>47.30063412423931</v>
+        <v>30.61055300860447</v>
       </c>
       <c r="J4" t="n">
-        <v>44.10983428112775</v>
+        <v>30.54864047304081</v>
       </c>
       <c r="K4" t="n">
-        <v>38.90783684475243</v>
+        <v>38.46762503667086</v>
       </c>
       <c r="L4" t="n">
-        <v>114404</v>
+        <v>199419.6</v>
       </c>
       <c r="M4" t="n">
-        <v>52411.55</v>
+        <v>125585</v>
       </c>
       <c r="N4" t="n">
-        <v>56384.3</v>
+        <v>144531.35</v>
       </c>
       <c r="O4" t="n">
-        <v>2.18280131001659</v>
+        <v>1.5879253095513</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3541664574205825</v>
+        <v>-0.1281232606445268</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.3738599196238003</v>
+        <v>-0.08383887415678533</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01969346220321783</v>
+        <v>-0.04428438648774151</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02974251528031374</v>
+        <v>-0.04247929157827249</v>
       </c>
       <c r="T4" t="n">
-        <v>0.002979082424031165</v>
+        <v>-0.03498809082202311</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1024,10 +1024,10 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -1036,10 +1036,10 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
@@ -1048,11 +1048,11 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>8929</t>
+          <t>7811</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>富堡</t>
+          <t>民盛</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1081,49 +1081,49 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>13.44999980926514</v>
+        <v>71</v>
       </c>
       <c r="G5" t="n">
-        <v>13.45999994277954</v>
+        <v>71.29999923706055</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>38.18233954465142</v>
+        <v>44.9428471642375</v>
       </c>
       <c r="J5" t="n">
-        <v>36.83460112557794</v>
+        <v>40.90299747932674</v>
       </c>
       <c r="K5" t="n">
-        <v>44.55253100806173</v>
+        <v>31.36503982144893</v>
       </c>
       <c r="L5" t="n">
-        <v>40499.6</v>
+        <v>33451</v>
       </c>
       <c r="M5" t="n">
-        <v>22745.95</v>
+        <v>22117</v>
       </c>
       <c r="N5" t="n">
-        <v>29520.075</v>
+        <v>17584.425</v>
       </c>
       <c r="O5" t="n">
-        <v>1.780519169346631</v>
+        <v>1.512456481439617</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1882241743919622</v>
+        <v>-1.190152686403295</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2239131305076552</v>
+        <v>-1.454705298879741</v>
       </c>
       <c r="R5" t="n">
-        <v>0.03568895611569309</v>
+        <v>0.2645526124764466</v>
       </c>
       <c r="S5" t="n">
-        <v>0.024780297944378</v>
+        <v>0.2621648795687959</v>
       </c>
       <c r="T5" t="n">
-        <v>0.00359926344323161</v>
+        <v>0.2585502023494664</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1198,153 +1198,7 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>70</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>7811</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>民盛</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>71</v>
-      </c>
-      <c r="G6" t="n">
-        <v>71.31499938964843</v>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>42.41427074573702</v>
-      </c>
-      <c r="J6" t="n">
-        <v>38.88307262489973</v>
-      </c>
-      <c r="K6" t="n">
-        <v>31.92329749824945</v>
-      </c>
-      <c r="L6" t="n">
-        <v>31967.4</v>
-      </c>
-      <c r="M6" t="n">
-        <v>21296.1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>16698.975</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.501091749193515</v>
-      </c>
-      <c r="P6" t="n">
-        <v>-1.258008372619415</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>-1.519861978969336</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.2618536063499217</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.2582145309148196</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.2335083796902859</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -625,67 +625,67 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8467</t>
+          <t>8342</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>波力-KY</t>
+          <t>益張</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>101.5</v>
+        <v>87.19999694824219</v>
       </c>
       <c r="G2" t="n">
-        <v>101.65</v>
+        <v>88.73999977111816</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>37.23667206776477</v>
+        <v>49.90617637001312</v>
       </c>
       <c r="J2" t="n">
-        <v>37.22565329518393</v>
+        <v>43.75009207564154</v>
       </c>
       <c r="K2" t="n">
-        <v>42.55488443910907</v>
+        <v>39.1147730689353</v>
       </c>
       <c r="L2" t="n">
-        <v>43666.6</v>
+        <v>3618</v>
       </c>
       <c r="M2" t="n">
-        <v>22617.5</v>
+        <v>2004.6</v>
       </c>
       <c r="N2" t="n">
-        <v>19960.6</v>
+        <v>2154.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.930655465900298</v>
+        <v>1.804848847650404</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.500376453504416</v>
+        <v>-0.6055156444235621</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.565717376411674</v>
+        <v>-0.5592947951834357</v>
       </c>
       <c r="R2" t="n">
-        <v>1.065340922907258</v>
+        <v>-0.04622084924012637</v>
       </c>
       <c r="S2" t="n">
-        <v>1.193251246566158</v>
+        <v>-0.001411482991145352</v>
       </c>
       <c r="T2" t="n">
-        <v>1.149629742067528</v>
+        <v>-0.08474471577809761</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -732,10 +732,10 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -744,10 +744,10 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
@@ -756,11 +756,11 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -775,63 +775,63 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6988</t>
+          <t>4584</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>威力暘-創</t>
+          <t>君帆</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>12.5</v>
+        <v>39.79999923706055</v>
       </c>
       <c r="G3" t="n">
-        <v>12.55</v>
+        <v>39.40750026702881</v>
       </c>
       <c r="H3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>45.87114106856269</v>
+        <v>44.71749116969745</v>
       </c>
       <c r="J3" t="n">
-        <v>44.07927794204367</v>
+        <v>41.44649892120882</v>
       </c>
       <c r="K3" t="n">
-        <v>47.44649627369037</v>
+        <v>49.63313696617928</v>
       </c>
       <c r="L3" t="n">
-        <v>54800</v>
+        <v>8077.8</v>
       </c>
       <c r="M3" t="n">
-        <v>32600.2</v>
+        <v>4668.35</v>
       </c>
       <c r="N3" t="n">
-        <v>34902.35</v>
+        <v>5891.575</v>
       </c>
       <c r="O3" t="n">
-        <v>1.680971282384771</v>
+        <v>1.730332987029678</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2262184506843976</v>
+        <v>-0.2509251721950676</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.3174875435626409</v>
+        <v>-0.3424985641775271</v>
       </c>
       <c r="R3" t="n">
-        <v>0.09126909287824325</v>
+        <v>0.09157339198245951</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1022516246019843</v>
+        <v>0.04415298686633379</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1161716889477103</v>
+        <v>0.01084492184506303</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -869,44 +869,44 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -921,63 +921,63 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1465</t>
+          <t>7819</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>偉全</t>
+          <t>精誠金融</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>12.14999961853027</v>
+        <v>35.84999847412109</v>
       </c>
       <c r="G4" t="n">
-        <v>12.52249999046326</v>
+        <v>35.40499992370606</v>
       </c>
       <c r="H4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>30.61055300860447</v>
+        <v>48.24483946451893</v>
       </c>
       <c r="J4" t="n">
-        <v>30.54864047304081</v>
+        <v>47.50377495528758</v>
       </c>
       <c r="K4" t="n">
-        <v>38.46762503667086</v>
+        <v>46.79476274213145</v>
       </c>
       <c r="L4" t="n">
-        <v>199419.6</v>
+        <v>97490.8</v>
       </c>
       <c r="M4" t="n">
-        <v>125585</v>
+        <v>56873.35</v>
       </c>
       <c r="N4" t="n">
-        <v>144531.35</v>
+        <v>69303.35000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>1.5879253095513</v>
+        <v>1.714173685917921</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1281232606445268</v>
+        <v>-0.7673380379722801</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.08383887415678533</v>
+        <v>-1.397098456175129</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.04428438648774151</v>
+        <v>0.6297604182028491</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.04247929157827249</v>
+        <v>0.7254691575985563</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.03498809082202311</v>
+        <v>0.5295582033396011</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>-24</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1024,10 +1024,10 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-24</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>-24</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -1036,10 +1036,10 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>-24</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-24</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
@@ -1048,11 +1048,11 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-24</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>7811</t>
+          <t>6020</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>民盛</t>
+          <t>大展證</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1081,49 +1081,49 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>71</v>
+        <v>20.60000038146973</v>
       </c>
       <c r="G5" t="n">
-        <v>71.29999923706055</v>
+        <v>21.06749992370606</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>44.9428471642375</v>
+        <v>49.30534459593568</v>
       </c>
       <c r="J5" t="n">
-        <v>40.90299747932674</v>
+        <v>48.43419468483906</v>
       </c>
       <c r="K5" t="n">
-        <v>31.36503982144893</v>
+        <v>40.55883946955406</v>
       </c>
       <c r="L5" t="n">
-        <v>33451</v>
+        <v>84400.2</v>
       </c>
       <c r="M5" t="n">
-        <v>22117</v>
+        <v>54310.6</v>
       </c>
       <c r="N5" t="n">
-        <v>17584.425</v>
+        <v>54258.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.512456481439617</v>
+        <v>1.554028127105942</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.190152686403295</v>
+        <v>-0.3285590825018545</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.454705298879741</v>
+        <v>-0.3521573628639053</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2645526124764466</v>
+        <v>0.02359828036205081</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2621648795687959</v>
+        <v>0.03611472135866739</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2585502023494664</v>
+        <v>0.01754449702771199</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -629,12 +629,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8342</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>益張</t>
+          <t>時報</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,49 +643,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>87.19999694824219</v>
+        <v>18.85000038146973</v>
       </c>
       <c r="G2" t="n">
-        <v>88.73999977111816</v>
+        <v>18.91250019073486</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>49.90617637001312</v>
+        <v>37.38776074978771</v>
       </c>
       <c r="J2" t="n">
-        <v>43.75009207564154</v>
+        <v>32.81662618768949</v>
       </c>
       <c r="K2" t="n">
-        <v>39.1147730689353</v>
+        <v>47.28624596376431</v>
       </c>
       <c r="L2" t="n">
-        <v>3618</v>
+        <v>28201.2</v>
       </c>
       <c r="M2" t="n">
-        <v>2004.6</v>
+        <v>12015.65</v>
       </c>
       <c r="N2" t="n">
-        <v>2154.8</v>
+        <v>8637.825000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>1.804848847650404</v>
+        <v>2.347039069879699</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.6055156444235621</v>
+        <v>-0.1174362084035323</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.5592947951834357</v>
+        <v>-0.1226297921312219</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.04622084924012637</v>
+        <v>0.005193583727689549</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.001411482991145352</v>
+        <v>-0.002956345945167554</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.08474471577809761</v>
+        <v>0.001363349996190324</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -775,12 +775,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4584</t>
+          <t>8409</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>君帆</t>
+          <t>商之器</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,49 +789,49 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>39.79999923706055</v>
+        <v>18.29999923706055</v>
       </c>
       <c r="G3" t="n">
-        <v>39.40750026702881</v>
+        <v>18.44000015258789</v>
       </c>
       <c r="H3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>44.71749116969745</v>
+        <v>37.89704488206014</v>
       </c>
       <c r="J3" t="n">
-        <v>41.44649892120882</v>
+        <v>33.49350415057427</v>
       </c>
       <c r="K3" t="n">
-        <v>49.63313696617928</v>
+        <v>46.37460019856501</v>
       </c>
       <c r="L3" t="n">
-        <v>8077.8</v>
+        <v>18021.2</v>
       </c>
       <c r="M3" t="n">
-        <v>4668.35</v>
+        <v>9415.6</v>
       </c>
       <c r="N3" t="n">
-        <v>5891.575</v>
+        <v>10409.05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.730332987029678</v>
+        <v>1.913972556183355</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2509251721950676</v>
+        <v>-0.1552324643155423</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.3424985641775271</v>
+        <v>-0.1984299724267301</v>
       </c>
       <c r="R3" t="n">
-        <v>0.09157339198245951</v>
+        <v>0.04319750811118783</v>
       </c>
       <c r="S3" t="n">
-        <v>0.04415298686633379</v>
+        <v>0.04856700662524713</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01084492184506303</v>
+        <v>-0.02533949637466779</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>7819</t>
+          <t>4584</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>精誠金融</t>
+          <t>君帆</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,49 +935,49 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>35.84999847412109</v>
+        <v>39.79999923706055</v>
       </c>
       <c r="G4" t="n">
-        <v>35.40499992370606</v>
+        <v>39.40750026702881</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>48.24483946451893</v>
+        <v>44.71749116969745</v>
       </c>
       <c r="J4" t="n">
-        <v>47.50377495528758</v>
+        <v>41.44649892120882</v>
       </c>
       <c r="K4" t="n">
-        <v>46.79476274213145</v>
+        <v>49.63313696617928</v>
       </c>
       <c r="L4" t="n">
-        <v>97490.8</v>
+        <v>8000.2</v>
       </c>
       <c r="M4" t="n">
-        <v>56873.35</v>
+        <v>4648.95</v>
       </c>
       <c r="N4" t="n">
-        <v>69303.35000000001</v>
+        <v>5881.875</v>
       </c>
       <c r="O4" t="n">
-        <v>1.714173685917921</v>
+        <v>1.720861699953753</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7673380379722801</v>
+        <v>-0.2509251721950676</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.397098456175129</v>
+        <v>-0.3424985641775271</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6297604182028491</v>
+        <v>0.09157339198245951</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7254691575985563</v>
+        <v>0.04415298686633379</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5295582033396011</v>
+        <v>0.01084492184506303</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6020</t>
+          <t>8342</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>大展證</t>
+          <t>益張</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1081,49 +1081,49 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>20.60000038146973</v>
+        <v>87.59999847412109</v>
       </c>
       <c r="G5" t="n">
-        <v>21.06749992370606</v>
+        <v>88.56499977111817</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>49.30534459593568</v>
+        <v>49.93745091334208</v>
       </c>
       <c r="J5" t="n">
-        <v>48.43419468483906</v>
+        <v>45.81254502154172</v>
       </c>
       <c r="K5" t="n">
-        <v>40.55883946955406</v>
+        <v>42.44062692058727</v>
       </c>
       <c r="L5" t="n">
-        <v>84400.2</v>
+        <v>3111.8</v>
       </c>
       <c r="M5" t="n">
-        <v>54310.6</v>
+        <v>2028.05</v>
       </c>
       <c r="N5" t="n">
-        <v>54258.2</v>
+        <v>2191.525</v>
       </c>
       <c r="O5" t="n">
-        <v>1.554028127105942</v>
+        <v>1.534380316067158</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3285590825018545</v>
+        <v>-0.6108665099546755</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.3521573628639053</v>
+        <v>-0.5696091381376837</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02359828036205081</v>
+        <v>-0.04125737181699185</v>
       </c>
       <c r="S5" t="n">
-        <v>0.03611472135866739</v>
+        <v>-0.04622084924012637</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01754449702771199</v>
+        <v>-0.001411482991145352</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -643,50 +643,50 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>18.85000038146973</v>
+        <v>18.64999961853027</v>
       </c>
       <c r="G2" t="n">
-        <v>18.91250019073486</v>
+        <v>18.8600001335144</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>37.38776074978771</v>
+        <v>33.25848067484701</v>
       </c>
       <c r="J2" t="n">
-        <v>32.81662618768949</v>
+        <v>32.96391100240162</v>
       </c>
       <c r="K2" t="n">
-        <v>47.28624596376431</v>
+        <v>42.91043896564534</v>
       </c>
       <c r="L2" t="n">
-        <v>28201.2</v>
+        <v>30001.2</v>
       </c>
       <c r="M2" t="n">
-        <v>12015.65</v>
+        <v>11915.65</v>
       </c>
       <c r="N2" t="n">
-        <v>8637.825000000001</v>
+        <v>8887.825000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>2.347039069879699</v>
+        <v>2.517798021929144</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1174362084035323</v>
+        <v>-0.1246498465442087</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1226297921312219</v>
+        <v>-0.1230338030138192</v>
       </c>
       <c r="R2" t="n">
+        <v>-0.001616043530389494</v>
+      </c>
+      <c r="S2" t="n">
         <v>0.005193583727689549</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>-0.002956345945167554</v>
       </c>
-      <c r="T2" t="n">
-        <v>0.001363349996190324</v>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>否</t>
@@ -760,7 +760,7 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -775,12 +775,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8409</t>
+          <t>6661</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>商之器</t>
+          <t>威健生技</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,49 +789,49 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>18.29999923706055</v>
+        <v>17</v>
       </c>
       <c r="G3" t="n">
-        <v>18.44000015258789</v>
+        <v>17.32999992370605</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>37.89704488206014</v>
+        <v>48.35923086390213</v>
       </c>
       <c r="J3" t="n">
-        <v>33.49350415057427</v>
+        <v>47.01255300555324</v>
       </c>
       <c r="K3" t="n">
-        <v>46.37460019856501</v>
+        <v>43.72982084623394</v>
       </c>
       <c r="L3" t="n">
-        <v>18021.2</v>
+        <v>9620</v>
       </c>
       <c r="M3" t="n">
-        <v>9415.6</v>
+        <v>4355.5</v>
       </c>
       <c r="N3" t="n">
-        <v>10409.05</v>
+        <v>6111.95</v>
       </c>
       <c r="O3" t="n">
-        <v>1.913972556183355</v>
+        <v>2.208701641602572</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1552324643155423</v>
+        <v>-0.19292524546346</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1984299724267301</v>
+        <v>-0.1135414172768312</v>
       </c>
       <c r="R3" t="n">
-        <v>0.04319750811118783</v>
+        <v>-0.07938382818662885</v>
       </c>
       <c r="S3" t="n">
-        <v>0.04856700662524713</v>
+        <v>-0.0976204054357751</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.02533949637466779</v>
+        <v>-0.09682486267147003</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4584</t>
+          <t>8409</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>君帆</t>
+          <t>商之器</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,49 +935,49 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>39.79999923706055</v>
+        <v>18.29999923706055</v>
       </c>
       <c r="G4" t="n">
-        <v>39.40750026702881</v>
+        <v>18.44000015258789</v>
       </c>
       <c r="H4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>44.71749116969745</v>
+        <v>37.89704488328402</v>
       </c>
       <c r="J4" t="n">
-        <v>41.44649892120882</v>
+        <v>33.49350417423594</v>
       </c>
       <c r="K4" t="n">
-        <v>49.63313696617928</v>
+        <v>46.13221330864257</v>
       </c>
       <c r="L4" t="n">
-        <v>8000.2</v>
+        <v>18000.4</v>
       </c>
       <c r="M4" t="n">
-        <v>4648.95</v>
+        <v>9410.4</v>
       </c>
       <c r="N4" t="n">
-        <v>5881.875</v>
+        <v>10406.45</v>
       </c>
       <c r="O4" t="n">
-        <v>1.720861699953753</v>
+        <v>1.912819858879538</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2509251721950676</v>
+        <v>-0.1552324643155423</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.3424985641775271</v>
+        <v>-0.1984299724267301</v>
       </c>
       <c r="R4" t="n">
-        <v>0.09157339198245951</v>
+        <v>0.04319750811118783</v>
       </c>
       <c r="S4" t="n">
-        <v>0.04415298686633379</v>
+        <v>0.04856700662524713</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01084492184506303</v>
+        <v>-0.02533949637466779</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -1081,49 +1081,49 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>87.59999847412109</v>
+        <v>87.40000152587891</v>
       </c>
       <c r="G5" t="n">
-        <v>88.56499977111817</v>
+        <v>88.37999992370605</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>49.93745091334208</v>
+        <v>47.57738715312724</v>
       </c>
       <c r="J5" t="n">
-        <v>45.81254502154172</v>
+        <v>46.40082572714077</v>
       </c>
       <c r="K5" t="n">
-        <v>42.44062692058727</v>
+        <v>40.65175616110128</v>
       </c>
       <c r="L5" t="n">
-        <v>3111.8</v>
+        <v>3927.6</v>
       </c>
       <c r="M5" t="n">
-        <v>2028.05</v>
+        <v>2282</v>
       </c>
       <c r="N5" t="n">
-        <v>2191.525</v>
+        <v>2268.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.534380316067158</v>
+        <v>1.721121822962314</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6108665099546755</v>
+        <v>-0.6327415330722346</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.5696091381376837</v>
+        <v>-0.5932282348656327</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.04125737181699185</v>
+        <v>-0.03951329820660188</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.04622084924012637</v>
+        <v>-0.0368994992554853</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.001411482991145352</v>
+        <v>-0.04152139793492093</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN5"/>
+  <dimension ref="A1:AN3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -655,10 +655,10 @@
         <v>33.25848067484701</v>
       </c>
       <c r="J2" t="n">
-        <v>32.96391100240162</v>
+        <v>32.96391100240168</v>
       </c>
       <c r="K2" t="n">
-        <v>42.91043896564534</v>
+        <v>45.1516167597907</v>
       </c>
       <c r="L2" t="n">
         <v>30001.2</v>
@@ -673,19 +673,19 @@
         <v>2.517798021929144</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1246498465442087</v>
+        <v>-0.1226392215458318</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1230338030138192</v>
+        <v>-0.1200893464844985</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.001616043530389494</v>
+        <v>-0.002549875061333334</v>
       </c>
       <c r="S2" t="n">
-        <v>0.005193583727689549</v>
+        <v>0.004186556618706108</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.002956345945167554</v>
+        <v>-0.004042153395988721</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -775,12 +775,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6661</t>
+          <t>2724</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>威健生技</t>
+          <t>藝舍-KY</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,49 +789,49 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>17</v>
+        <v>10.69999980926514</v>
       </c>
       <c r="G3" t="n">
-        <v>17.32999992370605</v>
+        <v>10.85249996185303</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>48.35923086390213</v>
+        <v>48.72958239602466</v>
       </c>
       <c r="J3" t="n">
-        <v>47.01255300555324</v>
+        <v>44.03436872915796</v>
       </c>
       <c r="K3" t="n">
-        <v>43.72982084623394</v>
+        <v>42.65765761022612</v>
       </c>
       <c r="L3" t="n">
-        <v>9620</v>
+        <v>73036</v>
       </c>
       <c r="M3" t="n">
-        <v>4355.5</v>
+        <v>32109</v>
       </c>
       <c r="N3" t="n">
-        <v>6111.95</v>
+        <v>23909.5</v>
       </c>
       <c r="O3" t="n">
-        <v>2.208701641602572</v>
+        <v>2.274627051605469</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.19292524546346</v>
+        <v>-0.2556198595796761</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1135414172768312</v>
+        <v>-0.282382201027134</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.07938382818662885</v>
+        <v>0.02676234144745782</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0976204054357751</v>
+        <v>0.01741148389431668</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.09682486267147003</v>
+        <v>0.02051376601574773</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -906,299 +906,7 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>70</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>8409</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>商之器</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>18.29999923706055</v>
-      </c>
-      <c r="G4" t="n">
-        <v>18.44000015258789</v>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>37.89704488328402</v>
-      </c>
-      <c r="J4" t="n">
-        <v>33.49350417423594</v>
-      </c>
-      <c r="K4" t="n">
-        <v>46.13221330864257</v>
-      </c>
-      <c r="L4" t="n">
-        <v>18000.4</v>
-      </c>
-      <c r="M4" t="n">
-        <v>9410.4</v>
-      </c>
-      <c r="N4" t="n">
-        <v>10406.45</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.912819858879538</v>
-      </c>
-      <c r="P4" t="n">
-        <v>-0.1552324643155423</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-0.1984299724267301</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.04319750811118783</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.04856700662524713</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-0.02533949637466779</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>70</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>8342</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>益張</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>87.40000152587891</v>
-      </c>
-      <c r="G5" t="n">
-        <v>88.37999992370605</v>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>47.57738715312724</v>
-      </c>
-      <c r="J5" t="n">
-        <v>46.40082572714077</v>
-      </c>
-      <c r="K5" t="n">
-        <v>40.65175616110128</v>
-      </c>
-      <c r="L5" t="n">
-        <v>3927.6</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2282</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2268.5</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.721121822962314</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-0.6327415330722346</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-0.5932282348656327</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-0.03951329820660188</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-0.0368994992554853</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-0.04152139793492093</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN3"/>
+  <dimension ref="A1:AN2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,49 +643,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>18.64999961853027</v>
+        <v>18.60000038146973</v>
       </c>
       <c r="G2" t="n">
-        <v>18.8600001335144</v>
+        <v>18.8225001335144</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>33.25848067484701</v>
+        <v>34.06258385838736</v>
       </c>
       <c r="J2" t="n">
-        <v>32.96391100240168</v>
+        <v>32.78385003853562</v>
       </c>
       <c r="K2" t="n">
-        <v>45.1516167597907</v>
+        <v>43.15707489886147</v>
       </c>
       <c r="L2" t="n">
-        <v>30001.2</v>
+        <v>17800</v>
       </c>
       <c r="M2" t="n">
-        <v>11915.65</v>
+        <v>11865.65</v>
       </c>
       <c r="N2" t="n">
-        <v>8887.825000000001</v>
+        <v>8510.325000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>2.517798021929144</v>
+        <v>1.50012852224699</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1226392215458318</v>
+        <v>-0.136715611585668</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1200893464844985</v>
+        <v>-0.1292344728517604</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.002549875061333334</v>
+        <v>-0.0074811387339076</v>
       </c>
       <c r="S2" t="n">
-        <v>0.004186556618706108</v>
+        <v>-0.003675970619922669</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.004042153395988721</v>
+        <v>-0.0005358144408473542</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -760,153 +760,7 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>70</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2724</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>藝舍-KY</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>10.69999980926514</v>
-      </c>
-      <c r="G3" t="n">
-        <v>10.85249996185303</v>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>48.72958239602466</v>
-      </c>
-      <c r="J3" t="n">
-        <v>44.03436872915796</v>
-      </c>
-      <c r="K3" t="n">
-        <v>42.65765761022612</v>
-      </c>
-      <c r="L3" t="n">
-        <v>73036</v>
-      </c>
-      <c r="M3" t="n">
-        <v>32109</v>
-      </c>
-      <c r="N3" t="n">
-        <v>23909.5</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2.274627051605469</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-0.2556198595796761</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-0.282382201027134</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.02676234144745782</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.01741148389431668</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.02051376601574773</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN2"/>
+  <dimension ref="A1:AN3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,136 +629,282 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>6907</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>雅特力-KY</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>180</v>
+      </c>
+      <c r="G2" t="n">
+        <v>179.15</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>43.36391340357704</v>
+      </c>
+      <c r="J2" t="n">
+        <v>42.82624677233818</v>
+      </c>
+      <c r="K2" t="n">
+        <v>48.51654402689286</v>
+      </c>
+      <c r="L2" t="n">
+        <v>3814129</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2372817.7</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2172090.625</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.607426057214593</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.273621053691357</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.146429830411354</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.1271912232800034</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.7148217626953706</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.4054525646158387</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>70</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>8923</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="F3" t="n">
         <v>18.60000038146973</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G3" t="n">
         <v>18.8225001335144</v>
       </c>
-      <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>34.06258385838736</v>
-      </c>
-      <c r="J2" t="n">
-        <v>32.78385003853562</v>
-      </c>
-      <c r="K2" t="n">
-        <v>43.15707489886147</v>
-      </c>
-      <c r="L2" t="n">
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>34.06258386144705</v>
+      </c>
+      <c r="J3" t="n">
+        <v>32.78385009717957</v>
+      </c>
+      <c r="K3" t="n">
+        <v>42.30433471869176</v>
+      </c>
+      <c r="L3" t="n">
         <v>17800</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M3" t="n">
         <v>11865.65</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N3" t="n">
         <v>8510.325000000001</v>
       </c>
-      <c r="O2" t="n">
+      <c r="O3" t="n">
         <v>1.50012852224699</v>
       </c>
-      <c r="P2" t="n">
-        <v>-0.136715611585668</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-0.1292344728517604</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-0.0074811387339076</v>
-      </c>
-      <c r="S2" t="n">
-        <v>-0.003675970619922669</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-0.0005358144408473542</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="P3" t="n">
+        <v>-0.1402002140320135</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-0.1343364616112708</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-0.005863752420742718</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-0.001931937384782173</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.00134450575415096</v>
+      </c>
+      <c r="U3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN3"/>
+  <dimension ref="A1:AN2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,63 +629,63 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6907</t>
+          <t>6550</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>雅特力-KY</t>
+          <t>北極星藥業-KY</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>180</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
-        <v>179.15</v>
+        <v>11.09000005722046</v>
       </c>
       <c r="H2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>43.36391340357704</v>
+        <v>48.13886385077568</v>
       </c>
       <c r="J2" t="n">
-        <v>42.82624677233818</v>
+        <v>44.85280594057446</v>
       </c>
       <c r="K2" t="n">
-        <v>48.51654402689286</v>
+        <v>43.58499099827454</v>
       </c>
       <c r="L2" t="n">
-        <v>3814129</v>
+        <v>2446713.6</v>
       </c>
       <c r="M2" t="n">
-        <v>2372817.7</v>
+        <v>1417155.75</v>
       </c>
       <c r="N2" t="n">
-        <v>2172090.625</v>
+        <v>1281346.85</v>
       </c>
       <c r="O2" t="n">
-        <v>1.607426057214593</v>
+        <v>1.726495905619407</v>
       </c>
       <c r="P2" t="n">
-        <v>1.273621053691357</v>
+        <v>-0.2731308478133201</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.146429830411354</v>
+        <v>-0.4055090282287857</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1271912232800034</v>
+        <v>0.1323781804154656</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7148217626953706</v>
+        <v>0.1608115895811605</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4054525646158387</v>
+        <v>0.1380148453021072</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -723,190 +723,44 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>-130</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>-132</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>-2222.561</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>-2223.561</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>-2209.906</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>-2224.905999999999</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>70</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>8923</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>時報</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>18.60000038146973</v>
-      </c>
-      <c r="G3" t="n">
-        <v>18.8225001335144</v>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>34.06258386144705</v>
-      </c>
-      <c r="J3" t="n">
-        <v>32.78385009717957</v>
-      </c>
-      <c r="K3" t="n">
-        <v>42.30433471869176</v>
-      </c>
-      <c r="L3" t="n">
-        <v>17800</v>
-      </c>
-      <c r="M3" t="n">
-        <v>11865.65</v>
-      </c>
-      <c r="N3" t="n">
-        <v>8510.325000000001</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.50012852224699</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-0.1402002140320135</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-0.1343364616112708</v>
-      </c>
-      <c r="R3" t="n">
-        <v>-0.005863752420742718</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-0.001931937384782173</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.00134450575415096</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN2"/>
+  <dimension ref="A1:AN1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -615,152 +615,6 @@
       <c r="AN1" t="inlineStr">
         <is>
           <t>最後更新日期</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>70</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>6550</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>北極星藥業-KY</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>11</v>
-      </c>
-      <c r="G2" t="n">
-        <v>11.09000005722046</v>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>48.13886385077568</v>
-      </c>
-      <c r="J2" t="n">
-        <v>44.85280594057446</v>
-      </c>
-      <c r="K2" t="n">
-        <v>43.58499099827454</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2446713.6</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1417155.75</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1281346.85</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.726495905619407</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-0.2731308478133201</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-0.4055090282287857</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.1323781804154656</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.1608115895811605</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.1380148453021072</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>-130</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-132</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-2222.561</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-2223.561</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-2209.906</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-15</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-2224.905999999999</v>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN1"/>
+  <dimension ref="A1:AN5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -615,6 +615,590 @@
       <c r="AN1" t="inlineStr">
         <is>
           <t>最後更新日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>70</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>6550</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>北極星藥業-KY</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>11.35000038146973</v>
+      </c>
+      <c r="G2" t="n">
+        <v>11.10250005722046</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>46.87397969520661</v>
+      </c>
+      <c r="J2" t="n">
+        <v>46.39462758901279</v>
+      </c>
+      <c r="K2" t="n">
+        <v>48.18984476592306</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2698115.2</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1463965.9</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1307351.675</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.843017791602933</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-0.181089991853197</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-0.3121791394883475</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.1310891476351506</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.1388136029897911</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.1241816137688709</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>74.182</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>79.182</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-3537.651</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>17.878</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-3519.773</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>-2613.951</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>-20</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>-2633.951</v>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>70</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>6542</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>隆中</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>45.86999988555908</v>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>40.30688338878142</v>
+      </c>
+      <c r="J3" t="n">
+        <v>33.28729277459881</v>
+      </c>
+      <c r="K3" t="n">
+        <v>43.55498438453485</v>
+      </c>
+      <c r="L3" t="n">
+        <v>15600</v>
+      </c>
+      <c r="M3" t="n">
+        <v>8734.75</v>
+      </c>
+      <c r="N3" t="n">
+        <v>8645.325000000001</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.785969833137754</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-0.5708410800254029</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-0.4544436828600001</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-0.1163973971654028</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-0.1326224917015854</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-0.2328665219159451</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>70</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>6228</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>全譜</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>17.29999923706055</v>
+      </c>
+      <c r="G4" t="n">
+        <v>17.68249979019165</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>44.48953589446234</v>
+      </c>
+      <c r="J4" t="n">
+        <v>33.84275607343196</v>
+      </c>
+      <c r="K4" t="n">
+        <v>43.21700973099448</v>
+      </c>
+      <c r="L4" t="n">
+        <v>6835.2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>4223.45</v>
+      </c>
+      <c r="N4" t="n">
+        <v>5068.975</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.618392546377961</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0.3861452062587496</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0.3965793047837565</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.01043409852500687</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.002720171082027711</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.01419004333247131</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>6222</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>立軒</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>20.04999923706055</v>
+      </c>
+      <c r="G5" t="n">
+        <v>20.37500009536743</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>47.26784087804582</v>
+      </c>
+      <c r="J5" t="n">
+        <v>42.12329245757009</v>
+      </c>
+      <c r="K5" t="n">
+        <v>44.69488075644762</v>
+      </c>
+      <c r="L5" t="n">
+        <v>17402</v>
+      </c>
+      <c r="M5" t="n">
+        <v>10761.8</v>
+      </c>
+      <c r="N5" t="n">
+        <v>10919.025</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.617015740861194</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.1221449479726964</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.1231954680025476</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.001050520029851273</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.01069981426369032</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.01373174288371459</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN5"/>
+  <dimension ref="A1:AN4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,142 +625,142 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6550</t>
+          <t>4609</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>北極星藥業-KY</t>
+          <t>唐鋒</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11.35000038146973</v>
+        <v>4.590000152587891</v>
       </c>
       <c r="G2" t="n">
-        <v>11.10250005722046</v>
+        <v>4.764500045776368</v>
       </c>
       <c r="H2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>46.87397969520661</v>
+        <v>39.24526664842698</v>
       </c>
       <c r="J2" t="n">
-        <v>46.39462758901279</v>
+        <v>31.14822243988785</v>
       </c>
       <c r="K2" t="n">
-        <v>48.18984476592306</v>
+        <v>44.46810715292703</v>
       </c>
       <c r="L2" t="n">
-        <v>2698115.2</v>
+        <v>40430.6</v>
       </c>
       <c r="M2" t="n">
-        <v>1463965.9</v>
+        <v>14912.65</v>
       </c>
       <c r="N2" t="n">
-        <v>1307351.675</v>
+        <v>9406.525</v>
       </c>
       <c r="O2" t="n">
-        <v>1.843017791602933</v>
+        <v>2.711161329475311</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.181089991853197</v>
+        <v>-0.1417454263268638</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.3121791394883475</v>
+        <v>-0.1291143198334029</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1310891476351506</v>
+        <v>-0.01263110649346094</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1388136029897911</v>
+        <v>-0.02161029515317797</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1241816137688709</v>
+        <v>-0.03535119910329143</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
       <c r="AB2" t="n">
-        <v>74.182</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>79.182</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>-3537.651</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>17.878</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>-3519.773</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-2613.951</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-2633.951</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
@@ -792,46 +792,46 @@
         <v>44.5</v>
       </c>
       <c r="G3" t="n">
-        <v>45.86999988555908</v>
+        <v>45.71999988555908</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>40.30688338878142</v>
+        <v>38.92797936854922</v>
       </c>
       <c r="J3" t="n">
-        <v>33.28729277459881</v>
+        <v>35.16752168622688</v>
       </c>
       <c r="K3" t="n">
-        <v>43.55498438453485</v>
+        <v>43.40723428889185</v>
       </c>
       <c r="L3" t="n">
-        <v>15600</v>
+        <v>15200</v>
       </c>
       <c r="M3" t="n">
-        <v>8734.75</v>
+        <v>8484.75</v>
       </c>
       <c r="N3" t="n">
-        <v>8645.325000000001</v>
+        <v>8295.325000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>1.785969833137754</v>
+        <v>1.791449365037273</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.5708410800254029</v>
+        <v>-0.5669700050867803</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.4544436828600001</v>
+        <v>-0.4675263528237529</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.1163973971654028</v>
+        <v>-0.09944365226302743</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1326224917015854</v>
+        <v>-0.1201292238367336</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2328665219159451</v>
+        <v>-0.1366461715483219</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6228</t>
+          <t>6227</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>全譜</t>
+          <t>茂綸</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,49 +935,49 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>17.29999923706055</v>
+        <v>113</v>
       </c>
       <c r="G4" t="n">
-        <v>17.68249979019165</v>
+        <v>121.6</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>44.48953589446234</v>
+        <v>30.88367611911146</v>
       </c>
       <c r="J4" t="n">
-        <v>33.84275607343196</v>
+        <v>30.39766425710232</v>
       </c>
       <c r="K4" t="n">
-        <v>43.21700973099448</v>
+        <v>42.14429574337748</v>
       </c>
       <c r="L4" t="n">
-        <v>6835.2</v>
+        <v>1055438</v>
       </c>
       <c r="M4" t="n">
-        <v>4223.45</v>
+        <v>603307.85</v>
       </c>
       <c r="N4" t="n">
-        <v>5068.975</v>
+        <v>506595.675</v>
       </c>
       <c r="O4" t="n">
-        <v>1.618392546377961</v>
+        <v>1.749418642571947</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3861452062587496</v>
+        <v>-0.1915979441394455</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.3965793047837565</v>
+        <v>0.4091599988347991</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01043409852500687</v>
+        <v>-0.6007579429742447</v>
       </c>
       <c r="S4" t="n">
-        <v>0.002720171082027711</v>
+        <v>-0.1267952254921575</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.01419004333247131</v>
+        <v>-0.5899587362438803</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1052,153 +1052,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>70</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>6222</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>立軒</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>20.04999923706055</v>
-      </c>
-      <c r="G5" t="n">
-        <v>20.37500009536743</v>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>47.26784087804582</v>
-      </c>
-      <c r="J5" t="n">
-        <v>42.12329245757009</v>
-      </c>
-      <c r="K5" t="n">
-        <v>44.69488075644762</v>
-      </c>
-      <c r="L5" t="n">
-        <v>17402</v>
-      </c>
-      <c r="M5" t="n">
-        <v>10761.8</v>
-      </c>
-      <c r="N5" t="n">
-        <v>10919.025</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.617015740861194</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-0.1221449479726964</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-0.1231954680025476</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.001050520029851273</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.01069981426369032</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-0.01373174288371459</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -625,142 +625,142 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4609</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>唐鋒</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.590000152587891</v>
+        <v>168</v>
       </c>
       <c r="G2" t="n">
-        <v>4.764500045776368</v>
+        <v>168.575</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>39.24526664842698</v>
+        <v>40.63733839315542</v>
       </c>
       <c r="J2" t="n">
-        <v>31.14822243988785</v>
+        <v>38.98813928163934</v>
       </c>
       <c r="K2" t="n">
-        <v>44.46810715292703</v>
+        <v>48.62712894236181</v>
       </c>
       <c r="L2" t="n">
-        <v>40430.6</v>
+        <v>434049.2</v>
       </c>
       <c r="M2" t="n">
-        <v>14912.65</v>
+        <v>270561.8</v>
       </c>
       <c r="N2" t="n">
-        <v>9406.525</v>
+        <v>332854.525</v>
       </c>
       <c r="O2" t="n">
-        <v>2.711161329475311</v>
+        <v>1.604251597971332</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1417454263268638</v>
+        <v>-3.261524819703368</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1291143198334029</v>
+        <v>-4.674034715563756</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.01263110649346094</v>
+        <v>1.412509895860389</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.02161029515317797</v>
+        <v>1.480065135753152</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.03535119910329143</v>
+        <v>1.638999725348588</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>-20.102</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>-4.311</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>-4.413</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>260.547</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>-5.157999999999999</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>275.389</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>-68.05500000000001</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>15.488</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>-88.36199999999999</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>-140.9290000000001</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -775,63 +775,63 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6542</t>
+          <t>9925</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>隆中</t>
+          <t>新保</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>44.5</v>
+        <v>40.04999923706055</v>
       </c>
       <c r="G3" t="n">
-        <v>45.71999988555908</v>
+        <v>39.97749996185303</v>
       </c>
       <c r="H3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>38.92797936854922</v>
+        <v>38.52803532260781</v>
       </c>
       <c r="J3" t="n">
-        <v>35.16752168622688</v>
+        <v>33.11910554402737</v>
       </c>
       <c r="K3" t="n">
-        <v>43.40723428889185</v>
+        <v>48.9439231709404</v>
       </c>
       <c r="L3" t="n">
-        <v>15200</v>
+        <v>2896579.2</v>
       </c>
       <c r="M3" t="n">
-        <v>8484.75</v>
+        <v>1190605.7</v>
       </c>
       <c r="N3" t="n">
-        <v>8295.325000000001</v>
+        <v>884572.425</v>
       </c>
       <c r="O3" t="n">
-        <v>1.791449365037273</v>
+        <v>2.432861861823776</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.5669700050867803</v>
+        <v>-0.1942060268055528</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.4675263528237529</v>
+        <v>-0.1939156910764807</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.09944365226302743</v>
+        <v>-0.0002903357290720276</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1201292238367336</v>
+        <v>-0.03105669733093042</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1366461715483219</v>
+        <v>0.001637612903149538</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -869,44 +869,44 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>316</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>-54.668</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>261.332</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>-2739.631</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>-28.838</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>-2768.469</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>-6926.824</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>62.002</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>-6864.822000000001</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6227</t>
+          <t>8444</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>茂綸</t>
+          <t>綠河-KY</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,49 +935,49 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>113</v>
+        <v>4.889999866485596</v>
       </c>
       <c r="G4" t="n">
-        <v>121.6</v>
+        <v>5.089000034332275</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>30.88367611911146</v>
+        <v>48.17172001257191</v>
       </c>
       <c r="J4" t="n">
-        <v>30.39766425710232</v>
+        <v>47.51413972720252</v>
       </c>
       <c r="K4" t="n">
-        <v>42.14429574337748</v>
+        <v>45.81499460867524</v>
       </c>
       <c r="L4" t="n">
-        <v>1055438</v>
+        <v>20450</v>
       </c>
       <c r="M4" t="n">
-        <v>603307.85</v>
+        <v>13460.75</v>
       </c>
       <c r="N4" t="n">
-        <v>506595.675</v>
+        <v>8305.375</v>
       </c>
       <c r="O4" t="n">
-        <v>1.749418642571947</v>
+        <v>1.519231840722099</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1915979441394455</v>
+        <v>-0.1143622958960417</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4091599988347991</v>
+        <v>-0.09286524852376615</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.6007579429742447</v>
+        <v>-0.02149704737227559</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1267952254921575</v>
+        <v>-0.02789654593372123</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5899587362438803</v>
+        <v>-0.01311907110652535</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN4"/>
+  <dimension ref="A1:AN5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,16 +625,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>1465</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>偉全</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,49 +643,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>168</v>
+        <v>12.14999961853027</v>
       </c>
       <c r="G2" t="n">
-        <v>168.575</v>
+        <v>12.1675000667572</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>40.63733839315542</v>
+        <v>48.08642059314924</v>
       </c>
       <c r="J2" t="n">
-        <v>38.98813928163934</v>
+        <v>40.65995778945945</v>
       </c>
       <c r="K2" t="n">
-        <v>48.62712894236181</v>
+        <v>46.67356983849211</v>
       </c>
       <c r="L2" t="n">
-        <v>434049.2</v>
+        <v>293107.4</v>
       </c>
       <c r="M2" t="n">
-        <v>270561.8</v>
+        <v>194721.2</v>
       </c>
       <c r="N2" t="n">
-        <v>332854.525</v>
+        <v>148682.375</v>
       </c>
       <c r="O2" t="n">
-        <v>1.604251597971332</v>
+        <v>1.50526701766423</v>
       </c>
       <c r="P2" t="n">
-        <v>-3.261524819703368</v>
+        <v>-0.1111415760929901</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.674034715563756</v>
+        <v>-0.1373876447224291</v>
       </c>
       <c r="R2" t="n">
-        <v>1.412509895860389</v>
+        <v>0.02624606862943893</v>
       </c>
       <c r="S2" t="n">
-        <v>1.480065135753152</v>
+        <v>0.02323696535995801</v>
       </c>
       <c r="T2" t="n">
-        <v>1.638999725348588</v>
+        <v>-0.001777285467496892</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -719,48 +719,48 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>-20.102</v>
+        <v>-7.835</v>
       </c>
       <c r="AC2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-4.311</v>
+        <v>-1</v>
       </c>
       <c r="AE2" t="n">
-        <v>-4.413</v>
+        <v>-8.835000000000001</v>
       </c>
       <c r="AF2" t="n">
-        <v>260.547</v>
+        <v>93.154</v>
       </c>
       <c r="AG2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-5.157999999999999</v>
+        <v>-2</v>
       </c>
       <c r="AI2" t="n">
-        <v>275.389</v>
+        <v>91.154</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-68.05500000000001</v>
+        <v>79.154</v>
       </c>
       <c r="AK2" t="n">
-        <v>15.488</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-88.36199999999999</v>
+        <v>-1</v>
       </c>
       <c r="AM2" t="n">
-        <v>-140.9290000000001</v>
+        <v>78.154</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
@@ -775,12 +775,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9925</t>
+          <t>2530</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>新保</t>
+          <t>華建</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,49 +789,49 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>40.04999923706055</v>
+        <v>19.25</v>
       </c>
       <c r="G3" t="n">
-        <v>39.97749996185303</v>
+        <v>19.39750003814697</v>
       </c>
       <c r="H3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>38.52803532260781</v>
+        <v>47.98557412587265</v>
       </c>
       <c r="J3" t="n">
-        <v>33.11910554402737</v>
+        <v>46.86092131658774</v>
       </c>
       <c r="K3" t="n">
-        <v>48.9439231709404</v>
+        <v>48.31578281323959</v>
       </c>
       <c r="L3" t="n">
-        <v>2896579.2</v>
+        <v>2660598.4</v>
       </c>
       <c r="M3" t="n">
-        <v>1190605.7</v>
+        <v>1059501.95</v>
       </c>
       <c r="N3" t="n">
-        <v>884572.425</v>
+        <v>996335.675</v>
       </c>
       <c r="O3" t="n">
-        <v>2.432861861823776</v>
+        <v>2.511178389053461</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1942060268055528</v>
+        <v>-0.07374934878184902</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1939156910764807</v>
+        <v>-0.06005546306619387</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.0002903357290720276</v>
+        <v>-0.01369388571565516</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.03105669733093042</v>
+        <v>-0.009323540466111266</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001637612903149538</v>
+        <v>-0.05165641910063603</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -869,44 +869,44 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>316</v>
+        <v>-433.208</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>-19.184</v>
       </c>
       <c r="AD3" t="n">
-        <v>-54.668</v>
+        <v>36</v>
       </c>
       <c r="AE3" t="n">
-        <v>261.332</v>
+        <v>-416.3920000000001</v>
       </c>
       <c r="AF3" t="n">
-        <v>-2739.631</v>
+        <v>-1925.51</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>-22.184</v>
       </c>
       <c r="AH3" t="n">
-        <v>-28.838</v>
+        <v>11</v>
       </c>
       <c r="AI3" t="n">
-        <v>-2768.469</v>
+        <v>-1936.694</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-6926.824</v>
+        <v>-1690.265</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>-54.228</v>
       </c>
       <c r="AL3" t="n">
-        <v>62.002</v>
+        <v>-781</v>
       </c>
       <c r="AM3" t="n">
-        <v>-6864.822000000001</v>
+        <v>-2525.493</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>8444</t>
+          <t>6227</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>綠河-KY</t>
+          <t>茂綸</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,49 +935,49 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.889999866485596</v>
+        <v>116</v>
       </c>
       <c r="G4" t="n">
-        <v>5.089000034332275</v>
+        <v>120.4</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>48.17172001257191</v>
+        <v>34.64091492825637</v>
       </c>
       <c r="J4" t="n">
-        <v>47.51413972720252</v>
+        <v>30.79359975733892</v>
       </c>
       <c r="K4" t="n">
-        <v>45.81499460867524</v>
+        <v>47.80055861706591</v>
       </c>
       <c r="L4" t="n">
-        <v>20450</v>
+        <v>1191907</v>
       </c>
       <c r="M4" t="n">
-        <v>13460.75</v>
+        <v>600671.35</v>
       </c>
       <c r="N4" t="n">
-        <v>8305.375</v>
+        <v>511200.775</v>
       </c>
       <c r="O4" t="n">
-        <v>1.519231840722099</v>
+        <v>1.984291409936565</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1143622958960417</v>
+        <v>-1.14675427467995</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.09286524852376615</v>
+        <v>-0.2970070595654647</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.02149704737227559</v>
+        <v>-0.8497472151144847</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.02789654593372123</v>
+        <v>-1.040778039090142</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.01311907110652535</v>
+        <v>-1.00273657762509</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1052,7 +1052,153 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>8940</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>新天地</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>15.10000038146973</v>
+      </c>
+      <c r="G5" t="n">
+        <v>15.3300000667572</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>35.25930465462448</v>
+      </c>
+      <c r="J5" t="n">
+        <v>34.52901657944073</v>
+      </c>
+      <c r="K5" t="n">
+        <v>40.28911598067277</v>
+      </c>
+      <c r="L5" t="n">
+        <v>76512.2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>44836.55</v>
+      </c>
+      <c r="N5" t="n">
+        <v>48583.25</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.706469387140625</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.1466393689532612</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.1706259203092211</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.02398655135595981</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.04018771560159415</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.02451660384770615</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-21</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-21</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-24</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-11</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-35</v>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -629,12 +629,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1465</t>
+          <t>2106</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>偉全</t>
+          <t>建大</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,53 +643,53 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>12.14999961853027</v>
+        <v>17.20000076293945</v>
       </c>
       <c r="G2" t="n">
-        <v>12.1675000667572</v>
+        <v>17.5625</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>48.08642059314924</v>
+        <v>39.77132117722304</v>
       </c>
       <c r="J2" t="n">
-        <v>40.65995778945945</v>
+        <v>32.2137549952864</v>
       </c>
       <c r="K2" t="n">
-        <v>46.67356983849211</v>
+        <v>43.21345266486828</v>
       </c>
       <c r="L2" t="n">
-        <v>293107.4</v>
+        <v>4413277.4</v>
       </c>
       <c r="M2" t="n">
-        <v>194721.2</v>
+        <v>2256736.5</v>
       </c>
       <c r="N2" t="n">
-        <v>148682.375</v>
+        <v>1704566.775</v>
       </c>
       <c r="O2" t="n">
-        <v>1.50526701766423</v>
+        <v>1.955601551177995</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1111415760929901</v>
+        <v>-0.187762020403099</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1373876447224291</v>
+        <v>-0.1663321102892028</v>
       </c>
       <c r="R2" t="n">
-        <v>0.02624606862943893</v>
+        <v>-0.02142991011389614</v>
       </c>
       <c r="S2" t="n">
-        <v>0.02323696535995801</v>
+        <v>-0.02678250327495299</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.001777285467496892</v>
+        <v>-0.0511044018189149</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -723,44 +723,44 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>-7.835</v>
+        <v>-455</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-1</v>
+        <v>-0.249</v>
       </c>
       <c r="AE2" t="n">
-        <v>-8.835000000000001</v>
+        <v>-455.249</v>
       </c>
       <c r="AF2" t="n">
-        <v>93.154</v>
+        <v>-1313.426</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-2</v>
+        <v>-1.667</v>
       </c>
       <c r="AI2" t="n">
-        <v>91.154</v>
+        <v>-1315.093</v>
       </c>
       <c r="AJ2" t="n">
-        <v>79.154</v>
+        <v>-8117.264000000001</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-1</v>
+        <v>79.18299999999999</v>
       </c>
       <c r="AM2" t="n">
-        <v>78.154</v>
+        <v>-8038.081</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
@@ -775,12 +775,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2530</t>
+          <t>2704</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>華建</t>
+          <t>國賓</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,49 +789,49 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>19.25</v>
+        <v>45.25</v>
       </c>
       <c r="G3" t="n">
-        <v>19.39750003814697</v>
+        <v>45.77499980926514</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>47.98557412587265</v>
+        <v>32.25842460499458</v>
       </c>
       <c r="J3" t="n">
-        <v>46.86092131658774</v>
+        <v>31.49296140852754</v>
       </c>
       <c r="K3" t="n">
-        <v>48.31578281323959</v>
+        <v>47.53913320856115</v>
       </c>
       <c r="L3" t="n">
-        <v>2660598.4</v>
+        <v>908680.2</v>
       </c>
       <c r="M3" t="n">
-        <v>1059501.95</v>
+        <v>310948</v>
       </c>
       <c r="N3" t="n">
-        <v>996335.675</v>
+        <v>215548.525</v>
       </c>
       <c r="O3" t="n">
-        <v>2.511178389053461</v>
+        <v>2.922289900562152</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.07374934878184902</v>
+        <v>-0.1890376227310355</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.06005546306619387</v>
+        <v>-0.0519490723817114</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.01369388571565516</v>
+        <v>-0.1370885503493241</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.009323540466111266</v>
+        <v>-0.1633282929777167</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.05165641910063603</v>
+        <v>-0.1810936432509944</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -869,44 +869,44 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>-433.208</v>
+        <v>13</v>
       </c>
       <c r="AC3" t="n">
-        <v>-19.184</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-416.3920000000001</v>
+        <v>13</v>
       </c>
       <c r="AF3" t="n">
-        <v>-1925.51</v>
+        <v>-349.6</v>
       </c>
       <c r="AG3" t="n">
-        <v>-22.184</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="AI3" t="n">
-        <v>-1936.694</v>
+        <v>-315.6</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-1690.265</v>
+        <v>-965.6</v>
       </c>
       <c r="AK3" t="n">
-        <v>-54.228</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-781</v>
+        <v>72</v>
       </c>
       <c r="AM3" t="n">
-        <v>-2525.493</v>
+        <v>-893.6</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
@@ -921,63 +921,63 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6227</t>
+          <t>9925</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>茂綸</t>
+          <t>新保</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>116</v>
+        <v>39.70000076293945</v>
       </c>
       <c r="G4" t="n">
-        <v>120.4</v>
+        <v>39.95500011444092</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>34.64091492825637</v>
+        <v>49.22235761647798</v>
       </c>
       <c r="J4" t="n">
-        <v>30.79359975733892</v>
+        <v>42.59622544825307</v>
       </c>
       <c r="K4" t="n">
-        <v>47.80055861706591</v>
+        <v>43.68429142240677</v>
       </c>
       <c r="L4" t="n">
-        <v>1191907</v>
+        <v>2903902</v>
       </c>
       <c r="M4" t="n">
-        <v>600671.35</v>
+        <v>1225104.45</v>
       </c>
       <c r="N4" t="n">
-        <v>511200.775</v>
+        <v>899215.675</v>
       </c>
       <c r="O4" t="n">
-        <v>1.984291409936565</v>
+        <v>2.370330137973134</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.14675427467995</v>
+        <v>-0.1774098468069099</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2970070595654647</v>
+        <v>-0.1883040406648572</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.8497472151144847</v>
+        <v>0.01089419385794738</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.040778039090142</v>
+        <v>0.01806395404082961</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.00273657762509</v>
+        <v>0.0002253833358206725</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1015,44 +1015,44 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>-836.457</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.998</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>-834.4589999999999</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>-2358.187</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>-20.002</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-2378.189</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>-7147.281</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>50.911</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>-7096.37</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
@@ -1067,63 +1067,63 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>8940</t>
+          <t>6535</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>順藥</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>15.10000038146973</v>
+        <v>75.5</v>
       </c>
       <c r="G5" t="n">
-        <v>15.3300000667572</v>
+        <v>82.54500007629395</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>35.25930465462448</v>
+        <v>31.5075704025027</v>
       </c>
       <c r="J5" t="n">
-        <v>34.52901657944073</v>
+        <v>30.25804520329676</v>
       </c>
       <c r="K5" t="n">
-        <v>40.28911598067277</v>
+        <v>37.17836291417249</v>
       </c>
       <c r="L5" t="n">
-        <v>76512.2</v>
+        <v>859238.6</v>
       </c>
       <c r="M5" t="n">
-        <v>44836.55</v>
+        <v>409810.85</v>
       </c>
       <c r="N5" t="n">
-        <v>48583.25</v>
+        <v>286565.875</v>
       </c>
       <c r="O5" t="n">
-        <v>1.706469387140625</v>
+        <v>2.096671183791254</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1466393689532612</v>
+        <v>-3.896573235028953</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1706259203092211</v>
+        <v>-3.86748031740224</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02398655135595981</v>
+        <v>-0.02909291762671273</v>
       </c>
       <c r="S5" t="n">
-        <v>0.04018771560159415</v>
+        <v>0.05416966693924463</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02451660384770615</v>
+        <v>-0.4435522587338143</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1170,10 +1170,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-21</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1182,23 +1182,23 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>-21</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-24</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>-35</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN5"/>
+  <dimension ref="A1:AN3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,16 +625,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>2704</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>建大</t>
+          <t>國賓</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,73 +643,73 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>17.20000076293945</v>
+        <v>45.5</v>
       </c>
       <c r="G2" t="n">
-        <v>17.5625</v>
+        <v>45.75749988555908</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>39.77132117722304</v>
+        <v>41.01783119166475</v>
       </c>
       <c r="J2" t="n">
-        <v>32.2137549952864</v>
+        <v>34.6679179853013</v>
       </c>
       <c r="K2" t="n">
-        <v>43.21345266486828</v>
+        <v>47.68797670930434</v>
       </c>
       <c r="L2" t="n">
-        <v>4413277.4</v>
+        <v>899332.6</v>
       </c>
       <c r="M2" t="n">
-        <v>2256736.5</v>
+        <v>311256.15</v>
       </c>
       <c r="N2" t="n">
-        <v>1704566.775</v>
+        <v>217058.625</v>
       </c>
       <c r="O2" t="n">
-        <v>1.955601551177995</v>
+        <v>2.889364916966299</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.187762020403099</v>
+        <v>-0.1794406981319199</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1663321102892028</v>
+        <v>-0.08529930157837143</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.02142991011389614</v>
+        <v>-0.09414139655354845</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.02678250327495299</v>
+        <v>-0.1339757706633029</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0511044018189149</v>
+        <v>-0.1599715274110831</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -723,44 +723,44 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>-455</v>
+        <v>14.217</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.249</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-455.249</v>
+        <v>14.217</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1313.426</v>
+        <v>-256.383</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-1.667</v>
+        <v>32</v>
       </c>
       <c r="AI2" t="n">
-        <v>-1315.093</v>
+        <v>-224.383</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-8117.264000000001</v>
+        <v>-940.383</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>79.18299999999999</v>
+        <v>72</v>
       </c>
       <c r="AM2" t="n">
-        <v>-8038.081</v>
+        <v>-868.383</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
@@ -775,63 +775,63 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2704</t>
+          <t>6535</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>國賓</t>
+          <t>順藥</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>45.25</v>
+        <v>79.69999694824219</v>
       </c>
       <c r="G3" t="n">
-        <v>45.77499980926514</v>
+        <v>81.97499999999999</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>32.25842460499458</v>
+        <v>37.26520550327341</v>
       </c>
       <c r="J3" t="n">
-        <v>31.49296140852754</v>
+        <v>32.59376532184708</v>
       </c>
       <c r="K3" t="n">
-        <v>47.53913320856115</v>
+        <v>44.60928521458295</v>
       </c>
       <c r="L3" t="n">
-        <v>908680.2</v>
+        <v>878468.4</v>
       </c>
       <c r="M3" t="n">
-        <v>310948</v>
+        <v>418926.6</v>
       </c>
       <c r="N3" t="n">
-        <v>215548.525</v>
+        <v>295074.6</v>
       </c>
       <c r="O3" t="n">
-        <v>2.922289900562152</v>
+        <v>2.096950635266417</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1890376227310355</v>
+        <v>-3.572540009941363</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.0519490723817114</v>
+        <v>-3.788862495793524</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.1370885503493241</v>
+        <v>0.2163224858521606</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1633282929777167</v>
+        <v>-0.03687486684175978</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1810936432509944</v>
+        <v>0.04577775302265463</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -878,327 +878,35 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-349.6</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-315.6</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-965.6</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-893.6</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>70</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>9925</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>新保</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>39.70000076293945</v>
-      </c>
-      <c r="G4" t="n">
-        <v>39.95500011444092</v>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>49.22235761647798</v>
-      </c>
-      <c r="J4" t="n">
-        <v>42.59622544825307</v>
-      </c>
-      <c r="K4" t="n">
-        <v>43.68429142240677</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2903902</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1225104.45</v>
-      </c>
-      <c r="N4" t="n">
-        <v>899215.675</v>
-      </c>
-      <c r="O4" t="n">
-        <v>2.370330137973134</v>
-      </c>
-      <c r="P4" t="n">
-        <v>-0.1774098468069099</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-0.1883040406648572</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.01089419385794738</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.01806395404082961</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.0002253833358206725</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>-836.457</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.998</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-834.4589999999999</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>-2358.187</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-20.002</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>-2378.189</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>-7147.281</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>50.911</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>-7096.37</v>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>70</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>6535</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>順藥</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>75.5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>82.54500007629395</v>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>31.5075704025027</v>
-      </c>
-      <c r="J5" t="n">
-        <v>30.25804520329676</v>
-      </c>
-      <c r="K5" t="n">
-        <v>37.17836291417249</v>
-      </c>
-      <c r="L5" t="n">
-        <v>859238.6</v>
-      </c>
-      <c r="M5" t="n">
-        <v>409810.85</v>
-      </c>
-      <c r="N5" t="n">
-        <v>286565.875</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.096671183791254</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-3.896573235028953</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-3.86748031740224</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-0.02909291762671273</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.05416966693924463</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-0.4435522587338143</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN3"/>
+  <dimension ref="A1:AN4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,16 +625,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2704</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>國賓</t>
+          <t>南染</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,87 +643,87 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>45.5</v>
+        <v>24.75</v>
       </c>
       <c r="G2" t="n">
-        <v>45.75749988555908</v>
+        <v>25.16499967575073</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>41.01783119166475</v>
+        <v>41.53221999262983</v>
       </c>
       <c r="J2" t="n">
-        <v>34.6679179853013</v>
+        <v>30.92729492314109</v>
       </c>
       <c r="K2" t="n">
-        <v>47.68797670930434</v>
+        <v>42.84013193989495</v>
       </c>
       <c r="L2" t="n">
-        <v>899332.6</v>
+        <v>158042.4</v>
       </c>
       <c r="M2" t="n">
-        <v>311256.15</v>
+        <v>91347.55</v>
       </c>
       <c r="N2" t="n">
-        <v>217058.625</v>
+        <v>104477.625</v>
       </c>
       <c r="O2" t="n">
-        <v>2.889364916966299</v>
+        <v>1.730121935399471</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1794406981319199</v>
+        <v>-0.3279423869955238</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.08529930157837143</v>
+        <v>-0.2970050668850561</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.09414139655354845</v>
+        <v>-0.03093732011046768</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1339757706633029</v>
+        <v>-0.05616015346633674</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1599715274110831</v>
+        <v>-0.06713371817698643</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
       <c r="AB2" t="n">
-        <v>14.217</v>
+        <v>7.003</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -732,35 +732,35 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>14.217</v>
+        <v>7.003</v>
       </c>
       <c r="AF2" t="n">
-        <v>-256.383</v>
+        <v>29.003</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
-        <v>-224.383</v>
+        <v>30.003</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-940.383</v>
+        <v>45.003</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>-868.383</v>
+        <v>46.003</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
@@ -775,12 +775,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6535</t>
+          <t>8066</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>順藥</t>
+          <t>來思達</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,49 +789,49 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>79.69999694824219</v>
+        <v>14.60000038146973</v>
       </c>
       <c r="G3" t="n">
-        <v>81.97499999999999</v>
+        <v>14.6625</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>37.26520550327341</v>
+        <v>36.01950815853459</v>
       </c>
       <c r="J3" t="n">
-        <v>32.59376532184708</v>
+        <v>31.30157680673906</v>
       </c>
       <c r="K3" t="n">
-        <v>44.60928521458295</v>
+        <v>46.49900023183958</v>
       </c>
       <c r="L3" t="n">
-        <v>878468.4</v>
+        <v>110119.4</v>
       </c>
       <c r="M3" t="n">
-        <v>418926.6</v>
+        <v>35797.4</v>
       </c>
       <c r="N3" t="n">
-        <v>295074.6</v>
+        <v>23647.975</v>
       </c>
       <c r="O3" t="n">
-        <v>2.096950635266417</v>
+        <v>3.076184303887992</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.572540009941363</v>
+        <v>-0.07770842759280328</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.788862495793524</v>
+        <v>-0.07981713894704977</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2163224858521606</v>
+        <v>0.002108711354246492</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.03687486684175978</v>
+        <v>-0.001253150284892132</v>
       </c>
       <c r="T3" t="n">
-        <v>0.04577775302265463</v>
+        <v>-0.01552515409852336</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -906,7 +906,153 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>70</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>8921</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>沈氏</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>16.60000038146973</v>
+      </c>
+      <c r="G4" t="n">
+        <v>17.05250015258789</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>38.46079581451455</v>
+      </c>
+      <c r="J4" t="n">
+        <v>32.30387795984601</v>
+      </c>
+      <c r="K4" t="n">
+        <v>40.2160164062549</v>
+      </c>
+      <c r="L4" t="n">
+        <v>8076.2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3570.8</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2810.425</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.261734065195474</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0.2694232018089799</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0.2074656312027846</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-0.06195757060619533</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-0.07987516441935788</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.08371633253146349</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN4"/>
+  <dimension ref="A1:AN5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,50 +643,50 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>24.75</v>
+        <v>24.54999923706055</v>
       </c>
       <c r="G2" t="n">
-        <v>25.16499967575073</v>
+        <v>25.11499967575073</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>41.53221999262983</v>
+        <v>41.32447089010093</v>
       </c>
       <c r="J2" t="n">
-        <v>30.92729492314109</v>
+        <v>34.39302024546104</v>
       </c>
       <c r="K2" t="n">
-        <v>42.84013193989495</v>
+        <v>40.43433517996497</v>
       </c>
       <c r="L2" t="n">
-        <v>158042.4</v>
+        <v>138425.2</v>
       </c>
       <c r="M2" t="n">
-        <v>91347.55</v>
+        <v>90905</v>
       </c>
       <c r="N2" t="n">
-        <v>104477.625</v>
+        <v>104381.35</v>
       </c>
       <c r="O2" t="n">
-        <v>1.730121935399471</v>
+        <v>1.52274572355756</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.3279423869955238</v>
+        <v>-0.326457809784845</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2970050668850561</v>
+        <v>-0.3028956154650139</v>
       </c>
       <c r="R2" t="n">
+        <v>-0.02356219431983103</v>
+      </c>
+      <c r="S2" t="n">
         <v>-0.03093732011046768</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>-0.05616015346633674</v>
       </c>
-      <c r="T2" t="n">
-        <v>-0.06713371817698643</v>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>是</t>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>7.003</v>
+        <v>-1.451</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -732,22 +732,22 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>7.003</v>
+        <v>-1.451</v>
       </c>
       <c r="AF2" t="n">
-        <v>29.003</v>
+        <v>19.552</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>30.003</v>
+        <v>19.552</v>
       </c>
       <c r="AJ2" t="n">
-        <v>45.003</v>
+        <v>45.552</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
@@ -756,11 +756,11 @@
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>46.003</v>
+        <v>46.552</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
@@ -775,12 +775,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>來思達</t>
+          <t>沈氏</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,49 +789,49 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>14.60000038146973</v>
+        <v>16.60000038146973</v>
       </c>
       <c r="G3" t="n">
-        <v>14.6625</v>
+        <v>17.05250015258789</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>36.01950815853459</v>
+        <v>38.46079581451455</v>
       </c>
       <c r="J3" t="n">
-        <v>31.30157680673906</v>
+        <v>32.30387795984601</v>
       </c>
       <c r="K3" t="n">
-        <v>46.49900023183958</v>
+        <v>40.2160164062549</v>
       </c>
       <c r="L3" t="n">
-        <v>110119.4</v>
+        <v>8077.6</v>
       </c>
       <c r="M3" t="n">
-        <v>35797.4</v>
+        <v>3571.15</v>
       </c>
       <c r="N3" t="n">
-        <v>23647.975</v>
+        <v>2810.6</v>
       </c>
       <c r="O3" t="n">
-        <v>3.076184303887992</v>
+        <v>2.261904428545427</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.07770842759280328</v>
+        <v>-0.2694232018089799</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.07981713894704977</v>
+        <v>-0.2074656312027846</v>
       </c>
       <c r="R3" t="n">
-        <v>0.002108711354246492</v>
+        <v>-0.06195757060619533</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.001253150284892132</v>
+        <v>-0.07987516441935788</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.01552515409852336</v>
+        <v>-0.08371633253146349</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>8921</t>
+          <t>3521</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>沈氏</t>
+          <t>台鋼建設</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,49 +935,49 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>16.60000038146973</v>
+        <v>12.14999961853027</v>
       </c>
       <c r="G4" t="n">
-        <v>17.05250015258789</v>
+        <v>12.21500000953674</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>38.46079581451455</v>
+        <v>46.69409356911476</v>
       </c>
       <c r="J4" t="n">
-        <v>32.30387795984601</v>
+        <v>42.74762946743159</v>
       </c>
       <c r="K4" t="n">
-        <v>40.2160164062549</v>
+        <v>48.0398238015276</v>
       </c>
       <c r="L4" t="n">
-        <v>8076.2</v>
+        <v>62923.8</v>
       </c>
       <c r="M4" t="n">
-        <v>3570.8</v>
+        <v>34486.85</v>
       </c>
       <c r="N4" t="n">
-        <v>2810.425</v>
+        <v>42097.45</v>
       </c>
       <c r="O4" t="n">
-        <v>2.261734065195474</v>
+        <v>1.824573714328795</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2694232018089799</v>
+        <v>-0.05472688942409754</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2074656312027846</v>
+        <v>-0.06108847333549031</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.06195757060619533</v>
+        <v>0.006361583911392778</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.07987516441935788</v>
+        <v>0.006236721568073048</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.08371633253146349</v>
+        <v>-0.003754271715911778</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1052,7 +1052,153 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>6861</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>睿生光電</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>195.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>195.175</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>41.88060879833343</v>
+      </c>
+      <c r="J5" t="n">
+        <v>36.13434987059616</v>
+      </c>
+      <c r="K5" t="n">
+        <v>47.06472449818138</v>
+      </c>
+      <c r="L5" t="n">
+        <v>558444.2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>356154.25</v>
+      </c>
+      <c r="N5" t="n">
+        <v>421384.025</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.567984096778292</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-9.545046899939052</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-11.5561982865137</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.011151386574648</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.270916659818736</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.075378023428398</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>-253.238</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>27.896</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-225.342</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-59.726</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>34.331</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-25.39500000000001</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>386.297</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>74.196</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>460.493</v>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN5"/>
+  <dimension ref="A1:AN2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,16 +625,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>6861</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>南染</t>
+          <t>睿生光電</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,78 +643,78 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>24.54999923706055</v>
+        <v>185.5</v>
       </c>
       <c r="G2" t="n">
-        <v>25.11499967575073</v>
+        <v>193.85</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>41.32447089010093</v>
+        <v>36.7254373111688</v>
       </c>
       <c r="J2" t="n">
-        <v>34.39302024546104</v>
+        <v>36.33137899951814</v>
       </c>
       <c r="K2" t="n">
-        <v>40.43433517996497</v>
+        <v>39.20935782198959</v>
       </c>
       <c r="L2" t="n">
-        <v>138425.2</v>
+        <v>716105.2</v>
       </c>
       <c r="M2" t="n">
-        <v>90905</v>
+        <v>389964.5</v>
       </c>
       <c r="N2" t="n">
-        <v>104381.35</v>
+        <v>422903.575</v>
       </c>
       <c r="O2" t="n">
-        <v>1.52274572355756</v>
+        <v>1.836334332996978</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.326457809784845</v>
+        <v>-9.325289574628755</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.3028956154650139</v>
+        <v>-11.19246153662619</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.02356219431983103</v>
+        <v>1.867171961997432</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.03093732011046768</v>
+        <v>2.043835573277878</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.05616015346633674</v>
+        <v>1.306162698268455</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -723,482 +723,44 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>-1.451</v>
+        <v>-156.804</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>-0.776</v>
       </c>
       <c r="AE2" t="n">
-        <v>-1.451</v>
+        <v>-157.58</v>
       </c>
       <c r="AF2" t="n">
-        <v>19.552</v>
+        <v>-219.8360000000001</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>33.36899999999999</v>
       </c>
       <c r="AI2" t="n">
-        <v>19.552</v>
+        <v>-186.467</v>
       </c>
       <c r="AJ2" t="n">
-        <v>45.552</v>
+        <v>243.3669999999999</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>1</v>
+        <v>73.26999999999998</v>
       </c>
       <c r="AM2" t="n">
-        <v>46.552</v>
+        <v>316.6370000000001</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>70</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>8921</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>沈氏</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>16.60000038146973</v>
-      </c>
-      <c r="G3" t="n">
-        <v>17.05250015258789</v>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>38.46079581451455</v>
-      </c>
-      <c r="J3" t="n">
-        <v>32.30387795984601</v>
-      </c>
-      <c r="K3" t="n">
-        <v>40.2160164062549</v>
-      </c>
-      <c r="L3" t="n">
-        <v>8077.6</v>
-      </c>
-      <c r="M3" t="n">
-        <v>3571.15</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2810.6</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2.261904428545427</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-0.2694232018089799</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-0.2074656312027846</v>
-      </c>
-      <c r="R3" t="n">
-        <v>-0.06195757060619533</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-0.07987516441935788</v>
-      </c>
-      <c r="T3" t="n">
-        <v>-0.08371633253146349</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>70</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>3521</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>台鋼建設</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>12.14999961853027</v>
-      </c>
-      <c r="G4" t="n">
-        <v>12.21500000953674</v>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>46.69409356911476</v>
-      </c>
-      <c r="J4" t="n">
-        <v>42.74762946743159</v>
-      </c>
-      <c r="K4" t="n">
-        <v>48.0398238015276</v>
-      </c>
-      <c r="L4" t="n">
-        <v>62923.8</v>
-      </c>
-      <c r="M4" t="n">
-        <v>34486.85</v>
-      </c>
-      <c r="N4" t="n">
-        <v>42097.45</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.824573714328795</v>
-      </c>
-      <c r="P4" t="n">
-        <v>-0.05472688942409754</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-0.06108847333549031</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.006361583911392778</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.006236721568073048</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-0.003754271715911778</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>70</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>6861</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>睿生光電</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>195.5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>195.175</v>
-      </c>
-      <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>41.88060879833343</v>
-      </c>
-      <c r="J5" t="n">
-        <v>36.13434987059616</v>
-      </c>
-      <c r="K5" t="n">
-        <v>47.06472449818138</v>
-      </c>
-      <c r="L5" t="n">
-        <v>558444.2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>356154.25</v>
-      </c>
-      <c r="N5" t="n">
-        <v>421384.025</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.567984096778292</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-9.545046899939052</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-11.5561982865137</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.011151386574648</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.270916659818736</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.075378023428398</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>-253.238</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>27.896</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-225.342</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-59.726</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>34.331</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-25.39500000000001</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>386.297</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>74.196</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>460.493</v>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN2"/>
+  <dimension ref="A1:AN4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,12 +629,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6861</t>
+          <t>5484</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>睿生光電</t>
+          <t>慧友</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,49 +643,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>185.5</v>
+        <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>193.85</v>
+        <v>40.30249996185303</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>36.7254373111688</v>
+        <v>42.74909033449763</v>
       </c>
       <c r="J2" t="n">
-        <v>36.33137899951814</v>
+        <v>40.49155499365212</v>
       </c>
       <c r="K2" t="n">
-        <v>39.20935782198959</v>
+        <v>46.5406159951201</v>
       </c>
       <c r="L2" t="n">
-        <v>716105.2</v>
+        <v>498522.2</v>
       </c>
       <c r="M2" t="n">
-        <v>389964.5</v>
+        <v>286548.55</v>
       </c>
       <c r="N2" t="n">
-        <v>422903.575</v>
+        <v>326955.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.836334332996978</v>
+        <v>1.739747767001439</v>
       </c>
       <c r="P2" t="n">
-        <v>-9.325289574628755</v>
+        <v>-0.295678032047185</v>
       </c>
       <c r="Q2" t="n">
-        <v>-11.19246153662619</v>
+        <v>-0.5284442352566132</v>
       </c>
       <c r="R2" t="n">
-        <v>1.867171961997432</v>
+        <v>0.2327662032094282</v>
       </c>
       <c r="S2" t="n">
-        <v>2.043835573277878</v>
+        <v>0.323124005390234</v>
       </c>
       <c r="T2" t="n">
-        <v>1.306162698268455</v>
+        <v>0.2807935835810635</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -723,44 +723,336 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>-156.804</v>
+        <v>7</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.776</v>
+        <v>2</v>
       </c>
       <c r="AE2" t="n">
-        <v>-157.58</v>
+        <v>9</v>
       </c>
       <c r="AF2" t="n">
-        <v>-219.8360000000001</v>
+        <v>-114.361</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>33.36899999999999</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
-        <v>-186.467</v>
+        <v>-113.361</v>
       </c>
       <c r="AJ2" t="n">
-        <v>243.3669999999999</v>
+        <v>-282.301</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>73.26999999999998</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>316.6370000000001</v>
+        <v>-282.301</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>70</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>8183</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>精星</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>29</v>
+      </c>
+      <c r="G3" t="n">
+        <v>29.00000019073486</v>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>39.28265128837484</v>
+      </c>
+      <c r="J3" t="n">
+        <v>30.0948415603707</v>
+      </c>
+      <c r="K3" t="n">
+        <v>47.67945729841337</v>
+      </c>
+      <c r="L3" t="n">
+        <v>440486.6</v>
+      </c>
+      <c r="M3" t="n">
+        <v>254056.55</v>
+      </c>
+      <c r="N3" t="n">
+        <v>261319.825</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.733813200250102</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-0.4364551931410965</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-0.4661209470337275</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.02966575389263104</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-0.02572725318953151</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-0.07961018225102978</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>70</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>5547</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>久舜</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>19.85000038146973</v>
+      </c>
+      <c r="G4" t="n">
+        <v>19.83500013351441</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>36.49663555454929</v>
+      </c>
+      <c r="J4" t="n">
+        <v>31.44023783877589</v>
+      </c>
+      <c r="K4" t="n">
+        <v>49.92325540376719</v>
+      </c>
+      <c r="L4" t="n">
+        <v>38248.6</v>
+      </c>
+      <c r="M4" t="n">
+        <v>22712.15</v>
+      </c>
+      <c r="N4" t="n">
+        <v>22210.275</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.684058972840528</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0.01404619684806718</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0.03195813837511535</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.01791194152704816</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.01907187934680239</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.01476655334961326</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN4"/>
+  <dimension ref="A1:AN3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,129 +625,129 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5484</t>
+          <t>4406</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>慧友</t>
+          <t>新昕纖</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>40.30249996185303</v>
+        <v>10.02700004577637</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>42.74909033449763</v>
+        <v>38.74853767215826</v>
       </c>
       <c r="J2" t="n">
-        <v>40.49155499365212</v>
+        <v>33.69818633041162</v>
       </c>
       <c r="K2" t="n">
-        <v>46.5406159951201</v>
+        <v>49.35789437444871</v>
       </c>
       <c r="L2" t="n">
-        <v>498522.2</v>
+        <v>54800</v>
       </c>
       <c r="M2" t="n">
-        <v>286548.55</v>
+        <v>28850</v>
       </c>
       <c r="N2" t="n">
-        <v>326955.8</v>
+        <v>35450</v>
       </c>
       <c r="O2" t="n">
-        <v>1.739747767001439</v>
+        <v>1.89948006932409</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.295678032047185</v>
+        <v>-0.005521283981343217</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.5284442352566132</v>
+        <v>0.003822729009781798</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2327662032094282</v>
+        <v>-0.009344012991125014</v>
       </c>
       <c r="S2" t="n">
-        <v>0.323124005390234</v>
+        <v>-0.01167934474599521</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2807935835810635</v>
+        <v>-0.01451802404534919</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
       <c r="AB2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>-114.361</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>-113.361</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-282.301</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
@@ -756,11 +756,11 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-282.301</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
@@ -771,67 +771,67 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8183</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>億泰</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>29</v>
+        <v>18.79999923706055</v>
       </c>
       <c r="G3" t="n">
-        <v>29.00000019073486</v>
+        <v>19.23249988555908</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>39.28265128837484</v>
+        <v>41.78723051632754</v>
       </c>
       <c r="J3" t="n">
-        <v>30.0948415603707</v>
+        <v>33.30550904920057</v>
       </c>
       <c r="K3" t="n">
-        <v>47.67945729841337</v>
+        <v>42.02824549427734</v>
       </c>
       <c r="L3" t="n">
-        <v>440486.6</v>
+        <v>595393.2</v>
       </c>
       <c r="M3" t="n">
-        <v>254056.55</v>
+        <v>344965.7</v>
       </c>
       <c r="N3" t="n">
-        <v>261319.825</v>
+        <v>385778.725</v>
       </c>
       <c r="O3" t="n">
-        <v>1.733813200250102</v>
+        <v>1.725948985652776</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4364551931410965</v>
+        <v>-0.2477411726811241</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.4661209470337275</v>
+        <v>-0.2266987258114353</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02966575389263104</v>
+        <v>-0.02104244686968873</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.02572725318953151</v>
+        <v>-0.01845864791455323</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.07961018225102978</v>
+        <v>-0.01975343893701209</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -860,199 +860,53 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>-2.964</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>-1.058</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>-4.022</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>376.06</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>-1.516</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>374.544</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>715.5960000000001</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.871</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>717.4669999999999</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>70</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>5547</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>久舜</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>19.85000038146973</v>
-      </c>
-      <c r="G4" t="n">
-        <v>19.83500013351441</v>
-      </c>
-      <c r="H4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>36.49663555454929</v>
-      </c>
-      <c r="J4" t="n">
-        <v>31.44023783877589</v>
-      </c>
-      <c r="K4" t="n">
-        <v>49.92325540376719</v>
-      </c>
-      <c r="L4" t="n">
-        <v>38248.6</v>
-      </c>
-      <c r="M4" t="n">
-        <v>22712.15</v>
-      </c>
-      <c r="N4" t="n">
-        <v>22210.275</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.684058972840528</v>
-      </c>
-      <c r="P4" t="n">
-        <v>-0.01404619684806718</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-0.03195813837511535</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.01791194152704816</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.01907187934680239</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.01476655334961326</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
